--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="223">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -490,6 +490,12 @@
     <t>['27', '68', '90']</t>
   </si>
   <si>
+    <t>['8', '11', '42']</t>
+  </si>
+  <si>
+    <t>['37', '45+6']</t>
+  </si>
+  <si>
     <t>['5', '42', '80', '90+2']</t>
   </si>
   <si>
@@ -665,6 +671,18 @@
   </si>
   <si>
     <t>['2', '33', '45+7']</t>
+  </si>
+  <si>
+    <t>['8', '18', '37', '53']</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['17', '90+8']</t>
+  </si>
+  <si>
+    <t>['17', '80']</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP109"/>
+  <dimension ref="A1:BP113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1694,7 +1712,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1900,7 +1918,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2518,7 +2536,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -2596,10 +2614,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ8">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2805,7 +2823,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3011,7 +3029,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3214,10 +3232,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3420,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ12">
         <v>1.11</v>
@@ -3626,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -3835,7 +3853,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
@@ -4244,7 +4262,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16">
         <v>1.67</v>
@@ -4372,7 +4390,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q17">
         <v>1.7</v>
@@ -4453,7 +4471,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR17">
         <v>1.31</v>
@@ -4578,7 +4596,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4656,7 +4674,7 @@
         <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ18">
         <v>1.67</v>
@@ -4784,7 +4802,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q19">
         <v>2.57</v>
@@ -4865,7 +4883,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ19">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR19">
         <v>1.28</v>
@@ -4990,7 +5008,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5402,7 +5420,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5608,7 +5626,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -5689,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR23">
         <v>1.55</v>
@@ -5892,7 +5910,7 @@
         <v>0.5</v>
       </c>
       <c r="AP24">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ24">
         <v>0.5600000000000001</v>
@@ -6020,7 +6038,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6226,7 +6244,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q26">
         <v>3.9</v>
@@ -6304,7 +6322,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ26">
         <v>2.44</v>
@@ -6513,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR27">
         <v>1.22</v>
@@ -6638,7 +6656,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6844,7 +6862,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7050,7 +7068,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7256,7 +7274,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7462,7 +7480,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q32">
         <v>3.6</v>
@@ -7540,7 +7558,7 @@
         <v>0.33</v>
       </c>
       <c r="AP32">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ32">
         <v>0.5600000000000001</v>
@@ -7668,7 +7686,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7746,10 +7764,10 @@
         <v>0.5</v>
       </c>
       <c r="AP33">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ33">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR33">
         <v>2.34</v>
@@ -7874,7 +7892,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -7952,7 +7970,7 @@
         <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ34">
         <v>1.11</v>
@@ -8080,7 +8098,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8158,7 +8176,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ35">
         <v>2.44</v>
@@ -8367,7 +8385,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR36">
         <v>1.33</v>
@@ -8573,7 +8591,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ37">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR37">
         <v>1.31</v>
@@ -8698,7 +8716,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8904,7 +8922,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q39">
         <v>4.33</v>
@@ -9110,7 +9128,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9316,7 +9334,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q41">
         <v>4.36</v>
@@ -10140,7 +10158,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10346,7 +10364,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10424,7 +10442,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ46">
         <v>2.44</v>
@@ -10552,7 +10570,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q47">
         <v>2.49</v>
@@ -10630,10 +10648,10 @@
         <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR47">
         <v>1.38</v>
@@ -10758,7 +10776,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q48">
         <v>2.48</v>
@@ -10839,7 +10857,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR48">
         <v>1.58</v>
@@ -11042,10 +11060,10 @@
         <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ49">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR49">
         <v>1.98</v>
@@ -11170,7 +11188,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11251,7 +11269,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ50">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR50">
         <v>1.39</v>
@@ -11454,7 +11472,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ51">
         <v>1.11</v>
@@ -11582,7 +11600,7 @@
         <v>82</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11663,7 +11681,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ52">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR52">
         <v>1.7</v>
@@ -11788,7 +11806,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q53">
         <v>3.22</v>
@@ -12200,7 +12218,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12406,7 +12424,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12484,7 +12502,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ56">
         <v>1.78</v>
@@ -12690,7 +12708,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -12818,7 +12836,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -12896,10 +12914,10 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR58">
         <v>1.32</v>
@@ -13105,7 +13123,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ59">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR59">
         <v>1.4</v>
@@ -13230,7 +13248,7 @@
         <v>85</v>
       </c>
       <c r="P60" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13436,7 +13454,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13720,7 +13738,7 @@
         <v>0.75</v>
       </c>
       <c r="AP62">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ62">
         <v>0.44</v>
@@ -13848,7 +13866,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -13929,7 +13947,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ63">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR63">
         <v>1.28</v>
@@ -14054,7 +14072,7 @@
         <v>129</v>
       </c>
       <c r="P64" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q64">
         <v>1.9</v>
@@ -14132,10 +14150,10 @@
         <v>0.8</v>
       </c>
       <c r="AP64">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ64">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR64">
         <v>1.94</v>
@@ -14260,7 +14278,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
@@ -14338,7 +14356,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ65">
         <v>0.5600000000000001</v>
@@ -14466,7 +14484,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14544,10 +14562,10 @@
         <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR66">
         <v>1.77</v>
@@ -14672,7 +14690,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14753,7 +14771,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ67">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR67">
         <v>1.44</v>
@@ -14878,7 +14896,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -14956,10 +14974,10 @@
         <v>0.8</v>
       </c>
       <c r="AP68">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ68">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR68">
         <v>1.28</v>
@@ -15162,10 +15180,10 @@
         <v>0.83</v>
       </c>
       <c r="AP69">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ69">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR69">
         <v>1.54</v>
@@ -15290,7 +15308,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q70">
         <v>2</v>
@@ -15368,7 +15386,7 @@
         <v>0.8</v>
       </c>
       <c r="AP70">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ70">
         <v>0.5600000000000001</v>
@@ -15496,7 +15514,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -15908,7 +15926,7 @@
         <v>137</v>
       </c>
       <c r="P73" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q73">
         <v>1.83</v>
@@ -16114,7 +16132,7 @@
         <v>82</v>
       </c>
       <c r="P74" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16526,7 +16544,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17225,7 +17243,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ79">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR79">
         <v>1.8</v>
@@ -17350,7 +17368,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q80">
         <v>4.5</v>
@@ -17428,7 +17446,7 @@
         <v>1.83</v>
       </c>
       <c r="AP80">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ80">
         <v>1.78</v>
@@ -17762,7 +17780,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -17843,7 +17861,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ82">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR82">
         <v>1.42</v>
@@ -18049,7 +18067,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR83">
         <v>1.68</v>
@@ -18252,7 +18270,7 @@
         <v>0.5</v>
       </c>
       <c r="AP84">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ84">
         <v>0.44</v>
@@ -18380,7 +18398,7 @@
         <v>141</v>
       </c>
       <c r="P85" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18586,7 +18604,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18667,7 +18685,7 @@
         <v>1</v>
       </c>
       <c r="AQ86">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR86">
         <v>1.53</v>
@@ -18792,7 +18810,7 @@
         <v>143</v>
       </c>
       <c r="P87" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -18870,7 +18888,7 @@
         <v>0.57</v>
       </c>
       <c r="AP87">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ87">
         <v>0.5600000000000001</v>
@@ -19076,7 +19094,7 @@
         <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ88">
         <v>1</v>
@@ -19204,7 +19222,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19282,10 +19300,10 @@
         <v>2.14</v>
       </c>
       <c r="AP89">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ89">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR89">
         <v>1.8</v>
@@ -19410,7 +19428,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19697,7 +19715,7 @@
         <v>2</v>
       </c>
       <c r="AQ91">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR91">
         <v>1.74</v>
@@ -19822,7 +19840,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -19900,7 +19918,7 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ92">
         <v>0.5600000000000001</v>
@@ -20028,7 +20046,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q93">
         <v>4</v>
@@ -20727,7 +20745,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR96">
         <v>1.35</v>
@@ -21058,7 +21076,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21139,7 +21157,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ98">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR98">
         <v>1.57</v>
@@ -21264,7 +21282,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21342,10 +21360,10 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ99">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR99">
         <v>1.48</v>
@@ -21548,7 +21566,7 @@
         <v>1.13</v>
       </c>
       <c r="AP100">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ100">
         <v>1.11</v>
@@ -21676,7 +21694,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21754,7 +21772,7 @@
         <v>2.75</v>
       </c>
       <c r="AP101">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ101">
         <v>2.44</v>
@@ -21882,7 +21900,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -21963,7 +21981,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ102">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR102">
         <v>1.31</v>
@@ -22088,7 +22106,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -22166,7 +22184,7 @@
         <v>0.5</v>
       </c>
       <c r="AP103">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ103">
         <v>0.5600000000000001</v>
@@ -22581,7 +22599,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR105">
         <v>1.8</v>
@@ -23481,6 +23499,830 @@
       </c>
       <c r="BP109">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7580438</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F110">
+        <v>19</v>
+      </c>
+      <c r="G110" t="s">
+        <v>76</v>
+      </c>
+      <c r="H110" t="s">
+        <v>74</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>3</v>
+      </c>
+      <c r="K110">
+        <v>3</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="M110">
+        <v>4</v>
+      </c>
+      <c r="N110">
+        <v>5</v>
+      </c>
+      <c r="O110" t="s">
+        <v>101</v>
+      </c>
+      <c r="P110" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q110">
+        <v>4.75</v>
+      </c>
+      <c r="R110">
+        <v>2.1</v>
+      </c>
+      <c r="S110">
+        <v>2.3</v>
+      </c>
+      <c r="T110">
+        <v>1.4</v>
+      </c>
+      <c r="U110">
+        <v>2.75</v>
+      </c>
+      <c r="V110">
+        <v>3</v>
+      </c>
+      <c r="W110">
+        <v>1.36</v>
+      </c>
+      <c r="X110">
+        <v>7</v>
+      </c>
+      <c r="Y110">
+        <v>1.08</v>
+      </c>
+      <c r="Z110">
+        <v>3.81</v>
+      </c>
+      <c r="AA110">
+        <v>3.33</v>
+      </c>
+      <c r="AB110">
+        <v>1.97</v>
+      </c>
+      <c r="AC110">
+        <v>1.03</v>
+      </c>
+      <c r="AD110">
+        <v>9</v>
+      </c>
+      <c r="AE110">
+        <v>1.3</v>
+      </c>
+      <c r="AF110">
+        <v>3.25</v>
+      </c>
+      <c r="AG110">
+        <v>1.98</v>
+      </c>
+      <c r="AH110">
+        <v>1.77</v>
+      </c>
+      <c r="AI110">
+        <v>1.83</v>
+      </c>
+      <c r="AJ110">
+        <v>1.83</v>
+      </c>
+      <c r="AK110">
+        <v>1.72</v>
+      </c>
+      <c r="AL110">
+        <v>1.25</v>
+      </c>
+      <c r="AM110">
+        <v>1.28</v>
+      </c>
+      <c r="AN110">
+        <v>1.44</v>
+      </c>
+      <c r="AO110">
+        <v>2</v>
+      </c>
+      <c r="AP110">
+        <v>1.3</v>
+      </c>
+      <c r="AQ110">
+        <v>2.1</v>
+      </c>
+      <c r="AR110">
+        <v>1.42</v>
+      </c>
+      <c r="AS110">
+        <v>1.58</v>
+      </c>
+      <c r="AT110">
+        <v>3</v>
+      </c>
+      <c r="AU110">
+        <v>3</v>
+      </c>
+      <c r="AV110">
+        <v>10</v>
+      </c>
+      <c r="AW110">
+        <v>7</v>
+      </c>
+      <c r="AX110">
+        <v>2</v>
+      </c>
+      <c r="AY110">
+        <v>10</v>
+      </c>
+      <c r="AZ110">
+        <v>12</v>
+      </c>
+      <c r="BA110">
+        <v>1</v>
+      </c>
+      <c r="BB110">
+        <v>2</v>
+      </c>
+      <c r="BC110">
+        <v>3</v>
+      </c>
+      <c r="BD110">
+        <v>0</v>
+      </c>
+      <c r="BE110">
+        <v>0</v>
+      </c>
+      <c r="BF110">
+        <v>0</v>
+      </c>
+      <c r="BG110">
+        <v>0</v>
+      </c>
+      <c r="BH110">
+        <v>0</v>
+      </c>
+      <c r="BI110">
+        <v>0</v>
+      </c>
+      <c r="BJ110">
+        <v>0</v>
+      </c>
+      <c r="BK110">
+        <v>1.85</v>
+      </c>
+      <c r="BL110">
+        <v>1.95</v>
+      </c>
+      <c r="BM110">
+        <v>0</v>
+      </c>
+      <c r="BN110">
+        <v>0</v>
+      </c>
+      <c r="BO110">
+        <v>0</v>
+      </c>
+      <c r="BP110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7580439</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F111">
+        <v>19</v>
+      </c>
+      <c r="G111" t="s">
+        <v>80</v>
+      </c>
+      <c r="H111" t="s">
+        <v>70</v>
+      </c>
+      <c r="I111">
+        <v>3</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>3</v>
+      </c>
+      <c r="L111">
+        <v>3</v>
+      </c>
+      <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
+        <v>4</v>
+      </c>
+      <c r="O111" t="s">
+        <v>158</v>
+      </c>
+      <c r="P111" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q111">
+        <v>2.1</v>
+      </c>
+      <c r="R111">
+        <v>2.25</v>
+      </c>
+      <c r="S111">
+        <v>5.5</v>
+      </c>
+      <c r="T111">
+        <v>1.36</v>
+      </c>
+      <c r="U111">
+        <v>3</v>
+      </c>
+      <c r="V111">
+        <v>2.63</v>
+      </c>
+      <c r="W111">
+        <v>1.44</v>
+      </c>
+      <c r="X111">
+        <v>6.5</v>
+      </c>
+      <c r="Y111">
+        <v>1.1</v>
+      </c>
+      <c r="Z111">
+        <v>1.53</v>
+      </c>
+      <c r="AA111">
+        <v>4.4</v>
+      </c>
+      <c r="AB111">
+        <v>5.3</v>
+      </c>
+      <c r="AC111">
+        <v>1.01</v>
+      </c>
+      <c r="AD111">
+        <v>11</v>
+      </c>
+      <c r="AE111">
+        <v>1.25</v>
+      </c>
+      <c r="AF111">
+        <v>3.75</v>
+      </c>
+      <c r="AG111">
+        <v>1.79</v>
+      </c>
+      <c r="AH111">
+        <v>1.95</v>
+      </c>
+      <c r="AI111">
+        <v>1.83</v>
+      </c>
+      <c r="AJ111">
+        <v>1.83</v>
+      </c>
+      <c r="AK111">
+        <v>1.09</v>
+      </c>
+      <c r="AL111">
+        <v>1.16</v>
+      </c>
+      <c r="AM111">
+        <v>2.5</v>
+      </c>
+      <c r="AN111">
+        <v>1</v>
+      </c>
+      <c r="AO111">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP111">
+        <v>1.2</v>
+      </c>
+      <c r="AQ111">
+        <v>0.5</v>
+      </c>
+      <c r="AR111">
+        <v>1.66</v>
+      </c>
+      <c r="AS111">
+        <v>1.41</v>
+      </c>
+      <c r="AT111">
+        <v>3.07</v>
+      </c>
+      <c r="AU111">
+        <v>11</v>
+      </c>
+      <c r="AV111">
+        <v>5</v>
+      </c>
+      <c r="AW111">
+        <v>11</v>
+      </c>
+      <c r="AX111">
+        <v>5</v>
+      </c>
+      <c r="AY111">
+        <v>22</v>
+      </c>
+      <c r="AZ111">
+        <v>10</v>
+      </c>
+      <c r="BA111">
+        <v>9</v>
+      </c>
+      <c r="BB111">
+        <v>0</v>
+      </c>
+      <c r="BC111">
+        <v>9</v>
+      </c>
+      <c r="BD111">
+        <v>0</v>
+      </c>
+      <c r="BE111">
+        <v>0</v>
+      </c>
+      <c r="BF111">
+        <v>0</v>
+      </c>
+      <c r="BG111">
+        <v>0</v>
+      </c>
+      <c r="BH111">
+        <v>0</v>
+      </c>
+      <c r="BI111">
+        <v>0</v>
+      </c>
+      <c r="BJ111">
+        <v>0</v>
+      </c>
+      <c r="BK111">
+        <v>0</v>
+      </c>
+      <c r="BL111">
+        <v>0</v>
+      </c>
+      <c r="BM111">
+        <v>0</v>
+      </c>
+      <c r="BN111">
+        <v>0</v>
+      </c>
+      <c r="BO111">
+        <v>0</v>
+      </c>
+      <c r="BP111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7580440</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F112">
+        <v>19</v>
+      </c>
+      <c r="G112" t="s">
+        <v>79</v>
+      </c>
+      <c r="H112" t="s">
+        <v>71</v>
+      </c>
+      <c r="I112">
+        <v>2</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>3</v>
+      </c>
+      <c r="L112">
+        <v>2</v>
+      </c>
+      <c r="M112">
+        <v>2</v>
+      </c>
+      <c r="N112">
+        <v>4</v>
+      </c>
+      <c r="O112" t="s">
+        <v>159</v>
+      </c>
+      <c r="P112" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q112">
+        <v>2.88</v>
+      </c>
+      <c r="R112">
+        <v>2.1</v>
+      </c>
+      <c r="S112">
+        <v>3.4</v>
+      </c>
+      <c r="T112">
+        <v>1.4</v>
+      </c>
+      <c r="U112">
+        <v>2.75</v>
+      </c>
+      <c r="V112">
+        <v>2.75</v>
+      </c>
+      <c r="W112">
+        <v>1.4</v>
+      </c>
+      <c r="X112">
+        <v>7</v>
+      </c>
+      <c r="Y112">
+        <v>1.08</v>
+      </c>
+      <c r="Z112">
+        <v>2.37</v>
+      </c>
+      <c r="AA112">
+        <v>3.37</v>
+      </c>
+      <c r="AB112">
+        <v>2.84</v>
+      </c>
+      <c r="AC112">
+        <v>1.03</v>
+      </c>
+      <c r="AD112">
+        <v>9</v>
+      </c>
+      <c r="AE112">
+        <v>1.28</v>
+      </c>
+      <c r="AF112">
+        <v>3.5</v>
+      </c>
+      <c r="AG112">
+        <v>1.87</v>
+      </c>
+      <c r="AH112">
+        <v>1.87</v>
+      </c>
+      <c r="AI112">
+        <v>1.73</v>
+      </c>
+      <c r="AJ112">
+        <v>2</v>
+      </c>
+      <c r="AK112">
+        <v>1.4</v>
+      </c>
+      <c r="AL112">
+        <v>1.28</v>
+      </c>
+      <c r="AM112">
+        <v>1.53</v>
+      </c>
+      <c r="AN112">
+        <v>1.44</v>
+      </c>
+      <c r="AO112">
+        <v>1.22</v>
+      </c>
+      <c r="AP112">
+        <v>1.4</v>
+      </c>
+      <c r="AQ112">
+        <v>1.2</v>
+      </c>
+      <c r="AR112">
+        <v>1.46</v>
+      </c>
+      <c r="AS112">
+        <v>1.38</v>
+      </c>
+      <c r="AT112">
+        <v>2.84</v>
+      </c>
+      <c r="AU112">
+        <v>4</v>
+      </c>
+      <c r="AV112">
+        <v>8</v>
+      </c>
+      <c r="AW112">
+        <v>5</v>
+      </c>
+      <c r="AX112">
+        <v>9</v>
+      </c>
+      <c r="AY112">
+        <v>9</v>
+      </c>
+      <c r="AZ112">
+        <v>17</v>
+      </c>
+      <c r="BA112">
+        <v>4</v>
+      </c>
+      <c r="BB112">
+        <v>6</v>
+      </c>
+      <c r="BC112">
+        <v>10</v>
+      </c>
+      <c r="BD112">
+        <v>0</v>
+      </c>
+      <c r="BE112">
+        <v>0</v>
+      </c>
+      <c r="BF112">
+        <v>0</v>
+      </c>
+      <c r="BG112">
+        <v>0</v>
+      </c>
+      <c r="BH112">
+        <v>0</v>
+      </c>
+      <c r="BI112">
+        <v>0</v>
+      </c>
+      <c r="BJ112">
+        <v>0</v>
+      </c>
+      <c r="BK112">
+        <v>0</v>
+      </c>
+      <c r="BL112">
+        <v>0</v>
+      </c>
+      <c r="BM112">
+        <v>0</v>
+      </c>
+      <c r="BN112">
+        <v>0</v>
+      </c>
+      <c r="BO112">
+        <v>0</v>
+      </c>
+      <c r="BP112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7580441</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45696.58333333334</v>
+      </c>
+      <c r="F113">
+        <v>19</v>
+      </c>
+      <c r="G113" t="s">
+        <v>81</v>
+      </c>
+      <c r="H113" t="s">
+        <v>73</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>2</v>
+      </c>
+      <c r="N113">
+        <v>2</v>
+      </c>
+      <c r="O113" t="s">
+        <v>82</v>
+      </c>
+      <c r="P113" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q113">
+        <v>2.1</v>
+      </c>
+      <c r="R113">
+        <v>2.3</v>
+      </c>
+      <c r="S113">
+        <v>5</v>
+      </c>
+      <c r="T113">
+        <v>1.33</v>
+      </c>
+      <c r="U113">
+        <v>3.25</v>
+      </c>
+      <c r="V113">
+        <v>2.5</v>
+      </c>
+      <c r="W113">
+        <v>1.5</v>
+      </c>
+      <c r="X113">
+        <v>6</v>
+      </c>
+      <c r="Y113">
+        <v>1.11</v>
+      </c>
+      <c r="Z113">
+        <v>1.49</v>
+      </c>
+      <c r="AA113">
+        <v>4.4</v>
+      </c>
+      <c r="AB113">
+        <v>5.8</v>
+      </c>
+      <c r="AC113">
+        <v>1</v>
+      </c>
+      <c r="AD113">
+        <v>9</v>
+      </c>
+      <c r="AE113">
+        <v>1.2</v>
+      </c>
+      <c r="AF113">
+        <v>4.33</v>
+      </c>
+      <c r="AG113">
+        <v>1.65</v>
+      </c>
+      <c r="AH113">
+        <v>2.05</v>
+      </c>
+      <c r="AI113">
+        <v>1.73</v>
+      </c>
+      <c r="AJ113">
+        <v>2</v>
+      </c>
+      <c r="AK113">
+        <v>1.09</v>
+      </c>
+      <c r="AL113">
+        <v>1.16</v>
+      </c>
+      <c r="AM113">
+        <v>2.5</v>
+      </c>
+      <c r="AN113">
+        <v>2.78</v>
+      </c>
+      <c r="AO113">
+        <v>1</v>
+      </c>
+      <c r="AP113">
+        <v>2.5</v>
+      </c>
+      <c r="AQ113">
+        <v>1.2</v>
+      </c>
+      <c r="AR113">
+        <v>1.8</v>
+      </c>
+      <c r="AS113">
+        <v>1.12</v>
+      </c>
+      <c r="AT113">
+        <v>2.92</v>
+      </c>
+      <c r="AU113">
+        <v>8</v>
+      </c>
+      <c r="AV113">
+        <v>6</v>
+      </c>
+      <c r="AW113">
+        <v>5</v>
+      </c>
+      <c r="AX113">
+        <v>4</v>
+      </c>
+      <c r="AY113">
+        <v>13</v>
+      </c>
+      <c r="AZ113">
+        <v>10</v>
+      </c>
+      <c r="BA113">
+        <v>8</v>
+      </c>
+      <c r="BB113">
+        <v>1</v>
+      </c>
+      <c r="BC113">
+        <v>9</v>
+      </c>
+      <c r="BD113">
+        <v>0</v>
+      </c>
+      <c r="BE113">
+        <v>0</v>
+      </c>
+      <c r="BF113">
+        <v>0</v>
+      </c>
+      <c r="BG113">
+        <v>0</v>
+      </c>
+      <c r="BH113">
+        <v>0</v>
+      </c>
+      <c r="BI113">
+        <v>0</v>
+      </c>
+      <c r="BJ113">
+        <v>0</v>
+      </c>
+      <c r="BK113">
+        <v>1.85</v>
+      </c>
+      <c r="BL113">
+        <v>1.95</v>
+      </c>
+      <c r="BM113">
+        <v>0</v>
+      </c>
+      <c r="BN113">
+        <v>0</v>
+      </c>
+      <c r="BO113">
+        <v>0</v>
+      </c>
+      <c r="BP113">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -496,6 +496,12 @@
     <t>['37', '45+6']</t>
   </si>
   <si>
+    <t>['27']</t>
+  </si>
+  <si>
+    <t>['44']</t>
+  </si>
+  <si>
     <t>['5', '42', '80', '90+2']</t>
   </si>
   <si>
@@ -683,6 +689,9 @@
   </si>
   <si>
     <t>['17', '80']</t>
+  </si>
+  <si>
+    <t>['21', '32', '48', '71', '83']</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP113"/>
+  <dimension ref="A1:BP115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1712,7 +1721,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1793,7 +1802,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ4">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1918,7 +1927,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2408,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ7">
         <v>0.44</v>
@@ -2536,7 +2545,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -2820,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ9">
         <v>1.2</v>
@@ -3441,7 +3450,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ12">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4056,7 +4065,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ15">
         <v>0.5600000000000001</v>
@@ -4390,7 +4399,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q17">
         <v>1.7</v>
@@ -4596,7 +4605,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4802,7 +4811,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q19">
         <v>2.57</v>
@@ -5008,7 +5017,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5086,7 +5095,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ20">
         <v>0.44</v>
@@ -5420,7 +5429,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5501,7 +5510,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ22">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>1.26</v>
@@ -5626,7 +5635,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -6038,7 +6047,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6116,7 +6125,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6244,7 +6253,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q26">
         <v>3.9</v>
@@ -6325,7 +6334,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ26">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR26">
         <v>1.52</v>
@@ -6656,7 +6665,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6862,7 +6871,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7068,7 +7077,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7274,7 +7283,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7480,7 +7489,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q32">
         <v>3.6</v>
@@ -7686,7 +7695,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7892,7 +7901,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -7973,7 +7982,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ34">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.38</v>
@@ -8098,7 +8107,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8179,7 +8188,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ35">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR35">
         <v>2.59</v>
@@ -8588,7 +8597,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ37">
         <v>1.2</v>
@@ -8716,7 +8725,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8794,7 +8803,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ38">
         <v>1.67</v>
@@ -8922,7 +8931,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q39">
         <v>4.33</v>
@@ -9128,7 +9137,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9334,7 +9343,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q41">
         <v>4.36</v>
@@ -10158,7 +10167,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10364,7 +10373,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10445,7 +10454,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ46">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR46">
         <v>1.09</v>
@@ -10570,7 +10579,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q47">
         <v>2.49</v>
@@ -10776,7 +10785,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q48">
         <v>2.48</v>
@@ -10854,7 +10863,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ48">
         <v>1.2</v>
@@ -11188,7 +11197,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11266,7 +11275,7 @@
         <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ50">
         <v>0.5</v>
@@ -11475,7 +11484,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ51">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>2.09</v>
@@ -11600,7 +11609,7 @@
         <v>82</v>
       </c>
       <c r="P52" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11806,7 +11815,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q53">
         <v>3.22</v>
@@ -12093,7 +12102,7 @@
         <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -12218,7 +12227,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12424,7 +12433,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12836,7 +12845,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13120,7 +13129,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ59">
         <v>0.5</v>
@@ -13248,7 +13257,7 @@
         <v>85</v>
       </c>
       <c r="P60" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13326,7 +13335,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ60">
         <v>1.67</v>
@@ -13454,7 +13463,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13535,7 +13544,7 @@
         <v>2</v>
       </c>
       <c r="AQ61">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR61">
         <v>1.75</v>
@@ -13866,7 +13875,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -14072,7 +14081,7 @@
         <v>129</v>
       </c>
       <c r="P64" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q64">
         <v>1.9</v>
@@ -14278,7 +14287,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
@@ -14484,7 +14493,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14690,7 +14699,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14768,7 +14777,7 @@
         <v>1.8</v>
       </c>
       <c r="AP67">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ67">
         <v>2.1</v>
@@ -14896,7 +14905,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15308,7 +15317,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q70">
         <v>2</v>
@@ -15514,7 +15523,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -15595,7 +15604,7 @@
         <v>1</v>
       </c>
       <c r="AQ71">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR71">
         <v>1.47</v>
@@ -15801,7 +15810,7 @@
         <v>2</v>
       </c>
       <c r="AQ72">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR72">
         <v>1.58</v>
@@ -15926,7 +15935,7 @@
         <v>137</v>
       </c>
       <c r="P73" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q73">
         <v>1.83</v>
@@ -16132,7 +16141,7 @@
         <v>82</v>
       </c>
       <c r="P74" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16544,7 +16553,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16625,7 +16634,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ76">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR76">
         <v>1.55</v>
@@ -17034,7 +17043,7 @@
         <v>2.2</v>
       </c>
       <c r="AP78">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ78">
         <v>1.78</v>
@@ -17368,7 +17377,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q80">
         <v>4.5</v>
@@ -17652,7 +17661,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ81">
         <v>0.5600000000000001</v>
@@ -17780,7 +17789,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -18398,7 +18407,7 @@
         <v>141</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18479,7 +18488,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ85">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR85">
         <v>1.4</v>
@@ -18604,7 +18613,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18810,7 +18819,7 @@
         <v>143</v>
       </c>
       <c r="P87" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19222,7 +19231,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19428,7 +19437,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19506,10 +19515,10 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ90">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.54</v>
@@ -19840,7 +19849,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20046,7 +20055,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q93">
         <v>4</v>
@@ -20124,7 +20133,7 @@
         <v>1.71</v>
       </c>
       <c r="AP93">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ93">
         <v>1.78</v>
@@ -20951,7 +20960,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ97">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.85</v>
@@ -21076,7 +21085,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21154,7 +21163,7 @@
         <v>1.88</v>
       </c>
       <c r="AP98">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ98">
         <v>2.1</v>
@@ -21282,7 +21291,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21569,7 +21578,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ100">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR100">
         <v>1.45</v>
@@ -21694,7 +21703,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21775,7 +21784,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ101">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR101">
         <v>1.8</v>
@@ -21900,7 +21909,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -22106,7 +22115,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -22390,7 +22399,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ104">
         <v>1</v>
@@ -23548,7 +23557,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23754,7 +23763,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -23960,7 +23969,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24166,7 +24175,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24323,6 +24332,418 @@
       </c>
       <c r="BP113">
         <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7580442</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45697.47916666666</v>
+      </c>
+      <c r="F114">
+        <v>19</v>
+      </c>
+      <c r="G114" t="s">
+        <v>77</v>
+      </c>
+      <c r="H114" t="s">
+        <v>72</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>1</v>
+      </c>
+      <c r="O114" t="s">
+        <v>160</v>
+      </c>
+      <c r="P114" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q114">
+        <v>2.5</v>
+      </c>
+      <c r="R114">
+        <v>2.2</v>
+      </c>
+      <c r="S114">
+        <v>4</v>
+      </c>
+      <c r="T114">
+        <v>1.36</v>
+      </c>
+      <c r="U114">
+        <v>3</v>
+      </c>
+      <c r="V114">
+        <v>2.63</v>
+      </c>
+      <c r="W114">
+        <v>1.44</v>
+      </c>
+      <c r="X114">
+        <v>6.5</v>
+      </c>
+      <c r="Y114">
+        <v>1.1</v>
+      </c>
+      <c r="Z114">
+        <v>1.8</v>
+      </c>
+      <c r="AA114">
+        <v>3.72</v>
+      </c>
+      <c r="AB114">
+        <v>4.1</v>
+      </c>
+      <c r="AC114">
+        <v>1.05</v>
+      </c>
+      <c r="AD114">
+        <v>8.5</v>
+      </c>
+      <c r="AE114">
+        <v>1.3</v>
+      </c>
+      <c r="AF114">
+        <v>3.3</v>
+      </c>
+      <c r="AG114">
+        <v>1.8</v>
+      </c>
+      <c r="AH114">
+        <v>1.94</v>
+      </c>
+      <c r="AI114">
+        <v>1.73</v>
+      </c>
+      <c r="AJ114">
+        <v>2</v>
+      </c>
+      <c r="AK114">
+        <v>1.29</v>
+      </c>
+      <c r="AL114">
+        <v>1.29</v>
+      </c>
+      <c r="AM114">
+        <v>1.75</v>
+      </c>
+      <c r="AN114">
+        <v>1.11</v>
+      </c>
+      <c r="AO114">
+        <v>1.11</v>
+      </c>
+      <c r="AP114">
+        <v>1.3</v>
+      </c>
+      <c r="AQ114">
+        <v>1</v>
+      </c>
+      <c r="AR114">
+        <v>1.54</v>
+      </c>
+      <c r="AS114">
+        <v>1.28</v>
+      </c>
+      <c r="AT114">
+        <v>2.82</v>
+      </c>
+      <c r="AU114">
+        <v>8</v>
+      </c>
+      <c r="AV114">
+        <v>4</v>
+      </c>
+      <c r="AW114">
+        <v>4</v>
+      </c>
+      <c r="AX114">
+        <v>6</v>
+      </c>
+      <c r="AY114">
+        <v>12</v>
+      </c>
+      <c r="AZ114">
+        <v>10</v>
+      </c>
+      <c r="BA114">
+        <v>6</v>
+      </c>
+      <c r="BB114">
+        <v>6</v>
+      </c>
+      <c r="BC114">
+        <v>12</v>
+      </c>
+      <c r="BD114">
+        <v>1.64</v>
+      </c>
+      <c r="BE114">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF114">
+        <v>2.62</v>
+      </c>
+      <c r="BG114">
+        <v>1.18</v>
+      </c>
+      <c r="BH114">
+        <v>3.92</v>
+      </c>
+      <c r="BI114">
+        <v>1.37</v>
+      </c>
+      <c r="BJ114">
+        <v>2.75</v>
+      </c>
+      <c r="BK114">
+        <v>1.67</v>
+      </c>
+      <c r="BL114">
+        <v>2.07</v>
+      </c>
+      <c r="BM114">
+        <v>2.09</v>
+      </c>
+      <c r="BN114">
+        <v>1.63</v>
+      </c>
+      <c r="BO114">
+        <v>2.7</v>
+      </c>
+      <c r="BP114">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7580437</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45697.47916666666</v>
+      </c>
+      <c r="F115">
+        <v>19</v>
+      </c>
+      <c r="G115" t="s">
+        <v>75</v>
+      </c>
+      <c r="H115" t="s">
+        <v>78</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>2</v>
+      </c>
+      <c r="K115">
+        <v>3</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <v>5</v>
+      </c>
+      <c r="N115">
+        <v>6</v>
+      </c>
+      <c r="O115" t="s">
+        <v>161</v>
+      </c>
+      <c r="P115" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q115">
+        <v>4.33</v>
+      </c>
+      <c r="R115">
+        <v>2.25</v>
+      </c>
+      <c r="S115">
+        <v>2.3</v>
+      </c>
+      <c r="T115">
+        <v>1.36</v>
+      </c>
+      <c r="U115">
+        <v>3</v>
+      </c>
+      <c r="V115">
+        <v>2.63</v>
+      </c>
+      <c r="W115">
+        <v>1.44</v>
+      </c>
+      <c r="X115">
+        <v>6</v>
+      </c>
+      <c r="Y115">
+        <v>1.11</v>
+      </c>
+      <c r="Z115">
+        <v>4.1</v>
+      </c>
+      <c r="AA115">
+        <v>4.1</v>
+      </c>
+      <c r="AB115">
+        <v>1.72</v>
+      </c>
+      <c r="AC115">
+        <v>1.04</v>
+      </c>
+      <c r="AD115">
+        <v>9</v>
+      </c>
+      <c r="AE115">
+        <v>1.25</v>
+      </c>
+      <c r="AF115">
+        <v>3.75</v>
+      </c>
+      <c r="AG115">
+        <v>1.67</v>
+      </c>
+      <c r="AH115">
+        <v>2</v>
+      </c>
+      <c r="AI115">
+        <v>1.73</v>
+      </c>
+      <c r="AJ115">
+        <v>2</v>
+      </c>
+      <c r="AK115">
+        <v>1.93</v>
+      </c>
+      <c r="AL115">
+        <v>1.26</v>
+      </c>
+      <c r="AM115">
+        <v>1.24</v>
+      </c>
+      <c r="AN115">
+        <v>1.33</v>
+      </c>
+      <c r="AO115">
+        <v>2.44</v>
+      </c>
+      <c r="AP115">
+        <v>1.2</v>
+      </c>
+      <c r="AQ115">
+        <v>2.5</v>
+      </c>
+      <c r="AR115">
+        <v>1.52</v>
+      </c>
+      <c r="AS115">
+        <v>1.66</v>
+      </c>
+      <c r="AT115">
+        <v>3.18</v>
+      </c>
+      <c r="AU115">
+        <v>2</v>
+      </c>
+      <c r="AV115">
+        <v>6</v>
+      </c>
+      <c r="AW115">
+        <v>0</v>
+      </c>
+      <c r="AX115">
+        <v>0</v>
+      </c>
+      <c r="AY115">
+        <v>2</v>
+      </c>
+      <c r="AZ115">
+        <v>6</v>
+      </c>
+      <c r="BA115">
+        <v>5</v>
+      </c>
+      <c r="BB115">
+        <v>3</v>
+      </c>
+      <c r="BC115">
+        <v>8</v>
+      </c>
+      <c r="BD115">
+        <v>2.4</v>
+      </c>
+      <c r="BE115">
+        <v>6.5</v>
+      </c>
+      <c r="BF115">
+        <v>1.87</v>
+      </c>
+      <c r="BG115">
+        <v>1.19</v>
+      </c>
+      <c r="BH115">
+        <v>3.8</v>
+      </c>
+      <c r="BI115">
+        <v>1.39</v>
+      </c>
+      <c r="BJ115">
+        <v>2.67</v>
+      </c>
+      <c r="BK115">
+        <v>1.71</v>
+      </c>
+      <c r="BL115">
+        <v>2.02</v>
+      </c>
+      <c r="BM115">
+        <v>2.14</v>
+      </c>
+      <c r="BN115">
+        <v>1.6</v>
+      </c>
+      <c r="BO115">
+        <v>2.81</v>
+      </c>
+      <c r="BP115">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,6 +502,12 @@
     <t>['44']</t>
   </si>
   <si>
+    <t>['43', '45+2', '67', '90+2']</t>
+  </si>
+  <si>
+    <t>['64', '69']</t>
+  </si>
+  <si>
     <t>['5', '42', '80', '90+2']</t>
   </si>
   <si>
@@ -692,6 +698,9 @@
   </si>
   <si>
     <t>['21', '32', '48', '71', '83']</t>
+  </si>
+  <si>
+    <t>['69']</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP115"/>
+  <dimension ref="A1:BP118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1593,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ3">
         <v>1.78</v>
@@ -1721,7 +1730,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1927,7 +1936,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2005,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ5">
         <v>1.67</v>
@@ -2214,7 +2223,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2420,7 +2429,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ7">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2545,7 +2554,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -3035,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ10">
         <v>1.2</v>
@@ -3859,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ14">
         <v>1.2</v>
@@ -4068,7 +4077,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ15">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>1.66</v>
@@ -4399,7 +4408,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q17">
         <v>1.7</v>
@@ -4477,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ17">
         <v>1.2</v>
@@ -4605,7 +4614,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4811,7 +4820,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q19">
         <v>2.57</v>
@@ -4889,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ19">
         <v>0.5</v>
@@ -5017,7 +5026,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5098,7 +5107,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ20">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR20">
         <v>1.25</v>
@@ -5429,7 +5438,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5507,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -5635,7 +5644,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -5922,7 +5931,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ24">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR24">
         <v>2.32</v>
@@ -6047,7 +6056,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6253,7 +6262,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q26">
         <v>3.9</v>
@@ -6665,7 +6674,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6871,7 +6880,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -6949,10 +6958,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ29">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR29">
         <v>1.86</v>
@@ -7077,7 +7086,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7155,7 +7164,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ30">
         <v>1.78</v>
@@ -7283,7 +7292,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7489,7 +7498,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q32">
         <v>3.6</v>
@@ -7570,7 +7579,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ32">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR32">
         <v>1.05</v>
@@ -7695,7 +7704,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7901,7 +7910,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8107,7 +8116,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8391,7 +8400,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ36">
         <v>2.1</v>
@@ -8725,7 +8734,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8931,7 +8940,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q39">
         <v>4.33</v>
@@ -9137,7 +9146,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9218,7 +9227,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ40">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -9343,7 +9352,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q41">
         <v>4.36</v>
@@ -9421,7 +9430,7 @@
         <v>1.67</v>
       </c>
       <c r="AP41">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ41">
         <v>1.78</v>
@@ -9627,7 +9636,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ42">
         <v>0.5600000000000001</v>
@@ -9836,7 +9845,7 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR43">
         <v>1.8</v>
@@ -10039,7 +10048,7 @@
         <v>1.25</v>
       </c>
       <c r="AP44">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10167,7 +10176,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10373,7 +10382,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10579,7 +10588,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q47">
         <v>2.49</v>
@@ -10785,7 +10794,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q48">
         <v>2.48</v>
@@ -11197,7 +11206,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11609,7 +11618,7 @@
         <v>82</v>
       </c>
       <c r="P52" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11687,7 +11696,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ52">
         <v>2.1</v>
@@ -11815,7 +11824,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q53">
         <v>3.22</v>
@@ -11893,7 +11902,7 @@
         <v>1.33</v>
       </c>
       <c r="AP53">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ53">
         <v>0.5600000000000001</v>
@@ -12227,7 +12236,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12305,10 +12314,10 @@
         <v>0.4</v>
       </c>
       <c r="AP55">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ55">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
         <v>1.52</v>
@@ -12433,7 +12442,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12845,7 +12854,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13257,7 +13266,7 @@
         <v>85</v>
       </c>
       <c r="P60" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13463,7 +13472,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13750,7 +13759,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ62">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR62">
         <v>2</v>
@@ -13875,7 +13884,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -14081,7 +14090,7 @@
         <v>129</v>
       </c>
       <c r="P64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q64">
         <v>1.9</v>
@@ -14287,7 +14296,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
@@ -14493,7 +14502,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14699,7 +14708,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14905,7 +14914,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15317,7 +15326,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q70">
         <v>2</v>
@@ -15523,7 +15532,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -15935,7 +15944,7 @@
         <v>137</v>
       </c>
       <c r="P73" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q73">
         <v>1.83</v>
@@ -16141,7 +16150,7 @@
         <v>82</v>
       </c>
       <c r="P74" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16425,10 +16434,10 @@
         <v>0.5</v>
       </c>
       <c r="AP75">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ75">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR75">
         <v>1.4</v>
@@ -16553,7 +16562,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16631,7 +16640,7 @@
         <v>3</v>
       </c>
       <c r="AP76">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ76">
         <v>2.5</v>
@@ -16840,7 +16849,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR77">
         <v>1.54</v>
@@ -17249,7 +17258,7 @@
         <v>0.67</v>
       </c>
       <c r="AP79">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ79">
         <v>0.5</v>
@@ -17377,7 +17386,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q80">
         <v>4.5</v>
@@ -17789,7 +17798,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -18073,7 +18082,7 @@
         <v>1.17</v>
       </c>
       <c r="AP83">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ83">
         <v>1.2</v>
@@ -18282,7 +18291,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ84">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR84">
         <v>1.59</v>
@@ -18407,7 +18416,7 @@
         <v>141</v>
       </c>
       <c r="P85" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18485,7 +18494,7 @@
         <v>3</v>
       </c>
       <c r="AP85">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ85">
         <v>2.5</v>
@@ -18613,7 +18622,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18819,7 +18828,7 @@
         <v>143</v>
       </c>
       <c r="P87" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -18900,7 +18909,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ87">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR87">
         <v>1.42</v>
@@ -19231,7 +19240,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19437,7 +19446,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19849,7 +19858,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20055,7 +20064,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q93">
         <v>4</v>
@@ -20339,7 +20348,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ94">
         <v>1.67</v>
@@ -20545,10 +20554,10 @@
         <v>0.57</v>
       </c>
       <c r="AP95">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ95">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR95">
         <v>1.73</v>
@@ -20957,7 +20966,7 @@
         <v>1.29</v>
       </c>
       <c r="AP97">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21085,7 +21094,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21291,7 +21300,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21703,7 +21712,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21909,7 +21918,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -21987,7 +21996,7 @@
         <v>0.5</v>
       </c>
       <c r="AP102">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ102">
         <v>0.5</v>
@@ -22115,7 +22124,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -22196,7 +22205,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ103">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR103">
         <v>1.57</v>
@@ -22811,7 +22820,7 @@
         <v>0.63</v>
       </c>
       <c r="AP106">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ106">
         <v>0.5600000000000001</v>
@@ -23017,7 +23026,7 @@
         <v>1.88</v>
       </c>
       <c r="AP107">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ107">
         <v>1.67</v>
@@ -23432,7 +23441,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ109">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR109">
         <v>1.38</v>
@@ -23557,7 +23566,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23763,7 +23772,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -23969,7 +23978,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24175,7 +24184,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24587,7 +24596,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24744,6 +24753,624 @@
       </c>
       <c r="BP115">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7580443</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45703.47916666666</v>
+      </c>
+      <c r="F116">
+        <v>20</v>
+      </c>
+      <c r="G116" t="s">
+        <v>73</v>
+      </c>
+      <c r="H116" t="s">
+        <v>76</v>
+      </c>
+      <c r="I116">
+        <v>2</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>2</v>
+      </c>
+      <c r="L116">
+        <v>4</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>4</v>
+      </c>
+      <c r="O116" t="s">
+        <v>162</v>
+      </c>
+      <c r="P116" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q116">
+        <v>2.31</v>
+      </c>
+      <c r="R116">
+        <v>2.14</v>
+      </c>
+      <c r="S116">
+        <v>4.9</v>
+      </c>
+      <c r="T116">
+        <v>1.39</v>
+      </c>
+      <c r="U116">
+        <v>2.81</v>
+      </c>
+      <c r="V116">
+        <v>2.85</v>
+      </c>
+      <c r="W116">
+        <v>1.38</v>
+      </c>
+      <c r="X116">
+        <v>6.8</v>
+      </c>
+      <c r="Y116">
+        <v>1.08</v>
+      </c>
+      <c r="Z116">
+        <v>2.07</v>
+      </c>
+      <c r="AA116">
+        <v>3.34</v>
+      </c>
+      <c r="AB116">
+        <v>3.47</v>
+      </c>
+      <c r="AC116">
+        <v>1</v>
+      </c>
+      <c r="AD116">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE116">
+        <v>1.26</v>
+      </c>
+      <c r="AF116">
+        <v>3.22</v>
+      </c>
+      <c r="AG116">
+        <v>1.95</v>
+      </c>
+      <c r="AH116">
+        <v>1.79</v>
+      </c>
+      <c r="AI116">
+        <v>1.85</v>
+      </c>
+      <c r="AJ116">
+        <v>1.85</v>
+      </c>
+      <c r="AK116">
+        <v>1.18</v>
+      </c>
+      <c r="AL116">
+        <v>1.26</v>
+      </c>
+      <c r="AM116">
+        <v>2.01</v>
+      </c>
+      <c r="AN116">
+        <v>1.22</v>
+      </c>
+      <c r="AO116">
+        <v>0.44</v>
+      </c>
+      <c r="AP116">
+        <v>1.4</v>
+      </c>
+      <c r="AQ116">
+        <v>0.4</v>
+      </c>
+      <c r="AR116">
+        <v>1.39</v>
+      </c>
+      <c r="AS116">
+        <v>1.22</v>
+      </c>
+      <c r="AT116">
+        <v>2.61</v>
+      </c>
+      <c r="AU116">
+        <v>9</v>
+      </c>
+      <c r="AV116">
+        <v>2</v>
+      </c>
+      <c r="AW116">
+        <v>10</v>
+      </c>
+      <c r="AX116">
+        <v>0</v>
+      </c>
+      <c r="AY116">
+        <v>19</v>
+      </c>
+      <c r="AZ116">
+        <v>2</v>
+      </c>
+      <c r="BA116">
+        <v>4</v>
+      </c>
+      <c r="BB116">
+        <v>0</v>
+      </c>
+      <c r="BC116">
+        <v>4</v>
+      </c>
+      <c r="BD116">
+        <v>1.49</v>
+      </c>
+      <c r="BE116">
+        <v>7.1</v>
+      </c>
+      <c r="BF116">
+        <v>3.4</v>
+      </c>
+      <c r="BG116">
+        <v>1.2</v>
+      </c>
+      <c r="BH116">
+        <v>3.85</v>
+      </c>
+      <c r="BI116">
+        <v>1.39</v>
+      </c>
+      <c r="BJ116">
+        <v>2.75</v>
+      </c>
+      <c r="BK116">
+        <v>1.67</v>
+      </c>
+      <c r="BL116">
+        <v>2.13</v>
+      </c>
+      <c r="BM116">
+        <v>2.07</v>
+      </c>
+      <c r="BN116">
+        <v>1.71</v>
+      </c>
+      <c r="BO116">
+        <v>2.6</v>
+      </c>
+      <c r="BP116">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7580447</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45703.47916666666</v>
+      </c>
+      <c r="F117">
+        <v>20</v>
+      </c>
+      <c r="G117" t="s">
+        <v>71</v>
+      </c>
+      <c r="H117" t="s">
+        <v>77</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>2</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="N117">
+        <v>3</v>
+      </c>
+      <c r="O117" t="s">
+        <v>163</v>
+      </c>
+      <c r="P117" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q117">
+        <v>2.44</v>
+      </c>
+      <c r="R117">
+        <v>2.2</v>
+      </c>
+      <c r="S117">
+        <v>4.15</v>
+      </c>
+      <c r="T117">
+        <v>1.33</v>
+      </c>
+      <c r="U117">
+        <v>3.1</v>
+      </c>
+      <c r="V117">
+        <v>2.62</v>
+      </c>
+      <c r="W117">
+        <v>1.44</v>
+      </c>
+      <c r="X117">
+        <v>5.9</v>
+      </c>
+      <c r="Y117">
+        <v>1.11</v>
+      </c>
+      <c r="Z117">
+        <v>1.64</v>
+      </c>
+      <c r="AA117">
+        <v>3.93</v>
+      </c>
+      <c r="AB117">
+        <v>4.8</v>
+      </c>
+      <c r="AC117">
+        <v>1.02</v>
+      </c>
+      <c r="AD117">
+        <v>10</v>
+      </c>
+      <c r="AE117">
+        <v>1.19</v>
+      </c>
+      <c r="AF117">
+        <v>3.78</v>
+      </c>
+      <c r="AG117">
+        <v>1.8</v>
+      </c>
+      <c r="AH117">
+        <v>1.94</v>
+      </c>
+      <c r="AI117">
+        <v>1.66</v>
+      </c>
+      <c r="AJ117">
+        <v>2.09</v>
+      </c>
+      <c r="AK117">
+        <v>1.26</v>
+      </c>
+      <c r="AL117">
+        <v>1.26</v>
+      </c>
+      <c r="AM117">
+        <v>1.85</v>
+      </c>
+      <c r="AN117">
+        <v>1.44</v>
+      </c>
+      <c r="AO117">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP117">
+        <v>1.6</v>
+      </c>
+      <c r="AQ117">
+        <v>0.5</v>
+      </c>
+      <c r="AR117">
+        <v>1.75</v>
+      </c>
+      <c r="AS117">
+        <v>1.15</v>
+      </c>
+      <c r="AT117">
+        <v>2.9</v>
+      </c>
+      <c r="AU117">
+        <v>9</v>
+      </c>
+      <c r="AV117">
+        <v>2</v>
+      </c>
+      <c r="AW117">
+        <v>8</v>
+      </c>
+      <c r="AX117">
+        <v>8</v>
+      </c>
+      <c r="AY117">
+        <v>17</v>
+      </c>
+      <c r="AZ117">
+        <v>10</v>
+      </c>
+      <c r="BA117">
+        <v>5</v>
+      </c>
+      <c r="BB117">
+        <v>0</v>
+      </c>
+      <c r="BC117">
+        <v>5</v>
+      </c>
+      <c r="BD117">
+        <v>1.53</v>
+      </c>
+      <c r="BE117">
+        <v>9.1</v>
+      </c>
+      <c r="BF117">
+        <v>2.92</v>
+      </c>
+      <c r="BG117">
+        <v>1.15</v>
+      </c>
+      <c r="BH117">
+        <v>4.45</v>
+      </c>
+      <c r="BI117">
+        <v>1.29</v>
+      </c>
+      <c r="BJ117">
+        <v>3.12</v>
+      </c>
+      <c r="BK117">
+        <v>1.53</v>
+      </c>
+      <c r="BL117">
+        <v>2.34</v>
+      </c>
+      <c r="BM117">
+        <v>1.95</v>
+      </c>
+      <c r="BN117">
+        <v>1.85</v>
+      </c>
+      <c r="BO117">
+        <v>2.35</v>
+      </c>
+      <c r="BP117">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7580446</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F118">
+        <v>20</v>
+      </c>
+      <c r="G118" t="s">
+        <v>78</v>
+      </c>
+      <c r="H118" t="s">
+        <v>79</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118">
+        <v>1</v>
+      </c>
+      <c r="N118">
+        <v>2</v>
+      </c>
+      <c r="O118" t="s">
+        <v>123</v>
+      </c>
+      <c r="P118" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q118">
+        <v>1.74</v>
+      </c>
+      <c r="R118">
+        <v>2.65</v>
+      </c>
+      <c r="S118">
+        <v>6.5</v>
+      </c>
+      <c r="T118">
+        <v>1.23</v>
+      </c>
+      <c r="U118">
+        <v>3.9</v>
+      </c>
+      <c r="V118">
+        <v>2.16</v>
+      </c>
+      <c r="W118">
+        <v>1.65</v>
+      </c>
+      <c r="X118">
+        <v>4.4</v>
+      </c>
+      <c r="Y118">
+        <v>1.19</v>
+      </c>
+      <c r="Z118">
+        <v>1.29</v>
+      </c>
+      <c r="AA118">
+        <v>5.7</v>
+      </c>
+      <c r="AB118">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AC118">
+        <v>1.01</v>
+      </c>
+      <c r="AD118">
+        <v>17</v>
+      </c>
+      <c r="AE118">
+        <v>1.11</v>
+      </c>
+      <c r="AF118">
+        <v>5</v>
+      </c>
+      <c r="AG118">
+        <v>1.42</v>
+      </c>
+      <c r="AH118">
+        <v>2.65</v>
+      </c>
+      <c r="AI118">
+        <v>1.73</v>
+      </c>
+      <c r="AJ118">
+        <v>1.99</v>
+      </c>
+      <c r="AK118">
+        <v>1.06</v>
+      </c>
+      <c r="AL118">
+        <v>1.14</v>
+      </c>
+      <c r="AM118">
+        <v>3.16</v>
+      </c>
+      <c r="AN118">
+        <v>2.44</v>
+      </c>
+      <c r="AO118">
+        <v>1</v>
+      </c>
+      <c r="AP118">
+        <v>2.3</v>
+      </c>
+      <c r="AQ118">
+        <v>1</v>
+      </c>
+      <c r="AR118">
+        <v>1.86</v>
+      </c>
+      <c r="AS118">
+        <v>1.44</v>
+      </c>
+      <c r="AT118">
+        <v>3.3</v>
+      </c>
+      <c r="AU118">
+        <v>7</v>
+      </c>
+      <c r="AV118">
+        <v>4</v>
+      </c>
+      <c r="AW118">
+        <v>17</v>
+      </c>
+      <c r="AX118">
+        <v>5</v>
+      </c>
+      <c r="AY118">
+        <v>24</v>
+      </c>
+      <c r="AZ118">
+        <v>9</v>
+      </c>
+      <c r="BA118">
+        <v>15</v>
+      </c>
+      <c r="BB118">
+        <v>2</v>
+      </c>
+      <c r="BC118">
+        <v>17</v>
+      </c>
+      <c r="BD118">
+        <v>1.3</v>
+      </c>
+      <c r="BE118">
+        <v>9.9</v>
+      </c>
+      <c r="BF118">
+        <v>4.25</v>
+      </c>
+      <c r="BG118">
+        <v>1.23</v>
+      </c>
+      <c r="BH118">
+        <v>3.42</v>
+      </c>
+      <c r="BI118">
+        <v>1.46</v>
+      </c>
+      <c r="BJ118">
+        <v>2.45</v>
+      </c>
+      <c r="BK118">
+        <v>1.95</v>
+      </c>
+      <c r="BL118">
+        <v>1.85</v>
+      </c>
+      <c r="BM118">
+        <v>2.32</v>
+      </c>
+      <c r="BN118">
+        <v>1.51</v>
+      </c>
+      <c r="BO118">
+        <v>3.08</v>
+      </c>
+      <c r="BP118">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,9 @@
     <t>['64', '69']</t>
   </si>
   <si>
+    <t>['73']</t>
+  </si>
+  <si>
     <t>['5', '42', '80', '90+2']</t>
   </si>
   <si>
@@ -650,9 +653,6 @@
   </si>
   <si>
     <t>['62', '90+12']</t>
-  </si>
-  <si>
-    <t>['73']</t>
   </si>
   <si>
     <t>['57', '90+3']</t>
@@ -1062,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP118"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1730,7 +1730,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1936,7 +1936,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2017,7 +2017,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ5">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ6">
         <v>0.5</v>
@@ -2554,7 +2554,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -4283,7 +4283,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ16">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR16">
         <v>2.2</v>
@@ -4408,7 +4408,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q17">
         <v>1.7</v>
@@ -4614,7 +4614,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4695,7 +4695,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ18">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR18">
         <v>1.61</v>
@@ -4820,7 +4820,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q19">
         <v>2.57</v>
@@ -5026,7 +5026,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5310,7 +5310,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ21">
         <v>1.78</v>
@@ -5438,7 +5438,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5644,7 +5644,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -5722,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ23">
         <v>2.1</v>
@@ -6056,7 +6056,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6262,7 +6262,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q26">
         <v>3.9</v>
@@ -6546,7 +6546,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27">
         <v>1.2</v>
@@ -6674,7 +6674,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6880,7 +6880,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7086,7 +7086,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7292,7 +7292,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7370,10 +7370,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ31">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -7498,7 +7498,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q32">
         <v>3.6</v>
@@ -7704,7 +7704,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7910,7 +7910,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8116,7 +8116,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8734,7 +8734,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8815,7 +8815,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ38">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR38">
         <v>1.64</v>
@@ -8940,7 +8940,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q39">
         <v>4.33</v>
@@ -9018,10 +9018,10 @@
         <v>1.75</v>
       </c>
       <c r="AP39">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ39">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR39">
         <v>1.56</v>
@@ -9146,7 +9146,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9352,7 +9352,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q41">
         <v>4.36</v>
@@ -9639,7 +9639,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ42">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -9842,7 +9842,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ43">
         <v>0.4</v>
@@ -10176,7 +10176,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10257,7 +10257,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ45">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR45">
         <v>1.33</v>
@@ -10382,7 +10382,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10588,7 +10588,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q47">
         <v>2.49</v>
@@ -10794,7 +10794,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q48">
         <v>2.48</v>
@@ -11206,7 +11206,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11618,7 +11618,7 @@
         <v>82</v>
       </c>
       <c r="P52" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11824,7 +11824,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q53">
         <v>3.22</v>
@@ -11905,7 +11905,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ53">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR53">
         <v>1.35</v>
@@ -12108,7 +12108,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12236,7 +12236,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12442,7 +12442,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12854,7 +12854,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13266,7 +13266,7 @@
         <v>85</v>
       </c>
       <c r="P60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13347,7 +13347,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ60">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR60">
         <v>1.37</v>
@@ -13472,7 +13472,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13550,7 +13550,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ61">
         <v>2.5</v>
@@ -13884,7 +13884,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -14090,7 +14090,7 @@
         <v>129</v>
       </c>
       <c r="P64" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q64">
         <v>1.9</v>
@@ -14296,7 +14296,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
@@ -14377,7 +14377,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ65">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR65">
         <v>1.47</v>
@@ -14502,7 +14502,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14708,7 +14708,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14914,7 +14914,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15326,7 +15326,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q70">
         <v>2</v>
@@ -15407,7 +15407,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ70">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR70">
         <v>1.9</v>
@@ -15532,7 +15532,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -15610,7 +15610,7 @@
         <v>3</v>
       </c>
       <c r="AP71">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ71">
         <v>2.5</v>
@@ -15816,7 +15816,7 @@
         <v>1.2</v>
       </c>
       <c r="AP72">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ72">
         <v>1</v>
@@ -15944,7 +15944,7 @@
         <v>137</v>
       </c>
       <c r="P73" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q73">
         <v>1.83</v>
@@ -16022,7 +16022,7 @@
         <v>0.83</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ73">
         <v>1</v>
@@ -16150,7 +16150,7 @@
         <v>82</v>
       </c>
       <c r="P74" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16231,7 +16231,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ74">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR74">
         <v>1.41</v>
@@ -16562,7 +16562,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16846,7 +16846,7 @@
         <v>0.6</v>
       </c>
       <c r="AP77">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ77">
         <v>0.4</v>
@@ -17386,7 +17386,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q80">
         <v>4.5</v>
@@ -17673,7 +17673,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ81">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR81">
         <v>1.54</v>
@@ -17798,7 +17798,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -18416,7 +18416,7 @@
         <v>141</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18700,7 +18700,7 @@
         <v>0.71</v>
       </c>
       <c r="AP86">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ86">
         <v>1.2</v>
@@ -19240,7 +19240,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19730,7 +19730,7 @@
         <v>0.57</v>
       </c>
       <c r="AP91">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ91">
         <v>0.5</v>
@@ -19939,7 +19939,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ92">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR92">
         <v>1.34</v>
@@ -20351,7 +20351,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ94">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR94">
         <v>1.72</v>
@@ -22614,7 +22614,7 @@
         <v>1.13</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ105">
         <v>1.2</v>
@@ -22823,7 +22823,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ106">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR106">
         <v>1.71</v>
@@ -23029,7 +23029,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ107">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR107">
         <v>1.92</v>
@@ -23232,7 +23232,7 @@
         <v>1.88</v>
       </c>
       <c r="AP108">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ108">
         <v>1.78</v>
@@ -25371,6 +25371,418 @@
       </c>
       <c r="BP118">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7580444</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45704.47916666666</v>
+      </c>
+      <c r="F119">
+        <v>20</v>
+      </c>
+      <c r="G119" t="s">
+        <v>70</v>
+      </c>
+      <c r="H119" t="s">
+        <v>75</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>1</v>
+      </c>
+      <c r="O119" t="s">
+        <v>92</v>
+      </c>
+      <c r="P119" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q119">
+        <v>3.13</v>
+      </c>
+      <c r="R119">
+        <v>2.19</v>
+      </c>
+      <c r="S119">
+        <v>3.38</v>
+      </c>
+      <c r="T119">
+        <v>1.37</v>
+      </c>
+      <c r="U119">
+        <v>2.95</v>
+      </c>
+      <c r="V119">
+        <v>2.89</v>
+      </c>
+      <c r="W119">
+        <v>1.39</v>
+      </c>
+      <c r="X119">
+        <v>6.5</v>
+      </c>
+      <c r="Y119">
+        <v>1.08</v>
+      </c>
+      <c r="Z119">
+        <v>2.34</v>
+      </c>
+      <c r="AA119">
+        <v>3.21</v>
+      </c>
+      <c r="AB119">
+        <v>3.01</v>
+      </c>
+      <c r="AC119">
+        <v>1.03</v>
+      </c>
+      <c r="AD119">
+        <v>9</v>
+      </c>
+      <c r="AE119">
+        <v>1.29</v>
+      </c>
+      <c r="AF119">
+        <v>3.3</v>
+      </c>
+      <c r="AG119">
+        <v>1.98</v>
+      </c>
+      <c r="AH119">
+        <v>1.77</v>
+      </c>
+      <c r="AI119">
+        <v>1.73</v>
+      </c>
+      <c r="AJ119">
+        <v>2</v>
+      </c>
+      <c r="AK119">
+        <v>1.44</v>
+      </c>
+      <c r="AL119">
+        <v>1.33</v>
+      </c>
+      <c r="AM119">
+        <v>1.53</v>
+      </c>
+      <c r="AN119">
+        <v>1</v>
+      </c>
+      <c r="AO119">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP119">
+        <v>1.2</v>
+      </c>
+      <c r="AQ119">
+        <v>0.5</v>
+      </c>
+      <c r="AR119">
+        <v>1.56</v>
+      </c>
+      <c r="AS119">
+        <v>1.23</v>
+      </c>
+      <c r="AT119">
+        <v>2.79</v>
+      </c>
+      <c r="AU119">
+        <v>4</v>
+      </c>
+      <c r="AV119">
+        <v>3</v>
+      </c>
+      <c r="AW119">
+        <v>6</v>
+      </c>
+      <c r="AX119">
+        <v>3</v>
+      </c>
+      <c r="AY119">
+        <v>10</v>
+      </c>
+      <c r="AZ119">
+        <v>6</v>
+      </c>
+      <c r="BA119">
+        <v>2</v>
+      </c>
+      <c r="BB119">
+        <v>4</v>
+      </c>
+      <c r="BC119">
+        <v>6</v>
+      </c>
+      <c r="BD119">
+        <v>1.69</v>
+      </c>
+      <c r="BE119">
+        <v>6.55</v>
+      </c>
+      <c r="BF119">
+        <v>2.77</v>
+      </c>
+      <c r="BG119">
+        <v>1.28</v>
+      </c>
+      <c r="BH119">
+        <v>3.25</v>
+      </c>
+      <c r="BI119">
+        <v>1.53</v>
+      </c>
+      <c r="BJ119">
+        <v>2.42</v>
+      </c>
+      <c r="BK119">
+        <v>1.9</v>
+      </c>
+      <c r="BL119">
+        <v>1.9</v>
+      </c>
+      <c r="BM119">
+        <v>2.39</v>
+      </c>
+      <c r="BN119">
+        <v>1.55</v>
+      </c>
+      <c r="BO119">
+        <v>3.12</v>
+      </c>
+      <c r="BP119">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7580445</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45704.47916666666</v>
+      </c>
+      <c r="F120">
+        <v>20</v>
+      </c>
+      <c r="G120" t="s">
+        <v>74</v>
+      </c>
+      <c r="H120" t="s">
+        <v>80</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120">
+        <v>1</v>
+      </c>
+      <c r="N120">
+        <v>2</v>
+      </c>
+      <c r="O120" t="s">
+        <v>164</v>
+      </c>
+      <c r="P120" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q120">
+        <v>2.71</v>
+      </c>
+      <c r="R120">
+        <v>2.14</v>
+      </c>
+      <c r="S120">
+        <v>4.23</v>
+      </c>
+      <c r="T120">
+        <v>1.42</v>
+      </c>
+      <c r="U120">
+        <v>2.76</v>
+      </c>
+      <c r="V120">
+        <v>3.13</v>
+      </c>
+      <c r="W120">
+        <v>1.34</v>
+      </c>
+      <c r="X120">
+        <v>7</v>
+      </c>
+      <c r="Y120">
+        <v>1.07</v>
+      </c>
+      <c r="Z120">
+        <v>2.01</v>
+      </c>
+      <c r="AA120">
+        <v>3.39</v>
+      </c>
+      <c r="AB120">
+        <v>3.61</v>
+      </c>
+      <c r="AC120">
+        <v>1.04</v>
+      </c>
+      <c r="AD120">
+        <v>8.5</v>
+      </c>
+      <c r="AE120">
+        <v>1.33</v>
+      </c>
+      <c r="AF120">
+        <v>3</v>
+      </c>
+      <c r="AG120">
+        <v>1.94</v>
+      </c>
+      <c r="AH120">
+        <v>1.8</v>
+      </c>
+      <c r="AI120">
+        <v>1.85</v>
+      </c>
+      <c r="AJ120">
+        <v>1.85</v>
+      </c>
+      <c r="AK120">
+        <v>1.3</v>
+      </c>
+      <c r="AL120">
+        <v>1.33</v>
+      </c>
+      <c r="AM120">
+        <v>1.73</v>
+      </c>
+      <c r="AN120">
+        <v>2</v>
+      </c>
+      <c r="AO120">
+        <v>1.67</v>
+      </c>
+      <c r="AP120">
+        <v>1.9</v>
+      </c>
+      <c r="AQ120">
+        <v>1.6</v>
+      </c>
+      <c r="AR120">
+        <v>1.84</v>
+      </c>
+      <c r="AS120">
+        <v>1.55</v>
+      </c>
+      <c r="AT120">
+        <v>3.39</v>
+      </c>
+      <c r="AU120">
+        <v>3</v>
+      </c>
+      <c r="AV120">
+        <v>6</v>
+      </c>
+      <c r="AW120">
+        <v>4</v>
+      </c>
+      <c r="AX120">
+        <v>2</v>
+      </c>
+      <c r="AY120">
+        <v>7</v>
+      </c>
+      <c r="AZ120">
+        <v>8</v>
+      </c>
+      <c r="BA120">
+        <v>2</v>
+      </c>
+      <c r="BB120">
+        <v>5</v>
+      </c>
+      <c r="BC120">
+        <v>7</v>
+      </c>
+      <c r="BD120">
+        <v>1.69</v>
+      </c>
+      <c r="BE120">
+        <v>6.5</v>
+      </c>
+      <c r="BF120">
+        <v>2.78</v>
+      </c>
+      <c r="BG120">
+        <v>1.3</v>
+      </c>
+      <c r="BH120">
+        <v>2.97</v>
+      </c>
+      <c r="BI120">
+        <v>1.57</v>
+      </c>
+      <c r="BJ120">
+        <v>2.19</v>
+      </c>
+      <c r="BK120">
+        <v>1.99</v>
+      </c>
+      <c r="BL120">
+        <v>1.73</v>
+      </c>
+      <c r="BM120">
+        <v>2.6</v>
+      </c>
+      <c r="BN120">
+        <v>1.41</v>
+      </c>
+      <c r="BO120">
+        <v>3.5</v>
+      </c>
+      <c r="BP120">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="231">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -509,6 +509,12 @@
   </si>
   <si>
     <t>['73']</t>
+  </si>
+  <si>
+    <t>['60', '80']</t>
+  </si>
+  <si>
+    <t>['74']</t>
   </si>
   <si>
     <t>['5', '42', '80', '90+2']</t>
@@ -1062,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1730,7 +1736,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1808,10 +1814,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ4">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1936,7 +1942,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2017,7 +2023,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ5">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2426,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ7">
         <v>0.4</v>
@@ -2554,7 +2560,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -2635,7 +2641,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2838,10 +2844,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ9">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3662,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -4074,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ15">
         <v>0.5</v>
@@ -4283,7 +4289,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ16">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR16">
         <v>2.2</v>
@@ -4408,7 +4414,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q17">
         <v>1.7</v>
@@ -4489,7 +4495,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ17">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR17">
         <v>1.31</v>
@@ -4614,7 +4620,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4695,7 +4701,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ18">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR18">
         <v>1.61</v>
@@ -4820,7 +4826,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q19">
         <v>2.57</v>
@@ -4901,7 +4907,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ19">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR19">
         <v>1.28</v>
@@ -5026,7 +5032,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5104,7 +5110,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ20">
         <v>0.4</v>
@@ -5438,7 +5444,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5644,7 +5650,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -5928,7 +5934,7 @@
         <v>0.5</v>
       </c>
       <c r="AP24">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ24">
         <v>0.5</v>
@@ -6056,7 +6062,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6134,7 +6140,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6262,7 +6268,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q26">
         <v>3.9</v>
@@ -6343,7 +6349,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ26">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR26">
         <v>1.52</v>
@@ -6549,7 +6555,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ27">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR27">
         <v>1.22</v>
@@ -6674,7 +6680,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6752,7 +6758,7 @@
         <v>0.67</v>
       </c>
       <c r="AP28">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -6880,7 +6886,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7086,7 +7092,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7292,7 +7298,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7498,7 +7504,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q32">
         <v>3.6</v>
@@ -7704,7 +7710,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7782,10 +7788,10 @@
         <v>0.5</v>
       </c>
       <c r="AP33">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ33">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR33">
         <v>2.34</v>
@@ -7910,7 +7916,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8116,7 +8122,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8197,7 +8203,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ35">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR35">
         <v>2.59</v>
@@ -8606,7 +8612,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ37">
         <v>1.2</v>
@@ -8734,7 +8740,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8812,10 +8818,10 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ38">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR38">
         <v>1.64</v>
@@ -8940,7 +8946,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q39">
         <v>4.33</v>
@@ -9021,7 +9027,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ39">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR39">
         <v>1.56</v>
@@ -9146,7 +9152,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9224,7 +9230,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ40">
         <v>0.5</v>
@@ -9352,7 +9358,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q41">
         <v>4.36</v>
@@ -10176,7 +10182,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10254,7 +10260,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ45">
         <v>0.5</v>
@@ -10382,7 +10388,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10463,7 +10469,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ46">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR46">
         <v>1.09</v>
@@ -10588,7 +10594,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q47">
         <v>2.49</v>
@@ -10669,7 +10675,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ47">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR47">
         <v>1.38</v>
@@ -10794,7 +10800,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q48">
         <v>2.48</v>
@@ -10872,7 +10878,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ48">
         <v>1.2</v>
@@ -11206,7 +11212,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11284,10 +11290,10 @@
         <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ50">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR50">
         <v>1.39</v>
@@ -11490,7 +11496,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -11618,7 +11624,7 @@
         <v>82</v>
       </c>
       <c r="P52" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11824,7 +11830,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q53">
         <v>3.22</v>
@@ -12236,7 +12242,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12442,7 +12448,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12854,7 +12860,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -12935,7 +12941,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ58">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR58">
         <v>1.32</v>
@@ -13138,10 +13144,10 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ59">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR59">
         <v>1.4</v>
@@ -13266,7 +13272,7 @@
         <v>85</v>
       </c>
       <c r="P60" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13344,10 +13350,10 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ60">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR60">
         <v>1.37</v>
@@ -13472,7 +13478,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13553,7 +13559,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ61">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR61">
         <v>1.75</v>
@@ -13756,7 +13762,7 @@
         <v>0.75</v>
       </c>
       <c r="AP62">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ62">
         <v>0.4</v>
@@ -13884,7 +13890,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -13962,7 +13968,7 @@
         <v>0.25</v>
       </c>
       <c r="AP63">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ63">
         <v>1.2</v>
@@ -14090,7 +14096,7 @@
         <v>129</v>
       </c>
       <c r="P64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q64">
         <v>1.9</v>
@@ -14168,7 +14174,7 @@
         <v>0.8</v>
       </c>
       <c r="AP64">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ64">
         <v>1.2</v>
@@ -14296,7 +14302,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
@@ -14502,7 +14508,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14583,7 +14589,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ66">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR66">
         <v>1.77</v>
@@ -14708,7 +14714,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14786,7 +14792,7 @@
         <v>1.8</v>
       </c>
       <c r="AP67">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ67">
         <v>2.1</v>
@@ -14914,7 +14920,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -14995,7 +15001,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ68">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR68">
         <v>1.28</v>
@@ -15326,7 +15332,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q70">
         <v>2</v>
@@ -15404,7 +15410,7 @@
         <v>0.8</v>
       </c>
       <c r="AP70">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ70">
         <v>0.5</v>
@@ -15532,7 +15538,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -15613,7 +15619,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ71">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR71">
         <v>1.47</v>
@@ -15944,7 +15950,7 @@
         <v>137</v>
       </c>
       <c r="P73" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q73">
         <v>1.83</v>
@@ -16150,7 +16156,7 @@
         <v>82</v>
       </c>
       <c r="P74" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16228,10 +16234,10 @@
         <v>1.83</v>
       </c>
       <c r="AP74">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ74">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR74">
         <v>1.41</v>
@@ -16562,7 +16568,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16643,7 +16649,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ76">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR76">
         <v>1.55</v>
@@ -17052,7 +17058,7 @@
         <v>2.2</v>
       </c>
       <c r="AP78">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ78">
         <v>1.78</v>
@@ -17261,7 +17267,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ79">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR79">
         <v>1.8</v>
@@ -17386,7 +17392,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q80">
         <v>4.5</v>
@@ -17670,7 +17676,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ81">
         <v>0.5</v>
@@ -17798,7 +17804,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -17876,7 +17882,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ82">
         <v>2.1</v>
@@ -18085,7 +18091,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ83">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR83">
         <v>1.68</v>
@@ -18497,7 +18503,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ85">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR85">
         <v>1.4</v>
@@ -18622,7 +18628,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18828,7 +18834,7 @@
         <v>143</v>
       </c>
       <c r="P87" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19240,7 +19246,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19318,7 +19324,7 @@
         <v>2.14</v>
       </c>
       <c r="AP89">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ89">
         <v>2.1</v>
@@ -19446,7 +19452,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19524,7 +19530,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -19733,7 +19739,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ91">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR91">
         <v>1.74</v>
@@ -19858,7 +19864,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20064,7 +20070,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q93">
         <v>4</v>
@@ -20142,7 +20148,7 @@
         <v>1.71</v>
       </c>
       <c r="AP93">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ93">
         <v>1.78</v>
@@ -20351,7 +20357,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ94">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR94">
         <v>1.72</v>
@@ -20760,10 +20766,10 @@
         <v>1.14</v>
       </c>
       <c r="AP96">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ96">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR96">
         <v>1.35</v>
@@ -21094,7 +21100,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21172,7 +21178,7 @@
         <v>1.88</v>
       </c>
       <c r="AP98">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ98">
         <v>2.1</v>
@@ -21300,7 +21306,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21712,7 +21718,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21790,10 +21796,10 @@
         <v>2.75</v>
       </c>
       <c r="AP101">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ101">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR101">
         <v>1.8</v>
@@ -21918,7 +21924,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -21999,7 +22005,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ102">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR102">
         <v>1.31</v>
@@ -22124,7 +22130,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -22408,7 +22414,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ104">
         <v>1</v>
@@ -22617,7 +22623,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ105">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR105">
         <v>1.8</v>
@@ -23029,7 +23035,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ107">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR107">
         <v>1.92</v>
@@ -23438,7 +23444,7 @@
         <v>0.5</v>
       </c>
       <c r="AP109">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ109">
         <v>0.4</v>
@@ -23566,7 +23572,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23772,7 +23778,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -23853,7 +23859,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ111">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR111">
         <v>1.66</v>
@@ -23978,7 +23984,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24184,7 +24190,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24262,10 +24268,10 @@
         <v>1</v>
       </c>
       <c r="AP113">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ113">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR113">
         <v>1.8</v>
@@ -24468,7 +24474,7 @@
         <v>1.11</v>
       </c>
       <c r="AP114">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ114">
         <v>1</v>
@@ -24596,7 +24602,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24674,10 +24680,10 @@
         <v>2.44</v>
       </c>
       <c r="AP115">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ115">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR115">
         <v>1.52</v>
@@ -25214,7 +25220,7 @@
         <v>123</v>
       </c>
       <c r="P118" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q118">
         <v>1.74</v>
@@ -25707,7 +25713,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ120">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR120">
         <v>1.84</v>
@@ -25783,6 +25789,830 @@
       </c>
       <c r="BP120">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7580450</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45710.47916666666</v>
+      </c>
+      <c r="F121">
+        <v>21</v>
+      </c>
+      <c r="G121" t="s">
+        <v>75</v>
+      </c>
+      <c r="H121" t="s">
+        <v>73</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>2</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>3</v>
+      </c>
+      <c r="O121" t="s">
+        <v>165</v>
+      </c>
+      <c r="P121" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q121">
+        <v>3.1</v>
+      </c>
+      <c r="R121">
+        <v>2.05</v>
+      </c>
+      <c r="S121">
+        <v>3.25</v>
+      </c>
+      <c r="T121">
+        <v>1.44</v>
+      </c>
+      <c r="U121">
+        <v>2.63</v>
+      </c>
+      <c r="V121">
+        <v>3</v>
+      </c>
+      <c r="W121">
+        <v>1.36</v>
+      </c>
+      <c r="X121">
+        <v>7</v>
+      </c>
+      <c r="Y121">
+        <v>1.08</v>
+      </c>
+      <c r="Z121">
+        <v>2.3</v>
+      </c>
+      <c r="AA121">
+        <v>3.27</v>
+      </c>
+      <c r="AB121">
+        <v>3.04</v>
+      </c>
+      <c r="AC121">
+        <v>1.01</v>
+      </c>
+      <c r="AD121">
+        <v>8.5</v>
+      </c>
+      <c r="AE121">
+        <v>1.27</v>
+      </c>
+      <c r="AF121">
+        <v>3.15</v>
+      </c>
+      <c r="AG121">
+        <v>1.94</v>
+      </c>
+      <c r="AH121">
+        <v>1.8</v>
+      </c>
+      <c r="AI121">
+        <v>1.73</v>
+      </c>
+      <c r="AJ121">
+        <v>2</v>
+      </c>
+      <c r="AK121">
+        <v>1.39</v>
+      </c>
+      <c r="AL121">
+        <v>1.3</v>
+      </c>
+      <c r="AM121">
+        <v>1.56</v>
+      </c>
+      <c r="AN121">
+        <v>1.2</v>
+      </c>
+      <c r="AO121">
+        <v>1.2</v>
+      </c>
+      <c r="AP121">
+        <v>1.36</v>
+      </c>
+      <c r="AQ121">
+        <v>1.09</v>
+      </c>
+      <c r="AR121">
+        <v>1.4</v>
+      </c>
+      <c r="AS121">
+        <v>1.15</v>
+      </c>
+      <c r="AT121">
+        <v>2.55</v>
+      </c>
+      <c r="AU121">
+        <v>8</v>
+      </c>
+      <c r="AV121">
+        <v>4</v>
+      </c>
+      <c r="AW121">
+        <v>6</v>
+      </c>
+      <c r="AX121">
+        <v>8</v>
+      </c>
+      <c r="AY121">
+        <v>14</v>
+      </c>
+      <c r="AZ121">
+        <v>12</v>
+      </c>
+      <c r="BA121">
+        <v>10</v>
+      </c>
+      <c r="BB121">
+        <v>0</v>
+      </c>
+      <c r="BC121">
+        <v>10</v>
+      </c>
+      <c r="BD121">
+        <v>1.7</v>
+      </c>
+      <c r="BE121">
+        <v>6.7</v>
+      </c>
+      <c r="BF121">
+        <v>2.72</v>
+      </c>
+      <c r="BG121">
+        <v>1.21</v>
+      </c>
+      <c r="BH121">
+        <v>3.78</v>
+      </c>
+      <c r="BI121">
+        <v>1.41</v>
+      </c>
+      <c r="BJ121">
+        <v>2.7</v>
+      </c>
+      <c r="BK121">
+        <v>1.69</v>
+      </c>
+      <c r="BL121">
+        <v>2.1</v>
+      </c>
+      <c r="BM121">
+        <v>2.1</v>
+      </c>
+      <c r="BN121">
+        <v>1.68</v>
+      </c>
+      <c r="BO121">
+        <v>2.65</v>
+      </c>
+      <c r="BP121">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7580452</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45710.47916666666</v>
+      </c>
+      <c r="F122">
+        <v>21</v>
+      </c>
+      <c r="G122" t="s">
+        <v>72</v>
+      </c>
+      <c r="H122" t="s">
+        <v>70</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122" t="s">
+        <v>82</v>
+      </c>
+      <c r="P122" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q122">
+        <v>2.88</v>
+      </c>
+      <c r="R122">
+        <v>2.2</v>
+      </c>
+      <c r="S122">
+        <v>3.4</v>
+      </c>
+      <c r="T122">
+        <v>1.36</v>
+      </c>
+      <c r="U122">
+        <v>3</v>
+      </c>
+      <c r="V122">
+        <v>2.75</v>
+      </c>
+      <c r="W122">
+        <v>1.4</v>
+      </c>
+      <c r="X122">
+        <v>6.5</v>
+      </c>
+      <c r="Y122">
+        <v>1.1</v>
+      </c>
+      <c r="Z122">
+        <v>2.51</v>
+      </c>
+      <c r="AA122">
+        <v>3.36</v>
+      </c>
+      <c r="AB122">
+        <v>2.68</v>
+      </c>
+      <c r="AC122">
+        <v>1.02</v>
+      </c>
+      <c r="AD122">
+        <v>10</v>
+      </c>
+      <c r="AE122">
+        <v>1.21</v>
+      </c>
+      <c r="AF122">
+        <v>3.6</v>
+      </c>
+      <c r="AG122">
+        <v>1.82</v>
+      </c>
+      <c r="AH122">
+        <v>1.92</v>
+      </c>
+      <c r="AI122">
+        <v>1.67</v>
+      </c>
+      <c r="AJ122">
+        <v>2.1</v>
+      </c>
+      <c r="AK122">
+        <v>1.44</v>
+      </c>
+      <c r="AL122">
+        <v>1.28</v>
+      </c>
+      <c r="AM122">
+        <v>1.51</v>
+      </c>
+      <c r="AN122">
+        <v>0.78</v>
+      </c>
+      <c r="AO122">
+        <v>0.5</v>
+      </c>
+      <c r="AP122">
+        <v>0.8</v>
+      </c>
+      <c r="AQ122">
+        <v>0.55</v>
+      </c>
+      <c r="AR122">
+        <v>1.44</v>
+      </c>
+      <c r="AS122">
+        <v>1.4</v>
+      </c>
+      <c r="AT122">
+        <v>2.84</v>
+      </c>
+      <c r="AU122">
+        <v>5</v>
+      </c>
+      <c r="AV122">
+        <v>2</v>
+      </c>
+      <c r="AW122">
+        <v>13</v>
+      </c>
+      <c r="AX122">
+        <v>4</v>
+      </c>
+      <c r="AY122">
+        <v>18</v>
+      </c>
+      <c r="AZ122">
+        <v>6</v>
+      </c>
+      <c r="BA122">
+        <v>5</v>
+      </c>
+      <c r="BB122">
+        <v>1</v>
+      </c>
+      <c r="BC122">
+        <v>6</v>
+      </c>
+      <c r="BD122">
+        <v>2.07</v>
+      </c>
+      <c r="BE122">
+        <v>6.25</v>
+      </c>
+      <c r="BF122">
+        <v>2.16</v>
+      </c>
+      <c r="BG122">
+        <v>1.28</v>
+      </c>
+      <c r="BH122">
+        <v>3.08</v>
+      </c>
+      <c r="BI122">
+        <v>1.53</v>
+      </c>
+      <c r="BJ122">
+        <v>2.27</v>
+      </c>
+      <c r="BK122">
+        <v>2</v>
+      </c>
+      <c r="BL122">
+        <v>1.8</v>
+      </c>
+      <c r="BM122">
+        <v>2.51</v>
+      </c>
+      <c r="BN122">
+        <v>1.44</v>
+      </c>
+      <c r="BO122">
+        <v>3.42</v>
+      </c>
+      <c r="BP122">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7580453</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45710.47916666666</v>
+      </c>
+      <c r="F123">
+        <v>21</v>
+      </c>
+      <c r="G123" t="s">
+        <v>77</v>
+      </c>
+      <c r="H123" t="s">
+        <v>78</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>1</v>
+      </c>
+      <c r="N123">
+        <v>2</v>
+      </c>
+      <c r="O123" t="s">
+        <v>166</v>
+      </c>
+      <c r="P123" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q123">
+        <v>6.04</v>
+      </c>
+      <c r="R123">
+        <v>2.64</v>
+      </c>
+      <c r="S123">
+        <v>1.88</v>
+      </c>
+      <c r="T123">
+        <v>1.24</v>
+      </c>
+      <c r="U123">
+        <v>3.8</v>
+      </c>
+      <c r="V123">
+        <v>2.31</v>
+      </c>
+      <c r="W123">
+        <v>1.58</v>
+      </c>
+      <c r="X123">
+        <v>4.8</v>
+      </c>
+      <c r="Y123">
+        <v>1.16</v>
+      </c>
+      <c r="Z123">
+        <v>5.3</v>
+      </c>
+      <c r="AA123">
+        <v>4.5</v>
+      </c>
+      <c r="AB123">
+        <v>1.52</v>
+      </c>
+      <c r="AC123">
+        <v>1</v>
+      </c>
+      <c r="AD123">
+        <v>12</v>
+      </c>
+      <c r="AE123">
+        <v>1.17</v>
+      </c>
+      <c r="AF123">
+        <v>4.6</v>
+      </c>
+      <c r="AG123">
+        <v>1.5</v>
+      </c>
+      <c r="AH123">
+        <v>2.3</v>
+      </c>
+      <c r="AI123">
+        <v>1.66</v>
+      </c>
+      <c r="AJ123">
+        <v>2.08</v>
+      </c>
+      <c r="AK123">
+        <v>2.46</v>
+      </c>
+      <c r="AL123">
+        <v>1.17</v>
+      </c>
+      <c r="AM123">
+        <v>1.13</v>
+      </c>
+      <c r="AN123">
+        <v>1.3</v>
+      </c>
+      <c r="AO123">
+        <v>2.5</v>
+      </c>
+      <c r="AP123">
+        <v>1.27</v>
+      </c>
+      <c r="AQ123">
+        <v>2.36</v>
+      </c>
+      <c r="AR123">
+        <v>1.56</v>
+      </c>
+      <c r="AS123">
+        <v>1.58</v>
+      </c>
+      <c r="AT123">
+        <v>3.14</v>
+      </c>
+      <c r="AU123">
+        <v>4</v>
+      </c>
+      <c r="AV123">
+        <v>7</v>
+      </c>
+      <c r="AW123">
+        <v>12</v>
+      </c>
+      <c r="AX123">
+        <v>10</v>
+      </c>
+      <c r="AY123">
+        <v>16</v>
+      </c>
+      <c r="AZ123">
+        <v>17</v>
+      </c>
+      <c r="BA123">
+        <v>2</v>
+      </c>
+      <c r="BB123">
+        <v>6</v>
+      </c>
+      <c r="BC123">
+        <v>8</v>
+      </c>
+      <c r="BD123">
+        <v>3.38</v>
+      </c>
+      <c r="BE123">
+        <v>9.1</v>
+      </c>
+      <c r="BF123">
+        <v>1.43</v>
+      </c>
+      <c r="BG123">
+        <v>1.25</v>
+      </c>
+      <c r="BH123">
+        <v>3.28</v>
+      </c>
+      <c r="BI123">
+        <v>1.5</v>
+      </c>
+      <c r="BJ123">
+        <v>2.35</v>
+      </c>
+      <c r="BK123">
+        <v>1.92</v>
+      </c>
+      <c r="BL123">
+        <v>1.88</v>
+      </c>
+      <c r="BM123">
+        <v>2.4</v>
+      </c>
+      <c r="BN123">
+        <v>1.48</v>
+      </c>
+      <c r="BO123">
+        <v>3.2</v>
+      </c>
+      <c r="BP123">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7580451</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45710.58333333334</v>
+      </c>
+      <c r="F124">
+        <v>21</v>
+      </c>
+      <c r="G124" t="s">
+        <v>81</v>
+      </c>
+      <c r="H124" t="s">
+        <v>80</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124">
+        <v>2</v>
+      </c>
+      <c r="O124" t="s">
+        <v>88</v>
+      </c>
+      <c r="P124" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q124">
+        <v>2.75</v>
+      </c>
+      <c r="R124">
+        <v>2.2</v>
+      </c>
+      <c r="S124">
+        <v>3.25</v>
+      </c>
+      <c r="T124">
+        <v>1.33</v>
+      </c>
+      <c r="U124">
+        <v>3.25</v>
+      </c>
+      <c r="V124">
+        <v>2.63</v>
+      </c>
+      <c r="W124">
+        <v>1.44</v>
+      </c>
+      <c r="X124">
+        <v>6</v>
+      </c>
+      <c r="Y124">
+        <v>1.11</v>
+      </c>
+      <c r="Z124">
+        <v>2.07</v>
+      </c>
+      <c r="AA124">
+        <v>3.31</v>
+      </c>
+      <c r="AB124">
+        <v>3.51</v>
+      </c>
+      <c r="AC124">
+        <v>1.01</v>
+      </c>
+      <c r="AD124">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE124">
+        <v>1.23</v>
+      </c>
+      <c r="AF124">
+        <v>3.9</v>
+      </c>
+      <c r="AG124">
+        <v>1.92</v>
+      </c>
+      <c r="AH124">
+        <v>1.82</v>
+      </c>
+      <c r="AI124">
+        <v>1.62</v>
+      </c>
+      <c r="AJ124">
+        <v>2.2</v>
+      </c>
+      <c r="AK124">
+        <v>1.42</v>
+      </c>
+      <c r="AL124">
+        <v>1.27</v>
+      </c>
+      <c r="AM124">
+        <v>1.53</v>
+      </c>
+      <c r="AN124">
+        <v>2.5</v>
+      </c>
+      <c r="AO124">
+        <v>1.6</v>
+      </c>
+      <c r="AP124">
+        <v>2.36</v>
+      </c>
+      <c r="AQ124">
+        <v>1.55</v>
+      </c>
+      <c r="AR124">
+        <v>1.82</v>
+      </c>
+      <c r="AS124">
+        <v>1.52</v>
+      </c>
+      <c r="AT124">
+        <v>3.34</v>
+      </c>
+      <c r="AU124">
+        <v>5</v>
+      </c>
+      <c r="AV124">
+        <v>3</v>
+      </c>
+      <c r="AW124">
+        <v>4</v>
+      </c>
+      <c r="AX124">
+        <v>7</v>
+      </c>
+      <c r="AY124">
+        <v>9</v>
+      </c>
+      <c r="AZ124">
+        <v>10</v>
+      </c>
+      <c r="BA124">
+        <v>2</v>
+      </c>
+      <c r="BB124">
+        <v>5</v>
+      </c>
+      <c r="BC124">
+        <v>7</v>
+      </c>
+      <c r="BD124">
+        <v>1.98</v>
+      </c>
+      <c r="BE124">
+        <v>6.4</v>
+      </c>
+      <c r="BF124">
+        <v>2.25</v>
+      </c>
+      <c r="BG124">
+        <v>1.22</v>
+      </c>
+      <c r="BH124">
+        <v>3.65</v>
+      </c>
+      <c r="BI124">
+        <v>1.43</v>
+      </c>
+      <c r="BJ124">
+        <v>2.62</v>
+      </c>
+      <c r="BK124">
+        <v>1.9</v>
+      </c>
+      <c r="BL124">
+        <v>1.9</v>
+      </c>
+      <c r="BM124">
+        <v>2.16</v>
+      </c>
+      <c r="BN124">
+        <v>1.65</v>
+      </c>
+      <c r="BO124">
+        <v>2.73</v>
+      </c>
+      <c r="BP124">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="232">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -515,6 +515,9 @@
   </si>
   <si>
     <t>['74']</t>
+  </si>
+  <si>
+    <t>['87']</t>
   </si>
   <si>
     <t>['5', '42', '80', '90+2']</t>
@@ -1068,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP124"/>
+  <dimension ref="A1:BP126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1736,7 +1739,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1942,7 +1945,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2226,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ6">
         <v>0.5</v>
@@ -2435,7 +2438,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ7">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2560,7 +2563,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -3053,7 +3056,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3256,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ11">
         <v>2.1</v>
@@ -3877,7 +3880,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ14">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
@@ -4414,7 +4417,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q17">
         <v>1.7</v>
@@ -4620,7 +4623,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4698,7 +4701,7 @@
         <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ18">
         <v>1.55</v>
@@ -4826,7 +4829,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q19">
         <v>2.57</v>
@@ -5032,7 +5035,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5113,7 +5116,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ20">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR20">
         <v>1.25</v>
@@ -5316,7 +5319,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ21">
         <v>1.78</v>
@@ -5444,7 +5447,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5650,7 +5653,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -6062,7 +6065,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6268,7 +6271,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q26">
         <v>3.9</v>
@@ -6680,7 +6683,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6886,7 +6889,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -6967,7 +6970,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ29">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR29">
         <v>1.86</v>
@@ -7092,7 +7095,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7298,7 +7301,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7376,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ31">
         <v>0.5</v>
@@ -7504,7 +7507,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q32">
         <v>3.6</v>
@@ -7582,7 +7585,7 @@
         <v>0.33</v>
       </c>
       <c r="AP32">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ32">
         <v>0.5</v>
@@ -7710,7 +7713,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7916,7 +7919,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8122,7 +8125,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8615,7 +8618,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ37">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR37">
         <v>1.31</v>
@@ -8740,7 +8743,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8946,7 +8949,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q39">
         <v>4.33</v>
@@ -9152,7 +9155,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9358,7 +9361,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q41">
         <v>4.36</v>
@@ -9848,10 +9851,10 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ43">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR43">
         <v>1.8</v>
@@ -10182,7 +10185,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10388,7 +10391,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10466,7 +10469,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ46">
         <v>2.36</v>
@@ -10594,7 +10597,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q47">
         <v>2.49</v>
@@ -10800,7 +10803,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q48">
         <v>2.48</v>
@@ -10881,7 +10884,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ48">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR48">
         <v>1.58</v>
@@ -11212,7 +11215,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11624,7 +11627,7 @@
         <v>82</v>
       </c>
       <c r="P52" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11830,7 +11833,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q53">
         <v>3.22</v>
@@ -12242,7 +12245,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12448,7 +12451,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12860,7 +12863,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -12938,7 +12941,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ58">
         <v>1.09</v>
@@ -13272,7 +13275,7 @@
         <v>85</v>
       </c>
       <c r="P60" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13478,7 +13481,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13556,7 +13559,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ61">
         <v>2.36</v>
@@ -13765,7 +13768,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ62">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR62">
         <v>2</v>
@@ -13890,7 +13893,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -13971,7 +13974,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ63">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR63">
         <v>1.28</v>
@@ -14096,7 +14099,7 @@
         <v>129</v>
       </c>
       <c r="P64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q64">
         <v>1.9</v>
@@ -14177,7 +14180,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ64">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR64">
         <v>1.94</v>
@@ -14302,7 +14305,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
@@ -14508,7 +14511,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14714,7 +14717,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14920,7 +14923,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -14998,7 +15001,7 @@
         <v>0.8</v>
       </c>
       <c r="AP68">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ68">
         <v>0.55</v>
@@ -15207,7 +15210,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ69">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR69">
         <v>1.54</v>
@@ -15332,7 +15335,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q70">
         <v>2</v>
@@ -15538,7 +15541,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -15822,7 +15825,7 @@
         <v>1.2</v>
       </c>
       <c r="AP72">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ72">
         <v>1</v>
@@ -15950,7 +15953,7 @@
         <v>137</v>
       </c>
       <c r="P73" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q73">
         <v>1.83</v>
@@ -16028,7 +16031,7 @@
         <v>0.83</v>
       </c>
       <c r="AP73">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ73">
         <v>1</v>
@@ -16156,7 +16159,7 @@
         <v>82</v>
       </c>
       <c r="P74" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16568,7 +16571,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16855,7 +16858,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ77">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR77">
         <v>1.54</v>
@@ -17392,7 +17395,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q80">
         <v>4.5</v>
@@ -17470,7 +17473,7 @@
         <v>1.83</v>
       </c>
       <c r="AP80">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ80">
         <v>1.78</v>
@@ -17804,7 +17807,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -18297,7 +18300,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ84">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR84">
         <v>1.59</v>
@@ -18628,7 +18631,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18709,7 +18712,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ86">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR86">
         <v>1.53</v>
@@ -18834,7 +18837,7 @@
         <v>143</v>
       </c>
       <c r="P87" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19246,7 +19249,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19452,7 +19455,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19736,7 +19739,7 @@
         <v>0.57</v>
       </c>
       <c r="AP91">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ91">
         <v>0.55</v>
@@ -19864,7 +19867,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -19942,7 +19945,7 @@
         <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ92">
         <v>0.5</v>
@@ -20070,7 +20073,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q93">
         <v>4</v>
@@ -20563,7 +20566,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ95">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR95">
         <v>1.73</v>
@@ -21100,7 +21103,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21306,7 +21309,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21387,7 +21390,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ99">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR99">
         <v>1.48</v>
@@ -21590,7 +21593,7 @@
         <v>1.13</v>
       </c>
       <c r="AP100">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ100">
         <v>1</v>
@@ -21718,7 +21721,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21924,7 +21927,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -22130,7 +22133,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -22620,7 +22623,7 @@
         <v>1.13</v>
       </c>
       <c r="AP105">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ105">
         <v>1.09</v>
@@ -23447,7 +23450,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ109">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR109">
         <v>1.38</v>
@@ -23572,7 +23575,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23778,7 +23781,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -23984,7 +23987,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24062,10 +24065,10 @@
         <v>1.22</v>
       </c>
       <c r="AP112">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ112">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR112">
         <v>1.46</v>
@@ -24190,7 +24193,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24602,7 +24605,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24889,7 +24892,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ116">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25220,7 +25223,7 @@
         <v>123</v>
       </c>
       <c r="P118" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q118">
         <v>1.74</v>
@@ -25710,7 +25713,7 @@
         <v>1.67</v>
       </c>
       <c r="AP120">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ120">
         <v>1.55</v>
@@ -26250,7 +26253,7 @@
         <v>166</v>
       </c>
       <c r="P123" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q123">
         <v>6.04</v>
@@ -26613,6 +26616,418 @@
       </c>
       <c r="BP124">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7580449</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45711.47916666666</v>
+      </c>
+      <c r="F125">
+        <v>21</v>
+      </c>
+      <c r="G125" t="s">
+        <v>74</v>
+      </c>
+      <c r="H125" t="s">
+        <v>71</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="M125">
+        <v>1</v>
+      </c>
+      <c r="N125">
+        <v>2</v>
+      </c>
+      <c r="O125" t="s">
+        <v>167</v>
+      </c>
+      <c r="P125" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q125">
+        <v>2.2</v>
+      </c>
+      <c r="R125">
+        <v>2.2</v>
+      </c>
+      <c r="S125">
+        <v>5</v>
+      </c>
+      <c r="T125">
+        <v>1.36</v>
+      </c>
+      <c r="U125">
+        <v>3</v>
+      </c>
+      <c r="V125">
+        <v>2.75</v>
+      </c>
+      <c r="W125">
+        <v>1.4</v>
+      </c>
+      <c r="X125">
+        <v>6.5</v>
+      </c>
+      <c r="Y125">
+        <v>1.1</v>
+      </c>
+      <c r="Z125">
+        <v>1.63</v>
+      </c>
+      <c r="AA125">
+        <v>3.92</v>
+      </c>
+      <c r="AB125">
+        <v>5</v>
+      </c>
+      <c r="AC125">
+        <v>1.02</v>
+      </c>
+      <c r="AD125">
+        <v>10</v>
+      </c>
+      <c r="AE125">
+        <v>1.26</v>
+      </c>
+      <c r="AF125">
+        <v>3.6</v>
+      </c>
+      <c r="AG125">
+        <v>1.82</v>
+      </c>
+      <c r="AH125">
+        <v>1.92</v>
+      </c>
+      <c r="AI125">
+        <v>1.83</v>
+      </c>
+      <c r="AJ125">
+        <v>1.83</v>
+      </c>
+      <c r="AK125">
+        <v>1.17</v>
+      </c>
+      <c r="AL125">
+        <v>1.23</v>
+      </c>
+      <c r="AM125">
+        <v>2.09</v>
+      </c>
+      <c r="AN125">
+        <v>1.9</v>
+      </c>
+      <c r="AO125">
+        <v>1.2</v>
+      </c>
+      <c r="AP125">
+        <v>1.82</v>
+      </c>
+      <c r="AQ125">
+        <v>1.18</v>
+      </c>
+      <c r="AR125">
+        <v>1.74</v>
+      </c>
+      <c r="AS125">
+        <v>1.46</v>
+      </c>
+      <c r="AT125">
+        <v>3.2</v>
+      </c>
+      <c r="AU125">
+        <v>4</v>
+      </c>
+      <c r="AV125">
+        <v>6</v>
+      </c>
+      <c r="AW125">
+        <v>8</v>
+      </c>
+      <c r="AX125">
+        <v>6</v>
+      </c>
+      <c r="AY125">
+        <v>12</v>
+      </c>
+      <c r="AZ125">
+        <v>12</v>
+      </c>
+      <c r="BA125">
+        <v>11</v>
+      </c>
+      <c r="BB125">
+        <v>3</v>
+      </c>
+      <c r="BC125">
+        <v>14</v>
+      </c>
+      <c r="BD125">
+        <v>1.44</v>
+      </c>
+      <c r="BE125">
+        <v>9</v>
+      </c>
+      <c r="BF125">
+        <v>3.34</v>
+      </c>
+      <c r="BG125">
+        <v>1.27</v>
+      </c>
+      <c r="BH125">
+        <v>3.27</v>
+      </c>
+      <c r="BI125">
+        <v>1.51</v>
+      </c>
+      <c r="BJ125">
+        <v>2.39</v>
+      </c>
+      <c r="BK125">
+        <v>2</v>
+      </c>
+      <c r="BL125">
+        <v>1.8</v>
+      </c>
+      <c r="BM125">
+        <v>2.36</v>
+      </c>
+      <c r="BN125">
+        <v>1.55</v>
+      </c>
+      <c r="BO125">
+        <v>3.1</v>
+      </c>
+      <c r="BP125">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7580454</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45711.47916666666</v>
+      </c>
+      <c r="F126">
+        <v>21</v>
+      </c>
+      <c r="G126" t="s">
+        <v>79</v>
+      </c>
+      <c r="H126" t="s">
+        <v>76</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>1</v>
+      </c>
+      <c r="O126" t="s">
+        <v>123</v>
+      </c>
+      <c r="P126" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q126">
+        <v>2.38</v>
+      </c>
+      <c r="R126">
+        <v>2.2</v>
+      </c>
+      <c r="S126">
+        <v>4.33</v>
+      </c>
+      <c r="T126">
+        <v>1.4</v>
+      </c>
+      <c r="U126">
+        <v>2.75</v>
+      </c>
+      <c r="V126">
+        <v>2.75</v>
+      </c>
+      <c r="W126">
+        <v>1.4</v>
+      </c>
+      <c r="X126">
+        <v>7</v>
+      </c>
+      <c r="Y126">
+        <v>1.08</v>
+      </c>
+      <c r="Z126">
+        <v>1.9</v>
+      </c>
+      <c r="AA126">
+        <v>3.53</v>
+      </c>
+      <c r="AB126">
+        <v>3.85</v>
+      </c>
+      <c r="AC126">
+        <v>1</v>
+      </c>
+      <c r="AD126">
+        <v>9</v>
+      </c>
+      <c r="AE126">
+        <v>1.27</v>
+      </c>
+      <c r="AF126">
+        <v>3.55</v>
+      </c>
+      <c r="AG126">
+        <v>1.87</v>
+      </c>
+      <c r="AH126">
+        <v>1.87</v>
+      </c>
+      <c r="AI126">
+        <v>1.8</v>
+      </c>
+      <c r="AJ126">
+        <v>1.91</v>
+      </c>
+      <c r="AK126">
+        <v>1.24</v>
+      </c>
+      <c r="AL126">
+        <v>1.26</v>
+      </c>
+      <c r="AM126">
+        <v>1.83</v>
+      </c>
+      <c r="AN126">
+        <v>1.4</v>
+      </c>
+      <c r="AO126">
+        <v>0.4</v>
+      </c>
+      <c r="AP126">
+        <v>1.55</v>
+      </c>
+      <c r="AQ126">
+        <v>0.36</v>
+      </c>
+      <c r="AR126">
+        <v>1.44</v>
+      </c>
+      <c r="AS126">
+        <v>1.14</v>
+      </c>
+      <c r="AT126">
+        <v>2.58</v>
+      </c>
+      <c r="AU126">
+        <v>4</v>
+      </c>
+      <c r="AV126">
+        <v>3</v>
+      </c>
+      <c r="AW126">
+        <v>8</v>
+      </c>
+      <c r="AX126">
+        <v>3</v>
+      </c>
+      <c r="AY126">
+        <v>12</v>
+      </c>
+      <c r="AZ126">
+        <v>6</v>
+      </c>
+      <c r="BA126">
+        <v>12</v>
+      </c>
+      <c r="BB126">
+        <v>7</v>
+      </c>
+      <c r="BC126">
+        <v>19</v>
+      </c>
+      <c r="BD126">
+        <v>1.47</v>
+      </c>
+      <c r="BE126">
+        <v>9</v>
+      </c>
+      <c r="BF126">
+        <v>3.18</v>
+      </c>
+      <c r="BG126">
+        <v>1.19</v>
+      </c>
+      <c r="BH126">
+        <v>3.78</v>
+      </c>
+      <c r="BI126">
+        <v>1.4</v>
+      </c>
+      <c r="BJ126">
+        <v>2.64</v>
+      </c>
+      <c r="BK126">
+        <v>1.71</v>
+      </c>
+      <c r="BL126">
+        <v>2.02</v>
+      </c>
+      <c r="BM126">
+        <v>2.14</v>
+      </c>
+      <c r="BN126">
+        <v>1.6</v>
+      </c>
+      <c r="BO126">
+        <v>2.81</v>
+      </c>
+      <c r="BP126">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AQ3">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1817,10 +1817,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AQ4">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AQ5">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2229,10 +2229,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="AQ7">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2635,25 +2635,25 @@
         <v>1.83</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP8">
-        <v>1.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ8">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AU8">
         <v>8</v>
@@ -2841,25 +2841,25 @@
         <v>1.99</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="AQ9">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AU9">
         <v>6</v>
@@ -3047,25 +3047,25 @@
         <v>3.05</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP10">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ10">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AU10">
         <v>4</v>
@@ -3253,25 +3253,25 @@
         <v>1.19</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP11">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AQ11">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AU11">
         <v>3</v>
@@ -3459,25 +3459,25 @@
         <v>2.83</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AU12">
         <v>9</v>
@@ -3665,25 +3665,25 @@
         <v>2.66</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO13">
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS13">
-        <v>0.79</v>
+        <v>1.2</v>
       </c>
       <c r="AT13">
-        <v>0.79</v>
+        <v>2.81</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3871,25 +3871,25 @@
         <v>1.63</v>
       </c>
       <c r="AN14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP14">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AQ14">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AR14">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AS14">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AT14">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AU14">
         <v>5</v>
@@ -4080,22 +4080,22 @@
         <v>1</v>
       </c>
       <c r="AO15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP15">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AR15">
         <v>1.66</v>
       </c>
       <c r="AS15">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AT15">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AU15">
         <v>3</v>
@@ -4286,22 +4286,22 @@
         <v>1</v>
       </c>
       <c r="AO16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP16">
-        <v>1.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ16">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR16">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AS16">
-        <v>1.31</v>
+        <v>1.95</v>
       </c>
       <c r="AT16">
-        <v>3.51</v>
+        <v>3.62</v>
       </c>
       <c r="AU16">
         <v>2</v>
@@ -4492,22 +4492,22 @@
         <v>3</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP17">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR17">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AS17">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="AT17">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="AU17">
         <v>8</v>
@@ -4695,25 +4695,25 @@
         <v>1.22</v>
       </c>
       <c r="AN18">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO18">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP18">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AQ18">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR18">
-        <v>1.61</v>
+        <v>1.12</v>
       </c>
       <c r="AS18">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AT18">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AU18">
         <v>0</v>
@@ -4901,25 +4901,25 @@
         <v>1.83</v>
       </c>
       <c r="AN19">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO19">
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AQ19">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR19">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AS19">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AT19">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="AU19">
         <v>13</v>
@@ -5107,25 +5107,25 @@
         <v>2.03</v>
       </c>
       <c r="AN20">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO20">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP20">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="AQ20">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR20">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AS20">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="AT20">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AU20">
         <v>5</v>
@@ -5316,22 +5316,22 @@
         <v>1</v>
       </c>
       <c r="AO21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP21">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AQ21">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AR21">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="AS21">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="AT21">
-        <v>3.51</v>
+        <v>3.45</v>
       </c>
       <c r="AU21">
         <v>3</v>
@@ -5519,25 +5519,25 @@
         <v>2.35</v>
       </c>
       <c r="AN22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR22">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AS22">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AT22">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AU22">
         <v>3</v>
@@ -5725,25 +5725,25 @@
         <v>1.25</v>
       </c>
       <c r="AN23">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO23">
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ23">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AR23">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AS23">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AT23">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="AU23">
         <v>2</v>
@@ -5931,25 +5931,25 @@
         <v>1.93</v>
       </c>
       <c r="AN24">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AO24">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="AP24">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AQ24">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AR24">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="AS24">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="AT24">
-        <v>3.37</v>
+        <v>3.03</v>
       </c>
       <c r="AU24">
         <v>7</v>
@@ -6143,19 +6143,19 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR25">
         <v>1.13</v>
       </c>
       <c r="AS25">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="AT25">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6343,25 +6343,25 @@
         <v>1.1</v>
       </c>
       <c r="AN26">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO26">
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ26">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AR26">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AS26">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AT26">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AU26">
         <v>4</v>
@@ -6552,22 +6552,22 @@
         <v>0.5</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AP27">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ27">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR27">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AS27">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AT27">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -6755,25 +6755,25 @@
         <v>1.51</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO28">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP28">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR28">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AS28">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AT28">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -6961,25 +6961,25 @@
         <v>1.76</v>
       </c>
       <c r="AN29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO29">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP29">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AQ29">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR29">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AS29">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AT29">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="AU29">
         <v>2</v>
@@ -7170,22 +7170,22 @@
         <v>3</v>
       </c>
       <c r="AO30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP30">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ30">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AR30">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AS30">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AT30">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="AU30">
         <v>3</v>
@@ -7373,25 +7373,25 @@
         <v>2.25</v>
       </c>
       <c r="AN31">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AP31">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AR31">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AT31">
-        <v>1.62</v>
+        <v>2.86</v>
       </c>
       <c r="AU31">
         <v>8</v>
@@ -7579,25 +7579,25 @@
         <v>1.3</v>
       </c>
       <c r="AN32">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AQ32">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AR32">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AS32">
-        <v>0.86</v>
+        <v>1.17</v>
       </c>
       <c r="AT32">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="AU32">
         <v>4</v>
@@ -7785,25 +7785,25 @@
         <v>3</v>
       </c>
       <c r="AN33">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AO33">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP33">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AQ33">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR33">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="AS33">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AT33">
-        <v>3.67</v>
+        <v>3.41</v>
       </c>
       <c r="AU33">
         <v>6</v>
@@ -7991,25 +7991,25 @@
         <v>2.25</v>
       </c>
       <c r="AN34">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO34">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP34">
-        <v>1.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR34">
         <v>1.38</v>
       </c>
       <c r="AS34">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AT34">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AU34">
         <v>7</v>
@@ -8197,25 +8197,25 @@
         <v>1.47</v>
       </c>
       <c r="AN35">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AO35">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AP35">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ35">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AR35">
-        <v>2.59</v>
+        <v>1.88</v>
       </c>
       <c r="AS35">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AT35">
-        <v>4.36</v>
+        <v>3.43</v>
       </c>
       <c r="AU35">
         <v>4</v>
@@ -8403,25 +8403,25 @@
         <v>1.3</v>
       </c>
       <c r="AN36">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AO36">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AP36">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AQ36">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AR36">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AS36">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AT36">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AU36">
         <v>6</v>
@@ -8609,25 +8609,25 @@
         <v>1.57</v>
       </c>
       <c r="AN37">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="AQ37">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AR37">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AS37">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AT37">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -8815,25 +8815,25 @@
         <v>1.41</v>
       </c>
       <c r="AN38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO38">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AP38">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="AQ38">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR38">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="AS38">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AT38">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AU38">
         <v>5</v>
@@ -9021,25 +9021,25 @@
         <v>1.21</v>
       </c>
       <c r="AN39">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO39">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AP39">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ39">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR39">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AS39">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AT39">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9227,25 +9227,25 @@
         <v>1.35</v>
       </c>
       <c r="AN40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO40">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AP40">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AQ40">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AR40">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AS40">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AT40">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AU40">
         <v>5</v>
@@ -9433,25 +9433,25 @@
         <v>1.25</v>
       </c>
       <c r="AN41">
-        <v>1.25</v>
+        <v>0.86</v>
       </c>
       <c r="AO41">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="AP41">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AQ41">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AR41">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AS41">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AT41">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="AU41">
         <v>4</v>
@@ -9639,25 +9639,25 @@
         <v>3.2</v>
       </c>
       <c r="AN42">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO42">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="AP42">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AR42">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AS42">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="AT42">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AU42">
         <v>9</v>
@@ -9845,25 +9845,25 @@
         <v>2.5</v>
       </c>
       <c r="AN43">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO43">
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AQ43">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR43">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AS43">
         <v>1.38</v>
       </c>
       <c r="AT43">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="AU43">
         <v>5</v>
@@ -10051,25 +10051,25 @@
         <v>2.15</v>
       </c>
       <c r="AN44">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO44">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR44">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AS44">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AT44">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="AU44">
         <v>7</v>
@@ -10257,25 +10257,25 @@
         <v>1.46</v>
       </c>
       <c r="AN45">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO45">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AQ45">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AR45">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AS45">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AT45">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AU45">
         <v>3</v>
@@ -10463,25 +10463,25 @@
         <v>1.08</v>
       </c>
       <c r="AN46">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="AO46">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="AP46">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AQ46">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AR46">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AS46">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AT46">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AU46">
         <v>10</v>
@@ -10669,25 +10669,25 @@
         <v>1.82</v>
       </c>
       <c r="AN47">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO47">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AP47">
-        <v>1.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ47">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR47">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AS47">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="AT47">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="AU47">
         <v>11</v>
@@ -10875,25 +10875,25 @@
         <v>1.7</v>
       </c>
       <c r="AN48">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="AO48">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AP48">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="AQ48">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AR48">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AS48">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AT48">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11081,25 +11081,25 @@
         <v>1.7</v>
       </c>
       <c r="AN49">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AO49">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AP49">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ49">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AR49">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="AS49">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AT49">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="AU49">
         <v>5</v>
@@ -11287,25 +11287,25 @@
         <v>1.84</v>
       </c>
       <c r="AN50">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AO50">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AP50">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="AQ50">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR50">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AS50">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AT50">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11493,25 +11493,25 @@
         <v>2.78</v>
       </c>
       <c r="AN51">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AO51">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AP51">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR51">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AS51">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AT51">
-        <v>3.39</v>
+        <v>3.09</v>
       </c>
       <c r="AU51">
         <v>5</v>
@@ -11699,25 +11699,25 @@
         <v>1.35</v>
       </c>
       <c r="AN52">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="AO52">
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AQ52">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AR52">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AS52">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AT52">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AU52">
         <v>2</v>
@@ -11908,22 +11908,22 @@
         <v>1</v>
       </c>
       <c r="AO53">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP53">
+        <v>1.24</v>
+      </c>
+      <c r="AQ53">
+        <v>0.95</v>
+      </c>
+      <c r="AR53">
+        <v>1.25</v>
+      </c>
+      <c r="AS53">
         <v>1.4</v>
       </c>
-      <c r="AQ53">
-        <v>0.5</v>
-      </c>
-      <c r="AR53">
-        <v>1.35</v>
-      </c>
-      <c r="AS53">
-        <v>1.45</v>
-      </c>
       <c r="AT53">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AU53">
         <v>7</v>
@@ -12111,25 +12111,25 @@
         <v>1.7</v>
       </c>
       <c r="AN54">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO54">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AP54">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR54">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS54">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AT54">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="AU54">
         <v>5</v>
@@ -12317,25 +12317,25 @@
         <v>2.78</v>
       </c>
       <c r="AN55">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AO55">
-        <v>0.4</v>
+        <v>0.78</v>
       </c>
       <c r="AP55">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AR55">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AS55">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AT55">
-        <v>2.64</v>
+        <v>2.96</v>
       </c>
       <c r="AU55">
         <v>11</v>
@@ -12523,25 +12523,25 @@
         <v>1.71</v>
       </c>
       <c r="AN56">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AO56">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP56">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ56">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AR56">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AS56">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AT56">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="AU56">
         <v>3</v>
@@ -12729,25 +12729,25 @@
         <v>1.92</v>
       </c>
       <c r="AN57">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AO57">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AP57">
-        <v>1.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR57">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AS57">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AT57">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AU57">
         <v>2</v>
@@ -12935,25 +12935,25 @@
         <v>1.53</v>
       </c>
       <c r="AN58">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AO58">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP58">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AQ58">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR58">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AS58">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AT58">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AU58">
         <v>5</v>
@@ -13141,25 +13141,25 @@
         <v>1.83</v>
       </c>
       <c r="AN59">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="AO59">
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="AQ59">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR59">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AS59">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AT59">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AU59">
         <v>7</v>
@@ -13347,25 +13347,25 @@
         <v>1.25</v>
       </c>
       <c r="AN60">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AO60">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AP60">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="AQ60">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR60">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AS60">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AT60">
-        <v>2.87</v>
+        <v>3.01</v>
       </c>
       <c r="AU60">
         <v>7</v>
@@ -13553,25 +13553,25 @@
         <v>1.42</v>
       </c>
       <c r="AN61">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO61">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="AP61">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AQ61">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AR61">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AS61">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AT61">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="AU61">
         <v>5</v>
@@ -13759,25 +13759,25 @@
         <v>3</v>
       </c>
       <c r="AN62">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="AO62">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP62">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AQ62">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR62">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AS62">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AT62">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="AU62">
         <v>5</v>
@@ -13965,25 +13965,25 @@
         <v>1.45</v>
       </c>
       <c r="AN63">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO63">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AP63">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AQ63">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AR63">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AS63">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AT63">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AU63">
         <v>6</v>
@@ -14171,25 +14171,25 @@
         <v>2.61</v>
       </c>
       <c r="AN64">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AO64">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AP64">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AQ64">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AR64">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AS64">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AT64">
-        <v>3.38</v>
+        <v>3.17</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14377,25 +14377,25 @@
         <v>1.6</v>
       </c>
       <c r="AN65">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AO65">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AP65">
-        <v>1.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ65">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AR65">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AS65">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AT65">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AU65">
         <v>5</v>
@@ -14583,25 +14583,25 @@
         <v>2.49</v>
       </c>
       <c r="AN66">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO66">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="AP66">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ66">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR66">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AS66">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AT66">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="AU66">
         <v>0</v>
@@ -14789,25 +14789,25 @@
         <v>1.23</v>
       </c>
       <c r="AN67">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AO67">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP67">
+        <v>0.9</v>
+      </c>
+      <c r="AQ67">
+        <v>1.95</v>
+      </c>
+      <c r="AR67">
         <v>1.27</v>
       </c>
-      <c r="AQ67">
-        <v>2.1</v>
-      </c>
-      <c r="AR67">
+      <c r="AS67">
         <v>1.44</v>
       </c>
-      <c r="AS67">
-        <v>1.29</v>
-      </c>
       <c r="AT67">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="AU67">
         <v>7</v>
@@ -14995,25 +14995,25 @@
         <v>1.6</v>
       </c>
       <c r="AN68">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AO68">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AP68">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AQ68">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR68">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AS68">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AT68">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="AU68">
         <v>6</v>
@@ -15201,25 +15201,25 @@
         <v>2.55</v>
       </c>
       <c r="AN69">
-        <v>0.8</v>
+        <v>1.36</v>
       </c>
       <c r="AO69">
-        <v>0.83</v>
+        <v>1.18</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ69">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AR69">
         <v>1.54</v>
       </c>
       <c r="AS69">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AT69">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="AU69">
         <v>7</v>
@@ -15407,25 +15407,25 @@
         <v>2.65</v>
       </c>
       <c r="AN70">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="AO70">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="AP70">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AQ70">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AR70">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AS70">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AT70">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="AU70">
         <v>4</v>
@@ -15613,25 +15613,25 @@
         <v>1.12</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AO71">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ71">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AR71">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AS71">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AT71">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="AU71">
         <v>7</v>
@@ -15819,25 +15819,25 @@
         <v>3.1</v>
       </c>
       <c r="AN72">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="AO72">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="AP72">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AQ72">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR72">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AS72">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AT72">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="AU72">
         <v>10</v>
@@ -16025,25 +16025,25 @@
         <v>2.85</v>
       </c>
       <c r="AN73">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO73">
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
       <c r="AP73">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR73">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AS73">
         <v>1.35</v>
       </c>
       <c r="AT73">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="AU73">
         <v>8</v>
@@ -16231,22 +16231,22 @@
         <v>1.12</v>
       </c>
       <c r="AN74">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AO74">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AP74">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AQ74">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR74">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AS74">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AT74">
         <v>2.95</v>
@@ -16437,25 +16437,25 @@
         <v>1.77</v>
       </c>
       <c r="AN75">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO75">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="AP75">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AQ75">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AR75">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AS75">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AT75">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="AU75">
         <v>4</v>
@@ -16643,25 +16643,25 @@
         <v>1.18</v>
       </c>
       <c r="AN76">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AO76">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AP76">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AQ76">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AR76">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AS76">
         <v>1.79</v>
       </c>
       <c r="AT76">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="AU76">
         <v>11</v>
@@ -16849,25 +16849,25 @@
         <v>1.66</v>
       </c>
       <c r="AN77">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AO77">
-        <v>0.6</v>
+        <v>1.08</v>
       </c>
       <c r="AP77">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ77">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR77">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS77">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AT77">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="AU77">
         <v>4</v>
@@ -17055,25 +17055,25 @@
         <v>1.28</v>
       </c>
       <c r="AN78">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AO78">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AP78">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="AQ78">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AR78">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AS78">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="AT78">
-        <v>2.84</v>
+        <v>3.03</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17261,25 +17261,25 @@
         <v>4.05</v>
       </c>
       <c r="AN79">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="AO79">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="AP79">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ79">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR79">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AS79">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AT79">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AU79">
         <v>5</v>
@@ -17467,25 +17467,25 @@
         <v>1.18</v>
       </c>
       <c r="AN80">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO80">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="AP80">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AQ80">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AR80">
         <v>1.35</v>
       </c>
       <c r="AS80">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AT80">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17673,25 +17673,25 @@
         <v>1.65</v>
       </c>
       <c r="AN81">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AO81">
-        <v>0.67</v>
+        <v>1.23</v>
       </c>
       <c r="AP81">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="AQ81">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AR81">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AS81">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AT81">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -17879,25 +17879,25 @@
         <v>1.13</v>
       </c>
       <c r="AN82">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO82">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AP82">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AQ82">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AR82">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AS82">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AT82">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AU82">
         <v>3</v>
@@ -18085,25 +18085,25 @@
         <v>1.83</v>
       </c>
       <c r="AN83">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO83">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AP83">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AQ83">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR83">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AS83">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AT83">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18291,25 +18291,25 @@
         <v>2.67</v>
       </c>
       <c r="AN84">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="AO84">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ84">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR84">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AS84">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AT84">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="AU84">
         <v>2</v>
@@ -18497,25 +18497,25 @@
         <v>1.15</v>
       </c>
       <c r="AN85">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AO85">
+        <v>2.62</v>
+      </c>
+      <c r="AP85">
+        <v>1.24</v>
+      </c>
+      <c r="AQ85">
+        <v>2.33</v>
+      </c>
+      <c r="AR85">
+        <v>1.25</v>
+      </c>
+      <c r="AS85">
+        <v>1.75</v>
+      </c>
+      <c r="AT85">
         <v>3</v>
-      </c>
-      <c r="AP85">
-        <v>1.4</v>
-      </c>
-      <c r="AQ85">
-        <v>2.36</v>
-      </c>
-      <c r="AR85">
-        <v>1.4</v>
-      </c>
-      <c r="AS85">
-        <v>1.77</v>
-      </c>
-      <c r="AT85">
-        <v>3.17</v>
       </c>
       <c r="AU85">
         <v>2</v>
@@ -18703,25 +18703,25 @@
         <v>1.45</v>
       </c>
       <c r="AN86">
-        <v>1.14</v>
+        <v>0.86</v>
       </c>
       <c r="AO86">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ86">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AR86">
+        <v>1.46</v>
+      </c>
+      <c r="AS86">
         <v>1.53</v>
       </c>
-      <c r="AS86">
-        <v>1.35</v>
-      </c>
       <c r="AT86">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AU86">
         <v>7</v>
@@ -18909,25 +18909,25 @@
         <v>1.8</v>
       </c>
       <c r="AN87">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AO87">
-        <v>0.57</v>
+        <v>0.93</v>
       </c>
       <c r="AP87">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AQ87">
+        <v>0.9</v>
+      </c>
+      <c r="AR87">
         <v>1.3</v>
       </c>
-      <c r="AQ87">
-        <v>0.5</v>
-      </c>
-      <c r="AR87">
-        <v>1.42</v>
-      </c>
       <c r="AS87">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AT87">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AU87">
         <v>6</v>
@@ -19115,22 +19115,22 @@
         <v>2.85</v>
       </c>
       <c r="AN88">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AO88">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR88">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AS88">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AT88">
         <v>2.89</v>
@@ -19321,25 +19321,25 @@
         <v>1.66</v>
       </c>
       <c r="AN89">
-        <v>2.71</v>
+        <v>2.21</v>
       </c>
       <c r="AO89">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AP89">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AQ89">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AR89">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AS89">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AT89">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="AU89">
         <v>4</v>
@@ -19527,25 +19527,25 @@
         <v>2.6</v>
       </c>
       <c r="AN90">
-        <v>1.71</v>
+        <v>1.21</v>
       </c>
       <c r="AO90">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP90">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR90">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AS90">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AT90">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AU90">
         <v>7</v>
@@ -19733,25 +19733,25 @@
         <v>2.65</v>
       </c>
       <c r="AN91">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AO91">
-        <v>0.57</v>
+        <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AQ91">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR91">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AS91">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AT91">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="AU91">
         <v>10</v>
@@ -19939,25 +19939,25 @@
         <v>1.5</v>
       </c>
       <c r="AN92">
+        <v>1.13</v>
+      </c>
+      <c r="AO92">
+        <v>1.13</v>
+      </c>
+      <c r="AP92">
         <v>1.29</v>
       </c>
-      <c r="AO92">
-        <v>0.71</v>
-      </c>
-      <c r="AP92">
-        <v>1.55</v>
-      </c>
       <c r="AQ92">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AR92">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AS92">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AT92">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AU92">
         <v>10</v>
@@ -20145,25 +20145,25 @@
         <v>1.28</v>
       </c>
       <c r="AN93">
-        <v>1.29</v>
+        <v>0.87</v>
       </c>
       <c r="AO93">
-        <v>1.71</v>
+        <v>2.27</v>
       </c>
       <c r="AP93">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="AQ93">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AR93">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AS93">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AT93">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AU93">
         <v>5</v>
@@ -20351,25 +20351,25 @@
         <v>1.44</v>
       </c>
       <c r="AN94">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AO94">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AP94">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AQ94">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR94">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AS94">
         <v>1.57</v>
       </c>
       <c r="AT94">
-        <v>3.29</v>
+        <v>3.08</v>
       </c>
       <c r="AU94">
         <v>7</v>
@@ -20557,25 +20557,25 @@
         <v>3.48</v>
       </c>
       <c r="AN95">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AO95">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="AP95">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ95">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR95">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AS95">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AT95">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="AU95">
         <v>11</v>
@@ -20763,25 +20763,25 @@
         <v>1.44</v>
       </c>
       <c r="AN96">
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="AO96">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AP96">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AQ96">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR96">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AS96">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AT96">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AU96">
         <v>6</v>
@@ -20969,25 +20969,25 @@
         <v>4.15</v>
       </c>
       <c r="AN97">
-        <v>2.29</v>
+        <v>2.53</v>
       </c>
       <c r="AO97">
-        <v>1.29</v>
+        <v>0.87</v>
       </c>
       <c r="AP97">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR97">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AS97">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AT97">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="AU97">
         <v>13</v>
@@ -21175,25 +21175,25 @@
         <v>1.37</v>
       </c>
       <c r="AN98">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="AO98">
         <v>1.88</v>
       </c>
       <c r="AP98">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="AQ98">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AR98">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS98">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AT98">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="AU98">
         <v>3</v>
@@ -21381,25 +21381,25 @@
         <v>1.53</v>
       </c>
       <c r="AN99">
-        <v>1.63</v>
+        <v>1.06</v>
       </c>
       <c r="AO99">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP99">
-        <v>1.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ99">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AR99">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AS99">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AT99">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AU99">
         <v>2</v>
@@ -21587,25 +21587,25 @@
         <v>1.9</v>
       </c>
       <c r="AN100">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO100">
-        <v>1.13</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP100">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR100">
         <v>1.45</v>
       </c>
       <c r="AS100">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AT100">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21793,25 +21793,25 @@
         <v>1.62</v>
       </c>
       <c r="AN101">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="AO101">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AP101">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AQ101">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AR101">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AS101">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AT101">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AU101">
         <v>8</v>
@@ -21999,25 +21999,25 @@
         <v>1.79</v>
       </c>
       <c r="AN102">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AO102">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AQ102">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR102">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AS102">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AT102">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="AU102">
         <v>7</v>
@@ -22205,25 +22205,25 @@
         <v>2.67</v>
       </c>
       <c r="AN103">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AO103">
-        <v>0.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP103">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ103">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AR103">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AS103">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AT103">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="AU103">
         <v>10</v>
@@ -22411,25 +22411,25 @@
         <v>1.65</v>
       </c>
       <c r="AN104">
-        <v>1.13</v>
+        <v>0.82</v>
       </c>
       <c r="AO104">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AP104">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="AQ104">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR104">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="AS104">
         <v>1.45</v>
       </c>
       <c r="AT104">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="AU104">
         <v>6</v>
@@ -22617,25 +22617,25 @@
         <v>2.41</v>
       </c>
       <c r="AN105">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AO105">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AP105">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AQ105">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR105">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AS105">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AT105">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="AU105">
         <v>8</v>
@@ -22823,25 +22823,25 @@
         <v>1.8</v>
       </c>
       <c r="AN106">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AO106">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AQ106">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AR106">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AS106">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AT106">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="AU106">
         <v>11</v>
@@ -23029,25 +23029,25 @@
         <v>2.34</v>
       </c>
       <c r="AN107">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AO107">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="AP107">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ107">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR107">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AS107">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="AT107">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23235,25 +23235,25 @@
         <v>1.21</v>
       </c>
       <c r="AN108">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AO108">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AP108">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ108">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AR108">
+        <v>1.49</v>
+      </c>
+      <c r="AS108">
         <v>1.59</v>
       </c>
-      <c r="AS108">
-        <v>1.35</v>
-      </c>
       <c r="AT108">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="AU108">
         <v>6</v>
@@ -23441,25 +23441,25 @@
         <v>1.44</v>
       </c>
       <c r="AN109">
-        <v>0.5</v>
+        <v>0.82</v>
       </c>
       <c r="AO109">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP109">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AQ109">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR109">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS109">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AT109">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="AU109">
         <v>9</v>
@@ -23647,25 +23647,25 @@
         <v>1.28</v>
       </c>
       <c r="AN110">
-        <v>1.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO110">
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>1.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ110">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AR110">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AS110">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AT110">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="AU110">
         <v>3</v>
@@ -23853,25 +23853,25 @@
         <v>2.5</v>
       </c>
       <c r="AN111">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO111">
-        <v>0.5600000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="AP111">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ111">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR111">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AS111">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AT111">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="AU111">
         <v>11</v>
@@ -24059,25 +24059,25 @@
         <v>1.53</v>
       </c>
       <c r="AN112">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AO112">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AQ112">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AR112">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AS112">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AT112">
-        <v>2.84</v>
+        <v>3.01</v>
       </c>
       <c r="AU112">
         <v>4</v>
@@ -24265,25 +24265,25 @@
         <v>2.5</v>
       </c>
       <c r="AN113">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="AO113">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP113">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AQ113">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR113">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AS113">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AT113">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="AU113">
         <v>8</v>
@@ -24471,25 +24471,25 @@
         <v>1.75</v>
       </c>
       <c r="AN114">
-        <v>1.11</v>
+        <v>0.83</v>
       </c>
       <c r="AO114">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP114">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="AQ114">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR114">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="AS114">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AT114">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="AU114">
         <v>8</v>
@@ -24677,25 +24677,25 @@
         <v>1.24</v>
       </c>
       <c r="AN115">
-        <v>1.33</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO115">
         <v>2.44</v>
       </c>
       <c r="AP115">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="AQ115">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AR115">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AS115">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AT115">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="AU115">
         <v>2</v>
@@ -24883,25 +24883,25 @@
         <v>2.01</v>
       </c>
       <c r="AN116">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AO116">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="AP116">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AQ116">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR116">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS116">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AT116">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AU116">
         <v>9</v>
@@ -25089,25 +25089,25 @@
         <v>1.85</v>
       </c>
       <c r="AN117">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AO117">
-        <v>0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="AP117">
+        <v>1.38</v>
+      </c>
+      <c r="AQ117">
+        <v>0.9</v>
+      </c>
+      <c r="AR117">
         <v>1.6</v>
       </c>
-      <c r="AQ117">
-        <v>0.5</v>
-      </c>
-      <c r="AR117">
-        <v>1.75</v>
-      </c>
       <c r="AS117">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AT117">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AU117">
         <v>9</v>
@@ -25295,25 +25295,25 @@
         <v>3.16</v>
       </c>
       <c r="AN118">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AO118">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AP118">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR118">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AS118">
         <v>1.44</v>
       </c>
       <c r="AT118">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25501,22 +25501,22 @@
         <v>1.53</v>
       </c>
       <c r="AN119">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AO119">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="AP119">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ119">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AR119">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AS119">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AT119">
         <v>2.79</v>
@@ -25707,25 +25707,25 @@
         <v>1.73</v>
       </c>
       <c r="AN120">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AO120">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AP120">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AQ120">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR120">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AS120">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AT120">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="AU120">
         <v>3</v>
@@ -25913,25 +25913,25 @@
         <v>1.56</v>
       </c>
       <c r="AN121">
-        <v>1.2</v>
+        <v>0.85</v>
       </c>
       <c r="AO121">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AP121">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="AQ121">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR121">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AS121">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AT121">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AU121">
         <v>8</v>
@@ -26119,25 +26119,25 @@
         <v>1.51</v>
       </c>
       <c r="AN122">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="AO122">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="AP122">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AQ122">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR122">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AS122">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AT122">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="AU122">
         <v>5</v>
@@ -26325,25 +26325,25 @@
         <v>1.13</v>
       </c>
       <c r="AN123">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="AO123">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AP123">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="AQ123">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AR123">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AS123">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AT123">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AU123">
         <v>4</v>
@@ -26531,25 +26531,25 @@
         <v>1.53</v>
       </c>
       <c r="AN124">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="AO124">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AP124">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AQ124">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AR124">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AS124">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AT124">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="AU124">
         <v>5</v>
@@ -26737,25 +26737,25 @@
         <v>2.09</v>
       </c>
       <c r="AN125">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AO125">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AP125">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AQ125">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AR125">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AS125">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="AT125">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="AU125">
         <v>4</v>
@@ -26943,25 +26943,25 @@
         <v>1.83</v>
       </c>
       <c r="AN126">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AO126">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="AP126">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AQ126">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR126">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AS126">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AT126">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="AU126">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="233">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -518,6 +518,9 @@
   </si>
   <si>
     <t>['87']</t>
+  </si>
+  <si>
+    <t>['17']</t>
   </si>
   <si>
     <t>['5', '42', '80', '90+2']</t>
@@ -1071,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1405,10 +1408,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ2">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1611,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AQ3">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1739,7 +1742,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1817,10 +1820,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1945,7 +1948,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2023,10 +2026,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AQ5">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2229,10 +2232,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ6">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2435,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="AQ7">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2563,7 +2566,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -2635,25 +2638,25 @@
         <v>1.83</v>
       </c>
       <c r="AN8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AQ8">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR8">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AU8">
         <v>8</v>
@@ -2841,25 +2844,25 @@
         <v>1.99</v>
       </c>
       <c r="AN9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="AQ9">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AR9">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AU9">
         <v>6</v>
@@ -3047,25 +3050,25 @@
         <v>3.05</v>
       </c>
       <c r="AN10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ10">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AR10">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>4</v>
@@ -3253,25 +3256,25 @@
         <v>1.19</v>
       </c>
       <c r="AN11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AQ11">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AR11">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>3</v>
@@ -3459,25 +3462,25 @@
         <v>2.83</v>
       </c>
       <c r="AN12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AR12">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>9</v>
@@ -3665,25 +3668,25 @@
         <v>2.66</v>
       </c>
       <c r="AN13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ13">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR13">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.2</v>
+        <v>0.79</v>
       </c>
       <c r="AT13">
-        <v>2.81</v>
+        <v>0.79</v>
       </c>
       <c r="AU13">
         <v>10</v>
@@ -3871,25 +3874,25 @@
         <v>1.63</v>
       </c>
       <c r="AN14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AQ14">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AR14">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AS14">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AT14">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AU14">
         <v>5</v>
@@ -4080,22 +4083,22 @@
         <v>1</v>
       </c>
       <c r="AO15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP15">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="AQ15">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>1.66</v>
       </c>
       <c r="AS15">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AT15">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AU15">
         <v>3</v>
@@ -4286,22 +4289,22 @@
         <v>1</v>
       </c>
       <c r="AO16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP16">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR16">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AS16">
-        <v>1.95</v>
+        <v>1.31</v>
       </c>
       <c r="AT16">
-        <v>3.62</v>
+        <v>3.51</v>
       </c>
       <c r="AU16">
         <v>2</v>
@@ -4417,7 +4420,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q17">
         <v>1.7</v>
@@ -4492,22 +4495,22 @@
         <v>3</v>
       </c>
       <c r="AO17">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ17">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AR17">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AS17">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AT17">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="AU17">
         <v>8</v>
@@ -4623,7 +4626,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4695,25 +4698,25 @@
         <v>1.22</v>
       </c>
       <c r="AN18">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AQ18">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR18">
-        <v>1.12</v>
+        <v>1.61</v>
       </c>
       <c r="AS18">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AT18">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AU18">
         <v>0</v>
@@ -4829,7 +4832,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q19">
         <v>2.57</v>
@@ -4901,25 +4904,25 @@
         <v>1.83</v>
       </c>
       <c r="AN19">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AO19">
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AQ19">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR19">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AS19">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AT19">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="AU19">
         <v>13</v>
@@ -5035,7 +5038,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5107,25 +5110,25 @@
         <v>2.03</v>
       </c>
       <c r="AN20">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO20">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP20">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="AQ20">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="AR20">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AS20">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="AT20">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AU20">
         <v>5</v>
@@ -5316,22 +5319,22 @@
         <v>1</v>
       </c>
       <c r="AO21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ21">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AR21">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="AS21">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="AT21">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="AU21">
         <v>3</v>
@@ -5447,7 +5450,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5519,25 +5522,25 @@
         <v>2.35</v>
       </c>
       <c r="AN22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AR22">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AS22">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AT22">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AU22">
         <v>3</v>
@@ -5653,7 +5656,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -5725,25 +5728,25 @@
         <v>1.25</v>
       </c>
       <c r="AN23">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO23">
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ23">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AR23">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AS23">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AT23">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="AU23">
         <v>2</v>
@@ -5931,25 +5934,25 @@
         <v>1.93</v>
       </c>
       <c r="AN24">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AP24">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ24">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AR24">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="AS24">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="AT24">
-        <v>3.03</v>
+        <v>3.37</v>
       </c>
       <c r="AU24">
         <v>7</v>
@@ -6065,7 +6068,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6143,19 +6146,19 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="AQ25">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>1.13</v>
       </c>
       <c r="AS25">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="AT25">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6271,7 +6274,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q26">
         <v>3.9</v>
@@ -6343,25 +6346,25 @@
         <v>1.1</v>
       </c>
       <c r="AN26">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO26">
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AQ26">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AR26">
+        <v>1.52</v>
+      </c>
+      <c r="AS26">
         <v>1.46</v>
       </c>
-      <c r="AS26">
-        <v>1.44</v>
-      </c>
       <c r="AT26">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AU26">
         <v>4</v>
@@ -6552,22 +6555,22 @@
         <v>0.5</v>
       </c>
       <c r="AO27">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AR27">
+        <v>1.22</v>
+      </c>
+      <c r="AS27">
         <v>1.28</v>
       </c>
-      <c r="AS27">
-        <v>1.31</v>
-      </c>
       <c r="AT27">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -6683,7 +6686,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6755,25 +6758,25 @@
         <v>1.51</v>
       </c>
       <c r="AN28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO28">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP28">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR28">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AS28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AT28">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -6889,7 +6892,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -6961,25 +6964,25 @@
         <v>1.76</v>
       </c>
       <c r="AN29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO29">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AQ29">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="AR29">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AS29">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AT29">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="AU29">
         <v>2</v>
@@ -7095,7 +7098,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7170,22 +7173,22 @@
         <v>3</v>
       </c>
       <c r="AO30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP30">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ30">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AR30">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AS30">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AT30">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="AU30">
         <v>3</v>
@@ -7301,7 +7304,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7373,25 +7376,25 @@
         <v>2.25</v>
       </c>
       <c r="AN31">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO31">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ31">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AR31">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AS31">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>2.86</v>
+        <v>1.62</v>
       </c>
       <c r="AU31">
         <v>8</v>
@@ -7507,7 +7510,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q32">
         <v>3.6</v>
@@ -7579,25 +7582,25 @@
         <v>1.3</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO32">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AP32">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AQ32">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AR32">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AS32">
-        <v>1.17</v>
+        <v>0.86</v>
       </c>
       <c r="AT32">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="AU32">
         <v>4</v>
@@ -7713,7 +7716,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7785,25 +7788,25 @@
         <v>3</v>
       </c>
       <c r="AN33">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AO33">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP33">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ33">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR33">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="AS33">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AT33">
-        <v>3.41</v>
+        <v>3.67</v>
       </c>
       <c r="AU33">
         <v>6</v>
@@ -7919,7 +7922,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -7991,25 +7994,25 @@
         <v>2.25</v>
       </c>
       <c r="AN34">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO34">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AQ34">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.38</v>
       </c>
       <c r="AS34">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AT34">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="AU34">
         <v>7</v>
@@ -8125,7 +8128,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8197,25 +8200,25 @@
         <v>1.47</v>
       </c>
       <c r="AN35">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO35">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ35">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AR35">
-        <v>1.88</v>
+        <v>2.59</v>
       </c>
       <c r="AS35">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AT35">
-        <v>3.43</v>
+        <v>4.36</v>
       </c>
       <c r="AU35">
         <v>4</v>
@@ -8403,25 +8406,25 @@
         <v>1.3</v>
       </c>
       <c r="AN36">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AO36">
+        <v>2</v>
+      </c>
+      <c r="AP36">
         <v>1.4</v>
       </c>
-      <c r="AP36">
-        <v>1.24</v>
-      </c>
       <c r="AQ36">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AR36">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AS36">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AT36">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AU36">
         <v>6</v>
@@ -8609,25 +8612,25 @@
         <v>1.57</v>
       </c>
       <c r="AN37">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP37">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="AQ37">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AR37">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AS37">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AT37">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -8743,7 +8746,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8815,25 +8818,25 @@
         <v>1.41</v>
       </c>
       <c r="AN38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO38">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="AQ38">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR38">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AS38">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AT38">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AU38">
         <v>5</v>
@@ -8949,7 +8952,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q39">
         <v>4.33</v>
@@ -9021,25 +9024,25 @@
         <v>1.21</v>
       </c>
       <c r="AN39">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO39">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AP39">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ39">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR39">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AS39">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AT39">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9155,7 +9158,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9227,25 +9230,25 @@
         <v>1.35</v>
       </c>
       <c r="AN40">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO40">
-        <v>0.86</v>
+        <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AQ40">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AR40">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AS40">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AT40">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AU40">
         <v>5</v>
@@ -9361,7 +9364,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q41">
         <v>4.36</v>
@@ -9433,25 +9436,25 @@
         <v>1.25</v>
       </c>
       <c r="AN41">
-        <v>0.86</v>
+        <v>1.25</v>
       </c>
       <c r="AO41">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP41">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AQ41">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AR41">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AS41">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AT41">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="AU41">
         <v>4</v>
@@ -9639,25 +9642,25 @@
         <v>3.2</v>
       </c>
       <c r="AN42">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO42">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ42">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AS42">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="AT42">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AU42">
         <v>9</v>
@@ -9845,25 +9848,25 @@
         <v>2.5</v>
       </c>
       <c r="AN43">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO43">
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ43">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="AR43">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AS43">
         <v>1.38</v>
       </c>
       <c r="AT43">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="AU43">
         <v>5</v>
@@ -10051,25 +10054,25 @@
         <v>2.15</v>
       </c>
       <c r="AN44">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO44">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AP44">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AQ44">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR44">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AS44">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AT44">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="AU44">
         <v>7</v>
@@ -10185,7 +10188,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10257,25 +10260,25 @@
         <v>1.46</v>
       </c>
       <c r="AN45">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO45">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AP45">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AQ45">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AR45">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AS45">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AT45">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AU45">
         <v>3</v>
@@ -10391,7 +10394,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10463,25 +10466,25 @@
         <v>1.08</v>
       </c>
       <c r="AN46">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="AO46">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AQ46">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AR46">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AS46">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AT46">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AU46">
         <v>10</v>
@@ -10597,7 +10600,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>2.49</v>
@@ -10669,25 +10672,25 @@
         <v>1.82</v>
       </c>
       <c r="AN47">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO47">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AQ47">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AR47">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AS47">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AT47">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="AU47">
         <v>11</v>
@@ -10803,7 +10806,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q48">
         <v>2.48</v>
@@ -10875,25 +10878,25 @@
         <v>1.7</v>
       </c>
       <c r="AN48">
-        <v>0.75</v>
+        <v>1.33</v>
       </c>
       <c r="AO48">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AP48">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="AQ48">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AR48">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="AS48">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AT48">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11081,25 +11084,25 @@
         <v>1.7</v>
       </c>
       <c r="AN49">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AO49">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ49">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AR49">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="AS49">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AT49">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="AU49">
         <v>5</v>
@@ -11215,7 +11218,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11287,25 +11290,25 @@
         <v>1.84</v>
       </c>
       <c r="AN50">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AO50">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="AQ50">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR50">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AS50">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AT50">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11493,25 +11496,25 @@
         <v>2.78</v>
       </c>
       <c r="AN51">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="AO51">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AP51">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ51">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AR51">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AS51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AT51">
-        <v>3.09</v>
+        <v>3.39</v>
       </c>
       <c r="AU51">
         <v>5</v>
@@ -11627,7 +11630,7 @@
         <v>82</v>
       </c>
       <c r="P52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11699,25 +11702,25 @@
         <v>1.35</v>
       </c>
       <c r="AN52">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="AO52">
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AQ52">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AR52">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AS52">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AT52">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="AU52">
         <v>2</v>
@@ -11833,7 +11836,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q53">
         <v>3.22</v>
@@ -11908,22 +11911,22 @@
         <v>1</v>
       </c>
       <c r="AO53">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP53">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AQ53">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AR53">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AS53">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AT53">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AU53">
         <v>7</v>
@@ -12111,25 +12114,25 @@
         <v>1.7</v>
       </c>
       <c r="AN54">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AO54">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ54">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AR54">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AS54">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AT54">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="AU54">
         <v>5</v>
@@ -12245,7 +12248,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12317,25 +12320,25 @@
         <v>2.78</v>
       </c>
       <c r="AN55">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AO55">
-        <v>0.78</v>
+        <v>0.4</v>
       </c>
       <c r="AP55">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ55">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AS55">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT55">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="AU55">
         <v>11</v>
@@ -12451,7 +12454,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12523,25 +12526,25 @@
         <v>1.71</v>
       </c>
       <c r="AN56">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AO56">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ56">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AR56">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AS56">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="AT56">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="AU56">
         <v>3</v>
@@ -12729,25 +12732,25 @@
         <v>1.92</v>
       </c>
       <c r="AN57">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AO57">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AP57">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AQ57">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR57">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AS57">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT57">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AU57">
         <v>2</v>
@@ -12863,7 +12866,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -12935,25 +12938,25 @@
         <v>1.53</v>
       </c>
       <c r="AN58">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AO58">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP58">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AQ58">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AR58">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AS58">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AT58">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AU58">
         <v>5</v>
@@ -13141,25 +13144,25 @@
         <v>1.83</v>
       </c>
       <c r="AN59">
-        <v>0.8</v>
+        <v>1.25</v>
       </c>
       <c r="AO59">
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="AQ59">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR59">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AS59">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT59">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AU59">
         <v>7</v>
@@ -13275,7 +13278,7 @@
         <v>85</v>
       </c>
       <c r="P60" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13347,25 +13350,25 @@
         <v>1.25</v>
       </c>
       <c r="AN60">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AO60">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AP60">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="AQ60">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR60">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AS60">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AT60">
-        <v>3.01</v>
+        <v>2.87</v>
       </c>
       <c r="AU60">
         <v>7</v>
@@ -13481,7 +13484,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13553,25 +13556,25 @@
         <v>1.42</v>
       </c>
       <c r="AN61">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO61">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ61">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AR61">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AS61">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AT61">
-        <v>3.33</v>
+        <v>3.65</v>
       </c>
       <c r="AU61">
         <v>5</v>
@@ -13759,25 +13762,25 @@
         <v>3</v>
       </c>
       <c r="AN62">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="AO62">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP62">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ62">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="AR62">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AS62">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AT62">
-        <v>3.06</v>
+        <v>3.27</v>
       </c>
       <c r="AU62">
         <v>5</v>
@@ -13893,7 +13896,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -13965,25 +13968,25 @@
         <v>1.45</v>
       </c>
       <c r="AN63">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO63">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AP63">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AQ63">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AR63">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AS63">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AT63">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AU63">
         <v>6</v>
@@ -14099,7 +14102,7 @@
         <v>129</v>
       </c>
       <c r="P64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q64">
         <v>1.9</v>
@@ -14171,25 +14174,25 @@
         <v>2.61</v>
       </c>
       <c r="AN64">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AO64">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AP64">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ64">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AR64">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AS64">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AT64">
-        <v>3.17</v>
+        <v>3.38</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14305,7 +14308,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
@@ -14377,25 +14380,25 @@
         <v>1.6</v>
       </c>
       <c r="AN65">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AO65">
+        <v>1</v>
+      </c>
+      <c r="AP65">
         <v>1.3</v>
       </c>
-      <c r="AP65">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="AQ65">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AR65">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AS65">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AT65">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AU65">
         <v>5</v>
@@ -14511,7 +14514,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14583,25 +14586,25 @@
         <v>2.49</v>
       </c>
       <c r="AN66">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO66">
+        <v>0.8</v>
+      </c>
+      <c r="AP66">
+        <v>1.2</v>
+      </c>
+      <c r="AQ66">
         <v>1.09</v>
       </c>
-      <c r="AP66">
-        <v>1.38</v>
-      </c>
-      <c r="AQ66">
-        <v>1.24</v>
-      </c>
       <c r="AR66">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AS66">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AT66">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="AU66">
         <v>0</v>
@@ -14717,7 +14720,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14789,25 +14792,25 @@
         <v>1.23</v>
       </c>
       <c r="AN67">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AO67">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP67">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="AQ67">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AR67">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AS67">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AT67">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AU67">
         <v>7</v>
@@ -14923,7 +14926,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -14995,25 +14998,25 @@
         <v>1.6</v>
       </c>
       <c r="AN68">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AO68">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AP68">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AQ68">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR68">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AS68">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AT68">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="AU68">
         <v>6</v>
@@ -15201,25 +15204,25 @@
         <v>2.55</v>
       </c>
       <c r="AN69">
-        <v>1.36</v>
+        <v>0.8</v>
       </c>
       <c r="AO69">
+        <v>0.83</v>
+      </c>
+      <c r="AP69">
+        <v>1.2</v>
+      </c>
+      <c r="AQ69">
         <v>1.18</v>
-      </c>
-      <c r="AP69">
-        <v>1.38</v>
-      </c>
-      <c r="AQ69">
-        <v>1.38</v>
       </c>
       <c r="AR69">
         <v>1.54</v>
       </c>
       <c r="AS69">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AT69">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="AU69">
         <v>7</v>
@@ -15335,7 +15338,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q70">
         <v>2</v>
@@ -15407,25 +15410,25 @@
         <v>2.65</v>
       </c>
       <c r="AN70">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="AO70">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="AP70">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ70">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AR70">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AS70">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AT70">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="AU70">
         <v>4</v>
@@ -15541,7 +15544,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -15613,25 +15616,25 @@
         <v>1.12</v>
       </c>
       <c r="AN71">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AO71">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP71">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ71">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AR71">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AS71">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AT71">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="AU71">
         <v>7</v>
@@ -15819,25 +15822,25 @@
         <v>3.1</v>
       </c>
       <c r="AN72">
-        <v>1.64</v>
+        <v>1.2</v>
       </c>
       <c r="AO72">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="AP72">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ72">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AR72">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AS72">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AT72">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AU72">
         <v>10</v>
@@ -15953,7 +15956,7 @@
         <v>137</v>
       </c>
       <c r="P73" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q73">
         <v>1.83</v>
@@ -16025,25 +16028,25 @@
         <v>2.85</v>
       </c>
       <c r="AN73">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO73">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AP73">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ73">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR73">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AS73">
         <v>1.35</v>
       </c>
       <c r="AT73">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="AU73">
         <v>8</v>
@@ -16159,7 +16162,7 @@
         <v>82</v>
       </c>
       <c r="P74" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16231,22 +16234,22 @@
         <v>1.12</v>
       </c>
       <c r="AN74">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="AO74">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AP74">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AQ74">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR74">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AS74">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AT74">
         <v>2.95</v>
@@ -16437,25 +16440,25 @@
         <v>1.77</v>
       </c>
       <c r="AN75">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO75">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="AP75">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AQ75">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AR75">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AS75">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AT75">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="AU75">
         <v>4</v>
@@ -16571,7 +16574,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16643,25 +16646,25 @@
         <v>1.18</v>
       </c>
       <c r="AN76">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="AO76">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="AP76">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AQ76">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AR76">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AS76">
         <v>1.79</v>
       </c>
       <c r="AT76">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="AU76">
         <v>11</v>
@@ -16849,25 +16852,25 @@
         <v>1.66</v>
       </c>
       <c r="AN77">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AO77">
-        <v>1.08</v>
+        <v>0.6</v>
       </c>
       <c r="AP77">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ77">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="AR77">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AS77">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AT77">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AU77">
         <v>4</v>
@@ -17055,25 +17058,25 @@
         <v>1.28</v>
       </c>
       <c r="AN78">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AO78">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AP78">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="AQ78">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AR78">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AS78">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="AT78">
-        <v>3.03</v>
+        <v>2.84</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17261,25 +17264,25 @@
         <v>4.05</v>
       </c>
       <c r="AN79">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="AO79">
-        <v>0.92</v>
+        <v>0.67</v>
       </c>
       <c r="AP79">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ79">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR79">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AS79">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AT79">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AU79">
         <v>5</v>
@@ -17395,7 +17398,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q80">
         <v>4.5</v>
@@ -17467,25 +17470,25 @@
         <v>1.18</v>
       </c>
       <c r="AN80">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO80">
-        <v>2.31</v>
+        <v>1.83</v>
       </c>
       <c r="AP80">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AQ80">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AR80">
         <v>1.35</v>
       </c>
       <c r="AS80">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AT80">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17673,25 +17676,25 @@
         <v>1.65</v>
       </c>
       <c r="AN81">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AO81">
-        <v>1.23</v>
+        <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="AQ81">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AR81">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AS81">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AT81">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -17807,7 +17810,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -17879,25 +17882,25 @@
         <v>1.13</v>
       </c>
       <c r="AN82">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AO82">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AQ82">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AR82">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AS82">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AT82">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AU82">
         <v>3</v>
@@ -18085,25 +18088,25 @@
         <v>1.83</v>
       </c>
       <c r="AN83">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO83">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AP83">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AQ83">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AR83">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AS83">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AT83">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18291,25 +18294,25 @@
         <v>2.67</v>
       </c>
       <c r="AN84">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AO84">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP84">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ84">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="AR84">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AS84">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AT84">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="AU84">
         <v>2</v>
@@ -18497,25 +18500,25 @@
         <v>1.15</v>
       </c>
       <c r="AN85">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AO85">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AP85">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AQ85">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AR85">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS85">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AT85">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="AU85">
         <v>2</v>
@@ -18631,7 +18634,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18703,25 +18706,25 @@
         <v>1.45</v>
       </c>
       <c r="AN86">
-        <v>0.86</v>
+        <v>1.14</v>
       </c>
       <c r="AO86">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AP86">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ86">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AR86">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AS86">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AT86">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AU86">
         <v>7</v>
@@ -18837,7 +18840,7 @@
         <v>143</v>
       </c>
       <c r="P87" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -18909,25 +18912,25 @@
         <v>1.8</v>
       </c>
       <c r="AN87">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AO87">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="AP87">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AQ87">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AR87">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AS87">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AT87">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AU87">
         <v>6</v>
@@ -19115,22 +19118,22 @@
         <v>2.85</v>
       </c>
       <c r="AN88">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AO88">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ88">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR88">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AS88">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AT88">
         <v>2.89</v>
@@ -19249,7 +19252,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19321,25 +19324,25 @@
         <v>1.66</v>
       </c>
       <c r="AN89">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AO89">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="AP89">
+        <v>2.36</v>
+      </c>
+      <c r="AQ89">
         <v>2.1</v>
       </c>
-      <c r="AQ89">
-        <v>1.95</v>
-      </c>
       <c r="AR89">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AS89">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AT89">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="AU89">
         <v>4</v>
@@ -19455,7 +19458,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19527,25 +19530,25 @@
         <v>2.6</v>
       </c>
       <c r="AN90">
-        <v>1.21</v>
+        <v>1.71</v>
       </c>
       <c r="AO90">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="AP90">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="AQ90">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AR90">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AS90">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AT90">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="AU90">
         <v>7</v>
@@ -19733,25 +19736,25 @@
         <v>2.65</v>
       </c>
       <c r="AN91">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AO91">
-        <v>0.8</v>
+        <v>0.57</v>
       </c>
       <c r="AP91">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ91">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR91">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AS91">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AT91">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="AU91">
         <v>10</v>
@@ -19867,7 +19870,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -19939,25 +19942,25 @@
         <v>1.5</v>
       </c>
       <c r="AN92">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AO92">
-        <v>1.13</v>
+        <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AQ92">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AR92">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AS92">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AT92">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="AU92">
         <v>10</v>
@@ -20073,7 +20076,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q93">
         <v>4</v>
@@ -20145,25 +20148,25 @@
         <v>1.28</v>
       </c>
       <c r="AN93">
-        <v>0.87</v>
+        <v>1.29</v>
       </c>
       <c r="AO93">
-        <v>2.27</v>
+        <v>1.71</v>
       </c>
       <c r="AP93">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="AQ93">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AR93">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AS93">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="AT93">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AU93">
         <v>5</v>
@@ -20351,25 +20354,25 @@
         <v>1.44</v>
       </c>
       <c r="AN94">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AO94">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AQ94">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR94">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AS94">
         <v>1.57</v>
       </c>
       <c r="AT94">
-        <v>3.08</v>
+        <v>3.29</v>
       </c>
       <c r="AU94">
         <v>7</v>
@@ -20557,25 +20560,25 @@
         <v>3.48</v>
       </c>
       <c r="AN95">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AO95">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="AP95">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ95">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="AR95">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AS95">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AT95">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="AU95">
         <v>11</v>
@@ -20763,25 +20766,25 @@
         <v>1.44</v>
       </c>
       <c r="AN96">
-        <v>0.86</v>
+        <v>0.43</v>
       </c>
       <c r="AO96">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AP96">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AR96">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AS96">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AT96">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="AU96">
         <v>6</v>
@@ -20969,25 +20972,25 @@
         <v>4.15</v>
       </c>
       <c r="AN97">
-        <v>2.53</v>
+        <v>2.29</v>
       </c>
       <c r="AO97">
-        <v>0.87</v>
+        <v>1.29</v>
       </c>
       <c r="AP97">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ97">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AR97">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AS97">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AT97">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="AU97">
         <v>13</v>
@@ -21103,7 +21106,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21175,25 +21178,25 @@
         <v>1.37</v>
       </c>
       <c r="AN98">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="AO98">
         <v>1.88</v>
       </c>
       <c r="AP98">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="AQ98">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AR98">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AS98">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AT98">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="AU98">
         <v>3</v>
@@ -21309,7 +21312,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21381,25 +21384,25 @@
         <v>1.53</v>
       </c>
       <c r="AN99">
-        <v>1.06</v>
+        <v>1.63</v>
       </c>
       <c r="AO99">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP99">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AQ99">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AR99">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AS99">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AT99">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="AU99">
         <v>2</v>
@@ -21587,25 +21590,25 @@
         <v>1.9</v>
       </c>
       <c r="AN100">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO100">
-        <v>0.8100000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="AP100">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AQ100">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AR100">
         <v>1.45</v>
       </c>
       <c r="AS100">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AT100">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21721,7 +21724,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21793,25 +21796,25 @@
         <v>1.62</v>
       </c>
       <c r="AN101">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="AO101">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AP101">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ101">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AR101">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AS101">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AT101">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="AU101">
         <v>8</v>
@@ -21927,7 +21930,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -21999,25 +22002,25 @@
         <v>1.79</v>
       </c>
       <c r="AN102">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AO102">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP102">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AQ102">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR102">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AS102">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AT102">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="AU102">
         <v>7</v>
@@ -22133,7 +22136,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -22205,25 +22208,25 @@
         <v>2.67</v>
       </c>
       <c r="AN103">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AO103">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP103">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ103">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AR103">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AS103">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AT103">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="AU103">
         <v>10</v>
@@ -22411,25 +22414,25 @@
         <v>1.65</v>
       </c>
       <c r="AN104">
-        <v>0.82</v>
+        <v>1.13</v>
       </c>
       <c r="AO104">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AP104">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="AQ104">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR104">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="AS104">
         <v>1.45</v>
       </c>
       <c r="AT104">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="AU104">
         <v>6</v>
@@ -22617,25 +22620,25 @@
         <v>2.41</v>
       </c>
       <c r="AN105">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AO105">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AP105">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ105">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AR105">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AS105">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AT105">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="AU105">
         <v>8</v>
@@ -22823,25 +22826,25 @@
         <v>1.8</v>
       </c>
       <c r="AN106">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AO106">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="AP106">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AQ106">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AR106">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="AS106">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AT106">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="AU106">
         <v>11</v>
@@ -23029,25 +23032,25 @@
         <v>2.34</v>
       </c>
       <c r="AN107">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AO107">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="AP107">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ107">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR107">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AS107">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AT107">
-        <v>3.37</v>
+        <v>3.43</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23235,25 +23238,25 @@
         <v>1.21</v>
       </c>
       <c r="AN108">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AO108">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AP108">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ108">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AR108">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AS108">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="AT108">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="AU108">
         <v>6</v>
@@ -23441,25 +23444,25 @@
         <v>1.44</v>
       </c>
       <c r="AN109">
-        <v>0.82</v>
+        <v>0.5</v>
       </c>
       <c r="AO109">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP109">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AQ109">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="AR109">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS109">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT109">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="AU109">
         <v>9</v>
@@ -23575,7 +23578,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23647,25 +23650,25 @@
         <v>1.28</v>
       </c>
       <c r="AN110">
-        <v>0.9399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="AO110">
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AQ110">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AR110">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AS110">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AT110">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="AU110">
         <v>3</v>
@@ -23781,7 +23784,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -23853,25 +23856,25 @@
         <v>2.5</v>
       </c>
       <c r="AN111">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO111">
-        <v>0.78</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP111">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ111">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR111">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AS111">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AT111">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="AU111">
         <v>11</v>
@@ -23987,7 +23990,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24059,25 +24062,25 @@
         <v>1.53</v>
       </c>
       <c r="AN112">
+        <v>1.44</v>
+      </c>
+      <c r="AO112">
         <v>1.22</v>
       </c>
-      <c r="AO112">
-        <v>1.33</v>
-      </c>
       <c r="AP112">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AQ112">
+        <v>1.18</v>
+      </c>
+      <c r="AR112">
+        <v>1.46</v>
+      </c>
+      <c r="AS112">
         <v>1.38</v>
       </c>
-      <c r="AR112">
-        <v>1.45</v>
-      </c>
-      <c r="AS112">
-        <v>1.56</v>
-      </c>
       <c r="AT112">
-        <v>3.01</v>
+        <v>2.84</v>
       </c>
       <c r="AU112">
         <v>4</v>
@@ -24193,7 +24196,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24265,25 +24268,25 @@
         <v>2.5</v>
       </c>
       <c r="AN113">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="AO113">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP113">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ113">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AR113">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AS113">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT113">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="AU113">
         <v>8</v>
@@ -24471,25 +24474,25 @@
         <v>1.75</v>
       </c>
       <c r="AN114">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="AO114">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="AP114">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="AQ114">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AR114">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AS114">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AT114">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="AU114">
         <v>8</v>
@@ -24605,7 +24608,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24677,25 +24680,25 @@
         <v>1.24</v>
       </c>
       <c r="AN115">
-        <v>0.9399999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="AO115">
         <v>2.44</v>
       </c>
       <c r="AP115">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="AQ115">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AR115">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AS115">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AT115">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="AU115">
         <v>2</v>
@@ -24883,25 +24886,25 @@
         <v>2.01</v>
       </c>
       <c r="AN116">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AO116">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="AP116">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AQ116">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="AR116">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AS116">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AT116">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AU116">
         <v>9</v>
@@ -25089,25 +25092,25 @@
         <v>1.85</v>
       </c>
       <c r="AN117">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AO117">
-        <v>0.95</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP117">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AQ117">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AR117">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AS117">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AT117">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AU117">
         <v>9</v>
@@ -25223,7 +25226,7 @@
         <v>123</v>
       </c>
       <c r="P118" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q118">
         <v>1.74</v>
@@ -25295,25 +25298,25 @@
         <v>3.16</v>
       </c>
       <c r="AN118">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AO118">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AP118">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ118">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AR118">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AS118">
         <v>1.44</v>
       </c>
       <c r="AT118">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25501,22 +25504,22 @@
         <v>1.53</v>
       </c>
       <c r="AN119">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AO119">
-        <v>0.89</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP119">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ119">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AR119">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AS119">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AT119">
         <v>2.79</v>
@@ -25707,25 +25710,25 @@
         <v>1.73</v>
       </c>
       <c r="AN120">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AO120">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AP120">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ120">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR120">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AS120">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AT120">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="AU120">
         <v>3</v>
@@ -25913,25 +25916,25 @@
         <v>1.56</v>
       </c>
       <c r="AN121">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="AO121">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AP121">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="AQ121">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AR121">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AS121">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AT121">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AU121">
         <v>8</v>
@@ -26119,25 +26122,25 @@
         <v>1.51</v>
       </c>
       <c r="AN122">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="AO122">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AQ122">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR122">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AS122">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AT122">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AU122">
         <v>5</v>
@@ -26253,7 +26256,7 @@
         <v>166</v>
       </c>
       <c r="P123" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q123">
         <v>6.04</v>
@@ -26325,25 +26328,25 @@
         <v>1.13</v>
       </c>
       <c r="AN123">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO123">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AP123">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="AQ123">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AR123">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AS123">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AT123">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="AU123">
         <v>4</v>
@@ -26531,25 +26534,25 @@
         <v>1.53</v>
       </c>
       <c r="AN124">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="AO124">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AP124">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ124">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR124">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AS124">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AT124">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="AU124">
         <v>5</v>
@@ -26665,7 +26668,7 @@
         <v>167</v>
       </c>
       <c r="P125" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q125">
         <v>2.2</v>
@@ -26737,25 +26740,25 @@
         <v>2.09</v>
       </c>
       <c r="AN125">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AO125">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ125">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AR125">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AS125">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="AT125">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="AU125">
         <v>4</v>
@@ -26943,25 +26946,25 @@
         <v>1.83</v>
       </c>
       <c r="AN126">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AO126">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="AP126">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AQ126">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="AR126">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AS126">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT126">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="AU126">
         <v>4</v>
@@ -27028,6 +27031,212 @@
       </c>
       <c r="BP126">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7580448</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45713.58333333334</v>
+      </c>
+      <c r="F127">
+        <v>20</v>
+      </c>
+      <c r="G127" t="s">
+        <v>72</v>
+      </c>
+      <c r="H127" t="s">
+        <v>81</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>1</v>
+      </c>
+      <c r="O127" t="s">
+        <v>168</v>
+      </c>
+      <c r="P127" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q127">
+        <v>5</v>
+      </c>
+      <c r="R127">
+        <v>2.32</v>
+      </c>
+      <c r="S127">
+        <v>2.11</v>
+      </c>
+      <c r="T127">
+        <v>1.28</v>
+      </c>
+      <c r="U127">
+        <v>3.38</v>
+      </c>
+      <c r="V127">
+        <v>2.45</v>
+      </c>
+      <c r="W127">
+        <v>1.5</v>
+      </c>
+      <c r="X127">
+        <v>5.1</v>
+      </c>
+      <c r="Y127">
+        <v>1.15</v>
+      </c>
+      <c r="Z127">
+        <v>4.4</v>
+      </c>
+      <c r="AA127">
+        <v>3.95</v>
+      </c>
+      <c r="AB127">
+        <v>1.7</v>
+      </c>
+      <c r="AC127">
+        <v>1.01</v>
+      </c>
+      <c r="AD127">
+        <v>11</v>
+      </c>
+      <c r="AE127">
+        <v>1.14</v>
+      </c>
+      <c r="AF127">
+        <v>4.33</v>
+      </c>
+      <c r="AG127">
+        <v>1.67</v>
+      </c>
+      <c r="AH127">
+        <v>2</v>
+      </c>
+      <c r="AI127">
+        <v>1.66</v>
+      </c>
+      <c r="AJ127">
+        <v>2.09</v>
+      </c>
+      <c r="AK127">
+        <v>2.26</v>
+      </c>
+      <c r="AL127">
+        <v>1.21</v>
+      </c>
+      <c r="AM127">
+        <v>1.16</v>
+      </c>
+      <c r="AN127">
+        <v>0.8</v>
+      </c>
+      <c r="AO127">
+        <v>1.78</v>
+      </c>
+      <c r="AP127">
+        <v>1</v>
+      </c>
+      <c r="AQ127">
+        <v>1.6</v>
+      </c>
+      <c r="AR127">
+        <v>1.51</v>
+      </c>
+      <c r="AS127">
+        <v>1.33</v>
+      </c>
+      <c r="AT127">
+        <v>2.84</v>
+      </c>
+      <c r="AU127">
+        <v>2</v>
+      </c>
+      <c r="AV127">
+        <v>8</v>
+      </c>
+      <c r="AW127">
+        <v>4</v>
+      </c>
+      <c r="AX127">
+        <v>17</v>
+      </c>
+      <c r="AY127">
+        <v>6</v>
+      </c>
+      <c r="AZ127">
+        <v>25</v>
+      </c>
+      <c r="BA127">
+        <v>2</v>
+      </c>
+      <c r="BB127">
+        <v>8</v>
+      </c>
+      <c r="BC127">
+        <v>10</v>
+      </c>
+      <c r="BD127">
+        <v>3.22</v>
+      </c>
+      <c r="BE127">
+        <v>9.1</v>
+      </c>
+      <c r="BF127">
+        <v>1.46</v>
+      </c>
+      <c r="BG127">
+        <v>1.28</v>
+      </c>
+      <c r="BH127">
+        <v>3.25</v>
+      </c>
+      <c r="BI127">
+        <v>1.52</v>
+      </c>
+      <c r="BJ127">
+        <v>2.37</v>
+      </c>
+      <c r="BK127">
+        <v>1.87</v>
+      </c>
+      <c r="BL127">
+        <v>1.87</v>
+      </c>
+      <c r="BM127">
+        <v>2.38</v>
+      </c>
+      <c r="BN127">
+        <v>1.54</v>
+      </c>
+      <c r="BO127">
+        <v>3.12</v>
+      </c>
+      <c r="BP127">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="240">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -523,6 +523,18 @@
     <t>['17']</t>
   </si>
   <si>
+    <t>['40', '54', '90+4']</t>
+  </si>
+  <si>
+    <t>['40', '43', '64']</t>
+  </si>
+  <si>
+    <t>['32', '62']</t>
+  </si>
+  <si>
+    <t>['75']</t>
+  </si>
+  <si>
     <t>['5', '42', '80', '90+2']</t>
   </si>
   <si>
@@ -713,6 +725,15 @@
   </si>
   <si>
     <t>['69']</t>
+  </si>
+  <si>
+    <t>['14', '51']</t>
+  </si>
+  <si>
+    <t>['75', '84']</t>
+  </si>
+  <si>
+    <t>['16', '34']</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1408,10 +1429,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1614,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ3">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1742,7 +1763,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1948,7 +1969,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2026,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ5">
         <v>1.55</v>
@@ -2235,7 +2256,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2566,7 +2587,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -2644,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ8">
         <v>0.55</v>
@@ -3056,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ10">
         <v>1.18</v>
@@ -3265,7 +3286,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ11">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3468,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3677,7 +3698,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3880,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ14">
         <v>1.18</v>
@@ -4089,7 +4110,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR15">
         <v>1.66</v>
@@ -4292,7 +4313,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ16">
         <v>1.55</v>
@@ -4420,7 +4441,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q17">
         <v>1.7</v>
@@ -4498,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ17">
         <v>1.09</v>
@@ -4626,7 +4647,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4832,7 +4853,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q19">
         <v>2.57</v>
@@ -4910,7 +4931,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ19">
         <v>0.55</v>
@@ -5038,7 +5059,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5325,7 +5346,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ21">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR21">
         <v>1.9</v>
@@ -5450,7 +5471,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5528,7 +5549,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -5656,7 +5677,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -5734,10 +5755,10 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR23">
         <v>1.55</v>
@@ -5943,7 +5964,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ24">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR24">
         <v>2.32</v>
@@ -6068,7 +6089,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q25">
         <v>2.2</v>
@@ -6149,7 +6170,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR25">
         <v>1.13</v>
@@ -6274,7 +6295,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q26">
         <v>3.9</v>
@@ -6352,7 +6373,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26">
         <v>2.36</v>
@@ -6558,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27">
         <v>1.09</v>
@@ -6686,7 +6707,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6767,7 +6788,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR28">
         <v>1.13</v>
@@ -6892,7 +6913,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -6970,7 +6991,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ29">
         <v>0.36</v>
@@ -7098,7 +7119,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7176,10 +7197,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ30">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR30">
         <v>1.44</v>
@@ -7304,7 +7325,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7385,7 +7406,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -7510,7 +7531,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q32">
         <v>3.6</v>
@@ -7591,7 +7612,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ32">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR32">
         <v>1.05</v>
@@ -7716,7 +7737,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7922,7 +7943,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8000,7 +8021,7 @@
         <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8128,7 +8149,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8206,7 +8227,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ35">
         <v>2.36</v>
@@ -8412,10 +8433,10 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ36">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR36">
         <v>1.33</v>
@@ -8746,7 +8767,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8952,7 +8973,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q39">
         <v>4.33</v>
@@ -9030,7 +9051,7 @@
         <v>1.75</v>
       </c>
       <c r="AP39">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ39">
         <v>1.55</v>
@@ -9158,7 +9179,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9239,7 +9260,7 @@
         <v>1</v>
       </c>
       <c r="AQ40">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -9364,7 +9385,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q41">
         <v>4.36</v>
@@ -9442,10 +9463,10 @@
         <v>1.67</v>
       </c>
       <c r="AP41">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ41">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR41">
         <v>1.42</v>
@@ -9648,10 +9669,10 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -10060,10 +10081,10 @@
         <v>1.25</v>
       </c>
       <c r="AP44">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10188,7 +10209,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10269,7 +10290,7 @@
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR45">
         <v>1.33</v>
@@ -10394,7 +10415,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10600,7 +10621,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q47">
         <v>2.49</v>
@@ -10678,7 +10699,7 @@
         <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ47">
         <v>1.09</v>
@@ -10806,7 +10827,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q48">
         <v>2.48</v>
@@ -11090,10 +11111,10 @@
         <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ49">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR49">
         <v>1.98</v>
@@ -11218,7 +11239,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11630,7 +11651,7 @@
         <v>82</v>
       </c>
       <c r="P52" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -11708,10 +11729,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ52">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR52">
         <v>1.7</v>
@@ -11836,7 +11857,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q53">
         <v>3.22</v>
@@ -11914,10 +11935,10 @@
         <v>1.33</v>
       </c>
       <c r="AP53">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ53">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR53">
         <v>1.35</v>
@@ -12120,7 +12141,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12248,7 +12269,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12326,10 +12347,10 @@
         <v>0.4</v>
       </c>
       <c r="AP55">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR55">
         <v>1.52</v>
@@ -12454,7 +12475,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12532,10 +12553,10 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ56">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR56">
         <v>1.86</v>
@@ -12738,10 +12759,10 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR57">
         <v>1.64</v>
@@ -12866,7 +12887,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13278,7 +13299,7 @@
         <v>85</v>
       </c>
       <c r="P60" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13484,7 +13505,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13896,7 +13917,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -14102,7 +14123,7 @@
         <v>129</v>
       </c>
       <c r="P64" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q64">
         <v>1.9</v>
@@ -14308,7 +14329,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
@@ -14386,10 +14407,10 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ65">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR65">
         <v>1.47</v>
@@ -14514,7 +14535,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14592,7 +14613,7 @@
         <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ66">
         <v>1.09</v>
@@ -14720,7 +14741,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14801,7 +14822,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ67">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR67">
         <v>1.44</v>
@@ -14926,7 +14947,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15210,7 +15231,7 @@
         <v>0.83</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ69">
         <v>1.18</v>
@@ -15338,7 +15359,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q70">
         <v>2</v>
@@ -15419,7 +15440,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ70">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR70">
         <v>1.9</v>
@@ -15544,7 +15565,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -15622,7 +15643,7 @@
         <v>3</v>
       </c>
       <c r="AP71">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ71">
         <v>2.36</v>
@@ -15956,7 +15977,7 @@
         <v>137</v>
       </c>
       <c r="P73" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q73">
         <v>1.83</v>
@@ -16037,7 +16058,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR73">
         <v>1.7</v>
@@ -16162,7 +16183,7 @@
         <v>82</v>
       </c>
       <c r="P74" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16446,10 +16467,10 @@
         <v>0.5</v>
       </c>
       <c r="AP75">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ75">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR75">
         <v>1.4</v>
@@ -16574,7 +16595,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16652,7 +16673,7 @@
         <v>3</v>
       </c>
       <c r="AP76">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ76">
         <v>2.36</v>
@@ -16858,7 +16879,7 @@
         <v>0.6</v>
       </c>
       <c r="AP77">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ77">
         <v>0.36</v>
@@ -17067,7 +17088,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ78">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR78">
         <v>1.45</v>
@@ -17270,7 +17291,7 @@
         <v>0.67</v>
       </c>
       <c r="AP79">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ79">
         <v>0.55</v>
@@ -17398,7 +17419,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q80">
         <v>4.5</v>
@@ -17479,7 +17500,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ80">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR80">
         <v>1.35</v>
@@ -17685,7 +17706,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ81">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR81">
         <v>1.54</v>
@@ -17810,7 +17831,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -17891,7 +17912,7 @@
         <v>1</v>
       </c>
       <c r="AQ82">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR82">
         <v>1.42</v>
@@ -18094,7 +18115,7 @@
         <v>1.17</v>
       </c>
       <c r="AP83">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ83">
         <v>1.09</v>
@@ -18300,7 +18321,7 @@
         <v>0.5</v>
       </c>
       <c r="AP84">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ84">
         <v>0.36</v>
@@ -18506,7 +18527,7 @@
         <v>3</v>
       </c>
       <c r="AP85">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ85">
         <v>2.36</v>
@@ -18634,7 +18655,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18712,7 +18733,7 @@
         <v>0.71</v>
       </c>
       <c r="AP86">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ86">
         <v>1.18</v>
@@ -18840,7 +18861,7 @@
         <v>143</v>
       </c>
       <c r="P87" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -18918,10 +18939,10 @@
         <v>0.57</v>
       </c>
       <c r="AP87">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ87">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR87">
         <v>1.42</v>
@@ -19124,10 +19145,10 @@
         <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR88">
         <v>1.54</v>
@@ -19252,7 +19273,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19333,7 +19354,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ89">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR89">
         <v>1.8</v>
@@ -19458,7 +19479,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19870,7 +19891,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -19951,7 +19972,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ92">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR92">
         <v>1.34</v>
@@ -20076,7 +20097,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q93">
         <v>4</v>
@@ -20157,7 +20178,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ93">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR93">
         <v>1.53</v>
@@ -20360,7 +20381,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ94">
         <v>1.55</v>
@@ -20566,7 +20587,7 @@
         <v>0.57</v>
       </c>
       <c r="AP95">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ95">
         <v>0.36</v>
@@ -20978,7 +20999,7 @@
         <v>1.29</v>
       </c>
       <c r="AP97">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21106,7 +21127,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21187,7 +21208,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ98">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR98">
         <v>1.57</v>
@@ -21312,7 +21333,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21390,7 +21411,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ99">
         <v>1.18</v>
@@ -21724,7 +21745,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21930,7 +21951,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -22008,7 +22029,7 @@
         <v>0.5</v>
       </c>
       <c r="AP102">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ102">
         <v>0.55</v>
@@ -22136,7 +22157,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -22214,10 +22235,10 @@
         <v>0.5</v>
       </c>
       <c r="AP103">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ103">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR103">
         <v>1.57</v>
@@ -22423,7 +22444,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ104">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR104">
         <v>1.51</v>
@@ -22832,10 +22853,10 @@
         <v>0.63</v>
       </c>
       <c r="AP106">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ106">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR106">
         <v>1.71</v>
@@ -23038,7 +23059,7 @@
         <v>1.88</v>
       </c>
       <c r="AP107">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ107">
         <v>1.55</v>
@@ -23244,10 +23265,10 @@
         <v>1.88</v>
       </c>
       <c r="AP108">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ108">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR108">
         <v>1.59</v>
@@ -23578,7 +23599,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23656,10 +23677,10 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ110">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -23784,7 +23805,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -23862,7 +23883,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP111">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ111">
         <v>0.55</v>
@@ -23990,7 +24011,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24196,7 +24217,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24608,7 +24629,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q115">
         <v>4.33</v>
@@ -24892,7 +24913,7 @@
         <v>0.44</v>
       </c>
       <c r="AP116">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ116">
         <v>0.36</v>
@@ -25098,10 +25119,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP117">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ117">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR117">
         <v>1.75</v>
@@ -25226,7 +25247,7 @@
         <v>123</v>
       </c>
       <c r="P118" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q118">
         <v>1.74</v>
@@ -25304,10 +25325,10 @@
         <v>1</v>
       </c>
       <c r="AP118">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR118">
         <v>1.86</v>
@@ -25510,10 +25531,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP119">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ119">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR119">
         <v>1.56</v>
@@ -26256,7 +26277,7 @@
         <v>166</v>
       </c>
       <c r="P123" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q123">
         <v>6.04</v>
@@ -26668,7 +26689,7 @@
         <v>167</v>
       </c>
       <c r="P125" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q125">
         <v>2.2</v>
@@ -27161,7 +27182,7 @@
         <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR127">
         <v>1.51</v>
@@ -27237,6 +27258,1242 @@
       </c>
       <c r="BP127">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7580458</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45717.47916666666</v>
+      </c>
+      <c r="F128">
+        <v>22</v>
+      </c>
+      <c r="G128" t="s">
+        <v>73</v>
+      </c>
+      <c r="H128" t="s">
+        <v>79</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="J128">
+        <v>1</v>
+      </c>
+      <c r="K128">
+        <v>2</v>
+      </c>
+      <c r="L128">
+        <v>3</v>
+      </c>
+      <c r="M128">
+        <v>2</v>
+      </c>
+      <c r="N128">
+        <v>5</v>
+      </c>
+      <c r="O128" t="s">
+        <v>169</v>
+      </c>
+      <c r="P128" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q128">
+        <v>2.28</v>
+      </c>
+      <c r="R128">
+        <v>2.2</v>
+      </c>
+      <c r="S128">
+        <v>4.8</v>
+      </c>
+      <c r="T128">
+        <v>1.43</v>
+      </c>
+      <c r="U128">
+        <v>2.65</v>
+      </c>
+      <c r="V128">
+        <v>2.7</v>
+      </c>
+      <c r="W128">
+        <v>1.41</v>
+      </c>
+      <c r="X128">
+        <v>6.7</v>
+      </c>
+      <c r="Y128">
+        <v>1.09</v>
+      </c>
+      <c r="Z128">
+        <v>1.85</v>
+      </c>
+      <c r="AA128">
+        <v>3.68</v>
+      </c>
+      <c r="AB128">
+        <v>3.89</v>
+      </c>
+      <c r="AC128">
+        <v>1</v>
+      </c>
+      <c r="AD128">
+        <v>9.1</v>
+      </c>
+      <c r="AE128">
+        <v>1.29</v>
+      </c>
+      <c r="AF128">
+        <v>3.4</v>
+      </c>
+      <c r="AG128">
+        <v>1.91</v>
+      </c>
+      <c r="AH128">
+        <v>1.83</v>
+      </c>
+      <c r="AI128">
+        <v>1.81</v>
+      </c>
+      <c r="AJ128">
+        <v>1.89</v>
+      </c>
+      <c r="AK128">
+        <v>1.19</v>
+      </c>
+      <c r="AL128">
+        <v>1.26</v>
+      </c>
+      <c r="AM128">
+        <v>1.94</v>
+      </c>
+      <c r="AN128">
+        <v>1.4</v>
+      </c>
+      <c r="AO128">
+        <v>1</v>
+      </c>
+      <c r="AP128">
+        <v>1.55</v>
+      </c>
+      <c r="AQ128">
+        <v>0.91</v>
+      </c>
+      <c r="AR128">
+        <v>1.48</v>
+      </c>
+      <c r="AS128">
+        <v>1.41</v>
+      </c>
+      <c r="AT128">
+        <v>2.89</v>
+      </c>
+      <c r="AU128">
+        <v>7</v>
+      </c>
+      <c r="AV128">
+        <v>5</v>
+      </c>
+      <c r="AW128">
+        <v>9</v>
+      </c>
+      <c r="AX128">
+        <v>1</v>
+      </c>
+      <c r="AY128">
+        <v>16</v>
+      </c>
+      <c r="AZ128">
+        <v>6</v>
+      </c>
+      <c r="BA128">
+        <v>13</v>
+      </c>
+      <c r="BB128">
+        <v>0</v>
+      </c>
+      <c r="BC128">
+        <v>13</v>
+      </c>
+      <c r="BD128">
+        <v>0</v>
+      </c>
+      <c r="BE128">
+        <v>0</v>
+      </c>
+      <c r="BF128">
+        <v>0</v>
+      </c>
+      <c r="BG128">
+        <v>0</v>
+      </c>
+      <c r="BH128">
+        <v>0</v>
+      </c>
+      <c r="BI128">
+        <v>0</v>
+      </c>
+      <c r="BJ128">
+        <v>0</v>
+      </c>
+      <c r="BK128">
+        <v>0</v>
+      </c>
+      <c r="BL128">
+        <v>0</v>
+      </c>
+      <c r="BM128">
+        <v>0</v>
+      </c>
+      <c r="BN128">
+        <v>0</v>
+      </c>
+      <c r="BO128">
+        <v>0</v>
+      </c>
+      <c r="BP128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7580457</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45717.47916666666</v>
+      </c>
+      <c r="F129">
+        <v>22</v>
+      </c>
+      <c r="G129" t="s">
+        <v>80</v>
+      </c>
+      <c r="H129" t="s">
+        <v>75</v>
+      </c>
+      <c r="I129">
+        <v>2</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>3</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>3</v>
+      </c>
+      <c r="O129" t="s">
+        <v>170</v>
+      </c>
+      <c r="P129" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q129">
+        <v>2.12</v>
+      </c>
+      <c r="R129">
+        <v>2.26</v>
+      </c>
+      <c r="S129">
+        <v>5.4</v>
+      </c>
+      <c r="T129">
+        <v>1.33</v>
+      </c>
+      <c r="U129">
+        <v>3.08</v>
+      </c>
+      <c r="V129">
+        <v>2.6</v>
+      </c>
+      <c r="W129">
+        <v>1.44</v>
+      </c>
+      <c r="X129">
+        <v>6.2</v>
+      </c>
+      <c r="Y129">
+        <v>1.1</v>
+      </c>
+      <c r="Z129">
+        <v>1.61</v>
+      </c>
+      <c r="AA129">
+        <v>4.3</v>
+      </c>
+      <c r="AB129">
+        <v>4.7</v>
+      </c>
+      <c r="AC129">
+        <v>1.02</v>
+      </c>
+      <c r="AD129">
+        <v>10</v>
+      </c>
+      <c r="AE129">
+        <v>1.27</v>
+      </c>
+      <c r="AF129">
+        <v>3.5</v>
+      </c>
+      <c r="AG129">
+        <v>1.83</v>
+      </c>
+      <c r="AH129">
+        <v>1.91</v>
+      </c>
+      <c r="AI129">
+        <v>1.86</v>
+      </c>
+      <c r="AJ129">
+        <v>1.84</v>
+      </c>
+      <c r="AK129">
+        <v>1.16</v>
+      </c>
+      <c r="AL129">
+        <v>1.2</v>
+      </c>
+      <c r="AM129">
+        <v>2.2</v>
+      </c>
+      <c r="AN129">
+        <v>1.2</v>
+      </c>
+      <c r="AO129">
+        <v>0.5</v>
+      </c>
+      <c r="AP129">
+        <v>1.36</v>
+      </c>
+      <c r="AQ129">
+        <v>0.45</v>
+      </c>
+      <c r="AR129">
+        <v>1.76</v>
+      </c>
+      <c r="AS129">
+        <v>1.22</v>
+      </c>
+      <c r="AT129">
+        <v>2.98</v>
+      </c>
+      <c r="AU129">
+        <v>5</v>
+      </c>
+      <c r="AV129">
+        <v>5</v>
+      </c>
+      <c r="AW129">
+        <v>12</v>
+      </c>
+      <c r="AX129">
+        <v>7</v>
+      </c>
+      <c r="AY129">
+        <v>17</v>
+      </c>
+      <c r="AZ129">
+        <v>12</v>
+      </c>
+      <c r="BA129">
+        <v>5</v>
+      </c>
+      <c r="BB129">
+        <v>10</v>
+      </c>
+      <c r="BC129">
+        <v>15</v>
+      </c>
+      <c r="BD129">
+        <v>1.33</v>
+      </c>
+      <c r="BE129">
+        <v>7.8</v>
+      </c>
+      <c r="BF129">
+        <v>4.45</v>
+      </c>
+      <c r="BG129">
+        <v>1.18</v>
+      </c>
+      <c r="BH129">
+        <v>3.9</v>
+      </c>
+      <c r="BI129">
+        <v>1.37</v>
+      </c>
+      <c r="BJ129">
+        <v>2.75</v>
+      </c>
+      <c r="BK129">
+        <v>1.68</v>
+      </c>
+      <c r="BL129">
+        <v>2.06</v>
+      </c>
+      <c r="BM129">
+        <v>2.09</v>
+      </c>
+      <c r="BN129">
+        <v>1.63</v>
+      </c>
+      <c r="BO129">
+        <v>2.7</v>
+      </c>
+      <c r="BP129">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7580459</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45717.47916666666</v>
+      </c>
+      <c r="F130">
+        <v>22</v>
+      </c>
+      <c r="G130" t="s">
+        <v>71</v>
+      </c>
+      <c r="H130" t="s">
+        <v>72</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>2</v>
+      </c>
+      <c r="M130">
+        <v>2</v>
+      </c>
+      <c r="N130">
+        <v>4</v>
+      </c>
+      <c r="O130" t="s">
+        <v>171</v>
+      </c>
+      <c r="P130" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q130">
+        <v>2</v>
+      </c>
+      <c r="R130">
+        <v>2.38</v>
+      </c>
+      <c r="S130">
+        <v>5.5</v>
+      </c>
+      <c r="T130">
+        <v>1.3</v>
+      </c>
+      <c r="U130">
+        <v>3.4</v>
+      </c>
+      <c r="V130">
+        <v>2.5</v>
+      </c>
+      <c r="W130">
+        <v>1.5</v>
+      </c>
+      <c r="X130">
+        <v>5.5</v>
+      </c>
+      <c r="Y130">
+        <v>1.13</v>
+      </c>
+      <c r="Z130">
+        <v>1.51</v>
+      </c>
+      <c r="AA130">
+        <v>4</v>
+      </c>
+      <c r="AB130">
+        <v>6.3</v>
+      </c>
+      <c r="AC130">
+        <v>1.04</v>
+      </c>
+      <c r="AD130">
+        <v>9</v>
+      </c>
+      <c r="AE130">
+        <v>1.19</v>
+      </c>
+      <c r="AF130">
+        <v>4.4</v>
+      </c>
+      <c r="AG130">
+        <v>1.89</v>
+      </c>
+      <c r="AH130">
+        <v>1.85</v>
+      </c>
+      <c r="AI130">
+        <v>1.8</v>
+      </c>
+      <c r="AJ130">
+        <v>1.91</v>
+      </c>
+      <c r="AK130">
+        <v>1.11</v>
+      </c>
+      <c r="AL130">
+        <v>1.21</v>
+      </c>
+      <c r="AM130">
+        <v>2.37</v>
+      </c>
+      <c r="AN130">
+        <v>1.6</v>
+      </c>
+      <c r="AO130">
+        <v>1</v>
+      </c>
+      <c r="AP130">
+        <v>1.55</v>
+      </c>
+      <c r="AQ130">
+        <v>1</v>
+      </c>
+      <c r="AR130">
+        <v>1.8</v>
+      </c>
+      <c r="AS130">
+        <v>1.29</v>
+      </c>
+      <c r="AT130">
+        <v>3.09</v>
+      </c>
+      <c r="AU130">
+        <v>6</v>
+      </c>
+      <c r="AV130">
+        <v>6</v>
+      </c>
+      <c r="AW130">
+        <v>3</v>
+      </c>
+      <c r="AX130">
+        <v>4</v>
+      </c>
+      <c r="AY130">
+        <v>9</v>
+      </c>
+      <c r="AZ130">
+        <v>10</v>
+      </c>
+      <c r="BA130">
+        <v>5</v>
+      </c>
+      <c r="BB130">
+        <v>5</v>
+      </c>
+      <c r="BC130">
+        <v>10</v>
+      </c>
+      <c r="BD130">
+        <v>0</v>
+      </c>
+      <c r="BE130">
+        <v>0</v>
+      </c>
+      <c r="BF130">
+        <v>0</v>
+      </c>
+      <c r="BG130">
+        <v>0</v>
+      </c>
+      <c r="BH130">
+        <v>0</v>
+      </c>
+      <c r="BI130">
+        <v>0</v>
+      </c>
+      <c r="BJ130">
+        <v>0</v>
+      </c>
+      <c r="BK130">
+        <v>0</v>
+      </c>
+      <c r="BL130">
+        <v>0</v>
+      </c>
+      <c r="BM130">
+        <v>0</v>
+      </c>
+      <c r="BN130">
+        <v>0</v>
+      </c>
+      <c r="BO130">
+        <v>0</v>
+      </c>
+      <c r="BP130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7580455</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45717.47916666666</v>
+      </c>
+      <c r="F131">
+        <v>22</v>
+      </c>
+      <c r="G131" t="s">
+        <v>76</v>
+      </c>
+      <c r="H131" t="s">
+        <v>81</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>2</v>
+      </c>
+      <c r="K131">
+        <v>2</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131">
+        <v>2</v>
+      </c>
+      <c r="N131">
+        <v>3</v>
+      </c>
+      <c r="O131" t="s">
+        <v>172</v>
+      </c>
+      <c r="P131" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q131">
+        <v>4.5</v>
+      </c>
+      <c r="R131">
+        <v>2.25</v>
+      </c>
+      <c r="S131">
+        <v>2.3</v>
+      </c>
+      <c r="T131">
+        <v>1.36</v>
+      </c>
+      <c r="U131">
+        <v>3</v>
+      </c>
+      <c r="V131">
+        <v>2.63</v>
+      </c>
+      <c r="W131">
+        <v>1.44</v>
+      </c>
+      <c r="X131">
+        <v>6</v>
+      </c>
+      <c r="Y131">
+        <v>1.11</v>
+      </c>
+      <c r="Z131">
+        <v>4.5</v>
+      </c>
+      <c r="AA131">
+        <v>3.74</v>
+      </c>
+      <c r="AB131">
+        <v>1.72</v>
+      </c>
+      <c r="AC131">
+        <v>1.04</v>
+      </c>
+      <c r="AD131">
+        <v>9</v>
+      </c>
+      <c r="AE131">
+        <v>1.24</v>
+      </c>
+      <c r="AF131">
+        <v>3.8</v>
+      </c>
+      <c r="AG131">
+        <v>1.78</v>
+      </c>
+      <c r="AH131">
+        <v>1.92</v>
+      </c>
+      <c r="AI131">
+        <v>1.73</v>
+      </c>
+      <c r="AJ131">
+        <v>2</v>
+      </c>
+      <c r="AK131">
+        <v>2</v>
+      </c>
+      <c r="AL131">
+        <v>1.24</v>
+      </c>
+      <c r="AM131">
+        <v>1.19</v>
+      </c>
+      <c r="AN131">
+        <v>1.3</v>
+      </c>
+      <c r="AO131">
+        <v>1.6</v>
+      </c>
+      <c r="AP131">
+        <v>1.18</v>
+      </c>
+      <c r="AQ131">
+        <v>1.73</v>
+      </c>
+      <c r="AR131">
+        <v>1.4</v>
+      </c>
+      <c r="AS131">
+        <v>1.47</v>
+      </c>
+      <c r="AT131">
+        <v>2.87</v>
+      </c>
+      <c r="AU131">
+        <v>3</v>
+      </c>
+      <c r="AV131">
+        <v>6</v>
+      </c>
+      <c r="AW131">
+        <v>7</v>
+      </c>
+      <c r="AX131">
+        <v>6</v>
+      </c>
+      <c r="AY131">
+        <v>10</v>
+      </c>
+      <c r="AZ131">
+        <v>12</v>
+      </c>
+      <c r="BA131">
+        <v>3</v>
+      </c>
+      <c r="BB131">
+        <v>3</v>
+      </c>
+      <c r="BC131">
+        <v>6</v>
+      </c>
+      <c r="BD131">
+        <v>3.52</v>
+      </c>
+      <c r="BE131">
+        <v>7.3</v>
+      </c>
+      <c r="BF131">
+        <v>1.46</v>
+      </c>
+      <c r="BG131">
+        <v>0</v>
+      </c>
+      <c r="BH131">
+        <v>0</v>
+      </c>
+      <c r="BI131">
+        <v>1.32</v>
+      </c>
+      <c r="BJ131">
+        <v>2.88</v>
+      </c>
+      <c r="BK131">
+        <v>1.59</v>
+      </c>
+      <c r="BL131">
+        <v>2.16</v>
+      </c>
+      <c r="BM131">
+        <v>1.99</v>
+      </c>
+      <c r="BN131">
+        <v>1.73</v>
+      </c>
+      <c r="BO131">
+        <v>2.57</v>
+      </c>
+      <c r="BP131">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7580456</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45717.47916666666</v>
+      </c>
+      <c r="F132">
+        <v>22</v>
+      </c>
+      <c r="G132" t="s">
+        <v>70</v>
+      </c>
+      <c r="H132" t="s">
+        <v>77</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132" t="s">
+        <v>82</v>
+      </c>
+      <c r="P132" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q132">
+        <v>2.47</v>
+      </c>
+      <c r="R132">
+        <v>2.18</v>
+      </c>
+      <c r="S132">
+        <v>4.2</v>
+      </c>
+      <c r="T132">
+        <v>1.36</v>
+      </c>
+      <c r="U132">
+        <v>2.94</v>
+      </c>
+      <c r="V132">
+        <v>2.65</v>
+      </c>
+      <c r="W132">
+        <v>1.42</v>
+      </c>
+      <c r="X132">
+        <v>6.5</v>
+      </c>
+      <c r="Y132">
+        <v>1.09</v>
+      </c>
+      <c r="Z132">
+        <v>1.98</v>
+      </c>
+      <c r="AA132">
+        <v>3.45</v>
+      </c>
+      <c r="AB132">
+        <v>3.65</v>
+      </c>
+      <c r="AC132">
+        <v>1.01</v>
+      </c>
+      <c r="AD132">
+        <v>8.9</v>
+      </c>
+      <c r="AE132">
+        <v>1.28</v>
+      </c>
+      <c r="AF132">
+        <v>3.45</v>
+      </c>
+      <c r="AG132">
+        <v>1.89</v>
+      </c>
+      <c r="AH132">
+        <v>1.85</v>
+      </c>
+      <c r="AI132">
+        <v>1.73</v>
+      </c>
+      <c r="AJ132">
+        <v>1.99</v>
+      </c>
+      <c r="AK132">
+        <v>1.25</v>
+      </c>
+      <c r="AL132">
+        <v>1.27</v>
+      </c>
+      <c r="AM132">
+        <v>1.78</v>
+      </c>
+      <c r="AN132">
+        <v>1.2</v>
+      </c>
+      <c r="AO132">
+        <v>0.5</v>
+      </c>
+      <c r="AP132">
+        <v>1.18</v>
+      </c>
+      <c r="AQ132">
+        <v>0.55</v>
+      </c>
+      <c r="AR132">
+        <v>1.53</v>
+      </c>
+      <c r="AS132">
+        <v>1.15</v>
+      </c>
+      <c r="AT132">
+        <v>2.68</v>
+      </c>
+      <c r="AU132">
+        <v>4</v>
+      </c>
+      <c r="AV132">
+        <v>2</v>
+      </c>
+      <c r="AW132">
+        <v>3</v>
+      </c>
+      <c r="AX132">
+        <v>5</v>
+      </c>
+      <c r="AY132">
+        <v>7</v>
+      </c>
+      <c r="AZ132">
+        <v>7</v>
+      </c>
+      <c r="BA132">
+        <v>0</v>
+      </c>
+      <c r="BB132">
+        <v>6</v>
+      </c>
+      <c r="BC132">
+        <v>6</v>
+      </c>
+      <c r="BD132">
+        <v>0</v>
+      </c>
+      <c r="BE132">
+        <v>0</v>
+      </c>
+      <c r="BF132">
+        <v>0</v>
+      </c>
+      <c r="BG132">
+        <v>0</v>
+      </c>
+      <c r="BH132">
+        <v>0</v>
+      </c>
+      <c r="BI132">
+        <v>0</v>
+      </c>
+      <c r="BJ132">
+        <v>0</v>
+      </c>
+      <c r="BK132">
+        <v>1.98</v>
+      </c>
+      <c r="BL132">
+        <v>1.82</v>
+      </c>
+      <c r="BM132">
+        <v>0</v>
+      </c>
+      <c r="BN132">
+        <v>0</v>
+      </c>
+      <c r="BO132">
+        <v>0</v>
+      </c>
+      <c r="BP132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7580460</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45717.47916666666</v>
+      </c>
+      <c r="F133">
+        <v>22</v>
+      </c>
+      <c r="G133" t="s">
+        <v>78</v>
+      </c>
+      <c r="H133" t="s">
+        <v>74</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>1</v>
+      </c>
+      <c r="N133">
+        <v>1</v>
+      </c>
+      <c r="O133" t="s">
+        <v>82</v>
+      </c>
+      <c r="P133" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q133">
+        <v>2.05</v>
+      </c>
+      <c r="R133">
+        <v>2.43</v>
+      </c>
+      <c r="S133">
+        <v>5</v>
+      </c>
+      <c r="T133">
+        <v>1.3</v>
+      </c>
+      <c r="U133">
+        <v>3.28</v>
+      </c>
+      <c r="V133">
+        <v>2.31</v>
+      </c>
+      <c r="W133">
+        <v>1.56</v>
+      </c>
+      <c r="X133">
+        <v>5.3</v>
+      </c>
+      <c r="Y133">
+        <v>1.14</v>
+      </c>
+      <c r="Z133">
+        <v>1.72</v>
+      </c>
+      <c r="AA133">
+        <v>3.9</v>
+      </c>
+      <c r="AB133">
+        <v>4.3</v>
+      </c>
+      <c r="AC133">
+        <v>1.01</v>
+      </c>
+      <c r="AD133">
+        <v>13</v>
+      </c>
+      <c r="AE133">
+        <v>1.19</v>
+      </c>
+      <c r="AF133">
+        <v>4.3</v>
+      </c>
+      <c r="AG133">
+        <v>1.85</v>
+      </c>
+      <c r="AH133">
+        <v>1.89</v>
+      </c>
+      <c r="AI133">
+        <v>1.63</v>
+      </c>
+      <c r="AJ133">
+        <v>2.13</v>
+      </c>
+      <c r="AK133">
+        <v>1.16</v>
+      </c>
+      <c r="AL133">
+        <v>1.23</v>
+      </c>
+      <c r="AM133">
+        <v>2.11</v>
+      </c>
+      <c r="AN133">
+        <v>2.3</v>
+      </c>
+      <c r="AO133">
+        <v>2.1</v>
+      </c>
+      <c r="AP133">
+        <v>2.09</v>
+      </c>
+      <c r="AQ133">
+        <v>2.18</v>
+      </c>
+      <c r="AR133">
+        <v>1.95</v>
+      </c>
+      <c r="AS133">
+        <v>1.61</v>
+      </c>
+      <c r="AT133">
+        <v>3.56</v>
+      </c>
+      <c r="AU133">
+        <v>5</v>
+      </c>
+      <c r="AV133">
+        <v>9</v>
+      </c>
+      <c r="AW133">
+        <v>15</v>
+      </c>
+      <c r="AX133">
+        <v>7</v>
+      </c>
+      <c r="AY133">
+        <v>20</v>
+      </c>
+      <c r="AZ133">
+        <v>16</v>
+      </c>
+      <c r="BA133">
+        <v>9</v>
+      </c>
+      <c r="BB133">
+        <v>2</v>
+      </c>
+      <c r="BC133">
+        <v>11</v>
+      </c>
+      <c r="BD133">
+        <v>1.78</v>
+      </c>
+      <c r="BE133">
+        <v>6.45</v>
+      </c>
+      <c r="BF133">
+        <v>2.57</v>
+      </c>
+      <c r="BG133">
+        <v>1.24</v>
+      </c>
+      <c r="BH133">
+        <v>3.34</v>
+      </c>
+      <c r="BI133">
+        <v>1.48</v>
+      </c>
+      <c r="BJ133">
+        <v>2.4</v>
+      </c>
+      <c r="BK133">
+        <v>1.85</v>
+      </c>
+      <c r="BL133">
+        <v>1.85</v>
+      </c>
+      <c r="BM133">
+        <v>2.38</v>
+      </c>
+      <c r="BN133">
+        <v>1.49</v>
+      </c>
+      <c r="BO133">
+        <v>3.14</v>
+      </c>
+      <c r="BP133">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -27400,31 +27400,31 @@
         <v>3.56</v>
       </c>
       <c r="AU128">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV128">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AW128">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AX128">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY128">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AZ128">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="BA128">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BB128">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC128">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD128">
         <v>1.78</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="243">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -535,6 +535,9 @@
     <t>['75']</t>
   </si>
   <si>
+    <t>['47']</t>
+  </si>
+  <si>
     <t>['5', '42', '80', '90+2']</t>
   </si>
   <si>
@@ -643,9 +646,6 @@
     <t>['27', '85']</t>
   </si>
   <si>
-    <t>['47']</t>
-  </si>
-  <si>
     <t>['15', '90+2']</t>
   </si>
   <si>
@@ -734,6 +734,15 @@
   </si>
   <si>
     <t>['16', '34']</t>
+  </si>
+  <si>
+    <t>['2', '66']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['34']</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP133"/>
+  <dimension ref="A1:BP137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1763,7 +1772,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1969,7 +1978,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2050,7 +2059,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ5">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2253,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ6">
         <v>0.55</v>
@@ -2459,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7">
         <v>0.36</v>
@@ -2587,7 +2596,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -2665,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3080,7 +3089,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3286,7 +3295,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3695,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ13">
         <v>0.91</v>
@@ -3904,7 +3913,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ14">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
@@ -4107,7 +4116,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15">
         <v>0.55</v>
@@ -4313,10 +4322,10 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ16">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR16">
         <v>2.2</v>
@@ -4441,7 +4450,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>2.57</v>
@@ -4522,7 +4531,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ17">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR17">
         <v>1.28</v>
@@ -4647,7 +4656,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4728,7 +4737,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ18">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR18">
         <v>1.61</v>
@@ -4853,7 +4862,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q19">
         <v>1.7</v>
@@ -5059,7 +5068,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5343,7 +5352,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ21">
         <v>1.73</v>
@@ -5471,7 +5480,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5552,7 +5561,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR22">
         <v>1.26</v>
@@ -5677,7 +5686,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -5961,7 +5970,7 @@
         <v>0.5</v>
       </c>
       <c r="AP24">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ24">
         <v>0.55</v>
@@ -6089,7 +6098,7 @@
         <v>82</v>
       </c>
       <c r="P25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q25">
         <v>3.9</v>
@@ -6167,7 +6176,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ25">
         <v>2.36</v>
@@ -6295,7 +6304,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6373,7 +6382,7 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ26">
         <v>0.91</v>
@@ -6707,7 +6716,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6913,7 +6922,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7119,7 +7128,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7325,7 +7334,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7403,7 +7412,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ31">
         <v>0.45</v>
@@ -7531,7 +7540,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q32">
         <v>2.1</v>
@@ -7609,10 +7618,10 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR32">
         <v>1.38</v>
@@ -7737,7 +7746,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7815,10 +7824,10 @@
         <v>0.5</v>
       </c>
       <c r="AP33">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ33">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR33">
         <v>2.34</v>
@@ -7943,7 +7952,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -8149,7 +8158,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8639,10 +8648,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR37">
         <v>1.31</v>
@@ -8767,7 +8776,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8848,7 +8857,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ38">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR38">
         <v>1.64</v>
@@ -8973,7 +8982,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q39">
         <v>4.36</v>
@@ -9179,7 +9188,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q40">
         <v>4.33</v>
@@ -9260,7 +9269,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ40">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR40">
         <v>1.56</v>
@@ -9385,7 +9394,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9875,7 +9884,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43">
         <v>0.36</v>
@@ -10209,7 +10218,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10415,7 +10424,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10621,7 +10630,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q47">
         <v>2.48</v>
@@ -10702,7 +10711,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ47">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR47">
         <v>1.58</v>
@@ -10827,7 +10836,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q48">
         <v>2.49</v>
@@ -10905,7 +10914,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ48">
         <v>1.09</v>
@@ -11239,7 +11248,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11317,10 +11326,10 @@
         <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ50">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR50">
         <v>1.39</v>
@@ -11523,10 +11532,10 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR51">
         <v>2.09</v>
@@ -11651,7 +11660,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q52">
         <v>3.22</v>
@@ -11938,7 +11947,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR53">
         <v>1.48</v>
@@ -12063,7 +12072,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54">
         <v>3.6</v>
@@ -12269,7 +12278,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12475,7 +12484,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12759,7 +12768,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ57">
         <v>0.91</v>
@@ -12887,7 +12896,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13093,7 +13102,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13171,10 +13180,10 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ59">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR59">
         <v>1.37</v>
@@ -13380,7 +13389,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ60">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR60">
         <v>1.4</v>
@@ -13505,7 +13514,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13583,7 +13592,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ61">
         <v>2.36</v>
@@ -13789,7 +13798,7 @@
         <v>0.75</v>
       </c>
       <c r="AP62">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ62">
         <v>0.36</v>
@@ -13917,7 +13926,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -13998,7 +14007,7 @@
         <v>1</v>
       </c>
       <c r="AQ63">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR63">
         <v>1.28</v>
@@ -14123,7 +14132,7 @@
         <v>129</v>
       </c>
       <c r="P64" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="Q64">
         <v>2.8</v>
@@ -14201,7 +14210,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ64">
         <v>0.45</v>
@@ -14407,10 +14416,10 @@
         <v>0.8</v>
       </c>
       <c r="AP65">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ65">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR65">
         <v>1.94</v>
@@ -15028,7 +15037,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ68">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR68">
         <v>1.28</v>
@@ -15231,7 +15240,7 @@
         <v>0.8</v>
       </c>
       <c r="AP69">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ69">
         <v>0.45</v>
@@ -15440,7 +15449,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ70">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR70">
         <v>1.54</v>
@@ -15849,10 +15858,10 @@
         <v>1.2</v>
       </c>
       <c r="AP72">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ72">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR72">
         <v>1.58</v>
@@ -16264,7 +16273,7 @@
         <v>1</v>
       </c>
       <c r="AQ74">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR74">
         <v>1.41</v>
@@ -16467,7 +16476,7 @@
         <v>0.83</v>
       </c>
       <c r="AP75">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ75">
         <v>0.91</v>
@@ -16879,7 +16888,7 @@
         <v>2.2</v>
       </c>
       <c r="AP77">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ77">
         <v>1.73</v>
@@ -17294,7 +17303,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ79">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR79">
         <v>1.8</v>
@@ -18736,7 +18745,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ86">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR86">
         <v>1.53</v>
@@ -19145,7 +19154,7 @@
         <v>0.57</v>
       </c>
       <c r="AP88">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ88">
         <v>0.55</v>
@@ -19273,7 +19282,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19351,7 +19360,7 @@
         <v>2.14</v>
       </c>
       <c r="AP89">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ89">
         <v>2.18</v>
@@ -19557,10 +19566,10 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR90">
         <v>1.54</v>
@@ -19969,10 +19978,10 @@
         <v>0.57</v>
       </c>
       <c r="AP92">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ92">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR92">
         <v>1.74</v>
@@ -20384,7 +20393,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ94">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR94">
         <v>1.72</v>
@@ -21002,7 +21011,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR97">
         <v>1.85</v>
@@ -21205,7 +21214,7 @@
         <v>1.88</v>
       </c>
       <c r="AP98">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ98">
         <v>2.18</v>
@@ -21411,10 +21420,10 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ99">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR99">
         <v>1.48</v>
@@ -21620,7 +21629,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR100">
         <v>1.45</v>
@@ -21823,7 +21832,7 @@
         <v>2.75</v>
       </c>
       <c r="AP101">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ101">
         <v>2.36</v>
@@ -22032,7 +22041,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ102">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR102">
         <v>1.31</v>
@@ -22647,7 +22656,7 @@
         <v>1.13</v>
       </c>
       <c r="AP105">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ105">
         <v>1.09</v>
@@ -23062,7 +23071,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ107">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR107">
         <v>1.92</v>
@@ -23677,7 +23686,7 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ110">
         <v>2.18</v>
@@ -23886,7 +23895,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ111">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR111">
         <v>1.66</v>
@@ -24092,7 +24101,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ112">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR112">
         <v>1.46</v>
@@ -24295,7 +24304,7 @@
         <v>1</v>
       </c>
       <c r="AP113">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ113">
         <v>1.09</v>
@@ -24501,7 +24510,7 @@
         <v>2.44</v>
       </c>
       <c r="AP114">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ114">
         <v>2.36</v>
@@ -24710,7 +24719,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR115">
         <v>1.54</v>
@@ -25737,10 +25746,10 @@
         <v>1.67</v>
       </c>
       <c r="AP120">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ120">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR120">
         <v>1.84</v>
@@ -25943,7 +25952,7 @@
         <v>1.2</v>
       </c>
       <c r="AP121">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ121">
         <v>1.09</v>
@@ -26152,7 +26161,7 @@
         <v>1</v>
       </c>
       <c r="AQ122">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR122">
         <v>1.44</v>
@@ -26561,10 +26570,10 @@
         <v>1.6</v>
       </c>
       <c r="AP124">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ124">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR124">
         <v>1.82</v>
@@ -26689,7 +26698,7 @@
         <v>167</v>
       </c>
       <c r="P125" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q125">
         <v>2.2</v>
@@ -26767,10 +26776,10 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ125">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR125">
         <v>1.74</v>
@@ -27307,7 +27316,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27594,7 +27603,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ129">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR129">
         <v>1.8</v>
@@ -28209,7 +28218,7 @@
         <v>1.6</v>
       </c>
       <c r="AP132">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ132">
         <v>1.73</v>
@@ -28494,6 +28503,830 @@
       </c>
       <c r="BP133">
         <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7844403</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45724.47916666666</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" t="s">
+        <v>81</v>
+      </c>
+      <c r="H134" t="s">
+        <v>71</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134" t="s">
+        <v>82</v>
+      </c>
+      <c r="P134" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q134">
+        <v>2.17</v>
+      </c>
+      <c r="R134">
+        <v>2.4</v>
+      </c>
+      <c r="S134">
+        <v>5.05</v>
+      </c>
+      <c r="T134">
+        <v>1.32</v>
+      </c>
+      <c r="U134">
+        <v>3.26</v>
+      </c>
+      <c r="V134">
+        <v>2.57</v>
+      </c>
+      <c r="W134">
+        <v>1.48</v>
+      </c>
+      <c r="X134">
+        <v>5.8</v>
+      </c>
+      <c r="Y134">
+        <v>1.12</v>
+      </c>
+      <c r="Z134">
+        <v>1.67</v>
+      </c>
+      <c r="AA134">
+        <v>3.93</v>
+      </c>
+      <c r="AB134">
+        <v>4.6</v>
+      </c>
+      <c r="AC134">
+        <v>1.01</v>
+      </c>
+      <c r="AD134">
+        <v>11</v>
+      </c>
+      <c r="AE134">
+        <v>1.2</v>
+      </c>
+      <c r="AF134">
+        <v>4</v>
+      </c>
+      <c r="AG134">
+        <v>1.67</v>
+      </c>
+      <c r="AH134">
+        <v>2</v>
+      </c>
+      <c r="AI134">
+        <v>1.71</v>
+      </c>
+      <c r="AJ134">
+        <v>2.08</v>
+      </c>
+      <c r="AK134">
+        <v>1.16</v>
+      </c>
+      <c r="AL134">
+        <v>1.23</v>
+      </c>
+      <c r="AM134">
+        <v>2.18</v>
+      </c>
+      <c r="AN134">
+        <v>2.36</v>
+      </c>
+      <c r="AO134">
+        <v>1.18</v>
+      </c>
+      <c r="AP134">
+        <v>2.25</v>
+      </c>
+      <c r="AQ134">
+        <v>1.17</v>
+      </c>
+      <c r="AR134">
+        <v>1.78</v>
+      </c>
+      <c r="AS134">
+        <v>1.47</v>
+      </c>
+      <c r="AT134">
+        <v>3.25</v>
+      </c>
+      <c r="AU134">
+        <v>3</v>
+      </c>
+      <c r="AV134">
+        <v>3</v>
+      </c>
+      <c r="AW134">
+        <v>9</v>
+      </c>
+      <c r="AX134">
+        <v>3</v>
+      </c>
+      <c r="AY134">
+        <v>12</v>
+      </c>
+      <c r="AZ134">
+        <v>6</v>
+      </c>
+      <c r="BA134">
+        <v>9</v>
+      </c>
+      <c r="BB134">
+        <v>3</v>
+      </c>
+      <c r="BC134">
+        <v>12</v>
+      </c>
+      <c r="BD134">
+        <v>1.59</v>
+      </c>
+      <c r="BE134">
+        <v>8.5</v>
+      </c>
+      <c r="BF134">
+        <v>2.78</v>
+      </c>
+      <c r="BG134">
+        <v>1.19</v>
+      </c>
+      <c r="BH134">
+        <v>3.98</v>
+      </c>
+      <c r="BI134">
+        <v>1.38</v>
+      </c>
+      <c r="BJ134">
+        <v>2.82</v>
+      </c>
+      <c r="BK134">
+        <v>1.63</v>
+      </c>
+      <c r="BL134">
+        <v>2.18</v>
+      </c>
+      <c r="BM134">
+        <v>2.02</v>
+      </c>
+      <c r="BN134">
+        <v>1.74</v>
+      </c>
+      <c r="BO134">
+        <v>2.53</v>
+      </c>
+      <c r="BP134">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7844404</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45724.47916666666</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135" t="s">
+        <v>76</v>
+      </c>
+      <c r="H135" t="s">
+        <v>70</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>2</v>
+      </c>
+      <c r="N135">
+        <v>2</v>
+      </c>
+      <c r="O135" t="s">
+        <v>82</v>
+      </c>
+      <c r="P135" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q135">
+        <v>3.27</v>
+      </c>
+      <c r="R135">
+        <v>2.09</v>
+      </c>
+      <c r="S135">
+        <v>3.48</v>
+      </c>
+      <c r="T135">
+        <v>1.44</v>
+      </c>
+      <c r="U135">
+        <v>2.69</v>
+      </c>
+      <c r="V135">
+        <v>3.23</v>
+      </c>
+      <c r="W135">
+        <v>1.32</v>
+      </c>
+      <c r="X135">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y135">
+        <v>1.05</v>
+      </c>
+      <c r="Z135">
+        <v>2.5</v>
+      </c>
+      <c r="AA135">
+        <v>3.15</v>
+      </c>
+      <c r="AB135">
+        <v>2.84</v>
+      </c>
+      <c r="AC135">
+        <v>1.05</v>
+      </c>
+      <c r="AD135">
+        <v>8</v>
+      </c>
+      <c r="AE135">
+        <v>1.33</v>
+      </c>
+      <c r="AF135">
+        <v>3</v>
+      </c>
+      <c r="AG135">
+        <v>1.89</v>
+      </c>
+      <c r="AH135">
+        <v>1.85</v>
+      </c>
+      <c r="AI135">
+        <v>1.87</v>
+      </c>
+      <c r="AJ135">
+        <v>1.89</v>
+      </c>
+      <c r="AK135">
+        <v>1.43</v>
+      </c>
+      <c r="AL135">
+        <v>1.32</v>
+      </c>
+      <c r="AM135">
+        <v>1.48</v>
+      </c>
+      <c r="AN135">
+        <v>1.18</v>
+      </c>
+      <c r="AO135">
+        <v>0.55</v>
+      </c>
+      <c r="AP135">
+        <v>1.08</v>
+      </c>
+      <c r="AQ135">
+        <v>0.75</v>
+      </c>
+      <c r="AR135">
+        <v>1.39</v>
+      </c>
+      <c r="AS135">
+        <v>1.34</v>
+      </c>
+      <c r="AT135">
+        <v>2.73</v>
+      </c>
+      <c r="AU135">
+        <v>3</v>
+      </c>
+      <c r="AV135">
+        <v>4</v>
+      </c>
+      <c r="AW135">
+        <v>4</v>
+      </c>
+      <c r="AX135">
+        <v>5</v>
+      </c>
+      <c r="AY135">
+        <v>7</v>
+      </c>
+      <c r="AZ135">
+        <v>9</v>
+      </c>
+      <c r="BA135">
+        <v>9</v>
+      </c>
+      <c r="BB135">
+        <v>4</v>
+      </c>
+      <c r="BC135">
+        <v>13</v>
+      </c>
+      <c r="BD135">
+        <v>2.33</v>
+      </c>
+      <c r="BE135">
+        <v>8</v>
+      </c>
+      <c r="BF135">
+        <v>1.82</v>
+      </c>
+      <c r="BG135">
+        <v>1.23</v>
+      </c>
+      <c r="BH135">
+        <v>3.6</v>
+      </c>
+      <c r="BI135">
+        <v>1.44</v>
+      </c>
+      <c r="BJ135">
+        <v>2.58</v>
+      </c>
+      <c r="BK135">
+        <v>1.74</v>
+      </c>
+      <c r="BL135">
+        <v>2.02</v>
+      </c>
+      <c r="BM135">
+        <v>2.19</v>
+      </c>
+      <c r="BN135">
+        <v>1.63</v>
+      </c>
+      <c r="BO135">
+        <v>2.77</v>
+      </c>
+      <c r="BP135">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7844405</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45724.47916666666</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136" t="s">
+        <v>75</v>
+      </c>
+      <c r="H136" t="s">
+        <v>72</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>1</v>
+      </c>
+      <c r="O136" t="s">
+        <v>82</v>
+      </c>
+      <c r="P136" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q136">
+        <v>2.5</v>
+      </c>
+      <c r="R136">
+        <v>2.25</v>
+      </c>
+      <c r="S136">
+        <v>4.39</v>
+      </c>
+      <c r="T136">
+        <v>1.36</v>
+      </c>
+      <c r="U136">
+        <v>3.01</v>
+      </c>
+      <c r="V136">
+        <v>2.84</v>
+      </c>
+      <c r="W136">
+        <v>1.4</v>
+      </c>
+      <c r="X136">
+        <v>6.7</v>
+      </c>
+      <c r="Y136">
+        <v>1.09</v>
+      </c>
+      <c r="Z136">
+        <v>1.95</v>
+      </c>
+      <c r="AA136">
+        <v>3.47</v>
+      </c>
+      <c r="AB136">
+        <v>3.73</v>
+      </c>
+      <c r="AC136">
+        <v>1.03</v>
+      </c>
+      <c r="AD136">
+        <v>9</v>
+      </c>
+      <c r="AE136">
+        <v>1.25</v>
+      </c>
+      <c r="AF136">
+        <v>3.6</v>
+      </c>
+      <c r="AG136">
+        <v>1.89</v>
+      </c>
+      <c r="AH136">
+        <v>1.85</v>
+      </c>
+      <c r="AI136">
+        <v>1.75</v>
+      </c>
+      <c r="AJ136">
+        <v>2.03</v>
+      </c>
+      <c r="AK136">
+        <v>1.25</v>
+      </c>
+      <c r="AL136">
+        <v>1.27</v>
+      </c>
+      <c r="AM136">
+        <v>1.85</v>
+      </c>
+      <c r="AN136">
+        <v>1.36</v>
+      </c>
+      <c r="AO136">
+        <v>1</v>
+      </c>
+      <c r="AP136">
+        <v>1.25</v>
+      </c>
+      <c r="AQ136">
+        <v>1.17</v>
+      </c>
+      <c r="AR136">
+        <v>1.47</v>
+      </c>
+      <c r="AS136">
+        <v>1.3</v>
+      </c>
+      <c r="AT136">
+        <v>2.77</v>
+      </c>
+      <c r="AU136">
+        <v>5</v>
+      </c>
+      <c r="AV136">
+        <v>2</v>
+      </c>
+      <c r="AW136">
+        <v>8</v>
+      </c>
+      <c r="AX136">
+        <v>3</v>
+      </c>
+      <c r="AY136">
+        <v>13</v>
+      </c>
+      <c r="AZ136">
+        <v>5</v>
+      </c>
+      <c r="BA136">
+        <v>4</v>
+      </c>
+      <c r="BB136">
+        <v>3</v>
+      </c>
+      <c r="BC136">
+        <v>7</v>
+      </c>
+      <c r="BD136">
+        <v>1.51</v>
+      </c>
+      <c r="BE136">
+        <v>8.5</v>
+      </c>
+      <c r="BF136">
+        <v>3.07</v>
+      </c>
+      <c r="BG136">
+        <v>1.23</v>
+      </c>
+      <c r="BH136">
+        <v>3.6</v>
+      </c>
+      <c r="BI136">
+        <v>1.44</v>
+      </c>
+      <c r="BJ136">
+        <v>2.58</v>
+      </c>
+      <c r="BK136">
+        <v>1.74</v>
+      </c>
+      <c r="BL136">
+        <v>2.02</v>
+      </c>
+      <c r="BM136">
+        <v>2.19</v>
+      </c>
+      <c r="BN136">
+        <v>1.63</v>
+      </c>
+      <c r="BO136">
+        <v>2.77</v>
+      </c>
+      <c r="BP136">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7844406</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45724.58333333334</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="G137" t="s">
+        <v>74</v>
+      </c>
+      <c r="H137" t="s">
+        <v>79</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="M137">
+        <v>1</v>
+      </c>
+      <c r="N137">
+        <v>2</v>
+      </c>
+      <c r="O137" t="s">
+        <v>173</v>
+      </c>
+      <c r="P137" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q137">
+        <v>2.68</v>
+      </c>
+      <c r="R137">
+        <v>2.18</v>
+      </c>
+      <c r="S137">
+        <v>4.16</v>
+      </c>
+      <c r="T137">
+        <v>1.39</v>
+      </c>
+      <c r="U137">
+        <v>2.86</v>
+      </c>
+      <c r="V137">
+        <v>3</v>
+      </c>
+      <c r="W137">
+        <v>1.36</v>
+      </c>
+      <c r="X137">
+        <v>7.3</v>
+      </c>
+      <c r="Y137">
+        <v>1.07</v>
+      </c>
+      <c r="Z137">
+        <v>2.11</v>
+      </c>
+      <c r="AA137">
+        <v>3.18</v>
+      </c>
+      <c r="AB137">
+        <v>3.56</v>
+      </c>
+      <c r="AC137">
+        <v>1.05</v>
+      </c>
+      <c r="AD137">
+        <v>8</v>
+      </c>
+      <c r="AE137">
+        <v>1.29</v>
+      </c>
+      <c r="AF137">
+        <v>3.3</v>
+      </c>
+      <c r="AG137">
+        <v>1.95</v>
+      </c>
+      <c r="AH137">
+        <v>1.79</v>
+      </c>
+      <c r="AI137">
+        <v>1.81</v>
+      </c>
+      <c r="AJ137">
+        <v>1.95</v>
+      </c>
+      <c r="AK137">
+        <v>1.28</v>
+      </c>
+      <c r="AL137">
+        <v>1.29</v>
+      </c>
+      <c r="AM137">
+        <v>1.72</v>
+      </c>
+      <c r="AN137">
+        <v>1.82</v>
+      </c>
+      <c r="AO137">
+        <v>1.55</v>
+      </c>
+      <c r="AP137">
+        <v>1.75</v>
+      </c>
+      <c r="AQ137">
+        <v>1.5</v>
+      </c>
+      <c r="AR137">
+        <v>1.74</v>
+      </c>
+      <c r="AS137">
+        <v>1.48</v>
+      </c>
+      <c r="AT137">
+        <v>3.22</v>
+      </c>
+      <c r="AU137">
+        <v>6</v>
+      </c>
+      <c r="AV137">
+        <v>2</v>
+      </c>
+      <c r="AW137">
+        <v>9</v>
+      </c>
+      <c r="AX137">
+        <v>13</v>
+      </c>
+      <c r="AY137">
+        <v>16</v>
+      </c>
+      <c r="AZ137">
+        <v>17</v>
+      </c>
+      <c r="BA137">
+        <v>7</v>
+      </c>
+      <c r="BB137">
+        <v>7</v>
+      </c>
+      <c r="BC137">
+        <v>14</v>
+      </c>
+      <c r="BD137">
+        <v>1.91</v>
+      </c>
+      <c r="BE137">
+        <v>7.5</v>
+      </c>
+      <c r="BF137">
+        <v>2.2</v>
+      </c>
+      <c r="BG137">
+        <v>1.43</v>
+      </c>
+      <c r="BH137">
+        <v>2.63</v>
+      </c>
+      <c r="BI137">
+        <v>1.74</v>
+      </c>
+      <c r="BJ137">
+        <v>2.02</v>
+      </c>
+      <c r="BK137">
+        <v>2.22</v>
+      </c>
+      <c r="BL137">
+        <v>1.62</v>
+      </c>
+      <c r="BM137">
+        <v>2.85</v>
+      </c>
+      <c r="BN137">
+        <v>1.37</v>
+      </c>
+      <c r="BO137">
+        <v>3.9</v>
+      </c>
+      <c r="BP137">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="247">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,10 +502,10 @@
     <t>['27']</t>
   </si>
   <si>
-    <t>['64', '69']</t>
+    <t>['43', '45+2', '67', '90+2']</t>
   </si>
   <si>
-    <t>['43', '45+2', '67', '90+2']</t>
+    <t>['64', '69']</t>
   </si>
   <si>
     <t>['73']</t>
@@ -536,6 +536,12 @@
   </si>
   <si>
     <t>['47']</t>
+  </si>
+  <si>
+    <t>['32', '57']</t>
+  </si>
+  <si>
+    <t>['29', '39', '90+3']</t>
   </si>
   <si>
     <t>['5', '42', '80', '90+2']</t>
@@ -743,6 +749,12 @@
   </si>
   <si>
     <t>['34']</t>
+  </si>
+  <si>
+    <t>['44', '45+4', '51']</t>
+  </si>
+  <si>
+    <t>['4', '82']</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP137"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1441,7 +1453,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ2">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1772,7 +1784,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1853,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1978,7 +1990,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2056,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ5">
         <v>1.5</v>
@@ -2596,7 +2608,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -2880,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ9">
         <v>1.09</v>
@@ -3707,7 +3719,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ13">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3910,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ14">
         <v>1.17</v>
@@ -4450,7 +4462,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q17">
         <v>2.57</v>
@@ -4656,7 +4668,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4862,7 +4874,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q19">
         <v>1.7</v>
@@ -5068,7 +5080,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5146,7 +5158,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ20">
         <v>0.36</v>
@@ -5480,7 +5492,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5558,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ22">
         <v>1.17</v>
@@ -5686,7 +5698,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -6098,7 +6110,7 @@
         <v>82</v>
       </c>
       <c r="P25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q25">
         <v>3.9</v>
@@ -6179,7 +6191,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ25">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR25">
         <v>1.52</v>
@@ -6304,7 +6316,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6385,7 +6397,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ26">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR26">
         <v>1.13</v>
@@ -6716,7 +6728,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6797,7 +6809,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR28">
         <v>1.13</v>
@@ -6922,7 +6934,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7128,7 +7140,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7334,7 +7346,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7540,7 +7552,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q32">
         <v>2.1</v>
@@ -7746,7 +7758,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7952,7 +7964,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -8158,7 +8170,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8239,7 +8251,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ35">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR35">
         <v>2.59</v>
@@ -8442,7 +8454,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ36">
         <v>2.18</v>
@@ -8776,7 +8788,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8854,7 +8866,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ38">
         <v>1.5</v>
@@ -8982,7 +8994,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q39">
         <v>4.36</v>
@@ -9060,7 +9072,7 @@
         <v>1.67</v>
       </c>
       <c r="AP39">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ39">
         <v>1.73</v>
@@ -9188,7 +9200,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q40">
         <v>4.33</v>
@@ -9394,7 +9406,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -10093,7 +10105,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ44">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10218,7 +10230,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10424,7 +10436,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10505,7 +10517,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ46">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR46">
         <v>1.09</v>
@@ -10630,7 +10642,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q47">
         <v>2.48</v>
@@ -10708,7 +10720,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ47">
         <v>1.17</v>
@@ -10836,7 +10848,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q48">
         <v>2.49</v>
@@ -11248,7 +11260,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11660,7 +11672,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q52">
         <v>3.22</v>
@@ -11738,7 +11750,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ52">
         <v>0.45</v>
@@ -12072,7 +12084,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q54">
         <v>3.6</v>
@@ -12278,7 +12290,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12484,7 +12496,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12771,7 +12783,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ57">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR57">
         <v>1.64</v>
@@ -12896,7 +12908,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13102,7 +13114,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13386,7 +13398,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ60">
         <v>0.75</v>
@@ -13514,7 +13526,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13595,7 +13607,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ61">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR61">
         <v>1.75</v>
@@ -13926,7 +13938,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -14338,7 +14350,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q65">
         <v>1.9</v>
@@ -14544,7 +14556,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14750,7 +14762,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14828,7 +14840,7 @@
         <v>1.8</v>
       </c>
       <c r="AP67">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ67">
         <v>2.18</v>
@@ -14956,7 +14968,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15162,7 +15174,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q69">
         <v>2</v>
@@ -15574,7 +15586,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -15655,7 +15667,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ71">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR71">
         <v>1.47</v>
@@ -16064,7 +16076,7 @@
         <v>0.5</v>
       </c>
       <c r="AP73">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ73">
         <v>0.55</v>
@@ -16192,7 +16204,7 @@
         <v>82</v>
       </c>
       <c r="P74" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16398,7 +16410,7 @@
         <v>137</v>
       </c>
       <c r="P75" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q75">
         <v>1.83</v>
@@ -16479,7 +16491,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ75">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR75">
         <v>1.7</v>
@@ -16604,7 +16616,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16685,7 +16697,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ76">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR76">
         <v>1.55</v>
@@ -17506,7 +17518,7 @@
         <v>0.67</v>
       </c>
       <c r="AP80">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ80">
         <v>0.45</v>
@@ -17634,7 +17646,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17840,7 +17852,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -18536,10 +18548,10 @@
         <v>3</v>
       </c>
       <c r="AP85">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ85">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR85">
         <v>1.4</v>
@@ -18664,7 +18676,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18951,7 +18963,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ87">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR87">
         <v>1.54</v>
@@ -19076,7 +19088,7 @@
         <v>143</v>
       </c>
       <c r="P88" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q88">
         <v>2.5</v>
@@ -19282,7 +19294,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19488,7 +19500,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19694,7 +19706,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -19772,7 +19784,7 @@
         <v>1.71</v>
       </c>
       <c r="AP91">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ91">
         <v>1.73</v>
@@ -20106,7 +20118,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -21136,7 +21148,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21342,7 +21354,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21754,7 +21766,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21835,7 +21847,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ101">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR101">
         <v>1.8</v>
@@ -21960,7 +21972,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -22038,7 +22050,7 @@
         <v>0.5</v>
       </c>
       <c r="AP102">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ102">
         <v>0.75</v>
@@ -22166,7 +22178,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -22862,10 +22874,10 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ106">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR106">
         <v>1.51</v>
@@ -23154,7 +23166,7 @@
         <v>107</v>
       </c>
       <c r="B108">
-        <v>7580433</v>
+        <v>7580431</v>
       </c>
       <c r="C108" t="s">
         <v>68</v>
@@ -23169,142 +23181,142 @@
         <v>18</v>
       </c>
       <c r="G108" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H108" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M108">
         <v>0</v>
       </c>
       <c r="N108">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O108" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="P108" t="s">
         <v>82</v>
       </c>
       <c r="Q108">
-        <v>3.28</v>
+        <v>4.55</v>
       </c>
       <c r="R108">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="S108">
-        <v>2.97</v>
+        <v>2.29</v>
       </c>
       <c r="T108">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="U108">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="V108">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="W108">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X108">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y108">
         <v>1.11</v>
       </c>
       <c r="Z108">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA108">
+        <v>3.1</v>
+      </c>
+      <c r="AB108">
+        <v>1.84</v>
+      </c>
+      <c r="AC108">
+        <v>1.01</v>
+      </c>
+      <c r="AD108">
+        <v>11</v>
+      </c>
+      <c r="AE108">
+        <v>1.19</v>
+      </c>
+      <c r="AF108">
+        <v>3.64</v>
+      </c>
+      <c r="AG108">
+        <v>1.81</v>
+      </c>
+      <c r="AH108">
+        <v>1.97</v>
+      </c>
+      <c r="AI108">
+        <v>1.7</v>
+      </c>
+      <c r="AJ108">
+        <v>2.03</v>
+      </c>
+      <c r="AK108">
+        <v>1.99</v>
+      </c>
+      <c r="AL108">
+        <v>1.25</v>
+      </c>
+      <c r="AM108">
+        <v>1.21</v>
+      </c>
+      <c r="AN108">
+        <v>1</v>
+      </c>
+      <c r="AO108">
+        <v>1.88</v>
+      </c>
+      <c r="AP108">
+        <v>1.18</v>
+      </c>
+      <c r="AQ108">
+        <v>1.73</v>
+      </c>
+      <c r="AR108">
+        <v>1.59</v>
+      </c>
+      <c r="AS108">
+        <v>1.35</v>
+      </c>
+      <c r="AT108">
+        <v>2.94</v>
+      </c>
+      <c r="AU108">
+        <v>6</v>
+      </c>
+      <c r="AV108">
         <v>3</v>
       </c>
-      <c r="AB108">
-        <v>2.29</v>
-      </c>
-      <c r="AC108">
-        <v>1.02</v>
-      </c>
-      <c r="AD108">
-        <v>10</v>
-      </c>
-      <c r="AE108">
-        <v>1.22</v>
-      </c>
-      <c r="AF108">
-        <v>3.35</v>
-      </c>
-      <c r="AG108">
-        <v>1.82</v>
-      </c>
-      <c r="AH108">
-        <v>1.96</v>
-      </c>
-      <c r="AI108">
-        <v>1.65</v>
-      </c>
-      <c r="AJ108">
-        <v>2.11</v>
-      </c>
-      <c r="AK108">
-        <v>1.52</v>
-      </c>
-      <c r="AL108">
-        <v>1.28</v>
-      </c>
-      <c r="AM108">
-        <v>1.44</v>
-      </c>
-      <c r="AN108">
-        <v>0.5</v>
-      </c>
-      <c r="AO108">
-        <v>0.5</v>
-      </c>
-      <c r="AP108">
-        <v>1</v>
-      </c>
-      <c r="AQ108">
-        <v>0.36</v>
-      </c>
-      <c r="AR108">
-        <v>1.38</v>
-      </c>
-      <c r="AS108">
-        <v>1.16</v>
-      </c>
-      <c r="AT108">
-        <v>2.54</v>
-      </c>
-      <c r="AU108">
-        <v>9</v>
-      </c>
-      <c r="AV108">
-        <v>8</v>
-      </c>
       <c r="AW108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX108">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AY108">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ108">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA108">
         <v>7</v>
@@ -23316,43 +23328,43 @@
         <v>11</v>
       </c>
       <c r="BD108">
+        <v>2.61</v>
+      </c>
+      <c r="BE108">
+        <v>8.1</v>
+      </c>
+      <c r="BF108">
+        <v>1.67</v>
+      </c>
+      <c r="BG108">
+        <v>1.29</v>
+      </c>
+      <c r="BH108">
+        <v>3.35</v>
+      </c>
+      <c r="BI108">
+        <v>1.53</v>
+      </c>
+      <c r="BJ108">
+        <v>2.41</v>
+      </c>
+      <c r="BK108">
+        <v>1.88</v>
+      </c>
+      <c r="BL108">
         <v>1.92</v>
       </c>
-      <c r="BE108">
-        <v>6.95</v>
-      </c>
-      <c r="BF108">
-        <v>2.27</v>
-      </c>
-      <c r="BG108">
-        <v>1.25</v>
-      </c>
-      <c r="BH108">
-        <v>3.68</v>
-      </c>
-      <c r="BI108">
-        <v>1.46</v>
-      </c>
-      <c r="BJ108">
-        <v>2.6</v>
-      </c>
-      <c r="BK108">
-        <v>1.76</v>
-      </c>
-      <c r="BL108">
-        <v>2</v>
-      </c>
       <c r="BM108">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="BN108">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="BO108">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="BP108">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="109" spans="1:68">
@@ -23360,7 +23372,7 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>7580431</v>
+        <v>7580433</v>
       </c>
       <c r="C109" t="s">
         <v>68</v>
@@ -23375,142 +23387,142 @@
         <v>18</v>
       </c>
       <c r="G109" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H109" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M109">
         <v>0</v>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O109" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="P109" t="s">
         <v>82</v>
       </c>
       <c r="Q109">
-        <v>4.55</v>
+        <v>3.28</v>
       </c>
       <c r="R109">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="S109">
-        <v>2.29</v>
+        <v>2.97</v>
       </c>
       <c r="T109">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="U109">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="V109">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="W109">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X109">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y109">
         <v>1.11</v>
       </c>
       <c r="Z109">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AA109">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB109">
-        <v>1.84</v>
+        <v>2.29</v>
       </c>
       <c r="AC109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD109">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE109">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF109">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="AG109">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AH109">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AI109">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AJ109">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AK109">
-        <v>1.99</v>
+        <v>1.52</v>
       </c>
       <c r="AL109">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AM109">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AN109">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO109">
-        <v>1.88</v>
+        <v>0.5</v>
       </c>
       <c r="AP109">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AQ109">
-        <v>1.73</v>
+        <v>0.36</v>
       </c>
       <c r="AR109">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AS109">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AT109">
-        <v>2.94</v>
+        <v>2.54</v>
       </c>
       <c r="AU109">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AV109">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AW109">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX109">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AY109">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AZ109">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA109">
         <v>7</v>
@@ -23522,43 +23534,43 @@
         <v>11</v>
       </c>
       <c r="BD109">
-        <v>2.61</v>
+        <v>1.92</v>
       </c>
       <c r="BE109">
-        <v>8.1</v>
+        <v>6.95</v>
       </c>
       <c r="BF109">
-        <v>1.67</v>
+        <v>2.27</v>
       </c>
       <c r="BG109">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BH109">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="BI109">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="BJ109">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="BK109">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="BL109">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="BM109">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="BN109">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="BO109">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="BP109">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="110" spans="1:68">
@@ -23608,7 +23620,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23814,7 +23826,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -24020,7 +24032,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24226,7 +24238,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24432,7 +24444,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24513,7 +24525,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ114">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR114">
         <v>1.52</v>
@@ -24716,7 +24728,7 @@
         <v>1.11</v>
       </c>
       <c r="AP115">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ115">
         <v>1.17</v>
@@ -24802,7 +24814,7 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>7580447</v>
+        <v>7580443</v>
       </c>
       <c r="C116" t="s">
         <v>68</v>
@@ -24817,124 +24829,124 @@
         <v>20</v>
       </c>
       <c r="G116" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H116" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N116">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O116" t="s">
         <v>162</v>
       </c>
       <c r="P116" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="Q116">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="R116">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S116">
-        <v>4.15</v>
+        <v>4.9</v>
       </c>
       <c r="T116">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="U116">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="V116">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="W116">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="X116">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="Y116">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z116">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="AA116">
-        <v>3.93</v>
+        <v>3.34</v>
       </c>
       <c r="AB116">
-        <v>4.8</v>
+        <v>3.47</v>
       </c>
       <c r="AC116">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AD116">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE116">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AF116">
-        <v>3.78</v>
+        <v>3.22</v>
       </c>
       <c r="AG116">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH116">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AI116">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AJ116">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AK116">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AL116">
         <v>1.26</v>
       </c>
       <c r="AM116">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AN116">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AO116">
-        <v>0.5600000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="AP116">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ116">
-        <v>0.55</v>
+        <v>0.36</v>
       </c>
       <c r="AR116">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AS116">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AT116">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="AU116">
         <v>9</v>
@@ -24943,64 +24955,64 @@
         <v>2</v>
       </c>
       <c r="AW116">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX116">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AY116">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ116">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BA116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB116">
         <v>0</v>
       </c>
       <c r="BC116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD116">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="BE116">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="BF116">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="BG116">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BH116">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="BI116">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="BJ116">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="BK116">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="BL116">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="BM116">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="BN116">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="BO116">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="BP116">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="117" spans="1:68">
@@ -25008,7 +25020,7 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>7580443</v>
+        <v>7580447</v>
       </c>
       <c r="C117" t="s">
         <v>68</v>
@@ -25023,124 +25035,124 @@
         <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H117" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L117">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N117">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O117" t="s">
         <v>163</v>
       </c>
       <c r="P117" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="Q117">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="R117">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S117">
-        <v>4.9</v>
+        <v>4.15</v>
       </c>
       <c r="T117">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="U117">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="V117">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="W117">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="X117">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y117">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z117">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="AA117">
-        <v>3.34</v>
+        <v>3.93</v>
       </c>
       <c r="AB117">
-        <v>3.47</v>
+        <v>4.8</v>
       </c>
       <c r="AC117">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AD117">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AE117">
+        <v>1.19</v>
+      </c>
+      <c r="AF117">
+        <v>3.78</v>
+      </c>
+      <c r="AG117">
+        <v>1.8</v>
+      </c>
+      <c r="AH117">
+        <v>1.94</v>
+      </c>
+      <c r="AI117">
+        <v>1.66</v>
+      </c>
+      <c r="AJ117">
+        <v>2.09</v>
+      </c>
+      <c r="AK117">
         <v>1.26</v>
-      </c>
-      <c r="AF117">
-        <v>3.22</v>
-      </c>
-      <c r="AG117">
-        <v>1.95</v>
-      </c>
-      <c r="AH117">
-        <v>1.79</v>
-      </c>
-      <c r="AI117">
-        <v>1.85</v>
-      </c>
-      <c r="AJ117">
-        <v>1.85</v>
-      </c>
-      <c r="AK117">
-        <v>1.18</v>
       </c>
       <c r="AL117">
         <v>1.26</v>
       </c>
       <c r="AM117">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AN117">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AO117">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP117">
         <v>1.55</v>
       </c>
       <c r="AQ117">
-        <v>0.36</v>
+        <v>0.55</v>
       </c>
       <c r="AR117">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="AS117">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AT117">
-        <v>2.61</v>
+        <v>2.9</v>
       </c>
       <c r="AU117">
         <v>9</v>
@@ -25149,64 +25161,64 @@
         <v>2</v>
       </c>
       <c r="AW117">
+        <v>8</v>
+      </c>
+      <c r="AX117">
+        <v>8</v>
+      </c>
+      <c r="AY117">
+        <v>17</v>
+      </c>
+      <c r="AZ117">
         <v>10</v>
       </c>
-      <c r="AX117">
-        <v>0</v>
-      </c>
-      <c r="AY117">
-        <v>19</v>
-      </c>
-      <c r="AZ117">
-        <v>2</v>
-      </c>
       <c r="BA117">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB117">
         <v>0</v>
       </c>
       <c r="BC117">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD117">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="BE117">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="BF117">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="BG117">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BH117">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="BI117">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="BJ117">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="BK117">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="BL117">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="BM117">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="BN117">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="BO117">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="BP117">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="118" spans="1:68">
@@ -25256,7 +25268,7 @@
         <v>123</v>
       </c>
       <c r="P118" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q118">
         <v>1.74</v>
@@ -25337,7 +25349,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ118">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR118">
         <v>1.86</v>
@@ -26286,7 +26298,7 @@
         <v>166</v>
       </c>
       <c r="P123" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q123">
         <v>6.04</v>
@@ -26364,10 +26376,10 @@
         <v>2.5</v>
       </c>
       <c r="AP123">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ123">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -26698,7 +26710,7 @@
         <v>167</v>
       </c>
       <c r="P125" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q125">
         <v>2.2</v>
@@ -27316,7 +27328,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27522,7 +27534,7 @@
         <v>169</v>
       </c>
       <c r="P129" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q129">
         <v>2</v>
@@ -27728,7 +27740,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q130">
         <v>2.28</v>
@@ -27806,10 +27818,10 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ130">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR130">
         <v>1.48</v>
@@ -28140,7 +28152,7 @@
         <v>172</v>
       </c>
       <c r="P132" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q132">
         <v>4.5</v>
@@ -28758,7 +28770,7 @@
         <v>82</v>
       </c>
       <c r="P135" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q135">
         <v>3.27</v>
@@ -28964,7 +28976,7 @@
         <v>82</v>
       </c>
       <c r="P136" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29170,7 +29182,7 @@
         <v>173</v>
       </c>
       <c r="P137" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q137">
         <v>2.68</v>
@@ -29327,6 +29339,418 @@
       </c>
       <c r="BP137">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7844407</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45725.47916666666</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138" t="s">
+        <v>73</v>
+      </c>
+      <c r="H138" t="s">
+        <v>78</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>2</v>
+      </c>
+      <c r="K138">
+        <v>3</v>
+      </c>
+      <c r="L138">
+        <v>2</v>
+      </c>
+      <c r="M138">
+        <v>3</v>
+      </c>
+      <c r="N138">
+        <v>5</v>
+      </c>
+      <c r="O138" t="s">
+        <v>174</v>
+      </c>
+      <c r="P138" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q138">
+        <v>4.2</v>
+      </c>
+      <c r="R138">
+        <v>2.3</v>
+      </c>
+      <c r="S138">
+        <v>2.3</v>
+      </c>
+      <c r="T138">
+        <v>1.35</v>
+      </c>
+      <c r="U138">
+        <v>3.07</v>
+      </c>
+      <c r="V138">
+        <v>2.39</v>
+      </c>
+      <c r="W138">
+        <v>1.54</v>
+      </c>
+      <c r="X138">
+        <v>5.3</v>
+      </c>
+      <c r="Y138">
+        <v>1.13</v>
+      </c>
+      <c r="Z138">
+        <v>3.97</v>
+      </c>
+      <c r="AA138">
+        <v>3.75</v>
+      </c>
+      <c r="AB138">
+        <v>1.81</v>
+      </c>
+      <c r="AC138">
+        <v>1.01</v>
+      </c>
+      <c r="AD138">
+        <v>13</v>
+      </c>
+      <c r="AE138">
+        <v>1.14</v>
+      </c>
+      <c r="AF138">
+        <v>4.8</v>
+      </c>
+      <c r="AG138">
+        <v>1.6</v>
+      </c>
+      <c r="AH138">
+        <v>2.15</v>
+      </c>
+      <c r="AI138">
+        <v>1.53</v>
+      </c>
+      <c r="AJ138">
+        <v>2.38</v>
+      </c>
+      <c r="AK138">
+        <v>1.99</v>
+      </c>
+      <c r="AL138">
+        <v>1.23</v>
+      </c>
+      <c r="AM138">
+        <v>1.23</v>
+      </c>
+      <c r="AN138">
+        <v>1.55</v>
+      </c>
+      <c r="AO138">
+        <v>2.36</v>
+      </c>
+      <c r="AP138">
+        <v>1.42</v>
+      </c>
+      <c r="AQ138">
+        <v>2.42</v>
+      </c>
+      <c r="AR138">
+        <v>1.56</v>
+      </c>
+      <c r="AS138">
+        <v>1.62</v>
+      </c>
+      <c r="AT138">
+        <v>3.18</v>
+      </c>
+      <c r="AU138">
+        <v>4</v>
+      </c>
+      <c r="AV138">
+        <v>11</v>
+      </c>
+      <c r="AW138">
+        <v>6</v>
+      </c>
+      <c r="AX138">
+        <v>9</v>
+      </c>
+      <c r="AY138">
+        <v>10</v>
+      </c>
+      <c r="AZ138">
+        <v>20</v>
+      </c>
+      <c r="BA138">
+        <v>2</v>
+      </c>
+      <c r="BB138">
+        <v>7</v>
+      </c>
+      <c r="BC138">
+        <v>9</v>
+      </c>
+      <c r="BD138">
+        <v>2.54</v>
+      </c>
+      <c r="BE138">
+        <v>8</v>
+      </c>
+      <c r="BF138">
+        <v>1.69</v>
+      </c>
+      <c r="BG138">
+        <v>1.28</v>
+      </c>
+      <c r="BH138">
+        <v>3.22</v>
+      </c>
+      <c r="BI138">
+        <v>1.52</v>
+      </c>
+      <c r="BJ138">
+        <v>2.36</v>
+      </c>
+      <c r="BK138">
+        <v>1.88</v>
+      </c>
+      <c r="BL138">
+        <v>1.86</v>
+      </c>
+      <c r="BM138">
+        <v>2.4</v>
+      </c>
+      <c r="BN138">
+        <v>1.53</v>
+      </c>
+      <c r="BO138">
+        <v>3.15</v>
+      </c>
+      <c r="BP138">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7844408</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45725.47916666666</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="G139" t="s">
+        <v>77</v>
+      </c>
+      <c r="H139" t="s">
+        <v>80</v>
+      </c>
+      <c r="I139">
+        <v>2</v>
+      </c>
+      <c r="J139">
+        <v>1</v>
+      </c>
+      <c r="K139">
+        <v>3</v>
+      </c>
+      <c r="L139">
+        <v>3</v>
+      </c>
+      <c r="M139">
+        <v>2</v>
+      </c>
+      <c r="N139">
+        <v>5</v>
+      </c>
+      <c r="O139" t="s">
+        <v>175</v>
+      </c>
+      <c r="P139" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q139">
+        <v>2.88</v>
+      </c>
+      <c r="R139">
+        <v>2.1</v>
+      </c>
+      <c r="S139">
+        <v>3.5</v>
+      </c>
+      <c r="T139">
+        <v>1.35</v>
+      </c>
+      <c r="U139">
+        <v>3.08</v>
+      </c>
+      <c r="V139">
+        <v>2.76</v>
+      </c>
+      <c r="W139">
+        <v>1.42</v>
+      </c>
+      <c r="X139">
+        <v>6.6</v>
+      </c>
+      <c r="Y139">
+        <v>1.09</v>
+      </c>
+      <c r="Z139">
+        <v>2.23</v>
+      </c>
+      <c r="AA139">
+        <v>3.37</v>
+      </c>
+      <c r="AB139">
+        <v>3.08</v>
+      </c>
+      <c r="AC139">
+        <v>1.03</v>
+      </c>
+      <c r="AD139">
+        <v>9</v>
+      </c>
+      <c r="AE139">
+        <v>1.22</v>
+      </c>
+      <c r="AF139">
+        <v>3.8</v>
+      </c>
+      <c r="AG139">
+        <v>1.83</v>
+      </c>
+      <c r="AH139">
+        <v>1.91</v>
+      </c>
+      <c r="AI139">
+        <v>1.62</v>
+      </c>
+      <c r="AJ139">
+        <v>2.2</v>
+      </c>
+      <c r="AK139">
+        <v>1.4</v>
+      </c>
+      <c r="AL139">
+        <v>1.28</v>
+      </c>
+      <c r="AM139">
+        <v>1.57</v>
+      </c>
+      <c r="AN139">
+        <v>1.27</v>
+      </c>
+      <c r="AO139">
+        <v>0.91</v>
+      </c>
+      <c r="AP139">
+        <v>1.42</v>
+      </c>
+      <c r="AQ139">
+        <v>0.83</v>
+      </c>
+      <c r="AR139">
+        <v>1.57</v>
+      </c>
+      <c r="AS139">
+        <v>1.37</v>
+      </c>
+      <c r="AT139">
+        <v>2.94</v>
+      </c>
+      <c r="AU139">
+        <v>8</v>
+      </c>
+      <c r="AV139">
+        <v>3</v>
+      </c>
+      <c r="AW139">
+        <v>8</v>
+      </c>
+      <c r="AX139">
+        <v>4</v>
+      </c>
+      <c r="AY139">
+        <v>16</v>
+      </c>
+      <c r="AZ139">
+        <v>7</v>
+      </c>
+      <c r="BA139">
+        <v>6</v>
+      </c>
+      <c r="BB139">
+        <v>6</v>
+      </c>
+      <c r="BC139">
+        <v>12</v>
+      </c>
+      <c r="BD139">
+        <v>1.95</v>
+      </c>
+      <c r="BE139">
+        <v>8</v>
+      </c>
+      <c r="BF139">
+        <v>2.1</v>
+      </c>
+      <c r="BG139">
+        <v>1.19</v>
+      </c>
+      <c r="BH139">
+        <v>3.98</v>
+      </c>
+      <c r="BI139">
+        <v>1.38</v>
+      </c>
+      <c r="BJ139">
+        <v>2.82</v>
+      </c>
+      <c r="BK139">
+        <v>1.63</v>
+      </c>
+      <c r="BL139">
+        <v>2.18</v>
+      </c>
+      <c r="BM139">
+        <v>2.02</v>
+      </c>
+      <c r="BN139">
+        <v>1.74</v>
+      </c>
+      <c r="BO139">
+        <v>2.53</v>
+      </c>
+      <c r="BP139">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="250">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -542,6 +542,15 @@
   </si>
   <si>
     <t>['29', '39', '90+3']</t>
+  </si>
+  <si>
+    <t>['52', '73']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['36', '40', '70']</t>
   </si>
   <si>
     <t>['5', '42', '80', '90+2']</t>
@@ -1116,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP139"/>
+  <dimension ref="A1:BP142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1450,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ2">
         <v>0.83</v>
@@ -1659,7 +1668,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ3">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1784,7 +1793,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1990,7 +1999,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2277,7 +2286,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ6">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2608,7 +2617,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -3304,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
         <v>1.17</v>
@@ -3510,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12">
         <v>2.18</v>
@@ -4131,7 +4140,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ15">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>1.66</v>
@@ -4462,7 +4471,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q17">
         <v>2.57</v>
@@ -4668,7 +4677,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4746,7 +4755,7 @@
         <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ18">
         <v>1.5</v>
@@ -4874,7 +4883,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q19">
         <v>1.7</v>
@@ -5080,7 +5089,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5367,7 +5376,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ21">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR21">
         <v>1.9</v>
@@ -5492,7 +5501,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5698,7 +5707,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -5776,7 +5785,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ23">
         <v>2.18</v>
@@ -5985,7 +5994,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ24">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR24">
         <v>2.32</v>
@@ -6110,7 +6119,7 @@
         <v>82</v>
       </c>
       <c r="P25" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q25">
         <v>3.9</v>
@@ -6316,7 +6325,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6600,7 +6609,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ27">
         <v>1.09</v>
@@ -6728,7 +6737,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6934,7 +6943,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7140,7 +7149,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7221,7 +7230,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ30">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR30">
         <v>1.44</v>
@@ -7346,7 +7355,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7427,7 +7436,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ31">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -7552,7 +7561,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q32">
         <v>2.1</v>
@@ -7758,7 +7767,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7964,7 +7973,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -8042,10 +8051,10 @@
         <v>0.33</v>
       </c>
       <c r="AP34">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ34">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR34">
         <v>1.05</v>
@@ -8170,7 +8179,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8248,7 +8257,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ35">
         <v>2.42</v>
@@ -8788,7 +8797,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8994,7 +9003,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q39">
         <v>4.36</v>
@@ -9075,7 +9084,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ39">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR39">
         <v>1.42</v>
@@ -9200,7 +9209,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q40">
         <v>4.33</v>
@@ -9278,7 +9287,7 @@
         <v>1.75</v>
       </c>
       <c r="AP40">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ40">
         <v>1.5</v>
@@ -9406,7 +9415,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9487,7 +9496,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR41">
         <v>1.37</v>
@@ -9693,7 +9702,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ42">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -10230,7 +10239,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10311,7 +10320,7 @@
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR45">
         <v>1.33</v>
@@ -10436,7 +10445,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10514,7 +10523,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ46">
         <v>2.42</v>
@@ -10642,7 +10651,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q47">
         <v>2.48</v>
@@ -10848,7 +10857,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q48">
         <v>2.49</v>
@@ -11132,7 +11141,7 @@
         <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ49">
         <v>2.18</v>
@@ -11260,7 +11269,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11672,7 +11681,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q52">
         <v>3.22</v>
@@ -11753,7 +11762,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ52">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR52">
         <v>1.35</v>
@@ -11956,7 +11965,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ53">
         <v>1.17</v>
@@ -12084,7 +12093,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q54">
         <v>3.6</v>
@@ -12290,7 +12299,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12371,7 +12380,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ55">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
         <v>1.52</v>
@@ -12496,7 +12505,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12574,10 +12583,10 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR56">
         <v>1.86</v>
@@ -12908,7 +12917,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -12986,7 +12995,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58">
         <v>1.09</v>
@@ -13114,7 +13123,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13526,7 +13535,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13938,7 +13947,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -14225,7 +14234,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ64">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR64">
         <v>1.47</v>
@@ -14350,7 +14359,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q65">
         <v>1.9</v>
@@ -14556,7 +14565,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14634,7 +14643,7 @@
         <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ66">
         <v>1.09</v>
@@ -14762,7 +14771,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14968,7 +14977,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15046,7 +15055,7 @@
         <v>0.8</v>
       </c>
       <c r="AP68">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ68">
         <v>0.75</v>
@@ -15174,7 +15183,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q69">
         <v>2</v>
@@ -15255,7 +15264,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ69">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR69">
         <v>1.9</v>
@@ -15458,7 +15467,7 @@
         <v>0.83</v>
       </c>
       <c r="AP70">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ70">
         <v>1.17</v>
@@ -15586,7 +15595,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -15664,7 +15673,7 @@
         <v>3</v>
       </c>
       <c r="AP71">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ71">
         <v>2.42</v>
@@ -16079,7 +16088,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ73">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR73">
         <v>1.4</v>
@@ -16204,7 +16213,7 @@
         <v>82</v>
       </c>
       <c r="P74" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16410,7 +16419,7 @@
         <v>137</v>
       </c>
       <c r="P75" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q75">
         <v>1.83</v>
@@ -16616,7 +16625,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16903,7 +16912,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ77">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR77">
         <v>1.45</v>
@@ -17106,7 +17115,7 @@
         <v>0.6</v>
       </c>
       <c r="AP78">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ78">
         <v>0.36</v>
@@ -17521,7 +17530,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ80">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR80">
         <v>1.54</v>
@@ -17646,7 +17655,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17724,10 +17733,10 @@
         <v>1.83</v>
       </c>
       <c r="AP81">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ81">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR81">
         <v>1.35</v>
@@ -17852,7 +17861,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -18342,7 +18351,7 @@
         <v>0.5</v>
       </c>
       <c r="AP84">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
         <v>0.36</v>
@@ -18676,7 +18685,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18754,7 +18763,7 @@
         <v>0.71</v>
       </c>
       <c r="AP86">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ86">
         <v>1.17</v>
@@ -18960,7 +18969,7 @@
         <v>0.71</v>
       </c>
       <c r="AP87">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87">
         <v>0.83</v>
@@ -19088,7 +19097,7 @@
         <v>143</v>
       </c>
       <c r="P88" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q88">
         <v>2.5</v>
@@ -19169,7 +19178,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ88">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR88">
         <v>1.42</v>
@@ -19294,7 +19303,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19500,7 +19509,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19706,7 +19715,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -19787,7 +19796,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ91">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -20118,7 +20127,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20196,10 +20205,10 @@
         <v>0.71</v>
       </c>
       <c r="AP93">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ93">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR93">
         <v>1.34</v>
@@ -21148,7 +21157,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21354,7 +21363,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21638,7 +21647,7 @@
         <v>1.13</v>
       </c>
       <c r="AP100">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ100">
         <v>1.17</v>
@@ -21766,7 +21775,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21972,7 +21981,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -22178,7 +22187,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -22256,10 +22265,10 @@
         <v>0.5</v>
       </c>
       <c r="AP103">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ103">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR103">
         <v>1.57</v>
@@ -22465,7 +22474,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ104">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR104">
         <v>1.71</v>
@@ -23286,10 +23295,10 @@
         <v>1.88</v>
       </c>
       <c r="AP108">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ108">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR108">
         <v>1.59</v>
@@ -23620,7 +23629,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23826,7 +23835,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -23904,7 +23913,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP111">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111">
         <v>0.75</v>
@@ -24032,7 +24041,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24110,7 +24119,7 @@
         <v>1.22</v>
       </c>
       <c r="AP112">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ112">
         <v>1.17</v>
@@ -24238,7 +24247,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24444,7 +24453,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -25143,7 +25152,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ117">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR117">
         <v>1.75</v>
@@ -25268,7 +25277,7 @@
         <v>123</v>
       </c>
       <c r="P118" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q118">
         <v>1.74</v>
@@ -25552,10 +25561,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP119">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ119">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR119">
         <v>1.56</v>
@@ -26298,7 +26307,7 @@
         <v>166</v>
       </c>
       <c r="P123" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q123">
         <v>6.04</v>
@@ -26710,7 +26719,7 @@
         <v>167</v>
       </c>
       <c r="P125" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q125">
         <v>2.2</v>
@@ -26994,7 +27003,7 @@
         <v>0.4</v>
       </c>
       <c r="AP126">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ126">
         <v>0.36</v>
@@ -27203,7 +27212,7 @@
         <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR127">
         <v>1.51</v>
@@ -27328,7 +27337,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27534,7 +27543,7 @@
         <v>169</v>
       </c>
       <c r="P129" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q129">
         <v>2</v>
@@ -27740,7 +27749,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q130">
         <v>2.28</v>
@@ -28024,10 +28033,10 @@
         <v>0.5</v>
       </c>
       <c r="AP131">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ131">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR131">
         <v>1.76</v>
@@ -28152,7 +28161,7 @@
         <v>172</v>
       </c>
       <c r="P132" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q132">
         <v>4.5</v>
@@ -28233,7 +28242,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ132">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR132">
         <v>1.4</v>
@@ -28436,10 +28445,10 @@
         <v>0.5</v>
       </c>
       <c r="AP133">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ133">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR133">
         <v>1.53</v>
@@ -28770,7 +28779,7 @@
         <v>82</v>
       </c>
       <c r="P135" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q135">
         <v>3.27</v>
@@ -28976,7 +28985,7 @@
         <v>82</v>
       </c>
       <c r="P136" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29182,7 +29191,7 @@
         <v>173</v>
       </c>
       <c r="P137" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q137">
         <v>2.68</v>
@@ -29388,7 +29397,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q138">
         <v>4.2</v>
@@ -29594,7 +29603,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -29751,6 +29760,624 @@
       </c>
       <c r="BP139">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7844411</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45731.47916666666</v>
+      </c>
+      <c r="F140">
+        <v>2</v>
+      </c>
+      <c r="G140" t="s">
+        <v>80</v>
+      </c>
+      <c r="H140" t="s">
+        <v>75</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>2</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>3</v>
+      </c>
+      <c r="O140" t="s">
+        <v>176</v>
+      </c>
+      <c r="P140" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q140">
+        <v>2.6</v>
+      </c>
+      <c r="R140">
+        <v>2.1</v>
+      </c>
+      <c r="S140">
+        <v>4</v>
+      </c>
+      <c r="T140">
+        <v>1.4</v>
+      </c>
+      <c r="U140">
+        <v>2.75</v>
+      </c>
+      <c r="V140">
+        <v>2.75</v>
+      </c>
+      <c r="W140">
+        <v>1.4</v>
+      </c>
+      <c r="X140">
+        <v>7</v>
+      </c>
+      <c r="Y140">
+        <v>1.08</v>
+      </c>
+      <c r="Z140">
+        <v>2.2</v>
+      </c>
+      <c r="AA140">
+        <v>3.47</v>
+      </c>
+      <c r="AB140">
+        <v>3.04</v>
+      </c>
+      <c r="AC140">
+        <v>1.05</v>
+      </c>
+      <c r="AD140">
+        <v>8.5</v>
+      </c>
+      <c r="AE140">
+        <v>1.3</v>
+      </c>
+      <c r="AF140">
+        <v>3.35</v>
+      </c>
+      <c r="AG140">
+        <v>1.8</v>
+      </c>
+      <c r="AH140">
+        <v>1.94</v>
+      </c>
+      <c r="AI140">
+        <v>1.8</v>
+      </c>
+      <c r="AJ140">
+        <v>1.91</v>
+      </c>
+      <c r="AK140">
+        <v>1.3</v>
+      </c>
+      <c r="AL140">
+        <v>1.29</v>
+      </c>
+      <c r="AM140">
+        <v>1.73</v>
+      </c>
+      <c r="AN140">
+        <v>1.55</v>
+      </c>
+      <c r="AO140">
+        <v>0.45</v>
+      </c>
+      <c r="AP140">
+        <v>1.67</v>
+      </c>
+      <c r="AQ140">
+        <v>0.42</v>
+      </c>
+      <c r="AR140">
+        <v>1.45</v>
+      </c>
+      <c r="AS140">
+        <v>1.26</v>
+      </c>
+      <c r="AT140">
+        <v>2.71</v>
+      </c>
+      <c r="AU140">
+        <v>6</v>
+      </c>
+      <c r="AV140">
+        <v>3</v>
+      </c>
+      <c r="AW140">
+        <v>10</v>
+      </c>
+      <c r="AX140">
+        <v>2</v>
+      </c>
+      <c r="AY140">
+        <v>16</v>
+      </c>
+      <c r="AZ140">
+        <v>5</v>
+      </c>
+      <c r="BA140">
+        <v>7</v>
+      </c>
+      <c r="BB140">
+        <v>3</v>
+      </c>
+      <c r="BC140">
+        <v>10</v>
+      </c>
+      <c r="BD140">
+        <v>2</v>
+      </c>
+      <c r="BE140">
+        <v>6.45</v>
+      </c>
+      <c r="BF140">
+        <v>2.22</v>
+      </c>
+      <c r="BG140">
+        <v>1.21</v>
+      </c>
+      <c r="BH140">
+        <v>3.78</v>
+      </c>
+      <c r="BI140">
+        <v>1.36</v>
+      </c>
+      <c r="BJ140">
+        <v>2.9</v>
+      </c>
+      <c r="BK140">
+        <v>1.7</v>
+      </c>
+      <c r="BL140">
+        <v>2.03</v>
+      </c>
+      <c r="BM140">
+        <v>2.05</v>
+      </c>
+      <c r="BN140">
+        <v>1.7</v>
+      </c>
+      <c r="BO140">
+        <v>2.8</v>
+      </c>
+      <c r="BP140">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7844410</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45731.47916666666</v>
+      </c>
+      <c r="F141">
+        <v>2</v>
+      </c>
+      <c r="G141" t="s">
+        <v>70</v>
+      </c>
+      <c r="H141" t="s">
+        <v>77</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>1</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="O141" t="s">
+        <v>177</v>
+      </c>
+      <c r="P141" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q141">
+        <v>2.6</v>
+      </c>
+      <c r="R141">
+        <v>2.1</v>
+      </c>
+      <c r="S141">
+        <v>4.33</v>
+      </c>
+      <c r="T141">
+        <v>1.44</v>
+      </c>
+      <c r="U141">
+        <v>2.63</v>
+      </c>
+      <c r="V141">
+        <v>3</v>
+      </c>
+      <c r="W141">
+        <v>1.36</v>
+      </c>
+      <c r="X141">
+        <v>7.5</v>
+      </c>
+      <c r="Y141">
+        <v>1.07</v>
+      </c>
+      <c r="Z141">
+        <v>2.07</v>
+      </c>
+      <c r="AA141">
+        <v>3.38</v>
+      </c>
+      <c r="AB141">
+        <v>3.45</v>
+      </c>
+      <c r="AC141">
+        <v>1.06</v>
+      </c>
+      <c r="AD141">
+        <v>8</v>
+      </c>
+      <c r="AE141">
+        <v>1.33</v>
+      </c>
+      <c r="AF141">
+        <v>3.1</v>
+      </c>
+      <c r="AG141">
+        <v>1.89</v>
+      </c>
+      <c r="AH141">
+        <v>1.85</v>
+      </c>
+      <c r="AI141">
+        <v>1.83</v>
+      </c>
+      <c r="AJ141">
+        <v>1.83</v>
+      </c>
+      <c r="AK141">
+        <v>1.28</v>
+      </c>
+      <c r="AL141">
+        <v>1.3</v>
+      </c>
+      <c r="AM141">
+        <v>1.75</v>
+      </c>
+      <c r="AN141">
+        <v>1.18</v>
+      </c>
+      <c r="AO141">
+        <v>0.55</v>
+      </c>
+      <c r="AP141">
+        <v>1.33</v>
+      </c>
+      <c r="AQ141">
+        <v>0.5</v>
+      </c>
+      <c r="AR141">
+        <v>1.49</v>
+      </c>
+      <c r="AS141">
+        <v>1.15</v>
+      </c>
+      <c r="AT141">
+        <v>2.64</v>
+      </c>
+      <c r="AU141">
+        <v>-1</v>
+      </c>
+      <c r="AV141">
+        <v>-1</v>
+      </c>
+      <c r="AW141">
+        <v>-1</v>
+      </c>
+      <c r="AX141">
+        <v>-1</v>
+      </c>
+      <c r="AY141">
+        <v>-1</v>
+      </c>
+      <c r="AZ141">
+        <v>-1</v>
+      </c>
+      <c r="BA141">
+        <v>7</v>
+      </c>
+      <c r="BB141">
+        <v>1</v>
+      </c>
+      <c r="BC141">
+        <v>8</v>
+      </c>
+      <c r="BD141">
+        <v>1.7</v>
+      </c>
+      <c r="BE141">
+        <v>6.45</v>
+      </c>
+      <c r="BF141">
+        <v>2.76</v>
+      </c>
+      <c r="BG141">
+        <v>1.31</v>
+      </c>
+      <c r="BH141">
+        <v>3.12</v>
+      </c>
+      <c r="BI141">
+        <v>1.54</v>
+      </c>
+      <c r="BJ141">
+        <v>2.32</v>
+      </c>
+      <c r="BK141">
+        <v>2</v>
+      </c>
+      <c r="BL141">
+        <v>1.8</v>
+      </c>
+      <c r="BM141">
+        <v>2.55</v>
+      </c>
+      <c r="BN141">
+        <v>1.45</v>
+      </c>
+      <c r="BO141">
+        <v>3.25</v>
+      </c>
+      <c r="BP141">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7844412</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45731.58333333334</v>
+      </c>
+      <c r="F142">
+        <v>2</v>
+      </c>
+      <c r="G142" t="s">
+        <v>79</v>
+      </c>
+      <c r="H142" t="s">
+        <v>81</v>
+      </c>
+      <c r="I142">
+        <v>2</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142">
+        <v>3</v>
+      </c>
+      <c r="L142">
+        <v>3</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+      <c r="N142">
+        <v>4</v>
+      </c>
+      <c r="O142" t="s">
+        <v>178</v>
+      </c>
+      <c r="P142" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q142">
+        <v>2.5</v>
+      </c>
+      <c r="R142">
+        <v>2.2</v>
+      </c>
+      <c r="S142">
+        <v>4</v>
+      </c>
+      <c r="T142">
+        <v>1.36</v>
+      </c>
+      <c r="U142">
+        <v>3</v>
+      </c>
+      <c r="V142">
+        <v>2.63</v>
+      </c>
+      <c r="W142">
+        <v>1.44</v>
+      </c>
+      <c r="X142">
+        <v>6.5</v>
+      </c>
+      <c r="Y142">
+        <v>1.1</v>
+      </c>
+      <c r="Z142">
+        <v>1.97</v>
+      </c>
+      <c r="AA142">
+        <v>3.5</v>
+      </c>
+      <c r="AB142">
+        <v>3.65</v>
+      </c>
+      <c r="AC142">
+        <v>1.05</v>
+      </c>
+      <c r="AD142">
+        <v>8.5</v>
+      </c>
+      <c r="AE142">
+        <v>1.28</v>
+      </c>
+      <c r="AF142">
+        <v>3.55</v>
+      </c>
+      <c r="AG142">
+        <v>1.85</v>
+      </c>
+      <c r="AH142">
+        <v>1.89</v>
+      </c>
+      <c r="AI142">
+        <v>1.73</v>
+      </c>
+      <c r="AJ142">
+        <v>2</v>
+      </c>
+      <c r="AK142">
+        <v>1.28</v>
+      </c>
+      <c r="AL142">
+        <v>1.28</v>
+      </c>
+      <c r="AM142">
+        <v>1.8</v>
+      </c>
+      <c r="AN142">
+        <v>1.36</v>
+      </c>
+      <c r="AO142">
+        <v>1.73</v>
+      </c>
+      <c r="AP142">
+        <v>1.5</v>
+      </c>
+      <c r="AQ142">
+        <v>1.58</v>
+      </c>
+      <c r="AR142">
+        <v>1.77</v>
+      </c>
+      <c r="AS142">
+        <v>1.49</v>
+      </c>
+      <c r="AT142">
+        <v>3.26</v>
+      </c>
+      <c r="AU142">
+        <v>-1</v>
+      </c>
+      <c r="AV142">
+        <v>-1</v>
+      </c>
+      <c r="AW142">
+        <v>-1</v>
+      </c>
+      <c r="AX142">
+        <v>-1</v>
+      </c>
+      <c r="AY142">
+        <v>-1</v>
+      </c>
+      <c r="AZ142">
+        <v>-1</v>
+      </c>
+      <c r="BA142">
+        <v>-1</v>
+      </c>
+      <c r="BB142">
+        <v>-1</v>
+      </c>
+      <c r="BC142">
+        <v>-1</v>
+      </c>
+      <c r="BD142">
+        <v>1.6</v>
+      </c>
+      <c r="BE142">
+        <v>6.85</v>
+      </c>
+      <c r="BF142">
+        <v>2.99</v>
+      </c>
+      <c r="BG142">
+        <v>1.18</v>
+      </c>
+      <c r="BH142">
+        <v>3.84</v>
+      </c>
+      <c r="BI142">
+        <v>1.39</v>
+      </c>
+      <c r="BJ142">
+        <v>2.67</v>
+      </c>
+      <c r="BK142">
+        <v>1.7</v>
+      </c>
+      <c r="BL142">
+        <v>2.03</v>
+      </c>
+      <c r="BM142">
+        <v>2.12</v>
+      </c>
+      <c r="BN142">
+        <v>1.61</v>
+      </c>
+      <c r="BO142">
+        <v>2.78</v>
+      </c>
+      <c r="BP142">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -30314,31 +30314,31 @@
         <v>3.26</v>
       </c>
       <c r="AU142">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV142">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW142">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX142">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AY142">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AZ142">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BA142">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB142">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BC142">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="BD142">
         <v>1.6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="252">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -553,6 +553,12 @@
     <t>['36', '40', '70']</t>
   </si>
   <si>
+    <t>['90+7']</t>
+  </si>
+  <si>
+    <t>['39', '73']</t>
+  </si>
+  <si>
     <t>['5', '42', '80', '90+2']</t>
   </si>
   <si>
@@ -679,9 +685,6 @@
     <t>['4', '45+3', '60']</t>
   </si>
   <si>
-    <t>['90+7']</t>
-  </si>
-  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -764,6 +767,9 @@
   </si>
   <si>
     <t>['4', '82']</t>
+  </si>
+  <si>
+    <t>['45+5']</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP142"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1665,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ3">
         <v>1.58</v>
@@ -1793,7 +1799,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1871,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ4">
         <v>2.42</v>
@@ -1999,7 +2005,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2492,7 +2498,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ7">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2617,7 +2623,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -2904,7 +2910,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ9">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3107,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
         <v>1.17</v>
@@ -3522,7 +3528,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ12">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4471,7 +4477,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q17">
         <v>2.57</v>
@@ -4549,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ17">
         <v>0.75</v>
@@ -4677,7 +4683,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4883,7 +4889,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q19">
         <v>1.7</v>
@@ -4961,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR19">
         <v>1.31</v>
@@ -5089,7 +5095,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5170,7 +5176,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ20">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR20">
         <v>1.25</v>
@@ -5501,7 +5507,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5707,7 +5713,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -5788,7 +5794,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ23">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR23">
         <v>1.55</v>
@@ -6119,7 +6125,7 @@
         <v>82</v>
       </c>
       <c r="P25" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q25">
         <v>3.9</v>
@@ -6325,7 +6331,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6612,7 +6618,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ27">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR27">
         <v>1.22</v>
@@ -6737,7 +6743,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6815,7 +6821,7 @@
         <v>0.67</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ28">
         <v>0.83</v>
@@ -6943,7 +6949,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7021,10 +7027,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ29">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR29">
         <v>1.86</v>
@@ -7149,7 +7155,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7227,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
         <v>1.58</v>
@@ -7355,7 +7361,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7561,7 +7567,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q32">
         <v>2.1</v>
@@ -7767,7 +7773,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7973,7 +7979,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -8179,7 +8185,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8466,7 +8472,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ36">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR36">
         <v>1.33</v>
@@ -8797,7 +8803,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9003,7 +9009,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q39">
         <v>4.36</v>
@@ -9209,7 +9215,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q40">
         <v>4.33</v>
@@ -9415,7 +9421,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9493,7 +9499,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ41">
         <v>0.5</v>
@@ -9699,7 +9705,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ42">
         <v>0.42</v>
@@ -9908,7 +9914,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR43">
         <v>1.8</v>
@@ -10111,7 +10117,7 @@
         <v>1.25</v>
       </c>
       <c r="AP44">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ44">
         <v>0.83</v>
@@ -10239,7 +10245,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10317,7 +10323,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ45">
         <v>0.42</v>
@@ -10445,7 +10451,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10651,7 +10657,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q47">
         <v>2.48</v>
@@ -10857,7 +10863,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q48">
         <v>2.49</v>
@@ -10938,7 +10944,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ48">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR48">
         <v>1.38</v>
@@ -11144,7 +11150,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR49">
         <v>1.98</v>
@@ -11269,7 +11275,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11681,7 +11687,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q52">
         <v>3.22</v>
@@ -12093,7 +12099,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q54">
         <v>3.6</v>
@@ -12171,10 +12177,10 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ54">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR54">
         <v>1.7</v>
@@ -12299,7 +12305,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12377,7 +12383,7 @@
         <v>0.4</v>
       </c>
       <c r="AP55">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
         <v>0.5</v>
@@ -12505,7 +12511,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12917,7 +12923,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -12998,7 +13004,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ58">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR58">
         <v>1.32</v>
@@ -13123,7 +13129,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13535,7 +13541,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13822,7 +13828,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ62">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR62">
         <v>2</v>
@@ -13947,7 +13953,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -14025,7 +14031,7 @@
         <v>0.25</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ63">
         <v>1.17</v>
@@ -14359,7 +14365,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q65">
         <v>1.9</v>
@@ -14565,7 +14571,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14646,7 +14652,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ66">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR66">
         <v>1.77</v>
@@ -14771,7 +14777,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14852,7 +14858,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ67">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR67">
         <v>1.44</v>
@@ -14977,7 +14983,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15183,7 +15189,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q69">
         <v>2</v>
@@ -15595,7 +15601,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -16213,7 +16219,7 @@
         <v>82</v>
       </c>
       <c r="P74" t="s">
-        <v>221</v>
+        <v>179</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16291,7 +16297,7 @@
         <v>1.83</v>
       </c>
       <c r="AP74">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ74">
         <v>1.5</v>
@@ -16419,7 +16425,7 @@
         <v>137</v>
       </c>
       <c r="P75" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q75">
         <v>1.83</v>
@@ -16625,7 +16631,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16703,7 +16709,7 @@
         <v>3</v>
       </c>
       <c r="AP76">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ76">
         <v>2.42</v>
@@ -17118,7 +17124,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ78">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17321,7 +17327,7 @@
         <v>0.67</v>
       </c>
       <c r="AP79">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>0.75</v>
@@ -17655,7 +17661,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17861,7 +17867,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -17939,10 +17945,10 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ82">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR82">
         <v>1.42</v>
@@ -18145,10 +18151,10 @@
         <v>1.17</v>
       </c>
       <c r="AP83">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ83">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR83">
         <v>1.68</v>
@@ -18354,7 +18360,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR84">
         <v>1.59</v>
@@ -18685,7 +18691,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19097,7 +19103,7 @@
         <v>143</v>
       </c>
       <c r="P88" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q88">
         <v>2.5</v>
@@ -19303,7 +19309,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19384,7 +19390,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ89">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR89">
         <v>1.8</v>
@@ -19509,7 +19515,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19715,7 +19721,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20127,7 +20133,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20411,7 +20417,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ94">
         <v>1.5</v>
@@ -20617,10 +20623,10 @@
         <v>1.14</v>
       </c>
       <c r="AP95">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ95">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR95">
         <v>1.35</v>
@@ -20823,10 +20829,10 @@
         <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR96">
         <v>1.73</v>
@@ -21029,7 +21035,7 @@
         <v>1.29</v>
       </c>
       <c r="AP97">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>1.17</v>
@@ -21157,7 +21163,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21238,7 +21244,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ98">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR98">
         <v>1.57</v>
@@ -21363,7 +21369,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21775,7 +21781,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21981,7 +21987,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -22187,7 +22193,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -22471,7 +22477,7 @@
         <v>0.63</v>
       </c>
       <c r="AP104">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ104">
         <v>0.42</v>
@@ -22680,7 +22686,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ105">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR105">
         <v>1.8</v>
@@ -23089,7 +23095,7 @@
         <v>1.88</v>
       </c>
       <c r="AP107">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ107">
         <v>1.5</v>
@@ -23501,10 +23507,10 @@
         <v>0.5</v>
       </c>
       <c r="AP109">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ109">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR109">
         <v>1.38</v>
@@ -23629,7 +23635,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23710,7 +23716,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ110">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -23835,7 +23841,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -24041,7 +24047,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24247,7 +24253,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24328,7 +24334,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ113">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR113">
         <v>1.8</v>
@@ -24453,7 +24459,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24946,7 +24952,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ116">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25149,7 +25155,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP117">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ117">
         <v>0.5</v>
@@ -25277,7 +25283,7 @@
         <v>123</v>
       </c>
       <c r="P118" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q118">
         <v>1.74</v>
@@ -25355,7 +25361,7 @@
         <v>1</v>
       </c>
       <c r="AP118">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ118">
         <v>0.83</v>
@@ -25976,7 +25982,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ121">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR121">
         <v>1.4</v>
@@ -26179,7 +26185,7 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ122">
         <v>0.75</v>
@@ -26307,7 +26313,7 @@
         <v>166</v>
       </c>
       <c r="P123" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q123">
         <v>6.04</v>
@@ -26719,7 +26725,7 @@
         <v>167</v>
       </c>
       <c r="P125" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q125">
         <v>2.2</v>
@@ -27006,7 +27012,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ126">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR126">
         <v>1.44</v>
@@ -27209,7 +27215,7 @@
         <v>1.78</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ127">
         <v>1.58</v>
@@ -27337,7 +27343,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27415,10 +27421,10 @@
         <v>2.1</v>
       </c>
       <c r="AP128">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ128">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR128">
         <v>1.95</v>
@@ -27543,7 +27549,7 @@
         <v>169</v>
       </c>
       <c r="P129" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q129">
         <v>2</v>
@@ -27621,7 +27627,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ129">
         <v>1.17</v>
@@ -27749,7 +27755,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q130">
         <v>2.28</v>
@@ -28161,7 +28167,7 @@
         <v>172</v>
       </c>
       <c r="P132" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q132">
         <v>4.5</v>
@@ -28779,7 +28785,7 @@
         <v>82</v>
       </c>
       <c r="P135" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q135">
         <v>3.27</v>
@@ -28985,7 +28991,7 @@
         <v>82</v>
       </c>
       <c r="P136" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29191,7 +29197,7 @@
         <v>173</v>
       </c>
       <c r="P137" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q137">
         <v>2.68</v>
@@ -29397,7 +29403,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q138">
         <v>4.2</v>
@@ -29603,7 +29609,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -30378,6 +30384,624 @@
       </c>
       <c r="BP142">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7844413</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45732.47916666666</v>
+      </c>
+      <c r="F143">
+        <v>2</v>
+      </c>
+      <c r="G143" t="s">
+        <v>78</v>
+      </c>
+      <c r="H143" t="s">
+        <v>74</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>1</v>
+      </c>
+      <c r="K143">
+        <v>1</v>
+      </c>
+      <c r="L143">
+        <v>1</v>
+      </c>
+      <c r="M143">
+        <v>1</v>
+      </c>
+      <c r="N143">
+        <v>2</v>
+      </c>
+      <c r="O143" t="s">
+        <v>179</v>
+      </c>
+      <c r="P143" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q143">
+        <v>2.2</v>
+      </c>
+      <c r="R143">
+        <v>2.38</v>
+      </c>
+      <c r="S143">
+        <v>4.33</v>
+      </c>
+      <c r="T143">
+        <v>1.3</v>
+      </c>
+      <c r="U143">
+        <v>3.4</v>
+      </c>
+      <c r="V143">
+        <v>2.38</v>
+      </c>
+      <c r="W143">
+        <v>1.53</v>
+      </c>
+      <c r="X143">
+        <v>5</v>
+      </c>
+      <c r="Y143">
+        <v>1.14</v>
+      </c>
+      <c r="Z143">
+        <v>1.69</v>
+      </c>
+      <c r="AA143">
+        <v>3.62</v>
+      </c>
+      <c r="AB143">
+        <v>4.9</v>
+      </c>
+      <c r="AC143">
+        <v>1.04</v>
+      </c>
+      <c r="AD143">
+        <v>9</v>
+      </c>
+      <c r="AE143">
+        <v>1.2</v>
+      </c>
+      <c r="AF143">
+        <v>4.2</v>
+      </c>
+      <c r="AG143">
+        <v>1.6</v>
+      </c>
+      <c r="AH143">
+        <v>2.15</v>
+      </c>
+      <c r="AI143">
+        <v>1.62</v>
+      </c>
+      <c r="AJ143">
+        <v>2.2</v>
+      </c>
+      <c r="AK143">
+        <v>1.19</v>
+      </c>
+      <c r="AL143">
+        <v>1.23</v>
+      </c>
+      <c r="AM143">
+        <v>2.15</v>
+      </c>
+      <c r="AN143">
+        <v>2.09</v>
+      </c>
+      <c r="AO143">
+        <v>2.18</v>
+      </c>
+      <c r="AP143">
+        <v>2</v>
+      </c>
+      <c r="AQ143">
+        <v>2.08</v>
+      </c>
+      <c r="AR143">
+        <v>1.96</v>
+      </c>
+      <c r="AS143">
+        <v>1.64</v>
+      </c>
+      <c r="AT143">
+        <v>3.6</v>
+      </c>
+      <c r="AU143">
+        <v>4</v>
+      </c>
+      <c r="AV143">
+        <v>3</v>
+      </c>
+      <c r="AW143">
+        <v>7</v>
+      </c>
+      <c r="AX143">
+        <v>6</v>
+      </c>
+      <c r="AY143">
+        <v>11</v>
+      </c>
+      <c r="AZ143">
+        <v>9</v>
+      </c>
+      <c r="BA143">
+        <v>2</v>
+      </c>
+      <c r="BB143">
+        <v>2</v>
+      </c>
+      <c r="BC143">
+        <v>4</v>
+      </c>
+      <c r="BD143">
+        <v>1.59</v>
+      </c>
+      <c r="BE143">
+        <v>6.75</v>
+      </c>
+      <c r="BF143">
+        <v>3.04</v>
+      </c>
+      <c r="BG143">
+        <v>1.21</v>
+      </c>
+      <c r="BH143">
+        <v>3.58</v>
+      </c>
+      <c r="BI143">
+        <v>1.43</v>
+      </c>
+      <c r="BJ143">
+        <v>2.54</v>
+      </c>
+      <c r="BK143">
+        <v>1.77</v>
+      </c>
+      <c r="BL143">
+        <v>1.94</v>
+      </c>
+      <c r="BM143">
+        <v>2.23</v>
+      </c>
+      <c r="BN143">
+        <v>1.55</v>
+      </c>
+      <c r="BO143">
+        <v>2.97</v>
+      </c>
+      <c r="BP143">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7844414</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45732.47916666666</v>
+      </c>
+      <c r="F144">
+        <v>2</v>
+      </c>
+      <c r="G144" t="s">
+        <v>72</v>
+      </c>
+      <c r="H144" t="s">
+        <v>76</v>
+      </c>
+      <c r="I144">
+        <v>1</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>1</v>
+      </c>
+      <c r="L144">
+        <v>2</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>3</v>
+      </c>
+      <c r="O144" t="s">
+        <v>180</v>
+      </c>
+      <c r="P144" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q144">
+        <v>2.6</v>
+      </c>
+      <c r="R144">
+        <v>2.05</v>
+      </c>
+      <c r="S144">
+        <v>4.33</v>
+      </c>
+      <c r="T144">
+        <v>1.44</v>
+      </c>
+      <c r="U144">
+        <v>2.63</v>
+      </c>
+      <c r="V144">
+        <v>3.25</v>
+      </c>
+      <c r="W144">
+        <v>1.33</v>
+      </c>
+      <c r="X144">
+        <v>7.5</v>
+      </c>
+      <c r="Y144">
+        <v>1.07</v>
+      </c>
+      <c r="Z144">
+        <v>2.13</v>
+      </c>
+      <c r="AA144">
+        <v>3.23</v>
+      </c>
+      <c r="AB144">
+        <v>3.45</v>
+      </c>
+      <c r="AC144">
+        <v>1.06</v>
+      </c>
+      <c r="AD144">
+        <v>8</v>
+      </c>
+      <c r="AE144">
+        <v>1.36</v>
+      </c>
+      <c r="AF144">
+        <v>3</v>
+      </c>
+      <c r="AG144">
+        <v>1.95</v>
+      </c>
+      <c r="AH144">
+        <v>1.7</v>
+      </c>
+      <c r="AI144">
+        <v>1.91</v>
+      </c>
+      <c r="AJ144">
+        <v>1.8</v>
+      </c>
+      <c r="AK144">
+        <v>1.25</v>
+      </c>
+      <c r="AL144">
+        <v>1.28</v>
+      </c>
+      <c r="AM144">
+        <v>1.75</v>
+      </c>
+      <c r="AN144">
+        <v>1</v>
+      </c>
+      <c r="AO144">
+        <v>0.36</v>
+      </c>
+      <c r="AP144">
+        <v>1.17</v>
+      </c>
+      <c r="AQ144">
+        <v>0.33</v>
+      </c>
+      <c r="AR144">
+        <v>1.44</v>
+      </c>
+      <c r="AS144">
+        <v>1.12</v>
+      </c>
+      <c r="AT144">
+        <v>2.56</v>
+      </c>
+      <c r="AU144">
+        <v>7</v>
+      </c>
+      <c r="AV144">
+        <v>3</v>
+      </c>
+      <c r="AW144">
+        <v>3</v>
+      </c>
+      <c r="AX144">
+        <v>9</v>
+      </c>
+      <c r="AY144">
+        <v>10</v>
+      </c>
+      <c r="AZ144">
+        <v>12</v>
+      </c>
+      <c r="BA144">
+        <v>2</v>
+      </c>
+      <c r="BB144">
+        <v>5</v>
+      </c>
+      <c r="BC144">
+        <v>7</v>
+      </c>
+      <c r="BD144">
+        <v>1.65</v>
+      </c>
+      <c r="BE144">
+        <v>6.65</v>
+      </c>
+      <c r="BF144">
+        <v>2.86</v>
+      </c>
+      <c r="BG144">
+        <v>1.18</v>
+      </c>
+      <c r="BH144">
+        <v>3.84</v>
+      </c>
+      <c r="BI144">
+        <v>1.38</v>
+      </c>
+      <c r="BJ144">
+        <v>2.71</v>
+      </c>
+      <c r="BK144">
+        <v>1.69</v>
+      </c>
+      <c r="BL144">
+        <v>2.04</v>
+      </c>
+      <c r="BM144">
+        <v>2.12</v>
+      </c>
+      <c r="BN144">
+        <v>1.61</v>
+      </c>
+      <c r="BO144">
+        <v>2.74</v>
+      </c>
+      <c r="BP144">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7844409</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45732.47916666666</v>
+      </c>
+      <c r="F145">
+        <v>2</v>
+      </c>
+      <c r="G145" t="s">
+        <v>71</v>
+      </c>
+      <c r="H145" t="s">
+        <v>73</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>1</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145" t="s">
+        <v>82</v>
+      </c>
+      <c r="P145" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q145">
+        <v>2.75</v>
+      </c>
+      <c r="R145">
+        <v>2.1</v>
+      </c>
+      <c r="S145">
+        <v>3.75</v>
+      </c>
+      <c r="T145">
+        <v>1.4</v>
+      </c>
+      <c r="U145">
+        <v>2.75</v>
+      </c>
+      <c r="V145">
+        <v>3</v>
+      </c>
+      <c r="W145">
+        <v>1.36</v>
+      </c>
+      <c r="X145">
+        <v>7</v>
+      </c>
+      <c r="Y145">
+        <v>1.08</v>
+      </c>
+      <c r="Z145">
+        <v>2</v>
+      </c>
+      <c r="AA145">
+        <v>3.25</v>
+      </c>
+      <c r="AB145">
+        <v>3.4</v>
+      </c>
+      <c r="AC145">
+        <v>1.05</v>
+      </c>
+      <c r="AD145">
+        <v>8.5</v>
+      </c>
+      <c r="AE145">
+        <v>1.3</v>
+      </c>
+      <c r="AF145">
+        <v>3.3</v>
+      </c>
+      <c r="AG145">
+        <v>1.85</v>
+      </c>
+      <c r="AH145">
+        <v>1.75</v>
+      </c>
+      <c r="AI145">
+        <v>1.73</v>
+      </c>
+      <c r="AJ145">
+        <v>2</v>
+      </c>
+      <c r="AK145">
+        <v>1.29</v>
+      </c>
+      <c r="AL145">
+        <v>1.3</v>
+      </c>
+      <c r="AM145">
+        <v>1.75</v>
+      </c>
+      <c r="AN145">
+        <v>1.55</v>
+      </c>
+      <c r="AO145">
+        <v>1.09</v>
+      </c>
+      <c r="AP145">
+        <v>1.42</v>
+      </c>
+      <c r="AQ145">
+        <v>1.25</v>
+      </c>
+      <c r="AR145">
+        <v>1.76</v>
+      </c>
+      <c r="AS145">
+        <v>1.18</v>
+      </c>
+      <c r="AT145">
+        <v>2.94</v>
+      </c>
+      <c r="AU145">
+        <v>0</v>
+      </c>
+      <c r="AV145">
+        <v>2</v>
+      </c>
+      <c r="AW145">
+        <v>2</v>
+      </c>
+      <c r="AX145">
+        <v>7</v>
+      </c>
+      <c r="AY145">
+        <v>2</v>
+      </c>
+      <c r="AZ145">
+        <v>9</v>
+      </c>
+      <c r="BA145">
+        <v>3</v>
+      </c>
+      <c r="BB145">
+        <v>6</v>
+      </c>
+      <c r="BC145">
+        <v>9</v>
+      </c>
+      <c r="BD145">
+        <v>1.7</v>
+      </c>
+      <c r="BE145">
+        <v>6.7</v>
+      </c>
+      <c r="BF145">
+        <v>2.72</v>
+      </c>
+      <c r="BG145">
+        <v>1.19</v>
+      </c>
+      <c r="BH145">
+        <v>3.92</v>
+      </c>
+      <c r="BI145">
+        <v>1.33</v>
+      </c>
+      <c r="BJ145">
+        <v>2.83</v>
+      </c>
+      <c r="BK145">
+        <v>1.61</v>
+      </c>
+      <c r="BL145">
+        <v>2.12</v>
+      </c>
+      <c r="BM145">
+        <v>2.04</v>
+      </c>
+      <c r="BN145">
+        <v>1.69</v>
+      </c>
+      <c r="BO145">
+        <v>2.64</v>
+      </c>
+      <c r="BP145">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -30114,22 +30114,22 @@
         <v>2.64</v>
       </c>
       <c r="AU141">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV141">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW141">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AX141">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AY141">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AZ141">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BA141">
         <v>7</v>
@@ -30338,13 +30338,13 @@
         <v>11</v>
       </c>
       <c r="BA142">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB142">
         <v>8</v>
       </c>
       <c r="BC142">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD142">
         <v>1.6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -30959,10 +30959,10 @@
         <v>3</v>
       </c>
       <c r="BB145">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC145">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD145">
         <v>1.7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="254">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -559,6 +559,9 @@
     <t>['39', '73']</t>
   </si>
   <si>
+    <t>['59', '85', '90+2']</t>
+  </si>
+  <si>
     <t>['5', '42', '80', '90+2']</t>
   </si>
   <si>
@@ -770,6 +773,9 @@
   </si>
   <si>
     <t>['45+5']</t>
+  </si>
+  <si>
+    <t>['82']</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1799,7 +1805,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -2005,7 +2011,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2623,7 +2629,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -3113,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ10">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3940,7 +3946,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ14">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
@@ -4477,7 +4483,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q17">
         <v>2.57</v>
@@ -4683,7 +4689,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4889,7 +4895,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q19">
         <v>1.7</v>
@@ -4967,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ19">
         <v>1.25</v>
@@ -5095,7 +5101,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5507,7 +5513,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5713,7 +5719,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -6125,7 +6131,7 @@
         <v>82</v>
       </c>
       <c r="P25" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q25">
         <v>3.9</v>
@@ -6331,7 +6337,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6743,7 +6749,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6949,7 +6955,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7155,7 +7161,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7233,7 +7239,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ30">
         <v>1.58</v>
@@ -7361,7 +7367,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7567,7 +7573,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q32">
         <v>2.1</v>
@@ -7773,7 +7779,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7979,7 +7985,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -8185,7 +8191,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8678,7 +8684,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR37">
         <v>1.31</v>
@@ -8803,7 +8809,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9009,7 +9015,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q39">
         <v>4.36</v>
@@ -9215,7 +9221,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q40">
         <v>4.33</v>
@@ -9421,7 +9427,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9705,7 +9711,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ42">
         <v>0.42</v>
@@ -10245,7 +10251,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10451,7 +10457,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10657,7 +10663,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q47">
         <v>2.48</v>
@@ -10738,7 +10744,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ47">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR47">
         <v>1.58</v>
@@ -10863,7 +10869,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q48">
         <v>2.49</v>
@@ -11275,7 +11281,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11687,7 +11693,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q52">
         <v>3.22</v>
@@ -12099,7 +12105,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q54">
         <v>3.6</v>
@@ -12305,7 +12311,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12383,7 +12389,7 @@
         <v>0.4</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ55">
         <v>0.5</v>
@@ -12511,7 +12517,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12923,7 +12929,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13129,7 +13135,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13541,7 +13547,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13953,7 +13959,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -14034,7 +14040,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ63">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR63">
         <v>1.28</v>
@@ -14365,7 +14371,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q65">
         <v>1.9</v>
@@ -14446,7 +14452,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ65">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR65">
         <v>1.94</v>
@@ -14571,7 +14577,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14777,7 +14783,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14983,7 +14989,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15189,7 +15195,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q69">
         <v>2</v>
@@ -15476,7 +15482,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ70">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR70">
         <v>1.54</v>
@@ -15601,7 +15607,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -16425,7 +16431,7 @@
         <v>137</v>
       </c>
       <c r="P75" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q75">
         <v>1.83</v>
@@ -16631,7 +16637,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17327,7 +17333,7 @@
         <v>0.67</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ79">
         <v>0.75</v>
@@ -17661,7 +17667,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17867,7 +17873,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -18691,7 +18697,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18772,7 +18778,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ86">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR86">
         <v>1.53</v>
@@ -19103,7 +19109,7 @@
         <v>143</v>
       </c>
       <c r="P88" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q88">
         <v>2.5</v>
@@ -19309,7 +19315,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19515,7 +19521,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19721,7 +19727,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20133,7 +20139,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20829,7 +20835,7 @@
         <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ96">
         <v>0.33</v>
@@ -21035,7 +21041,7 @@
         <v>1.29</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ97">
         <v>1.17</v>
@@ -21163,7 +21169,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21369,7 +21375,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21450,7 +21456,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ99">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR99">
         <v>1.48</v>
@@ -21781,7 +21787,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21987,7 +21993,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -22193,7 +22199,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -23095,7 +23101,7 @@
         <v>1.88</v>
       </c>
       <c r="AP107">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ107">
         <v>1.5</v>
@@ -23635,7 +23641,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23841,7 +23847,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -24047,7 +24053,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24128,7 +24134,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ112">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR112">
         <v>1.46</v>
@@ -24253,7 +24259,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24459,7 +24465,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -25283,7 +25289,7 @@
         <v>123</v>
       </c>
       <c r="P118" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q118">
         <v>1.74</v>
@@ -25361,7 +25367,7 @@
         <v>1</v>
       </c>
       <c r="AP118">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ118">
         <v>0.83</v>
@@ -26313,7 +26319,7 @@
         <v>166</v>
       </c>
       <c r="P123" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q123">
         <v>6.04</v>
@@ -26725,7 +26731,7 @@
         <v>167</v>
       </c>
       <c r="P125" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q125">
         <v>2.2</v>
@@ -26806,7 +26812,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ125">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR125">
         <v>1.74</v>
@@ -27343,7 +27349,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27421,7 +27427,7 @@
         <v>2.1</v>
       </c>
       <c r="AP128">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ128">
         <v>2.08</v>
@@ -27549,7 +27555,7 @@
         <v>169</v>
       </c>
       <c r="P129" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q129">
         <v>2</v>
@@ -27755,7 +27761,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q130">
         <v>2.28</v>
@@ -28167,7 +28173,7 @@
         <v>172</v>
       </c>
       <c r="P132" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q132">
         <v>4.5</v>
@@ -28660,7 +28666,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ134">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR134">
         <v>1.78</v>
@@ -28785,7 +28791,7 @@
         <v>82</v>
       </c>
       <c r="P135" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q135">
         <v>3.27</v>
@@ -28991,7 +28997,7 @@
         <v>82</v>
       </c>
       <c r="P136" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29197,7 +29203,7 @@
         <v>173</v>
       </c>
       <c r="P137" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q137">
         <v>2.68</v>
@@ -29403,7 +29409,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q138">
         <v>4.2</v>
@@ -29609,7 +29615,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -30433,7 +30439,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q143">
         <v>2.2</v>
@@ -30511,7 +30517,7 @@
         <v>2.18</v>
       </c>
       <c r="AP143">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ143">
         <v>2.08</v>
@@ -31001,6 +31007,212 @@
         <v>2.64</v>
       </c>
       <c r="BP145">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7844415</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F146">
+        <v>3</v>
+      </c>
+      <c r="G146" t="s">
+        <v>78</v>
+      </c>
+      <c r="H146" t="s">
+        <v>71</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>3</v>
+      </c>
+      <c r="M146">
+        <v>1</v>
+      </c>
+      <c r="N146">
+        <v>4</v>
+      </c>
+      <c r="O146" t="s">
+        <v>181</v>
+      </c>
+      <c r="P146" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q146">
+        <v>1.83</v>
+      </c>
+      <c r="R146">
+        <v>2.5</v>
+      </c>
+      <c r="S146">
+        <v>6</v>
+      </c>
+      <c r="T146">
+        <v>1.29</v>
+      </c>
+      <c r="U146">
+        <v>3.5</v>
+      </c>
+      <c r="V146">
+        <v>2.25</v>
+      </c>
+      <c r="W146">
+        <v>1.57</v>
+      </c>
+      <c r="X146">
+        <v>5</v>
+      </c>
+      <c r="Y146">
+        <v>1.14</v>
+      </c>
+      <c r="Z146">
+        <v>1.39</v>
+      </c>
+      <c r="AA146">
+        <v>4.9</v>
+      </c>
+      <c r="AB146">
+        <v>6.9</v>
+      </c>
+      <c r="AC146">
+        <v>1</v>
+      </c>
+      <c r="AD146">
+        <v>15</v>
+      </c>
+      <c r="AE146">
+        <v>1.16</v>
+      </c>
+      <c r="AF146">
+        <v>4.83</v>
+      </c>
+      <c r="AG146">
+        <v>1.46</v>
+      </c>
+      <c r="AH146">
+        <v>2.52</v>
+      </c>
+      <c r="AI146">
+        <v>1.8</v>
+      </c>
+      <c r="AJ146">
+        <v>1.91</v>
+      </c>
+      <c r="AK146">
+        <v>1.08</v>
+      </c>
+      <c r="AL146">
+        <v>1.16</v>
+      </c>
+      <c r="AM146">
+        <v>2.91</v>
+      </c>
+      <c r="AN146">
+        <v>2</v>
+      </c>
+      <c r="AO146">
+        <v>1.17</v>
+      </c>
+      <c r="AP146">
+        <v>2.08</v>
+      </c>
+      <c r="AQ146">
+        <v>1.08</v>
+      </c>
+      <c r="AR146">
+        <v>1.92</v>
+      </c>
+      <c r="AS146">
+        <v>1.42</v>
+      </c>
+      <c r="AT146">
+        <v>3.34</v>
+      </c>
+      <c r="AU146">
+        <v>-1</v>
+      </c>
+      <c r="AV146">
+        <v>-1</v>
+      </c>
+      <c r="AW146">
+        <v>-1</v>
+      </c>
+      <c r="AX146">
+        <v>-1</v>
+      </c>
+      <c r="AY146">
+        <v>-1</v>
+      </c>
+      <c r="AZ146">
+        <v>-1</v>
+      </c>
+      <c r="BA146">
+        <v>-1</v>
+      </c>
+      <c r="BB146">
+        <v>-1</v>
+      </c>
+      <c r="BC146">
+        <v>-1</v>
+      </c>
+      <c r="BD146">
+        <v>1.25</v>
+      </c>
+      <c r="BE146">
+        <v>10.5</v>
+      </c>
+      <c r="BF146">
+        <v>4.75</v>
+      </c>
+      <c r="BG146">
+        <v>1.19</v>
+      </c>
+      <c r="BH146">
+        <v>3.92</v>
+      </c>
+      <c r="BI146">
+        <v>1.33</v>
+      </c>
+      <c r="BJ146">
+        <v>2.83</v>
+      </c>
+      <c r="BK146">
+        <v>1.61</v>
+      </c>
+      <c r="BL146">
+        <v>2.12</v>
+      </c>
+      <c r="BM146">
+        <v>2.03</v>
+      </c>
+      <c r="BN146">
+        <v>1.7</v>
+      </c>
+      <c r="BO146">
+        <v>2.64</v>
+      </c>
+      <c r="BP146">
         <v>1.4</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="262">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -562,6 +562,18 @@
     <t>['59', '85', '90+2']</t>
   </si>
   <si>
+    <t>['33', '42']</t>
+  </si>
+  <si>
+    <t>['23', '38', '78']</t>
+  </si>
+  <si>
+    <t>['15', '90+8']</t>
+  </si>
+  <si>
+    <t>['34', '42']</t>
+  </si>
+  <si>
     <t>['5', '42', '80', '90+2']</t>
   </si>
   <si>
@@ -776,6 +788,18 @@
   </si>
   <si>
     <t>['82']</t>
+  </si>
+  <si>
+    <t>['69', '75', '88']</t>
+  </si>
+  <si>
+    <t>['36', '89']</t>
+  </si>
+  <si>
+    <t>['36', '51']</t>
+  </si>
+  <si>
+    <t>['22', '30', '58', '71']</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP146"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1474,7 +1498,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ2">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1680,7 +1704,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ3">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1805,7 +1829,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1883,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ4">
         <v>2.42</v>
@@ -2011,7 +2035,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2089,10 +2113,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2295,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2501,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ7">
         <v>0.33</v>
@@ -2629,7 +2653,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -2707,10 +2731,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3740,7 +3764,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ13">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3943,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ14">
         <v>1.08</v>
@@ -4149,10 +4173,10 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR15">
         <v>1.66</v>
@@ -4355,10 +4379,10 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR16">
         <v>2.2</v>
@@ -4483,7 +4507,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q17">
         <v>2.57</v>
@@ -4564,7 +4588,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ17">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR17">
         <v>1.28</v>
@@ -4689,7 +4713,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4770,7 +4794,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ18">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR18">
         <v>1.61</v>
@@ -4895,7 +4919,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q19">
         <v>1.7</v>
@@ -5101,7 +5125,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5385,10 +5409,10 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ21">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR21">
         <v>1.9</v>
@@ -5513,7 +5537,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5591,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ22">
         <v>1.17</v>
@@ -5719,7 +5743,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -6006,7 +6030,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ24">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR24">
         <v>2.32</v>
@@ -6131,7 +6155,7 @@
         <v>82</v>
       </c>
       <c r="P25" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q25">
         <v>3.9</v>
@@ -6209,7 +6233,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ25">
         <v>2.42</v>
@@ -6337,7 +6361,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6415,10 +6439,10 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ26">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR26">
         <v>1.13</v>
@@ -6749,7 +6773,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6827,10 +6851,10 @@
         <v>0.67</v>
       </c>
       <c r="AP28">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ28">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>1.13</v>
@@ -6955,7 +6979,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7161,7 +7185,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7242,7 +7266,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ30">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR30">
         <v>1.44</v>
@@ -7367,7 +7391,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7445,7 +7469,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ31">
         <v>0.42</v>
@@ -7573,7 +7597,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q32">
         <v>2.1</v>
@@ -7651,7 +7675,7 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ32">
         <v>1.17</v>
@@ -7779,7 +7803,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7860,7 +7884,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ33">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR33">
         <v>2.34</v>
@@ -7985,7 +8009,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -8066,7 +8090,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ34">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR34">
         <v>1.05</v>
@@ -8191,7 +8215,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8475,7 +8499,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ36">
         <v>2.08</v>
@@ -8681,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ37">
         <v>1.08</v>
@@ -8809,7 +8833,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8890,7 +8914,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ38">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR38">
         <v>1.64</v>
@@ -9015,7 +9039,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q39">
         <v>4.36</v>
@@ -9093,10 +9117,10 @@
         <v>1.67</v>
       </c>
       <c r="AP39">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ39">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR39">
         <v>1.42</v>
@@ -9221,7 +9245,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q40">
         <v>4.33</v>
@@ -9302,7 +9326,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ40">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR40">
         <v>1.56</v>
@@ -9427,7 +9451,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9505,10 +9529,10 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ41">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR41">
         <v>1.37</v>
@@ -9917,7 +9941,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ43">
         <v>0.33</v>
@@ -10126,7 +10150,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ44">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10251,7 +10275,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10329,7 +10353,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ45">
         <v>0.42</v>
@@ -10457,7 +10481,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10663,7 +10687,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q47">
         <v>2.48</v>
@@ -10869,7 +10893,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q48">
         <v>2.49</v>
@@ -10947,7 +10971,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
         <v>1.25</v>
@@ -11281,7 +11305,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11359,10 +11383,10 @@
         <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ50">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR50">
         <v>1.39</v>
@@ -11693,7 +11717,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q52">
         <v>3.22</v>
@@ -11771,7 +11795,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ52">
         <v>0.42</v>
@@ -12105,7 +12129,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q54">
         <v>3.6</v>
@@ -12311,7 +12335,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12392,7 +12416,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR55">
         <v>1.52</v>
@@ -12517,7 +12541,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12598,7 +12622,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR56">
         <v>1.86</v>
@@ -12801,10 +12825,10 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ57">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>1.64</v>
@@ -12929,7 +12953,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13135,7 +13159,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13213,10 +13237,10 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ59">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR59">
         <v>1.37</v>
@@ -13422,7 +13446,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ60">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR60">
         <v>1.4</v>
@@ -13547,7 +13571,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13625,7 +13649,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ61">
         <v>2.42</v>
@@ -13959,7 +13983,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -14037,7 +14061,7 @@
         <v>0.25</v>
       </c>
       <c r="AP63">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ63">
         <v>1.08</v>
@@ -14243,7 +14267,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ64">
         <v>0.42</v>
@@ -14371,7 +14395,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q65">
         <v>1.9</v>
@@ -14577,7 +14601,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14783,7 +14807,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14989,7 +15013,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15070,7 +15094,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ68">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR68">
         <v>1.28</v>
@@ -15195,7 +15219,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q69">
         <v>2</v>
@@ -15607,7 +15631,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -15891,7 +15915,7 @@
         <v>1.2</v>
       </c>
       <c r="AP72">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ72">
         <v>1.17</v>
@@ -16097,10 +16121,10 @@
         <v>0.5</v>
       </c>
       <c r="AP73">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ73">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR73">
         <v>1.4</v>
@@ -16303,10 +16327,10 @@
         <v>1.83</v>
       </c>
       <c r="AP74">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ74">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR74">
         <v>1.41</v>
@@ -16431,7 +16455,7 @@
         <v>137</v>
       </c>
       <c r="P75" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q75">
         <v>1.83</v>
@@ -16509,10 +16533,10 @@
         <v>0.83</v>
       </c>
       <c r="AP75">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ75">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>1.7</v>
@@ -16637,7 +16661,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16921,10 +16945,10 @@
         <v>2.2</v>
       </c>
       <c r="AP77">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ77">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR77">
         <v>1.45</v>
@@ -17336,7 +17360,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ79">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR79">
         <v>1.8</v>
@@ -17667,7 +17691,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17748,7 +17772,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ81">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR81">
         <v>1.35</v>
@@ -17873,7 +17897,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -17951,7 +17975,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ82">
         <v>2.08</v>
@@ -18569,7 +18593,7 @@
         <v>3</v>
       </c>
       <c r="AP85">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ85">
         <v>2.42</v>
@@ -18697,7 +18721,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18984,7 +19008,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ87">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR87">
         <v>1.54</v>
@@ -19109,7 +19133,7 @@
         <v>143</v>
       </c>
       <c r="P88" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q88">
         <v>2.5</v>
@@ -19187,10 +19211,10 @@
         <v>0.57</v>
       </c>
       <c r="AP88">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ88">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR88">
         <v>1.42</v>
@@ -19315,7 +19339,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19521,7 +19545,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19599,7 +19623,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ90">
         <v>1.17</v>
@@ -19727,7 +19751,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -19808,7 +19832,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ91">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -20011,10 +20035,10 @@
         <v>0.57</v>
       </c>
       <c r="AP92">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ92">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR92">
         <v>1.74</v>
@@ -20139,7 +20163,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20426,7 +20450,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ94">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR94">
         <v>1.72</v>
@@ -20629,7 +20653,7 @@
         <v>1.14</v>
       </c>
       <c r="AP95">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ95">
         <v>1.25</v>
@@ -21169,7 +21193,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21247,7 +21271,7 @@
         <v>1.88</v>
       </c>
       <c r="AP98">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ98">
         <v>2.08</v>
@@ -21375,7 +21399,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21453,7 +21477,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
         <v>1.08</v>
@@ -21787,7 +21811,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21993,7 +22017,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -22071,10 +22095,10 @@
         <v>0.5</v>
       </c>
       <c r="AP102">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ102">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR102">
         <v>1.31</v>
@@ -22199,7 +22223,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -22280,7 +22304,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ103">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR103">
         <v>1.57</v>
@@ -22689,7 +22713,7 @@
         <v>1.13</v>
       </c>
       <c r="AP105">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ105">
         <v>1.25</v>
@@ -22898,7 +22922,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ106">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR106">
         <v>1.51</v>
@@ -23104,7 +23128,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ107">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR107">
         <v>1.92</v>
@@ -23310,7 +23334,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ108">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR108">
         <v>1.59</v>
@@ -23513,7 +23537,7 @@
         <v>0.5</v>
       </c>
       <c r="AP109">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ109">
         <v>0.33</v>
@@ -23641,7 +23665,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23719,7 +23743,7 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ110">
         <v>2.08</v>
@@ -23847,7 +23871,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -23928,7 +23952,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR111">
         <v>1.66</v>
@@ -24053,7 +24077,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24259,7 +24283,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24465,7 +24489,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24543,7 +24567,7 @@
         <v>2.44</v>
       </c>
       <c r="AP114">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ114">
         <v>2.42</v>
@@ -24955,7 +24979,7 @@
         <v>0.44</v>
       </c>
       <c r="AP116">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ116">
         <v>0.33</v>
@@ -25164,7 +25188,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ117">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR117">
         <v>1.75</v>
@@ -25289,7 +25313,7 @@
         <v>123</v>
       </c>
       <c r="P118" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q118">
         <v>1.74</v>
@@ -25370,7 +25394,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ118">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR118">
         <v>1.86</v>
@@ -25779,10 +25803,10 @@
         <v>1.67</v>
       </c>
       <c r="AP120">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ120">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR120">
         <v>1.84</v>
@@ -25985,7 +26009,7 @@
         <v>1.2</v>
       </c>
       <c r="AP121">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ121">
         <v>1.25</v>
@@ -26191,10 +26215,10 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ122">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR122">
         <v>1.44</v>
@@ -26319,7 +26343,7 @@
         <v>166</v>
       </c>
       <c r="P123" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q123">
         <v>6.04</v>
@@ -26606,7 +26630,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ124">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR124">
         <v>1.82</v>
@@ -26731,7 +26755,7 @@
         <v>167</v>
       </c>
       <c r="P125" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q125">
         <v>2.2</v>
@@ -26809,7 +26833,7 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ125">
         <v>1.08</v>
@@ -27221,10 +27245,10 @@
         <v>1.78</v>
       </c>
       <c r="AP127">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ127">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR127">
         <v>1.51</v>
@@ -27349,7 +27373,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27555,7 +27579,7 @@
         <v>169</v>
       </c>
       <c r="P129" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q129">
         <v>2</v>
@@ -27761,7 +27785,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q130">
         <v>2.28</v>
@@ -27839,10 +27863,10 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ130">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR130">
         <v>1.48</v>
@@ -28173,7 +28197,7 @@
         <v>172</v>
       </c>
       <c r="P132" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q132">
         <v>4.5</v>
@@ -28251,10 +28275,10 @@
         <v>1.6</v>
       </c>
       <c r="AP132">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR132">
         <v>1.4</v>
@@ -28460,7 +28484,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ133">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR133">
         <v>1.53</v>
@@ -28791,7 +28815,7 @@
         <v>82</v>
       </c>
       <c r="P135" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q135">
         <v>3.27</v>
@@ -28869,10 +28893,10 @@
         <v>0.55</v>
       </c>
       <c r="AP135">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ135">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR135">
         <v>1.39</v>
@@ -28997,7 +29021,7 @@
         <v>82</v>
       </c>
       <c r="P136" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29075,7 +29099,7 @@
         <v>1</v>
       </c>
       <c r="AP136">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ136">
         <v>1.17</v>
@@ -29203,7 +29227,7 @@
         <v>173</v>
       </c>
       <c r="P137" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q137">
         <v>2.68</v>
@@ -29281,10 +29305,10 @@
         <v>1.55</v>
       </c>
       <c r="AP137">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ137">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR137">
         <v>1.74</v>
@@ -29409,7 +29433,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q138">
         <v>4.2</v>
@@ -29487,7 +29511,7 @@
         <v>2.36</v>
       </c>
       <c r="AP138">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ138">
         <v>2.42</v>
@@ -29615,7 +29639,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -29696,7 +29720,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ139">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR139">
         <v>1.57</v>
@@ -30108,7 +30132,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ141">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR141">
         <v>1.49</v>
@@ -30314,7 +30338,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ142">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR142">
         <v>1.77</v>
@@ -30439,7 +30463,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q143">
         <v>2.2</v>
@@ -30723,7 +30747,7 @@
         <v>0.36</v>
       </c>
       <c r="AP144">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ144">
         <v>0.33</v>
@@ -31057,7 +31081,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q146">
         <v>1.83</v>
@@ -31150,31 +31174,31 @@
         <v>3.34</v>
       </c>
       <c r="AU146">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV146">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW146">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AX146">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY146">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AZ146">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BA146">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB146">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC146">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD146">
         <v>1.25</v>
@@ -31214,6 +31238,1036 @@
       </c>
       <c r="BP146">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:68">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>7844416</v>
+      </c>
+      <c r="C147" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F147">
+        <v>3</v>
+      </c>
+      <c r="G147" t="s">
+        <v>76</v>
+      </c>
+      <c r="H147" t="s">
+        <v>77</v>
+      </c>
+      <c r="I147">
+        <v>2</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>2</v>
+      </c>
+      <c r="L147">
+        <v>2</v>
+      </c>
+      <c r="M147">
+        <v>3</v>
+      </c>
+      <c r="N147">
+        <v>5</v>
+      </c>
+      <c r="O147" t="s">
+        <v>182</v>
+      </c>
+      <c r="P147" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q147">
+        <v>2.88</v>
+      </c>
+      <c r="R147">
+        <v>2.1</v>
+      </c>
+      <c r="S147">
+        <v>3.6</v>
+      </c>
+      <c r="T147">
+        <v>1.4</v>
+      </c>
+      <c r="U147">
+        <v>2.75</v>
+      </c>
+      <c r="V147">
+        <v>3</v>
+      </c>
+      <c r="W147">
+        <v>1.36</v>
+      </c>
+      <c r="X147">
+        <v>7</v>
+      </c>
+      <c r="Y147">
+        <v>1.08</v>
+      </c>
+      <c r="Z147">
+        <v>2.24</v>
+      </c>
+      <c r="AA147">
+        <v>3.29</v>
+      </c>
+      <c r="AB147">
+        <v>3.12</v>
+      </c>
+      <c r="AC147">
+        <v>1.01</v>
+      </c>
+      <c r="AD147">
+        <v>8.5</v>
+      </c>
+      <c r="AE147">
+        <v>1.28</v>
+      </c>
+      <c r="AF147">
+        <v>3.33</v>
+      </c>
+      <c r="AG147">
+        <v>1.95</v>
+      </c>
+      <c r="AH147">
+        <v>1.79</v>
+      </c>
+      <c r="AI147">
+        <v>1.8</v>
+      </c>
+      <c r="AJ147">
+        <v>1.91</v>
+      </c>
+      <c r="AK147">
+        <v>1.34</v>
+      </c>
+      <c r="AL147">
+        <v>1.3</v>
+      </c>
+      <c r="AM147">
+        <v>1.63</v>
+      </c>
+      <c r="AN147">
+        <v>1.08</v>
+      </c>
+      <c r="AO147">
+        <v>0.5</v>
+      </c>
+      <c r="AP147">
+        <v>1</v>
+      </c>
+      <c r="AQ147">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR147">
+        <v>1.38</v>
+      </c>
+      <c r="AS147">
+        <v>1.11</v>
+      </c>
+      <c r="AT147">
+        <v>2.49</v>
+      </c>
+      <c r="AU147">
+        <v>4</v>
+      </c>
+      <c r="AV147">
+        <v>4</v>
+      </c>
+      <c r="AW147">
+        <v>5</v>
+      </c>
+      <c r="AX147">
+        <v>13</v>
+      </c>
+      <c r="AY147">
+        <v>9</v>
+      </c>
+      <c r="AZ147">
+        <v>18</v>
+      </c>
+      <c r="BA147">
+        <v>6</v>
+      </c>
+      <c r="BB147">
+        <v>11</v>
+      </c>
+      <c r="BC147">
+        <v>17</v>
+      </c>
+      <c r="BD147">
+        <v>1.89</v>
+      </c>
+      <c r="BE147">
+        <v>6.45</v>
+      </c>
+      <c r="BF147">
+        <v>2.38</v>
+      </c>
+      <c r="BG147">
+        <v>1.22</v>
+      </c>
+      <c r="BH147">
+        <v>3.5</v>
+      </c>
+      <c r="BI147">
+        <v>1.44</v>
+      </c>
+      <c r="BJ147">
+        <v>2.51</v>
+      </c>
+      <c r="BK147">
+        <v>1.92</v>
+      </c>
+      <c r="BL147">
+        <v>1.88</v>
+      </c>
+      <c r="BM147">
+        <v>2.25</v>
+      </c>
+      <c r="BN147">
+        <v>1.54</v>
+      </c>
+      <c r="BO147">
+        <v>2.97</v>
+      </c>
+      <c r="BP147">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7844417</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F148">
+        <v>3</v>
+      </c>
+      <c r="G148" t="s">
+        <v>75</v>
+      </c>
+      <c r="H148" t="s">
+        <v>70</v>
+      </c>
+      <c r="I148">
+        <v>2</v>
+      </c>
+      <c r="J148">
+        <v>1</v>
+      </c>
+      <c r="K148">
+        <v>3</v>
+      </c>
+      <c r="L148">
+        <v>3</v>
+      </c>
+      <c r="M148">
+        <v>2</v>
+      </c>
+      <c r="N148">
+        <v>5</v>
+      </c>
+      <c r="O148" t="s">
+        <v>183</v>
+      </c>
+      <c r="P148" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q148">
+        <v>3</v>
+      </c>
+      <c r="R148">
+        <v>1.95</v>
+      </c>
+      <c r="S148">
+        <v>3.75</v>
+      </c>
+      <c r="T148">
+        <v>1.5</v>
+      </c>
+      <c r="U148">
+        <v>2.5</v>
+      </c>
+      <c r="V148">
+        <v>3.4</v>
+      </c>
+      <c r="W148">
+        <v>1.3</v>
+      </c>
+      <c r="X148">
+        <v>8</v>
+      </c>
+      <c r="Y148">
+        <v>1.06</v>
+      </c>
+      <c r="Z148">
+        <v>2.13</v>
+      </c>
+      <c r="AA148">
+        <v>3.17</v>
+      </c>
+      <c r="AB148">
+        <v>3.5</v>
+      </c>
+      <c r="AC148">
+        <v>1.03</v>
+      </c>
+      <c r="AD148">
+        <v>7.6</v>
+      </c>
+      <c r="AE148">
+        <v>1.39</v>
+      </c>
+      <c r="AF148">
+        <v>2.86</v>
+      </c>
+      <c r="AG148">
+        <v>2.15</v>
+      </c>
+      <c r="AH148">
+        <v>1.57</v>
+      </c>
+      <c r="AI148">
+        <v>1.91</v>
+      </c>
+      <c r="AJ148">
+        <v>1.8</v>
+      </c>
+      <c r="AK148">
+        <v>1.33</v>
+      </c>
+      <c r="AL148">
+        <v>1.32</v>
+      </c>
+      <c r="AM148">
+        <v>1.61</v>
+      </c>
+      <c r="AN148">
+        <v>1.25</v>
+      </c>
+      <c r="AO148">
+        <v>0.75</v>
+      </c>
+      <c r="AP148">
+        <v>1.38</v>
+      </c>
+      <c r="AQ148">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR148">
+        <v>1.5</v>
+      </c>
+      <c r="AS148">
+        <v>1.33</v>
+      </c>
+      <c r="AT148">
+        <v>2.83</v>
+      </c>
+      <c r="AU148">
+        <v>8</v>
+      </c>
+      <c r="AV148">
+        <v>4</v>
+      </c>
+      <c r="AW148">
+        <v>5</v>
+      </c>
+      <c r="AX148">
+        <v>4</v>
+      </c>
+      <c r="AY148">
+        <v>13</v>
+      </c>
+      <c r="AZ148">
+        <v>8</v>
+      </c>
+      <c r="BA148">
+        <v>3</v>
+      </c>
+      <c r="BB148">
+        <v>4</v>
+      </c>
+      <c r="BC148">
+        <v>7</v>
+      </c>
+      <c r="BD148">
+        <v>1.56</v>
+      </c>
+      <c r="BE148">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF148">
+        <v>2.86</v>
+      </c>
+      <c r="BG148">
+        <v>1.22</v>
+      </c>
+      <c r="BH148">
+        <v>3.5</v>
+      </c>
+      <c r="BI148">
+        <v>1.44</v>
+      </c>
+      <c r="BJ148">
+        <v>2.51</v>
+      </c>
+      <c r="BK148">
+        <v>1.78</v>
+      </c>
+      <c r="BL148">
+        <v>1.93</v>
+      </c>
+      <c r="BM148">
+        <v>2.27</v>
+      </c>
+      <c r="BN148">
+        <v>1.53</v>
+      </c>
+      <c r="BO148">
+        <v>2.97</v>
+      </c>
+      <c r="BP148">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7844418</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45745.58333333334</v>
+      </c>
+      <c r="F149">
+        <v>3</v>
+      </c>
+      <c r="G149" t="s">
+        <v>73</v>
+      </c>
+      <c r="H149" t="s">
+        <v>79</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="J149">
+        <v>1</v>
+      </c>
+      <c r="K149">
+        <v>2</v>
+      </c>
+      <c r="L149">
+        <v>2</v>
+      </c>
+      <c r="M149">
+        <v>2</v>
+      </c>
+      <c r="N149">
+        <v>4</v>
+      </c>
+      <c r="O149" t="s">
+        <v>184</v>
+      </c>
+      <c r="P149" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q149">
+        <v>3.6</v>
+      </c>
+      <c r="R149">
+        <v>2.1</v>
+      </c>
+      <c r="S149">
+        <v>2.88</v>
+      </c>
+      <c r="T149">
+        <v>1.4</v>
+      </c>
+      <c r="U149">
+        <v>2.75</v>
+      </c>
+      <c r="V149">
+        <v>3</v>
+      </c>
+      <c r="W149">
+        <v>1.36</v>
+      </c>
+      <c r="X149">
+        <v>7</v>
+      </c>
+      <c r="Y149">
+        <v>1.08</v>
+      </c>
+      <c r="Z149">
+        <v>3.14</v>
+      </c>
+      <c r="AA149">
+        <v>3.25</v>
+      </c>
+      <c r="AB149">
+        <v>2.25</v>
+      </c>
+      <c r="AC149">
+        <v>1.02</v>
+      </c>
+      <c r="AD149">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="AE149">
+        <v>1.33</v>
+      </c>
+      <c r="AF149">
+        <v>3.17</v>
+      </c>
+      <c r="AG149">
+        <v>1.98</v>
+      </c>
+      <c r="AH149">
+        <v>1.77</v>
+      </c>
+      <c r="AI149">
+        <v>1.8</v>
+      </c>
+      <c r="AJ149">
+        <v>1.91</v>
+      </c>
+      <c r="AK149">
+        <v>1.6</v>
+      </c>
+      <c r="AL149">
+        <v>1.32</v>
+      </c>
+      <c r="AM149">
+        <v>1.34</v>
+      </c>
+      <c r="AN149">
+        <v>1.42</v>
+      </c>
+      <c r="AO149">
+        <v>1.5</v>
+      </c>
+      <c r="AP149">
+        <v>1.38</v>
+      </c>
+      <c r="AQ149">
+        <v>1.46</v>
+      </c>
+      <c r="AR149">
+        <v>1.53</v>
+      </c>
+      <c r="AS149">
+        <v>1.48</v>
+      </c>
+      <c r="AT149">
+        <v>3.01</v>
+      </c>
+      <c r="AU149">
+        <v>4</v>
+      </c>
+      <c r="AV149">
+        <v>5</v>
+      </c>
+      <c r="AW149">
+        <v>15</v>
+      </c>
+      <c r="AX149">
+        <v>3</v>
+      </c>
+      <c r="AY149">
+        <v>24</v>
+      </c>
+      <c r="AZ149">
+        <v>8</v>
+      </c>
+      <c r="BA149">
+        <v>7</v>
+      </c>
+      <c r="BB149">
+        <v>2</v>
+      </c>
+      <c r="BC149">
+        <v>9</v>
+      </c>
+      <c r="BD149">
+        <v>2.25</v>
+      </c>
+      <c r="BE149">
+        <v>6.5</v>
+      </c>
+      <c r="BF149">
+        <v>1.97</v>
+      </c>
+      <c r="BG149">
+        <v>1.21</v>
+      </c>
+      <c r="BH149">
+        <v>3.78</v>
+      </c>
+      <c r="BI149">
+        <v>1.36</v>
+      </c>
+      <c r="BJ149">
+        <v>2.7</v>
+      </c>
+      <c r="BK149">
+        <v>1.82</v>
+      </c>
+      <c r="BL149">
+        <v>1.98</v>
+      </c>
+      <c r="BM149">
+        <v>2.11</v>
+      </c>
+      <c r="BN149">
+        <v>1.65</v>
+      </c>
+      <c r="BO149">
+        <v>2.75</v>
+      </c>
+      <c r="BP149">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7844419</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45746.4375</v>
+      </c>
+      <c r="F150">
+        <v>3</v>
+      </c>
+      <c r="G150" t="s">
+        <v>74</v>
+      </c>
+      <c r="H150" t="s">
+        <v>81</v>
+      </c>
+      <c r="I150">
+        <v>2</v>
+      </c>
+      <c r="J150">
+        <v>2</v>
+      </c>
+      <c r="K150">
+        <v>4</v>
+      </c>
+      <c r="L150">
+        <v>2</v>
+      </c>
+      <c r="M150">
+        <v>4</v>
+      </c>
+      <c r="N150">
+        <v>6</v>
+      </c>
+      <c r="O150" t="s">
+        <v>185</v>
+      </c>
+      <c r="P150" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q150">
+        <v>2.75</v>
+      </c>
+      <c r="R150">
+        <v>2.05</v>
+      </c>
+      <c r="S150">
+        <v>3.75</v>
+      </c>
+      <c r="T150">
+        <v>1.44</v>
+      </c>
+      <c r="U150">
+        <v>2.63</v>
+      </c>
+      <c r="V150">
+        <v>3.25</v>
+      </c>
+      <c r="W150">
+        <v>1.33</v>
+      </c>
+      <c r="X150">
+        <v>7.5</v>
+      </c>
+      <c r="Y150">
+        <v>1.07</v>
+      </c>
+      <c r="Z150">
+        <v>2.11</v>
+      </c>
+      <c r="AA150">
+        <v>3.41</v>
+      </c>
+      <c r="AB150">
+        <v>3.3</v>
+      </c>
+      <c r="AC150">
+        <v>1.01</v>
+      </c>
+      <c r="AD150">
+        <v>8.4</v>
+      </c>
+      <c r="AE150">
+        <v>1.34</v>
+      </c>
+      <c r="AF150">
+        <v>3.04</v>
+      </c>
+      <c r="AG150">
+        <v>2</v>
+      </c>
+      <c r="AH150">
+        <v>1.67</v>
+      </c>
+      <c r="AI150">
+        <v>1.91</v>
+      </c>
+      <c r="AJ150">
+        <v>1.8</v>
+      </c>
+      <c r="AK150">
+        <v>1.3</v>
+      </c>
+      <c r="AL150">
+        <v>1.31</v>
+      </c>
+      <c r="AM150">
+        <v>1.67</v>
+      </c>
+      <c r="AN150">
+        <v>1.75</v>
+      </c>
+      <c r="AO150">
+        <v>1.58</v>
+      </c>
+      <c r="AP150">
+        <v>1.62</v>
+      </c>
+      <c r="AQ150">
+        <v>1.69</v>
+      </c>
+      <c r="AR150">
+        <v>1.75</v>
+      </c>
+      <c r="AS150">
+        <v>1.49</v>
+      </c>
+      <c r="AT150">
+        <v>3.24</v>
+      </c>
+      <c r="AU150">
+        <v>6</v>
+      </c>
+      <c r="AV150">
+        <v>6</v>
+      </c>
+      <c r="AW150">
+        <v>6</v>
+      </c>
+      <c r="AX150">
+        <v>2</v>
+      </c>
+      <c r="AY150">
+        <v>12</v>
+      </c>
+      <c r="AZ150">
+        <v>8</v>
+      </c>
+      <c r="BA150">
+        <v>6</v>
+      </c>
+      <c r="BB150">
+        <v>0</v>
+      </c>
+      <c r="BC150">
+        <v>6</v>
+      </c>
+      <c r="BD150">
+        <v>1.71</v>
+      </c>
+      <c r="BE150">
+        <v>8.4</v>
+      </c>
+      <c r="BF150">
+        <v>2.49</v>
+      </c>
+      <c r="BG150">
+        <v>1.22</v>
+      </c>
+      <c r="BH150">
+        <v>3.5</v>
+      </c>
+      <c r="BI150">
+        <v>1.44</v>
+      </c>
+      <c r="BJ150">
+        <v>2.51</v>
+      </c>
+      <c r="BK150">
+        <v>1.92</v>
+      </c>
+      <c r="BL150">
+        <v>1.88</v>
+      </c>
+      <c r="BM150">
+        <v>2.28</v>
+      </c>
+      <c r="BN150">
+        <v>1.53</v>
+      </c>
+      <c r="BO150">
+        <v>3.04</v>
+      </c>
+      <c r="BP150">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7844420</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45746.4375</v>
+      </c>
+      <c r="F151">
+        <v>3</v>
+      </c>
+      <c r="G151" t="s">
+        <v>72</v>
+      </c>
+      <c r="H151" t="s">
+        <v>80</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+      <c r="K151">
+        <v>1</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>1</v>
+      </c>
+      <c r="O151" t="s">
+        <v>82</v>
+      </c>
+      <c r="P151" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q151">
+        <v>3</v>
+      </c>
+      <c r="R151">
+        <v>2.2</v>
+      </c>
+      <c r="S151">
+        <v>3.2</v>
+      </c>
+      <c r="T151">
+        <v>1.36</v>
+      </c>
+      <c r="U151">
+        <v>3</v>
+      </c>
+      <c r="V151">
+        <v>2.63</v>
+      </c>
+      <c r="W151">
+        <v>1.44</v>
+      </c>
+      <c r="X151">
+        <v>6.5</v>
+      </c>
+      <c r="Y151">
+        <v>1.1</v>
+      </c>
+      <c r="Z151">
+        <v>2.59</v>
+      </c>
+      <c r="AA151">
+        <v>2.88</v>
+      </c>
+      <c r="AB151">
+        <v>2.96</v>
+      </c>
+      <c r="AC151">
+        <v>1.02</v>
+      </c>
+      <c r="AD151">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE151">
+        <v>1.24</v>
+      </c>
+      <c r="AF151">
+        <v>3.86</v>
+      </c>
+      <c r="AG151">
+        <v>1.85</v>
+      </c>
+      <c r="AH151">
+        <v>1.89</v>
+      </c>
+      <c r="AI151">
+        <v>1.62</v>
+      </c>
+      <c r="AJ151">
+        <v>2.2</v>
+      </c>
+      <c r="AK151">
+        <v>1.36</v>
+      </c>
+      <c r="AL151">
+        <v>1.35</v>
+      </c>
+      <c r="AM151">
+        <v>1.53</v>
+      </c>
+      <c r="AN151">
+        <v>1.17</v>
+      </c>
+      <c r="AO151">
+        <v>0.83</v>
+      </c>
+      <c r="AP151">
+        <v>1.08</v>
+      </c>
+      <c r="AQ151">
+        <v>1</v>
+      </c>
+      <c r="AR151">
+        <v>1.43</v>
+      </c>
+      <c r="AS151">
+        <v>1.34</v>
+      </c>
+      <c r="AT151">
+        <v>2.77</v>
+      </c>
+      <c r="AU151">
+        <v>5</v>
+      </c>
+      <c r="AV151">
+        <v>3</v>
+      </c>
+      <c r="AW151">
+        <v>3</v>
+      </c>
+      <c r="AX151">
+        <v>5</v>
+      </c>
+      <c r="AY151">
+        <v>8</v>
+      </c>
+      <c r="AZ151">
+        <v>8</v>
+      </c>
+      <c r="BA151">
+        <v>2</v>
+      </c>
+      <c r="BB151">
+        <v>7</v>
+      </c>
+      <c r="BC151">
+        <v>9</v>
+      </c>
+      <c r="BD151">
+        <v>2.16</v>
+      </c>
+      <c r="BE151">
+        <v>6.45</v>
+      </c>
+      <c r="BF151">
+        <v>2.05</v>
+      </c>
+      <c r="BG151">
+        <v>1.23</v>
+      </c>
+      <c r="BH151">
+        <v>3.6</v>
+      </c>
+      <c r="BI151">
+        <v>1.44</v>
+      </c>
+      <c r="BJ151">
+        <v>2.6</v>
+      </c>
+      <c r="BK151">
+        <v>1.8</v>
+      </c>
+      <c r="BL151">
+        <v>2</v>
+      </c>
+      <c r="BM151">
+        <v>2.18</v>
+      </c>
+      <c r="BN151">
+        <v>1.64</v>
+      </c>
+      <c r="BO151">
+        <v>2.77</v>
+      </c>
+      <c r="BP151">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="264">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -574,6 +574,12 @@
     <t>['34', '42']</t>
   </si>
   <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['68']</t>
+  </si>
+  <si>
     <t>['5', '42', '80', '90+2']</t>
   </si>
   <si>
@@ -625,9 +631,6 @@
     <t>['44', '72']</t>
   </si>
   <si>
-    <t>['53']</t>
-  </si>
-  <si>
     <t>['56', '89']</t>
   </si>
   <si>
@@ -674,9 +677,6 @@
   </si>
   <si>
     <t>['12']</t>
-  </si>
-  <si>
-    <t>['68']</t>
   </si>
   <si>
     <t>['27', '85']</t>
@@ -800,6 +800,12 @@
   </si>
   <si>
     <t>['22', '30', '58', '71']</t>
+  </si>
+  <si>
+    <t>['20']</t>
+  </si>
+  <si>
+    <t>['11', '13', '46', '72', '84']</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1495,10 +1501,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1829,7 +1835,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -1910,7 +1916,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ4">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2035,7 +2041,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2653,7 +2659,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -2937,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ9">
         <v>1.25</v>
@@ -3146,7 +3152,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ10">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3349,10 +3355,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ11">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3761,10 +3767,10 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3970,7 +3976,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ14">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR14">
         <v>1.21</v>
@@ -4507,7 +4513,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q17">
         <v>2.57</v>
@@ -4713,7 +4719,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4919,7 +4925,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q19">
         <v>1.7</v>
@@ -5125,7 +5131,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5203,7 +5209,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ20">
         <v>0.33</v>
@@ -5537,7 +5543,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5618,7 +5624,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ22">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR22">
         <v>1.26</v>
@@ -5743,7 +5749,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -5821,7 +5827,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ23">
         <v>2.08</v>
@@ -6027,7 +6033,7 @@
         <v>0.5</v>
       </c>
       <c r="AP24">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ24">
         <v>0.6899999999999999</v>
@@ -6155,7 +6161,7 @@
         <v>82</v>
       </c>
       <c r="P25" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q25">
         <v>3.9</v>
@@ -6236,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="AQ25">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR25">
         <v>1.52</v>
@@ -6361,7 +6367,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6442,7 +6448,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR26">
         <v>1.13</v>
@@ -6645,7 +6651,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ27">
         <v>1.25</v>
@@ -6773,7 +6779,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6854,7 +6860,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR28">
         <v>1.13</v>
@@ -6979,7 +6985,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7185,7 +7191,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7391,7 +7397,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7597,7 +7603,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q32">
         <v>2.1</v>
@@ -7678,7 +7684,7 @@
         <v>1</v>
       </c>
       <c r="AQ32">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR32">
         <v>1.38</v>
@@ -7803,7 +7809,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -7881,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP33">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ33">
         <v>0.6899999999999999</v>
@@ -8009,7 +8015,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -8215,7 +8221,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8293,10 +8299,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ35">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR35">
         <v>2.59</v>
@@ -8708,7 +8714,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ37">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR37">
         <v>1.31</v>
@@ -8833,7 +8839,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -8911,7 +8917,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ38">
         <v>1.46</v>
@@ -9039,7 +9045,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q39">
         <v>4.36</v>
@@ -9245,7 +9251,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q40">
         <v>4.33</v>
@@ -9323,7 +9329,7 @@
         <v>1.75</v>
       </c>
       <c r="AP40">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ40">
         <v>1.46</v>
@@ -9451,7 +9457,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -10150,7 +10156,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10275,7 +10281,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10481,7 +10487,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10562,7 +10568,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ46">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR46">
         <v>1.09</v>
@@ -10687,7 +10693,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q47">
         <v>2.48</v>
@@ -10765,10 +10771,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ47">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR47">
         <v>1.58</v>
@@ -10893,7 +10899,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q48">
         <v>2.49</v>
@@ -11177,7 +11183,7 @@
         <v>1.67</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ49">
         <v>2.08</v>
@@ -11305,7 +11311,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11589,10 +11595,10 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ51">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR51">
         <v>2.09</v>
@@ -11717,7 +11723,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q52">
         <v>3.22</v>
@@ -12001,10 +12007,10 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ53">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR53">
         <v>1.48</v>
@@ -12129,7 +12135,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q54">
         <v>3.6</v>
@@ -12335,7 +12341,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12541,7 +12547,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12619,7 +12625,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ56">
         <v>1.69</v>
@@ -12828,7 +12834,7 @@
         <v>1</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR57">
         <v>1.64</v>
@@ -12953,7 +12959,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13159,7 +13165,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13443,7 +13449,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ60">
         <v>0.6899999999999999</v>
@@ -13571,7 +13577,7 @@
         <v>82</v>
       </c>
       <c r="P61" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13652,7 +13658,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ61">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR61">
         <v>1.75</v>
@@ -13855,7 +13861,7 @@
         <v>0.75</v>
       </c>
       <c r="AP62">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ62">
         <v>0.33</v>
@@ -14064,7 +14070,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ63">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR63">
         <v>1.28</v>
@@ -14473,10 +14479,10 @@
         <v>0.8</v>
       </c>
       <c r="AP65">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ65">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR65">
         <v>1.94</v>
@@ -14679,7 +14685,7 @@
         <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ66">
         <v>1.25</v>
@@ -14885,7 +14891,7 @@
         <v>1.8</v>
       </c>
       <c r="AP67">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ67">
         <v>2.08</v>
@@ -15297,7 +15303,7 @@
         <v>0.8</v>
       </c>
       <c r="AP69">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ69">
         <v>0.42</v>
@@ -15503,10 +15509,10 @@
         <v>0.83</v>
       </c>
       <c r="AP70">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ70">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR70">
         <v>1.54</v>
@@ -15709,10 +15715,10 @@
         <v>3</v>
       </c>
       <c r="AP71">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ71">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR71">
         <v>1.47</v>
@@ -15918,7 +15924,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ72">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR72">
         <v>1.58</v>
@@ -16536,7 +16542,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR75">
         <v>1.7</v>
@@ -16742,7 +16748,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ76">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR76">
         <v>1.55</v>
@@ -17151,7 +17157,7 @@
         <v>0.6</v>
       </c>
       <c r="AP78">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ78">
         <v>0.33</v>
@@ -17563,7 +17569,7 @@
         <v>0.67</v>
       </c>
       <c r="AP80">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ80">
         <v>0.42</v>
@@ -18387,7 +18393,7 @@
         <v>0.5</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ84">
         <v>0.33</v>
@@ -18596,7 +18602,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ85">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR85">
         <v>1.4</v>
@@ -18799,10 +18805,10 @@
         <v>0.71</v>
       </c>
       <c r="AP86">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ86">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR86">
         <v>1.53</v>
@@ -19005,10 +19011,10 @@
         <v>0.71</v>
       </c>
       <c r="AP87">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ87">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR87">
         <v>1.54</v>
@@ -19339,7 +19345,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19417,7 +19423,7 @@
         <v>2.14</v>
       </c>
       <c r="AP89">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ89">
         <v>2.08</v>
@@ -19626,7 +19632,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ90">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR90">
         <v>1.54</v>
@@ -19829,7 +19835,7 @@
         <v>1.71</v>
       </c>
       <c r="AP91">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ91">
         <v>1.69</v>
@@ -21068,7 +21074,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ97">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR97">
         <v>1.85</v>
@@ -21480,7 +21486,7 @@
         <v>1</v>
       </c>
       <c r="AQ99">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR99">
         <v>1.48</v>
@@ -21686,7 +21692,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ100">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR100">
         <v>1.45</v>
@@ -21889,10 +21895,10 @@
         <v>2.75</v>
       </c>
       <c r="AP101">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ101">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR101">
         <v>1.8</v>
@@ -22301,7 +22307,7 @@
         <v>0.5</v>
       </c>
       <c r="AP103">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ103">
         <v>0.6899999999999999</v>
@@ -22919,10 +22925,10 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR106">
         <v>1.51</v>
@@ -23331,7 +23337,7 @@
         <v>1.88</v>
       </c>
       <c r="AP108">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ108">
         <v>1.69</v>
@@ -23949,7 +23955,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ111">
         <v>0.6899999999999999</v>
@@ -24158,7 +24164,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ112">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR112">
         <v>1.46</v>
@@ -24361,7 +24367,7 @@
         <v>1</v>
       </c>
       <c r="AP113">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ113">
         <v>1.25</v>
@@ -24570,7 +24576,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ114">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR114">
         <v>1.52</v>
@@ -24773,10 +24779,10 @@
         <v>1.11</v>
       </c>
       <c r="AP115">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ115">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR115">
         <v>1.54</v>
@@ -25394,7 +25400,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR118">
         <v>1.86</v>
@@ -25597,7 +25603,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP119">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ119">
         <v>0.42</v>
@@ -26421,10 +26427,10 @@
         <v>2.5</v>
       </c>
       <c r="AP123">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ123">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -26627,7 +26633,7 @@
         <v>1.6</v>
       </c>
       <c r="AP124">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ124">
         <v>1.46</v>
@@ -26755,7 +26761,7 @@
         <v>167</v>
       </c>
       <c r="P125" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q125">
         <v>2.2</v>
@@ -26836,7 +26842,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ125">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR125">
         <v>1.74</v>
@@ -27373,7 +27379,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27660,7 +27666,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ129">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR129">
         <v>1.8</v>
@@ -27866,7 +27872,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR130">
         <v>1.48</v>
@@ -28069,7 +28075,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ131">
         <v>0.42</v>
@@ -28481,7 +28487,7 @@
         <v>0.5</v>
       </c>
       <c r="AP133">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ133">
         <v>0.6899999999999999</v>
@@ -28687,10 +28693,10 @@
         <v>1.18</v>
       </c>
       <c r="AP134">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ134">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR134">
         <v>1.78</v>
@@ -29102,7 +29108,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ136">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR136">
         <v>1.47</v>
@@ -29514,7 +29520,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ138">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR138">
         <v>1.56</v>
@@ -29717,10 +29723,10 @@
         <v>0.91</v>
       </c>
       <c r="AP139">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ139">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR139">
         <v>1.57</v>
@@ -30129,7 +30135,7 @@
         <v>0.55</v>
       </c>
       <c r="AP141">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ141">
         <v>0.6899999999999999</v>
@@ -30335,7 +30341,7 @@
         <v>1.73</v>
       </c>
       <c r="AP142">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ142">
         <v>1.69</v>
@@ -31162,7 +31168,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ146">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR146">
         <v>1.92</v>
@@ -32192,7 +32198,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ151">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR151">
         <v>1.43</v>
@@ -32268,6 +32274,830 @@
       </c>
       <c r="BP151">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7844421</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45752.4375</v>
+      </c>
+      <c r="F152">
+        <v>4</v>
+      </c>
+      <c r="G152" t="s">
+        <v>79</v>
+      </c>
+      <c r="H152" t="s">
+        <v>71</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+      <c r="J152">
+        <v>1</v>
+      </c>
+      <c r="K152">
+        <v>2</v>
+      </c>
+      <c r="L152">
+        <v>1</v>
+      </c>
+      <c r="M152">
+        <v>1</v>
+      </c>
+      <c r="N152">
+        <v>2</v>
+      </c>
+      <c r="O152" t="s">
+        <v>108</v>
+      </c>
+      <c r="P152" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q152">
+        <v>2.3</v>
+      </c>
+      <c r="R152">
+        <v>2.2</v>
+      </c>
+      <c r="S152">
+        <v>4.75</v>
+      </c>
+      <c r="T152">
+        <v>1.36</v>
+      </c>
+      <c r="U152">
+        <v>3</v>
+      </c>
+      <c r="V152">
+        <v>2.75</v>
+      </c>
+      <c r="W152">
+        <v>1.4</v>
+      </c>
+      <c r="X152">
+        <v>6.5</v>
+      </c>
+      <c r="Y152">
+        <v>1.1</v>
+      </c>
+      <c r="Z152">
+        <v>1.61</v>
+      </c>
+      <c r="AA152">
+        <v>3.94</v>
+      </c>
+      <c r="AB152">
+        <v>5.1</v>
+      </c>
+      <c r="AC152">
+        <v>1.04</v>
+      </c>
+      <c r="AD152">
+        <v>9</v>
+      </c>
+      <c r="AE152">
+        <v>1.28</v>
+      </c>
+      <c r="AF152">
+        <v>3.55</v>
+      </c>
+      <c r="AG152">
+        <v>1.8</v>
+      </c>
+      <c r="AH152">
+        <v>1.94</v>
+      </c>
+      <c r="AI152">
+        <v>1.83</v>
+      </c>
+      <c r="AJ152">
+        <v>1.83</v>
+      </c>
+      <c r="AK152">
+        <v>1.19</v>
+      </c>
+      <c r="AL152">
+        <v>1.25</v>
+      </c>
+      <c r="AM152">
+        <v>2.1</v>
+      </c>
+      <c r="AN152">
+        <v>1.5</v>
+      </c>
+      <c r="AO152">
+        <v>1.08</v>
+      </c>
+      <c r="AP152">
+        <v>1.46</v>
+      </c>
+      <c r="AQ152">
+        <v>1.07</v>
+      </c>
+      <c r="AR152">
+        <v>1.76</v>
+      </c>
+      <c r="AS152">
+        <v>1.42</v>
+      </c>
+      <c r="AT152">
+        <v>3.18</v>
+      </c>
+      <c r="AU152">
+        <v>5</v>
+      </c>
+      <c r="AV152">
+        <v>7</v>
+      </c>
+      <c r="AW152">
+        <v>18</v>
+      </c>
+      <c r="AX152">
+        <v>6</v>
+      </c>
+      <c r="AY152">
+        <v>23</v>
+      </c>
+      <c r="AZ152">
+        <v>13</v>
+      </c>
+      <c r="BA152">
+        <v>1</v>
+      </c>
+      <c r="BB152">
+        <v>3</v>
+      </c>
+      <c r="BC152">
+        <v>4</v>
+      </c>
+      <c r="BD152">
+        <v>1.39</v>
+      </c>
+      <c r="BE152">
+        <v>9.6</v>
+      </c>
+      <c r="BF152">
+        <v>3.54</v>
+      </c>
+      <c r="BG152">
+        <v>1.17</v>
+      </c>
+      <c r="BH152">
+        <v>4.2</v>
+      </c>
+      <c r="BI152">
+        <v>1.28</v>
+      </c>
+      <c r="BJ152">
+        <v>3.05</v>
+      </c>
+      <c r="BK152">
+        <v>1.54</v>
+      </c>
+      <c r="BL152">
+        <v>2.25</v>
+      </c>
+      <c r="BM152">
+        <v>1.92</v>
+      </c>
+      <c r="BN152">
+        <v>1.79</v>
+      </c>
+      <c r="BO152">
+        <v>2.45</v>
+      </c>
+      <c r="BP152">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7844422</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45752.4375</v>
+      </c>
+      <c r="F153">
+        <v>4</v>
+      </c>
+      <c r="G153" t="s">
+        <v>77</v>
+      </c>
+      <c r="H153" t="s">
+        <v>72</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>1</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>1</v>
+      </c>
+      <c r="O153" t="s">
+        <v>186</v>
+      </c>
+      <c r="P153" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q153">
+        <v>2.63</v>
+      </c>
+      <c r="R153">
+        <v>2.1</v>
+      </c>
+      <c r="S153">
+        <v>3.75</v>
+      </c>
+      <c r="T153">
+        <v>1.4</v>
+      </c>
+      <c r="U153">
+        <v>2.75</v>
+      </c>
+      <c r="V153">
+        <v>2.75</v>
+      </c>
+      <c r="W153">
+        <v>1.4</v>
+      </c>
+      <c r="X153">
+        <v>7</v>
+      </c>
+      <c r="Y153">
+        <v>1.08</v>
+      </c>
+      <c r="Z153">
+        <v>1.92</v>
+      </c>
+      <c r="AA153">
+        <v>3.53</v>
+      </c>
+      <c r="AB153">
+        <v>3.74</v>
+      </c>
+      <c r="AC153">
+        <v>1.05</v>
+      </c>
+      <c r="AD153">
+        <v>8.5</v>
+      </c>
+      <c r="AE153">
+        <v>1.28</v>
+      </c>
+      <c r="AF153">
+        <v>3.4</v>
+      </c>
+      <c r="AG153">
+        <v>1.83</v>
+      </c>
+      <c r="AH153">
+        <v>1.91</v>
+      </c>
+      <c r="AI153">
+        <v>1.73</v>
+      </c>
+      <c r="AJ153">
+        <v>2</v>
+      </c>
+      <c r="AK153">
+        <v>1.23</v>
+      </c>
+      <c r="AL153">
+        <v>1.27</v>
+      </c>
+      <c r="AM153">
+        <v>1.9</v>
+      </c>
+      <c r="AN153">
+        <v>1.42</v>
+      </c>
+      <c r="AO153">
+        <v>1.17</v>
+      </c>
+      <c r="AP153">
+        <v>1.54</v>
+      </c>
+      <c r="AQ153">
+        <v>1.08</v>
+      </c>
+      <c r="AR153">
+        <v>1.59</v>
+      </c>
+      <c r="AS153">
+        <v>1.27</v>
+      </c>
+      <c r="AT153">
+        <v>2.86</v>
+      </c>
+      <c r="AU153">
+        <v>11</v>
+      </c>
+      <c r="AV153">
+        <v>2</v>
+      </c>
+      <c r="AW153">
+        <v>2</v>
+      </c>
+      <c r="AX153">
+        <v>10</v>
+      </c>
+      <c r="AY153">
+        <v>13</v>
+      </c>
+      <c r="AZ153">
+        <v>12</v>
+      </c>
+      <c r="BA153">
+        <v>2</v>
+      </c>
+      <c r="BB153">
+        <v>1</v>
+      </c>
+      <c r="BC153">
+        <v>3</v>
+      </c>
+      <c r="BD153">
+        <v>1.46</v>
+      </c>
+      <c r="BE153">
+        <v>9.1</v>
+      </c>
+      <c r="BF153">
+        <v>3.22</v>
+      </c>
+      <c r="BG153">
+        <v>1.21</v>
+      </c>
+      <c r="BH153">
+        <v>3.58</v>
+      </c>
+      <c r="BI153">
+        <v>1.42</v>
+      </c>
+      <c r="BJ153">
+        <v>2.57</v>
+      </c>
+      <c r="BK153">
+        <v>1.76</v>
+      </c>
+      <c r="BL153">
+        <v>1.95</v>
+      </c>
+      <c r="BM153">
+        <v>2.21</v>
+      </c>
+      <c r="BN153">
+        <v>1.56</v>
+      </c>
+      <c r="BO153">
+        <v>2.92</v>
+      </c>
+      <c r="BP153">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7844423</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45752.4375</v>
+      </c>
+      <c r="F154">
+        <v>4</v>
+      </c>
+      <c r="G154" t="s">
+        <v>70</v>
+      </c>
+      <c r="H154" t="s">
+        <v>80</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>1</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+      <c r="N154">
+        <v>1</v>
+      </c>
+      <c r="O154" t="s">
+        <v>187</v>
+      </c>
+      <c r="P154" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q154">
+        <v>2.88</v>
+      </c>
+      <c r="R154">
+        <v>2.05</v>
+      </c>
+      <c r="S154">
+        <v>3.6</v>
+      </c>
+      <c r="T154">
+        <v>1.44</v>
+      </c>
+      <c r="U154">
+        <v>2.63</v>
+      </c>
+      <c r="V154">
+        <v>3</v>
+      </c>
+      <c r="W154">
+        <v>1.36</v>
+      </c>
+      <c r="X154">
+        <v>7.5</v>
+      </c>
+      <c r="Y154">
+        <v>1.07</v>
+      </c>
+      <c r="Z154">
+        <v>2.25</v>
+      </c>
+      <c r="AA154">
+        <v>3.06</v>
+      </c>
+      <c r="AB154">
+        <v>3.34</v>
+      </c>
+      <c r="AC154">
+        <v>1.07</v>
+      </c>
+      <c r="AD154">
+        <v>7.5</v>
+      </c>
+      <c r="AE154">
+        <v>1.35</v>
+      </c>
+      <c r="AF154">
+        <v>3</v>
+      </c>
+      <c r="AG154">
+        <v>1.98</v>
+      </c>
+      <c r="AH154">
+        <v>1.77</v>
+      </c>
+      <c r="AI154">
+        <v>1.8</v>
+      </c>
+      <c r="AJ154">
+        <v>1.91</v>
+      </c>
+      <c r="AK154">
+        <v>1.32</v>
+      </c>
+      <c r="AL154">
+        <v>1.32</v>
+      </c>
+      <c r="AM154">
+        <v>1.63</v>
+      </c>
+      <c r="AN154">
+        <v>1.33</v>
+      </c>
+      <c r="AO154">
+        <v>1</v>
+      </c>
+      <c r="AP154">
+        <v>1.46</v>
+      </c>
+      <c r="AQ154">
+        <v>0.93</v>
+      </c>
+      <c r="AR154">
+        <v>1.44</v>
+      </c>
+      <c r="AS154">
+        <v>1.32</v>
+      </c>
+      <c r="AT154">
+        <v>2.76</v>
+      </c>
+      <c r="AU154">
+        <v>5</v>
+      </c>
+      <c r="AV154">
+        <v>3</v>
+      </c>
+      <c r="AW154">
+        <v>5</v>
+      </c>
+      <c r="AX154">
+        <v>7</v>
+      </c>
+      <c r="AY154">
+        <v>10</v>
+      </c>
+      <c r="AZ154">
+        <v>10</v>
+      </c>
+      <c r="BA154">
+        <v>1</v>
+      </c>
+      <c r="BB154">
+        <v>1</v>
+      </c>
+      <c r="BC154">
+        <v>2</v>
+      </c>
+      <c r="BD154">
+        <v>1.71</v>
+      </c>
+      <c r="BE154">
+        <v>6.65</v>
+      </c>
+      <c r="BF154">
+        <v>2.7</v>
+      </c>
+      <c r="BG154">
+        <v>1.19</v>
+      </c>
+      <c r="BH154">
+        <v>3.78</v>
+      </c>
+      <c r="BI154">
+        <v>1.4</v>
+      </c>
+      <c r="BJ154">
+        <v>2.64</v>
+      </c>
+      <c r="BK154">
+        <v>1.71</v>
+      </c>
+      <c r="BL154">
+        <v>2.02</v>
+      </c>
+      <c r="BM154">
+        <v>2.15</v>
+      </c>
+      <c r="BN154">
+        <v>1.59</v>
+      </c>
+      <c r="BO154">
+        <v>2.83</v>
+      </c>
+      <c r="BP154">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7844424</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45752.54166666666</v>
+      </c>
+      <c r="F155">
+        <v>4</v>
+      </c>
+      <c r="G155" t="s">
+        <v>81</v>
+      </c>
+      <c r="H155" t="s">
+        <v>78</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>2</v>
+      </c>
+      <c r="K155">
+        <v>2</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>5</v>
+      </c>
+      <c r="N155">
+        <v>5</v>
+      </c>
+      <c r="O155" t="s">
+        <v>82</v>
+      </c>
+      <c r="P155" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q155">
+        <v>3</v>
+      </c>
+      <c r="R155">
+        <v>2.25</v>
+      </c>
+      <c r="S155">
+        <v>3</v>
+      </c>
+      <c r="T155">
+        <v>1.33</v>
+      </c>
+      <c r="U155">
+        <v>3.25</v>
+      </c>
+      <c r="V155">
+        <v>2.5</v>
+      </c>
+      <c r="W155">
+        <v>1.5</v>
+      </c>
+      <c r="X155">
+        <v>6</v>
+      </c>
+      <c r="Y155">
+        <v>1.11</v>
+      </c>
+      <c r="Z155">
+        <v>2.82</v>
+      </c>
+      <c r="AA155">
+        <v>3.35</v>
+      </c>
+      <c r="AB155">
+        <v>2.4</v>
+      </c>
+      <c r="AC155">
+        <v>1.04</v>
+      </c>
+      <c r="AD155">
+        <v>9</v>
+      </c>
+      <c r="AE155">
+        <v>1.22</v>
+      </c>
+      <c r="AF155">
+        <v>4</v>
+      </c>
+      <c r="AG155">
+        <v>1.61</v>
+      </c>
+      <c r="AH155">
+        <v>2.1</v>
+      </c>
+      <c r="AI155">
+        <v>1.57</v>
+      </c>
+      <c r="AJ155">
+        <v>2.25</v>
+      </c>
+      <c r="AK155">
+        <v>1.55</v>
+      </c>
+      <c r="AL155">
+        <v>1.28</v>
+      </c>
+      <c r="AM155">
+        <v>1.44</v>
+      </c>
+      <c r="AN155">
+        <v>2.25</v>
+      </c>
+      <c r="AO155">
+        <v>2.42</v>
+      </c>
+      <c r="AP155">
+        <v>2.08</v>
+      </c>
+      <c r="AQ155">
+        <v>2.46</v>
+      </c>
+      <c r="AR155">
+        <v>1.75</v>
+      </c>
+      <c r="AS155">
+        <v>1.68</v>
+      </c>
+      <c r="AT155">
+        <v>3.43</v>
+      </c>
+      <c r="AU155">
+        <v>4</v>
+      </c>
+      <c r="AV155">
+        <v>8</v>
+      </c>
+      <c r="AW155">
+        <v>8</v>
+      </c>
+      <c r="AX155">
+        <v>6</v>
+      </c>
+      <c r="AY155">
+        <v>12</v>
+      </c>
+      <c r="AZ155">
+        <v>14</v>
+      </c>
+      <c r="BA155">
+        <v>5</v>
+      </c>
+      <c r="BB155">
+        <v>6</v>
+      </c>
+      <c r="BC155">
+        <v>11</v>
+      </c>
+      <c r="BD155">
+        <v>2.16</v>
+      </c>
+      <c r="BE155">
+        <v>6.45</v>
+      </c>
+      <c r="BF155">
+        <v>2.05</v>
+      </c>
+      <c r="BG155">
+        <v>1.19</v>
+      </c>
+      <c r="BH155">
+        <v>3.74</v>
+      </c>
+      <c r="BI155">
+        <v>1.4</v>
+      </c>
+      <c r="BJ155">
+        <v>2.64</v>
+      </c>
+      <c r="BK155">
+        <v>1.72</v>
+      </c>
+      <c r="BL155">
+        <v>2</v>
+      </c>
+      <c r="BM155">
+        <v>2.17</v>
+      </c>
+      <c r="BN155">
+        <v>1.58</v>
+      </c>
+      <c r="BO155">
+        <v>2.83</v>
+      </c>
+      <c r="BP155">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="266">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -580,6 +580,9 @@
     <t>['68']</t>
   </si>
   <si>
+    <t>['28', '67']</t>
+  </si>
+  <si>
     <t>['5', '42', '80', '90+2']</t>
   </si>
   <si>
@@ -806,6 +809,9 @@
   </si>
   <si>
     <t>['11', '13', '46', '72', '84']</t>
+  </si>
+  <si>
+    <t>['51', '59']</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1835,7 +1841,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q4">
         <v>4.75</v>
@@ -2041,7 +2047,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2119,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
         <v>1.46</v>
@@ -2531,10 +2537,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ7">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2659,7 +2665,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q8">
         <v>2.56</v>
@@ -3564,7 +3570,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ12">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3973,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ14">
         <v>1.07</v>
@@ -4179,7 +4185,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ15">
         <v>0.6899999999999999</v>
@@ -4513,7 +4519,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q17">
         <v>2.57</v>
@@ -4719,7 +4725,7 @@
         <v>82</v>
       </c>
       <c r="P18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q18">
         <v>4.5</v>
@@ -4925,7 +4931,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q19">
         <v>1.7</v>
@@ -5131,7 +5137,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q20">
         <v>2.07</v>
@@ -5212,7 +5218,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ20">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR20">
         <v>1.25</v>
@@ -5543,7 +5549,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -5621,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>1.08</v>
@@ -5749,7 +5755,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q23">
         <v>4.95</v>
@@ -5830,7 +5836,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ23">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR23">
         <v>1.55</v>
@@ -6161,7 +6167,7 @@
         <v>82</v>
       </c>
       <c r="P25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q25">
         <v>3.9</v>
@@ -6367,7 +6373,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6445,7 +6451,7 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ26">
         <v>0.93</v>
@@ -6779,7 +6785,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6985,7 +6991,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q29">
         <v>2.53</v>
@@ -7066,7 +7072,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ29">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR29">
         <v>1.86</v>
@@ -7191,7 +7197,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7397,7 +7403,7 @@
         <v>102</v>
       </c>
       <c r="P31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -7603,7 +7609,7 @@
         <v>103</v>
       </c>
       <c r="P32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q32">
         <v>2.1</v>
@@ -7809,7 +7815,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -8221,7 +8227,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8505,10 +8511,10 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR36">
         <v>1.33</v>
@@ -8711,7 +8717,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ37">
         <v>1.07</v>
@@ -8839,7 +8845,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9045,7 +9051,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q39">
         <v>4.36</v>
@@ -9123,7 +9129,7 @@
         <v>1.67</v>
       </c>
       <c r="AP39">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39">
         <v>1.69</v>
@@ -9251,7 +9257,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q40">
         <v>4.33</v>
@@ -9457,7 +9463,7 @@
         <v>111</v>
       </c>
       <c r="P41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9950,7 +9956,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ43">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR43">
         <v>1.8</v>
@@ -10281,7 +10287,7 @@
         <v>115</v>
       </c>
       <c r="P45" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10487,7 +10493,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10693,7 +10699,7 @@
         <v>117</v>
       </c>
       <c r="P47" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q47">
         <v>2.48</v>
@@ -10899,7 +10905,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q48">
         <v>2.49</v>
@@ -11186,7 +11192,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ49">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR49">
         <v>1.98</v>
@@ -11311,7 +11317,7 @@
         <v>119</v>
       </c>
       <c r="P50" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q50">
         <v>2.5</v>
@@ -11389,7 +11395,7 @@
         <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ50">
         <v>0.6899999999999999</v>
@@ -11723,7 +11729,7 @@
         <v>121</v>
       </c>
       <c r="P52" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q52">
         <v>3.22</v>
@@ -11801,7 +11807,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ52">
         <v>0.42</v>
@@ -12135,7 +12141,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q54">
         <v>3.6</v>
@@ -12216,7 +12222,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ54">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR54">
         <v>1.7</v>
@@ -12341,7 +12347,7 @@
         <v>123</v>
       </c>
       <c r="P55" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12547,7 +12553,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q56">
         <v>2.58</v>
@@ -12959,7 +12965,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13165,7 +13171,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13243,7 +13249,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ59">
         <v>1.46</v>
@@ -13864,7 +13870,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ62">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR62">
         <v>2</v>
@@ -13989,7 +13995,7 @@
         <v>128</v>
       </c>
       <c r="P63" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -14401,7 +14407,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q65">
         <v>1.9</v>
@@ -14607,7 +14613,7 @@
         <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q66">
         <v>2.02</v>
@@ -14813,7 +14819,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q67">
         <v>3.75</v>
@@ -14894,7 +14900,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ67">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR67">
         <v>1.44</v>
@@ -15019,7 +15025,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15225,7 +15231,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q69">
         <v>2</v>
@@ -15637,7 +15643,7 @@
         <v>135</v>
       </c>
       <c r="P71" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -16127,7 +16133,7 @@
         <v>0.5</v>
       </c>
       <c r="AP73">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ73">
         <v>0.6899999999999999</v>
@@ -16461,7 +16467,7 @@
         <v>137</v>
       </c>
       <c r="P75" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q75">
         <v>1.83</v>
@@ -16667,7 +16673,7 @@
         <v>93</v>
       </c>
       <c r="P76" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16951,7 +16957,7 @@
         <v>2.2</v>
       </c>
       <c r="AP77">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ77">
         <v>1.69</v>
@@ -17160,7 +17166,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ78">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17697,7 +17703,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17903,7 +17909,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q82">
         <v>5.35</v>
@@ -17984,7 +17990,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ82">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR82">
         <v>1.42</v>
@@ -18396,7 +18402,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ84">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR84">
         <v>1.59</v>
@@ -18599,7 +18605,7 @@
         <v>3</v>
       </c>
       <c r="AP85">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ85">
         <v>2.46</v>
@@ -18727,7 +18733,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19139,7 +19145,7 @@
         <v>143</v>
       </c>
       <c r="P88" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q88">
         <v>2.5</v>
@@ -19345,7 +19351,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19426,7 +19432,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ89">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR89">
         <v>1.8</v>
@@ -19551,7 +19557,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19629,7 +19635,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ90">
         <v>1.08</v>
@@ -19757,7 +19763,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20169,7 +20175,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20868,7 +20874,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ96">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR96">
         <v>1.73</v>
@@ -21199,7 +21205,7 @@
         <v>82</v>
       </c>
       <c r="P98" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q98">
         <v>3.65</v>
@@ -21277,10 +21283,10 @@
         <v>1.88</v>
       </c>
       <c r="AP98">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ98">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR98">
         <v>1.57</v>
@@ -21405,7 +21411,7 @@
         <v>82</v>
       </c>
       <c r="P99" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q99">
         <v>2.88</v>
@@ -21817,7 +21823,7 @@
         <v>152</v>
       </c>
       <c r="P101" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -22023,7 +22029,7 @@
         <v>153</v>
       </c>
       <c r="P102" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q102">
         <v>2.55</v>
@@ -22101,7 +22107,7 @@
         <v>0.5</v>
       </c>
       <c r="AP102">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102">
         <v>0.6899999999999999</v>
@@ -22229,7 +22235,7 @@
         <v>154</v>
       </c>
       <c r="P103" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q103">
         <v>1.94</v>
@@ -23546,7 +23552,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ109">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR109">
         <v>1.38</v>
@@ -23671,7 +23677,7 @@
         <v>101</v>
       </c>
       <c r="P110" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q110">
         <v>4.75</v>
@@ -23752,7 +23758,7 @@
         <v>1</v>
       </c>
       <c r="AQ110">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -23877,7 +23883,7 @@
         <v>158</v>
       </c>
       <c r="P111" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q111">
         <v>2.1</v>
@@ -24083,7 +24089,7 @@
         <v>159</v>
       </c>
       <c r="P112" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24289,7 +24295,7 @@
         <v>82</v>
       </c>
       <c r="P113" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q113">
         <v>2.1</v>
@@ -24495,7 +24501,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24573,7 +24579,7 @@
         <v>2.44</v>
       </c>
       <c r="AP114">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ114">
         <v>2.46</v>
@@ -24985,10 +24991,10 @@
         <v>0.44</v>
       </c>
       <c r="AP116">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ116">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25319,7 +25325,7 @@
         <v>123</v>
       </c>
       <c r="P118" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q118">
         <v>1.74</v>
@@ -26015,7 +26021,7 @@
         <v>1.2</v>
       </c>
       <c r="AP121">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ121">
         <v>1.25</v>
@@ -26349,7 +26355,7 @@
         <v>166</v>
       </c>
       <c r="P123" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q123">
         <v>6.04</v>
@@ -26761,7 +26767,7 @@
         <v>167</v>
       </c>
       <c r="P125" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q125">
         <v>2.2</v>
@@ -27048,7 +27054,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ126">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR126">
         <v>1.44</v>
@@ -27379,7 +27385,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27460,7 +27466,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ128">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR128">
         <v>1.95</v>
@@ -27585,7 +27591,7 @@
         <v>169</v>
       </c>
       <c r="P129" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q129">
         <v>2</v>
@@ -27791,7 +27797,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q130">
         <v>2.28</v>
@@ -27869,7 +27875,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ130">
         <v>0.93</v>
@@ -28203,7 +28209,7 @@
         <v>172</v>
       </c>
       <c r="P132" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q132">
         <v>4.5</v>
@@ -28821,7 +28827,7 @@
         <v>82</v>
       </c>
       <c r="P135" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q135">
         <v>3.27</v>
@@ -29027,7 +29033,7 @@
         <v>82</v>
       </c>
       <c r="P136" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29105,7 +29111,7 @@
         <v>1</v>
       </c>
       <c r="AP136">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ136">
         <v>1.08</v>
@@ -29233,7 +29239,7 @@
         <v>173</v>
       </c>
       <c r="P137" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q137">
         <v>2.68</v>
@@ -29439,7 +29445,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q138">
         <v>4.2</v>
@@ -29517,7 +29523,7 @@
         <v>2.36</v>
       </c>
       <c r="AP138">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ138">
         <v>2.46</v>
@@ -29645,7 +29651,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -30469,7 +30475,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q143">
         <v>2.2</v>
@@ -30550,7 +30556,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ143">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AR143">
         <v>1.96</v>
@@ -30756,7 +30762,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ144">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR144">
         <v>1.44</v>
@@ -31087,7 +31093,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q146">
         <v>1.83</v>
@@ -31293,7 +31299,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q147">
         <v>2.88</v>
@@ -31499,7 +31505,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q148">
         <v>3</v>
@@ -31577,7 +31583,7 @@
         <v>0.75</v>
       </c>
       <c r="AP148">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ148">
         <v>0.6899999999999999</v>
@@ -31705,7 +31711,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q149">
         <v>3.6</v>
@@ -31783,7 +31789,7 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ149">
         <v>1.46</v>
@@ -31911,7 +31917,7 @@
         <v>185</v>
       </c>
       <c r="P150" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q150">
         <v>2.75</v>
@@ -32117,7 +32123,7 @@
         <v>82</v>
       </c>
       <c r="P151" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -32323,7 +32329,7 @@
         <v>108</v>
       </c>
       <c r="P152" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q152">
         <v>2.3</v>
@@ -32941,7 +32947,7 @@
         <v>82</v>
       </c>
       <c r="P155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33098,6 +33104,418 @@
       </c>
       <c r="BP155">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7844425</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45753.4375</v>
+      </c>
+      <c r="F156">
+        <v>4</v>
+      </c>
+      <c r="G156" t="s">
+        <v>73</v>
+      </c>
+      <c r="H156" t="s">
+        <v>74</v>
+      </c>
+      <c r="I156">
+        <v>1</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156">
+        <v>2</v>
+      </c>
+      <c r="M156">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>3</v>
+      </c>
+      <c r="O156" t="s">
+        <v>188</v>
+      </c>
+      <c r="P156" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q156">
+        <v>3.58</v>
+      </c>
+      <c r="R156">
+        <v>2.12</v>
+      </c>
+      <c r="S156">
+        <v>2.83</v>
+      </c>
+      <c r="T156">
+        <v>1.37</v>
+      </c>
+      <c r="U156">
+        <v>2.85</v>
+      </c>
+      <c r="V156">
+        <v>2.73</v>
+      </c>
+      <c r="W156">
+        <v>1.4</v>
+      </c>
+      <c r="X156">
+        <v>6.7</v>
+      </c>
+      <c r="Y156">
+        <v>1.09</v>
+      </c>
+      <c r="Z156">
+        <v>2.82</v>
+      </c>
+      <c r="AA156">
+        <v>3.33</v>
+      </c>
+      <c r="AB156">
+        <v>2.41</v>
+      </c>
+      <c r="AC156">
+        <v>1.01</v>
+      </c>
+      <c r="AD156">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE156">
+        <v>1.25</v>
+      </c>
+      <c r="AF156">
+        <v>3.28</v>
+      </c>
+      <c r="AG156">
+        <v>1.98</v>
+      </c>
+      <c r="AH156">
+        <v>1.77</v>
+      </c>
+      <c r="AI156">
+        <v>1.71</v>
+      </c>
+      <c r="AJ156">
+        <v>2.02</v>
+      </c>
+      <c r="AK156">
+        <v>1.6</v>
+      </c>
+      <c r="AL156">
+        <v>1.3</v>
+      </c>
+      <c r="AM156">
+        <v>1.38</v>
+      </c>
+      <c r="AN156">
+        <v>1.38</v>
+      </c>
+      <c r="AO156">
+        <v>2.08</v>
+      </c>
+      <c r="AP156">
+        <v>1.5</v>
+      </c>
+      <c r="AQ156">
+        <v>1.92</v>
+      </c>
+      <c r="AR156">
+        <v>1.57</v>
+      </c>
+      <c r="AS156">
+        <v>1.58</v>
+      </c>
+      <c r="AT156">
+        <v>3.15</v>
+      </c>
+      <c r="AU156">
+        <v>7</v>
+      </c>
+      <c r="AV156">
+        <v>6</v>
+      </c>
+      <c r="AW156">
+        <v>3</v>
+      </c>
+      <c r="AX156">
+        <v>9</v>
+      </c>
+      <c r="AY156">
+        <v>10</v>
+      </c>
+      <c r="AZ156">
+        <v>15</v>
+      </c>
+      <c r="BA156">
+        <v>5</v>
+      </c>
+      <c r="BB156">
+        <v>6</v>
+      </c>
+      <c r="BC156">
+        <v>11</v>
+      </c>
+      <c r="BD156">
+        <v>2.09</v>
+      </c>
+      <c r="BE156">
+        <v>6.2</v>
+      </c>
+      <c r="BF156">
+        <v>2.15</v>
+      </c>
+      <c r="BG156">
+        <v>1.31</v>
+      </c>
+      <c r="BH156">
+        <v>2.92</v>
+      </c>
+      <c r="BI156">
+        <v>1.61</v>
+      </c>
+      <c r="BJ156">
+        <v>2.24</v>
+      </c>
+      <c r="BK156">
+        <v>2.01</v>
+      </c>
+      <c r="BL156">
+        <v>1.79</v>
+      </c>
+      <c r="BM156">
+        <v>2.49</v>
+      </c>
+      <c r="BN156">
+        <v>1.49</v>
+      </c>
+      <c r="BO156">
+        <v>3.7</v>
+      </c>
+      <c r="BP156">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7844426</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45753.4375</v>
+      </c>
+      <c r="F157">
+        <v>4</v>
+      </c>
+      <c r="G157" t="s">
+        <v>75</v>
+      </c>
+      <c r="H157" t="s">
+        <v>76</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>1</v>
+      </c>
+      <c r="M157">
+        <v>2</v>
+      </c>
+      <c r="N157">
+        <v>3</v>
+      </c>
+      <c r="O157" t="s">
+        <v>167</v>
+      </c>
+      <c r="P157" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q157">
+        <v>2.38</v>
+      </c>
+      <c r="R157">
+        <v>2.14</v>
+      </c>
+      <c r="S157">
+        <v>4.65</v>
+      </c>
+      <c r="T157">
+        <v>1.35</v>
+      </c>
+      <c r="U157">
+        <v>2.94</v>
+      </c>
+      <c r="V157">
+        <v>2.81</v>
+      </c>
+      <c r="W157">
+        <v>1.38</v>
+      </c>
+      <c r="X157">
+        <v>7</v>
+      </c>
+      <c r="Y157">
+        <v>1.08</v>
+      </c>
+      <c r="Z157">
+        <v>1.75</v>
+      </c>
+      <c r="AA157">
+        <v>3.47</v>
+      </c>
+      <c r="AB157">
+        <v>4.75</v>
+      </c>
+      <c r="AC157">
+        <v>1</v>
+      </c>
+      <c r="AD157">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE157">
+        <v>1.23</v>
+      </c>
+      <c r="AF157">
+        <v>3.44</v>
+      </c>
+      <c r="AG157">
+        <v>1.98</v>
+      </c>
+      <c r="AH157">
+        <v>1.77</v>
+      </c>
+      <c r="AI157">
+        <v>1.77</v>
+      </c>
+      <c r="AJ157">
+        <v>1.94</v>
+      </c>
+      <c r="AK157">
+        <v>1.22</v>
+      </c>
+      <c r="AL157">
+        <v>1.27</v>
+      </c>
+      <c r="AM157">
+        <v>1.96</v>
+      </c>
+      <c r="AN157">
+        <v>1.38</v>
+      </c>
+      <c r="AO157">
+        <v>0.33</v>
+      </c>
+      <c r="AP157">
+        <v>1.29</v>
+      </c>
+      <c r="AQ157">
+        <v>0.54</v>
+      </c>
+      <c r="AR157">
+        <v>1.52</v>
+      </c>
+      <c r="AS157">
+        <v>1.14</v>
+      </c>
+      <c r="AT157">
+        <v>2.66</v>
+      </c>
+      <c r="AU157">
+        <v>5</v>
+      </c>
+      <c r="AV157">
+        <v>5</v>
+      </c>
+      <c r="AW157">
+        <v>1</v>
+      </c>
+      <c r="AX157">
+        <v>1</v>
+      </c>
+      <c r="AY157">
+        <v>6</v>
+      </c>
+      <c r="AZ157">
+        <v>6</v>
+      </c>
+      <c r="BA157">
+        <v>10</v>
+      </c>
+      <c r="BB157">
+        <v>1</v>
+      </c>
+      <c r="BC157">
+        <v>11</v>
+      </c>
+      <c r="BD157">
+        <v>1.42</v>
+      </c>
+      <c r="BE157">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF157">
+        <v>3.4</v>
+      </c>
+      <c r="BG157">
+        <v>1.19</v>
+      </c>
+      <c r="BH157">
+        <v>3.95</v>
+      </c>
+      <c r="BI157">
+        <v>1.33</v>
+      </c>
+      <c r="BJ157">
+        <v>2.83</v>
+      </c>
+      <c r="BK157">
+        <v>1.65</v>
+      </c>
+      <c r="BL157">
+        <v>2.2</v>
+      </c>
+      <c r="BM157">
+        <v>2.05</v>
+      </c>
+      <c r="BN157">
+        <v>1.75</v>
+      </c>
+      <c r="BO157">
+        <v>2.6</v>
+      </c>
+      <c r="BP157">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -33246,22 +33246,22 @@
         <v>3.15</v>
       </c>
       <c r="AU156">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV156">
         <v>6</v>
       </c>
       <c r="AW156">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX156">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY156">
         <v>10</v>
       </c>
       <c r="AZ156">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA156">
         <v>5</v>
@@ -33452,22 +33452,22 @@
         <v>2.66</v>
       </c>
       <c r="AU157">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV157">
         <v>5</v>
       </c>
       <c r="AW157">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX157">
         <v>1</v>
       </c>
       <c r="AY157">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AZ157">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA157">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -32440,13 +32440,13 @@
         <v>13</v>
       </c>
       <c r="BA152">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BB152">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC152">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BD152">
         <v>1.39</v>
@@ -32646,13 +32646,13 @@
         <v>12</v>
       </c>
       <c r="BA153">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB153">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BC153">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BD153">
         <v>1.46</v>
@@ -32852,13 +32852,13 @@
         <v>10</v>
       </c>
       <c r="BA154">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BB154">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC154">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BD154">
         <v>1.71</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Slovakia Super Liga_20242025.xlsx
@@ -1672,10 +1672,10 @@
         <v>4</v>
       </c>
       <c r="AY2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA2">
         <v>8</v>
@@ -1881,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="AZ3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA3">
         <v>8</v>
@@ -2084,10 +2084,10 @@
         <v>4</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BA4">
         <v>3</v>
@@ -2290,10 +2290,10 @@
         <v>2</v>
       </c>
       <c r="AY5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA5">
         <v>6</v>
@@ -2496,10 +2496,10 @@
         <v>3</v>
       </c>
       <c r="AY6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA6">
         <v>6</v>
@@ -2702,10 +2702,10 @@
         <v>5</v>
       </c>
       <c r="AY7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA7">
         <v>7</v>
@@ -2908,7 +2908,7 @@
         <v>7</v>
       </c>
       <c r="AY8">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ8">
         <v>12</v>
@@ -3114,10 +3114,10 @@
         <v>9</v>
       </c>
       <c r="AY9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ9">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA9">
         <v>2</v>
@@ -3320,10 +3320,10 @@
         <v>4</v>
       </c>
       <c r="AY10">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA10">
         <v>2</v>
@@ -3526,10 +3526,10 @@
         <v>5</v>
       </c>
       <c r="AY11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA11">
         <v>4</v>
@@ -3732,10 +3732,10 @@
         <v>4</v>
       </c>
       <c r="AY12">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AZ12">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA12">
         <v>10</v>
@@ -4350,10 +4350,10 @@
         <v>7</v>
       </c>
       <c r="AY15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AZ15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA15">
         <v>4</v>
@@ -4556,19 +4556,19 @@
         <v>14</v>
       </c>
       <c r="AY16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ16">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="BA16">
         <v>5</v>
       </c>
       <c r="BB16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD16">
         <v>2.4</v>
@@ -4762,10 +4762,10 @@
         <v>4</v>
       </c>
       <c r="AY17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ17">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA17">
         <v>6</v>
@@ -4968,10 +4968,10 @@
         <v>9</v>
       </c>
       <c r="AY18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ18">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA18">
         <v>4</v>
@@ -5174,7 +5174,7 @@
         <v>4</v>
       </c>
       <c r="AY19">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ19">
         <v>9</v>
@@ -5380,10 +5380,10 @@
         <v>5</v>
       </c>
       <c r="AY20">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ20">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA20">
         <v>8</v>
@@ -5586,10 +5586,10 @@
         <v>4</v>
       </c>
       <c r="AY21">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ21">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA21">
         <v>3</v>
@@ -5792,10 +5792,10 @@
         <v>5</v>
       </c>
       <c r="AY22">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AZ22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA22">
         <v>12</v>
@@ -5998,10 +5998,10 @@
         <v>6</v>
       </c>
       <c r="AY23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ23">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA23">
         <v>1</v>
@@ -6204,10 +6204,10 @@
         <v>1</v>
       </c>
       <c r="AY24">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AZ24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA24">
         <v>13</v>
@@ -6410,10 +6410,10 @@
         <v>9</v>
       </c>
       <c r="AY25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ25">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA25">
         <v>5</v>
@@ -6616,10 +6616,10 @@
         <v>5</v>
       </c>
       <c r="AY26">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ26">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA26">
         <v>7</v>
@@ -6822,10 +6822,10 @@
         <v>2</v>
       </c>
       <c r="AY27">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ27">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA27">
         <v>2</v>
@@ -7028,10 +7028,10 @@
         <v>1</v>
       </c>
       <c r="AY28">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AZ28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA28">
         <v>9</v>
@@ -7234,10 +7234,10 @@
         <v>8</v>
       </c>
       <c r="AY29">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ29">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA29">
         <v>6</v>
@@ -7440,10 +7440,10 @@
         <v>4</v>
       </c>
       <c r="AY30">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ30">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA30">
         <v>4</v>
@@ -7646,7 +7646,7 @@
         <v>3</v>
       </c>
       <c r="AY31">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AZ31">
         <v>6</v>
@@ -7852,10 +7852,10 @@
         <v>4</v>
       </c>
       <c r="AY32">
+        <v>8</v>
+      </c>
+      <c r="AZ32">
         <v>14</v>
-      </c>
-      <c r="AZ32">
-        <v>18</v>
       </c>
       <c r="BA32">
         <v>5</v>
@@ -8058,10 +8058,10 @@
         <v>9</v>
       </c>
       <c r="AY33">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ33">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BA33">
         <v>10</v>
@@ -8264,10 +8264,10 @@
         <v>3</v>
       </c>
       <c r="AY34">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AZ34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA34">
         <v>4</v>
@@ -8470,10 +8470,10 @@
         <v>3</v>
       </c>
       <c r="AY35">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ35">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BA35">
         <v>9</v>
@@ -8676,10 +8676,10 @@
         <v>2</v>
       </c>
       <c r="AY36">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA36">
         <v>8</v>
@@ -8882,10 +8882,10 @@
         <v>5</v>
       </c>
       <c r="AY37">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ37">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA37">
         <v>7</v>
@@ -9088,10 +9088,10 @@
         <v>3</v>
       </c>
       <c r="AY38">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ38">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA38">
         <v>3</v>
@@ -9294,10 +9294,10 @@
         <v>9</v>
       </c>
       <c r="AY39">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ39">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA39">
         <v>2</v>
@@ -9500,10 +9500,10 @@
         <v>2</v>
       </c>
       <c r="AY40">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ40">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA40">
         <v>5</v>
@@ -9706,10 +9706,10 @@
         <v>2</v>
       </c>
       <c r="AY41">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ41">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BA41">
         <v>5</v>
@@ -9912,10 +9912,10 @@
         <v>2</v>
       </c>
       <c r="AY42">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ42">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA42">
         <v>5</v>
@@ -10118,10 +10118,10 @@
         <v>6</v>
       </c>
       <c r="AY43">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ43">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA43">
         <v>7</v>
@@ -10324,10 +10324,10 @@
         <v>7</v>
       </c>
       <c r="AY44">
+        <v>13</v>
+      </c>
+      <c r="AZ44">
         <v>16</v>
-      </c>
-      <c r="AZ44">
-        <v>17</v>
       </c>
       <c r="BA44">
         <v>3</v>
@@ -10530,10 +10530,10 @@
         <v>5</v>
       </c>
       <c r="AY45">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ45">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA45">
         <v>6</v>
@@ -10736,10 +10736,10 @@
         <v>6</v>
       </c>
       <c r="AY46">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ46">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA46">
         <v>5</v>
@@ -10942,10 +10942,10 @@
         <v>5</v>
       </c>
       <c r="AY47">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AZ47">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BA47">
         <v>5</v>
@@ -11148,7 +11148,7 @@
         <v>3</v>
       </c>
       <c r="AY48">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AZ48">
         <v>9</v>
@@ -11354,10 +11354,10 @@
         <v>4</v>
       </c>
       <c r="AY49">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ49">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA49">
         <v>5</v>
@@ -11560,10 +11560,10 @@
         <v>5</v>
       </c>
       <c r="AY50">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ50">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA50">
         <v>5</v>
@@ -11766,10 +11766,10 @@
         <v>10</v>
       </c>
       <c r="AY51">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ51">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA51">
         <v>6</v>
@@ -11972,7 +11972,7 @@
         <v>6</v>
       </c>
       <c r="AY52">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ52">
         <v>13</v>
@@ -12384,10 +12384,10 @@
         <v>6</v>
       </c>
       <c r="AY54">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ54">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA54">
         <v>7</v>
@@ -13208,10 +13208,10 @@
         <v>9</v>
       </c>
       <c r="AY58">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ58">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA58">
         <v>7</v>
@@ -13414,10 +13414,10 @@
         <v>6</v>
       </c>
       <c r="AY59">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ59">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA59">
         <v>4</v>
@@ -13620,10 +13620,10 @@
         <v>4</v>
       </c>
       <c r="AY60">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ60">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA60">
         <v>4</v>
@@ -14032,10 +14032,10 @@
         <v>5</v>
       </c>
       <c r="AY62">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ62">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA62">
         <v>7</v>
@@ -14238,10 +14238,10 @@
         <v>2</v>
       </c>
       <c r="AY63">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ63">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA63">
         <v>6</v>
@@ -14444,10 +14444,10 @@
         <v>6</v>
       </c>
       <c r="AY64">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ64">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="BA64">
         <v>2</v>
@@ -14650,10 +14650,10 @@
         <v>5</v>
       </c>
       <c r="AY65">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ65">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA65">
         <v>4</v>
@@ -15062,10 +15062,10 @@
         <v>1</v>
       </c>
       <c r="AY67">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ67">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA67">
         <v>2</v>
@@ -15268,10 +15268,10 @@
         <v>11</v>
       </c>
       <c r="AY68">
+        <v>16</v>
+      </c>
+      <c r="AZ68">
         <v>23</v>
-      </c>
-      <c r="AZ68">
-        <v>25</v>
       </c>
       <c r="BA68">
         <v>12</v>
@@ -15474,7 +15474,7 @@
         <v>2</v>
       </c>
       <c r="AY69">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ69">
         <v>4</v>
@@ -15680,10 +15680,10 @@
         <v>6</v>
       </c>
       <c r="AY70">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ70">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA70">
         <v>2</v>
@@ -15886,7 +15886,7 @@
         <v>5</v>
       </c>
       <c r="AY71">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ71">
         <v>16</v>
@@ -16092,10 +16092,10 @@
         <v>6</v>
       </c>
       <c r="AY72">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AZ72">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BA72">
         <v>6</v>
@@ -16298,10 +16298,10 @@
         <v>4</v>
       </c>
       <c r="AY73">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ73">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA73">
         <v>4</v>
@@ -16504,10 +16504,10 @@
         <v>5</v>
       </c>
       <c r="AY74">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA74">
         <v>5</v>
@@ -16710,10 +16710,10 @@
         <v>5</v>
       </c>
       <c r="AY75">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ75">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA75">
         <v>3</v>
@@ -16916,10 +16916,10 @@
         <v>4</v>
       </c>
       <c r="AY76">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ76">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA76">
         <v>7</v>
@@ -17122,10 +17122,10 @@
         <v>5</v>
       </c>
       <c r="AY77">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ77">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA77">
         <v>6</v>
@@ -17328,10 +17328,10 @@
         <v>8</v>
       </c>
       <c r="AY78">
+        <v>10</v>
+      </c>
+      <c r="AZ78">
         <v>12</v>
-      </c>
-      <c r="AZ78">
-        <v>17</v>
       </c>
       <c r="BA78">
         <v>8</v>
@@ -17534,10 +17534,10 @@
         <v>5</v>
       </c>
       <c r="AY79">
+        <v>10</v>
+      </c>
+      <c r="AZ79">
         <v>13</v>
-      </c>
-      <c r="AZ79">
-        <v>18</v>
       </c>
       <c r="BA79">
         <v>5</v>
@@ -17740,10 +17740,10 @@
         <v>1</v>
       </c>
       <c r="AY80">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA80">
         <v>3</v>
@@ -17946,10 +17946,10 @@
         <v>5</v>
       </c>
       <c r="AY81">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ81">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA81">
         <v>7</v>
@@ -18152,10 +18152,10 @@
         <v>4</v>
       </c>
       <c r="AY82">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AZ82">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA82">
         <v>0</v>
@@ -18358,10 +18358,10 @@
         <v>3</v>
       </c>
       <c r="AY83">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ83">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA83">
         <v>5</v>
@@ -18564,10 +18564,10 @@
         <v>1</v>
       </c>
       <c r="AY84">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ84">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA84">
         <v>2</v>
@@ -20006,7 +20006,7 @@
         <v>4</v>
       </c>
       <c r="AY91">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ91">
         <v>7</v>
@@ -20212,10 +20212,10 @@
         <v>3</v>
       </c>
       <c r="AY92">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ92">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA92">
         <v>7</v>
@@ -20418,10 +20418,10 @@
         <v>4</v>
       </c>
       <c r="AY93">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ93">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA93">
         <v>8</v>
@@ -20624,10 +20624,10 @@
         <v>4</v>
       </c>
       <c r="AY94">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ94">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA94">
         <v>4</v>
@@ -20830,10 +20830,10 @@
         <v>3</v>
       </c>
       <c r="AY95">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ95">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA95">
         <v>9</v>
@@ -21036,10 +21036,10 @@
         <v>6</v>
       </c>
       <c r="AY96">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ96">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA96">
         <v>6</v>
@@ -21242,10 +21242,10 @@
         <v>6</v>
       </c>
       <c r="AY97">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ97">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA97">
         <v>0</v>
@@ -21448,10 +21448,10 @@
         <v>7</v>
       </c>
       <c r="AY98">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ98">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA98">
         <v>3</v>
@@ -21654,10 +21654,10 @@
         <v>3</v>
       </c>
       <c r="AY99">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ99">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA99">
         <v>3</v>
@@ -21860,10 +21860,10 @@
         <v>4</v>
       </c>
       <c r="AY100">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ100">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA100">
         <v>8</v>
@@ -22066,10 +22066,10 @@
         <v>3</v>
       </c>
       <c r="AY101">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ101">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA101">
         <v>6</v>
@@ -22272,10 +22272,10 @@
         <v>7</v>
       </c>
       <c r="AY102">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AZ102">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA102">
         <v>5</v>
@@ -22478,10 +22478,10 @@
         <v>6</v>
       </c>
       <c r="AY103">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ103">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA103">
         <v>5</v>
@@ -23302,10 +23302,10 @@
         <v>8</v>
       </c>
       <c r="AY107">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ107">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA107">
         <v>6</v>
@@ -23508,10 +23508,10 @@
         <v>5</v>
       </c>
       <c r="AY108">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ108">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA108">
         <v>7</v>
@@ -23714,10 +23714,10 @@
         <v>1</v>
       </c>
       <c r="AY109">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ109">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA109">
         <v>7</v>
@@ -29482,10 +29482,10 @@
         <v>13</v>
       </c>
       <c r="AY137">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ137">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA137">
         <v>7</v>
@@ -30518,13 +30518,13 @@
         <v>11</v>
       </c>
       <c r="BA142">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB142">
         <v>8</v>
       </c>
       <c r="BC142">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD142">
         <v>1.6</v>
@@ -30727,10 +30727,10 @@
         <v>3</v>
       </c>
       <c r="BB143">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC143">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD143">
         <v>1.7</v>
@@ -31545,7 +31545,7 @@
         <v>9</v>
       </c>
       <c r="AZ147">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA147">
         <v>6</v>
@@ -31954,7 +31954,7 @@
         <v>3</v>
       </c>
       <c r="AY149">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ149">
         <v>8</v>
@@ -33399,7 +33399,7 @@
         <v>10</v>
       </c>
       <c r="AZ156">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA156">
         <v>5</v>
@@ -33602,10 +33602,10 @@
         <v>1</v>
       </c>
       <c r="AY157">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ157">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA157">
         <v>10</v>
@@ -33808,19 +33808,19 @@
         <v>4</v>
       </c>
       <c r="AY158">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ158">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA158">
         <v>10</v>
       </c>
       <c r="BB158">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC158">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD158">
         <v>1.47</v>
@@ -34017,7 +34017,7 @@
         <v>14</v>
       </c>
       <c r="AZ159">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA159">
         <v>5</v>
@@ -34632,10 +34632,10 @@
         <v>4</v>
       </c>
       <c r="AY162">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ162">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA162">
         <v>3</v>
@@ -34838,10 +34838,10 @@
         <v>13</v>
       </c>
       <c r="AY163">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ163">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA163">
         <v>5</v>
@@ -35044,10 +35044,10 @@
         <v>3</v>
       </c>
       <c r="AY164">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ164">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA164">
         <v>5</v>
@@ -35250,10 +35250,10 @@
         <v>10</v>
       </c>
       <c r="AY165">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ165">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA165">
         <v>4</v>
@@ -35459,16 +35459,16 @@
         <v>5</v>
       </c>
       <c r="AZ166">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BA166">
         <v>5</v>
       </c>
       <c r="BB166">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC166">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD166">
         <v>0</v>
@@ -36074,7 +36074,7 @@
         <v>3</v>
       </c>
       <c r="AY169">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AZ169">
         <v>7</v>
@@ -37104,7 +37104,7 @@
         <v>2</v>
       </c>
       <c r="AY174">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AZ174">
         <v>5</v>
@@ -37113,10 +37113,10 @@
         <v>13</v>
       </c>
       <c r="BB174">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC174">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD174">
         <v>0</v>
@@ -38958,19 +38958,19 @@
         <v>5</v>
       </c>
       <c r="AY183">
+        <v>10</v>
+      </c>
+      <c r="AZ183">
         <v>12</v>
       </c>
-      <c r="AZ183">
-        <v>14</v>
-      </c>
       <c r="BA183">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB183">
         <v>9</v>
       </c>
       <c r="BC183">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD183">
         <v>1.53</v>
@@ -39164,19 +39164,19 @@
         <v>4</v>
       </c>
       <c r="AY184">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ184">
         <v>10</v>
       </c>
       <c r="BA184">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BB184">
         <v>4</v>
       </c>
       <c r="BC184">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="BD184">
         <v>2.4</v>
@@ -39370,19 +39370,19 @@
         <v>8</v>
       </c>
       <c r="AY185">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ185">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA185">
         <v>2</v>
       </c>
       <c r="BB185">
+        <v>6</v>
+      </c>
+      <c r="BC185">
         <v>8</v>
-      </c>
-      <c r="BC185">
-        <v>10</v>
       </c>
       <c r="BD185">
         <v>1.98</v>
@@ -39576,19 +39576,19 @@
         <v>9</v>
       </c>
       <c r="AY186">
+        <v>12</v>
+      </c>
+      <c r="AZ186">
         <v>16</v>
-      </c>
-      <c r="AZ186">
-        <v>18</v>
       </c>
       <c r="BA186">
         <v>5</v>
       </c>
       <c r="BB186">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC186">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BD186">
         <v>1.44</v>
@@ -41224,19 +41224,19 @@
         <v>2</v>
       </c>
       <c r="AY194">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ194">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA194">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BB194">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BC194">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BD194">
         <v>1.35</v>
@@ -41636,7 +41636,7 @@
         <v>4</v>
       </c>
       <c r="AY196">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="AZ196">
         <v>7</v>
